--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="327">
   <si>
     <t>type</t>
   </si>
@@ -664,12 +664,6 @@
     <t xml:space="preserve">Have the mother explain first and if she cannot then explain it to her. </t>
   </si>
   <si>
-    <t>question_to_client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you understand the importance of [] ? </t>
-  </si>
-  <si>
     <t xml:space="preserve">visit_summary </t>
   </si>
   <si>
@@ -1007,6 +1001,39 @@
   </si>
   <si>
     <t>${high_risk_manual}  = "true"  and ${is_high_risk_pregnancy_ML} = "true"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin repeat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">questions_to_client </t>
+  </si>
+  <si>
+    <t>questions_to_client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat_count </t>
+  </si>
+  <si>
+    <t>count(${mitigation_list})</t>
+  </si>
+  <si>
+    <t>current_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end repeat </t>
+  </si>
+  <si>
+    <t>imran</t>
+  </si>
+  <si>
+    <t>esmail</t>
+  </si>
+  <si>
+    <t>${mitigation_list}</t>
+  </si>
+  <si>
+    <t>indexed-repeat(${esmail}, ${imran}, position(..))</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1174,7 +1201,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1195,6 +1221,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,15 +1442,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z128"/>
+  <dimension ref="A1:AA133"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="265.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.40625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1435,59 +1465,62 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="2"/>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,11 +1532,11 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="3" t="b">
+      <c r="F2" s="1"/>
+      <c r="G2" s="3" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1514,7 +1547,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="2"/>
+      <c r="R2" s="1"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1523,8 +1556,9 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="AA2" s="2"/>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1535,7 +1569,7 @@
         <v>21</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -1557,8 +1591,9 @@
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="AA3" s="2"/>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1604,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -1591,13 +1626,14 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
-    </row>
-    <row r="5" spans="1:26" s="28" customFormat="1">
+      <c r="AA4" s="2"/>
+    </row>
+    <row r="5" spans="1:27" s="28" customFormat="1">
       <c r="A5" s="27" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>21</v>
@@ -1625,8 +1661,9 @@
       <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" s="16"/>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -1650,7 +1687,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="2"/>
+      <c r="R6" s="1"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1659,8 +1696,9 @@
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" s="2"/>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -1684,7 +1722,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="R7" s="2"/>
+      <c r="R7" s="1"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1693,8 +1731,9 @@
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
@@ -1718,7 +1757,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="R8" s="2"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1727,8 +1766,9 @@
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1752,7 +1792,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="16"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
@@ -1761,8 +1801,9 @@
       <c r="X9" s="16"/>
       <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" s="16"/>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1827,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-      <c r="R10" s="2"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -1795,8 +1836,9 @@
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" s="2"/>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1820,7 +1862,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="2"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -1829,8 +1871,9 @@
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" s="2"/>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1854,7 +1897,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="2"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -1863,8 +1906,9 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" s="2"/>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1888,7 +1932,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="2"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -1897,8 +1941,9 @@
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="AA13" s="2"/>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1920,7 +1965,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="R14" s="2"/>
+      <c r="R14" s="1"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -1929,8 +1974,9 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" s="2"/>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -1941,7 +1987,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1963,8 +2009,9 @@
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" s="2"/>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -1975,12 +2022,12 @@
         <v>21</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1999,8 +2046,9 @@
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -2011,7 +2059,7 @@
         <v>21</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2033,8 +2081,9 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
@@ -2045,7 +2094,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -2067,8 +2116,9 @@
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AA18" s="2"/>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
@@ -2077,7 +2127,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -2099,8 +2149,9 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AA19" s="2"/>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -2122,7 +2173,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="2"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
@@ -2131,8 +2182,9 @@
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" s="2"/>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -2143,22 +2195,22 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="1"/>
+      <c r="M21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="2"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
@@ -2167,8 +2219,9 @@
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" s="2"/>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2179,22 +2232,22 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-      <c r="R22" s="2"/>
+      <c r="R22" s="1"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
@@ -2203,8 +2256,9 @@
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" s="2"/>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -2215,22 +2269,22 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-      <c r="R23" s="2"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
@@ -2239,8 +2293,9 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" s="2"/>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="4" t="s">
         <v>41</v>
       </c>
@@ -2249,17 +2304,17 @@
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="2"/>
+      <c r="M24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -2273,8 +2328,9 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
@@ -2283,19 +2339,19 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="2"/>
+      <c r="M25" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="2"/>
+      <c r="O25" s="6"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -2307,8 +2363,9 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" s="2"/>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
@@ -2317,18 +2374,18 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="2"/>
+      <c r="M26" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="2"/>
+      <c r="N26" s="6"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
@@ -2341,8 +2398,9 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="AA26" s="2"/>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
@@ -2351,17 +2409,17 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="2"/>
+      <c r="M27" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -2375,8 +2433,9 @@
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" s="2"/>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
@@ -2385,22 +2444,22 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="29" t="s">
+      <c r="L28" s="2"/>
+      <c r="M28" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="2"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
@@ -2409,8 +2468,9 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" s="2"/>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
@@ -2419,18 +2479,18 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="2"/>
+      <c r="M29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="6"/>
-      <c r="N29" s="2"/>
+      <c r="N29" s="6"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
@@ -2443,8 +2503,9 @@
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" s="2"/>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="2" t="s">
         <v>41</v>
       </c>
@@ -2453,17 +2514,17 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="8">
+      <c r="L30" s="2"/>
+      <c r="M30" s="8">
         <v>7</v>
       </c>
-      <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2477,8 +2538,9 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="AA30" s="2"/>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="2" t="s">
         <v>41</v>
       </c>
@@ -2487,17 +2549,17 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="8">
+      <c r="L31" s="2"/>
+      <c r="M31" s="8">
         <v>30</v>
       </c>
-      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2511,8 +2573,9 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="AA31" s="2"/>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="4" t="s">
         <v>41</v>
       </c>
@@ -2521,18 +2584,18 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="2"/>
+      <c r="M32" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="2"/>
+      <c r="N32" s="6"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
@@ -2545,8 +2608,9 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" s="2"/>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="4" t="s">
         <v>41</v>
       </c>
@@ -2555,18 +2619,18 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M33" s="6"/>
-      <c r="N33" s="2"/>
+      <c r="N33" s="6"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
@@ -2579,8 +2643,9 @@
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AA33" s="2"/>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="4" t="s">
         <v>41</v>
       </c>
@@ -2589,18 +2654,18 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="9" t="s">
+      <c r="L34" s="2"/>
+      <c r="M34" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M34" s="6"/>
-      <c r="N34" s="2"/>
+      <c r="N34" s="6"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -2613,8 +2678,9 @@
       <c r="X34" s="2"/>
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AA34" s="2"/>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" s="4" t="s">
         <v>41</v>
       </c>
@@ -2623,18 +2689,18 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="9" t="s">
+      <c r="L35" s="2"/>
+      <c r="M35" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="2"/>
+      <c r="N35" s="6"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
@@ -2647,8 +2713,9 @@
       <c r="X35" s="2"/>
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AA35" s="2"/>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" s="2" t="s">
         <v>41</v>
       </c>
@@ -2657,17 +2724,17 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="E36" s="16"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="7" t="s">
+      <c r="L36" s="2"/>
+      <c r="M36" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -2681,8 +2748,9 @@
       <c r="X36" s="2"/>
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AA36" s="2"/>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
@@ -2691,18 +2759,18 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="2"/>
+      <c r="M37" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="2"/>
+      <c r="N37" s="6"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
@@ -2715,8 +2783,9 @@
       <c r="X37" s="2"/>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AA37" s="2"/>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" s="2" t="s">
         <v>41</v>
       </c>
@@ -2725,17 +2794,17 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="2"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="10"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="2"/>
+      <c r="M38" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -2749,8 +2818,9 @@
       <c r="X38" s="2"/>
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AA38" s="2"/>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
@@ -2759,17 +2829,17 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="2"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="10"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="2"/>
+      <c r="M39" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -2783,8 +2853,9 @@
       <c r="X39" s="2"/>
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AA39" s="2"/>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
@@ -2793,17 +2864,17 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="2"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="10"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="10" t="s">
+      <c r="L40" s="2"/>
+      <c r="M40" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -2817,8 +2888,9 @@
       <c r="X40" s="2"/>
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="AA40" s="2"/>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
@@ -2827,17 +2899,17 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="2"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="10"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="2" t="s">
+      <c r="L41" s="2"/>
+      <c r="M41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -2851,27 +2923,28 @@
       <c r="X41" s="2"/>
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
-    </row>
-    <row r="42" spans="1:26" s="28" customFormat="1">
+      <c r="AA41" s="2"/>
+    </row>
+    <row r="42" spans="1:27" s="28" customFormat="1">
       <c r="A42" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="10"/>
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
       <c r="J42" s="16"/>
       <c r="K42" s="16"/>
-      <c r="L42" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="M42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="27" t="s">
+        <v>306</v>
+      </c>
       <c r="N42" s="16"/>
       <c r="O42" s="16"/>
       <c r="P42" s="16"/>
@@ -2885,27 +2958,28 @@
       <c r="X42" s="16"/>
       <c r="Y42" s="16"/>
       <c r="Z42" s="16"/>
-    </row>
-    <row r="43" spans="1:26" s="28" customFormat="1">
+      <c r="AA42" s="16"/>
+    </row>
+    <row r="43" spans="1:27" s="28" customFormat="1">
       <c r="A43" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="10"/>
       <c r="H43" s="16"/>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
       <c r="K43" s="16"/>
-      <c r="L43" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="M43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="27" t="s">
+        <v>308</v>
+      </c>
       <c r="N43" s="16"/>
       <c r="O43" s="16"/>
       <c r="P43" s="16"/>
@@ -2919,8 +2993,9 @@
       <c r="X43" s="16"/>
       <c r="Y43" s="16"/>
       <c r="Z43" s="16"/>
-    </row>
-    <row r="44" spans="1:26">
+      <c r="AA43" s="16"/>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" s="27" t="s">
         <v>41</v>
       </c>
@@ -2930,16 +3005,16 @@
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="10"/>
       <c r="H44" s="16"/>
       <c r="I44" s="16"/>
       <c r="J44" s="16"/>
       <c r="K44" s="16"/>
-      <c r="L44" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="M44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="27" t="s">
+        <v>270</v>
+      </c>
       <c r="N44" s="16"/>
       <c r="O44" s="16"/>
       <c r="P44" s="16"/>
@@ -2953,27 +3028,28 @@
       <c r="X44" s="16"/>
       <c r="Y44" s="16"/>
       <c r="Z44" s="16"/>
-    </row>
-    <row r="45" spans="1:26" s="28" customFormat="1">
+      <c r="AA44" s="16"/>
+    </row>
+    <row r="45" spans="1:27" s="28" customFormat="1">
       <c r="A45" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="10"/>
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
       <c r="K45" s="16"/>
-      <c r="L45" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="M45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="27" t="s">
+        <v>300</v>
+      </c>
       <c r="N45" s="16"/>
       <c r="O45" s="16"/>
       <c r="P45" s="16"/>
@@ -2987,27 +3063,28 @@
       <c r="X45" s="16"/>
       <c r="Y45" s="16"/>
       <c r="Z45" s="16"/>
-    </row>
-    <row r="46" spans="1:26" s="28" customFormat="1">
+      <c r="AA45" s="16"/>
+    </row>
+    <row r="46" spans="1:27" s="28" customFormat="1">
       <c r="A46" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="10"/>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
       <c r="K46" s="16"/>
-      <c r="L46" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="M46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="27" t="s">
+        <v>303</v>
+      </c>
       <c r="N46" s="16"/>
       <c r="O46" s="16"/>
       <c r="P46" s="16"/>
@@ -3021,8 +3098,9 @@
       <c r="X46" s="16"/>
       <c r="Y46" s="16"/>
       <c r="Z46" s="16"/>
-    </row>
-    <row r="47" spans="1:26">
+      <c r="AA46" s="16"/>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" s="2" t="s">
         <v>41</v>
       </c>
@@ -3031,17 +3109,17 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="2"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="10"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="2"/>
+      <c r="M47" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -3055,8 +3133,9 @@
       <c r="X47" s="2"/>
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
-    </row>
-    <row r="48" spans="1:26">
+      <c r="AA47" s="2"/>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" s="2" t="s">
         <v>41</v>
       </c>
@@ -3065,17 +3144,17 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="2"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="10"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="2" t="s">
+      <c r="L48" s="2"/>
+      <c r="M48" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
@@ -3089,8 +3168,9 @@
       <c r="X48" s="2"/>
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
-    </row>
-    <row r="49" spans="1:26">
+      <c r="AA48" s="2"/>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" s="2" t="s">
         <v>41</v>
       </c>
@@ -3099,17 +3179,17 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="E49" s="16"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="2" t="s">
+      <c r="L49" s="2"/>
+      <c r="M49" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -3123,8 +3203,9 @@
       <c r="X49" s="2"/>
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
-    </row>
-    <row r="50" spans="1:26">
+      <c r="AA49" s="2"/>
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" s="2" t="s">
         <v>41</v>
       </c>
@@ -3133,17 +3214,17 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="2"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="10"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="2"/>
+      <c r="M50" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
@@ -3157,8 +3238,9 @@
       <c r="X50" s="2"/>
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
-    </row>
-    <row r="51" spans="1:26">
+      <c r="AA50" s="2"/>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" s="4" t="s">
         <v>89</v>
       </c>
@@ -3167,15 +3249,15 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="10"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -3189,8 +3271,9 @@
       <c r="X51" s="2"/>
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
-    </row>
-    <row r="52" spans="1:26">
+      <c r="AA51" s="2"/>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" s="4" t="s">
         <v>90</v>
       </c>
@@ -3199,15 +3282,15 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="10"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -3221,8 +3304,9 @@
       <c r="X52" s="2"/>
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
-    </row>
-    <row r="53" spans="1:26">
+      <c r="AA52" s="2"/>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" s="11" t="s">
         <v>91</v>
       </c>
@@ -3235,10 +3319,10 @@
       <c r="D53" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E53" s="11"/>
+      <c r="E53" s="12"/>
       <c r="F53" s="11"/>
       <c r="G53" s="11"/>
-      <c r="H53" s="2"/>
+      <c r="H53" s="11"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -3257,8 +3341,9 @@
       <c r="X53" s="2"/>
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
-    </row>
-    <row r="54" spans="1:26">
+      <c r="AA53" s="2"/>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" s="11" t="s">
         <v>95</v>
       </c>
@@ -3271,10 +3356,10 @@
       <c r="D54" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="11"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="11"/>
       <c r="G54" s="11"/>
-      <c r="H54" s="2"/>
+      <c r="H54" s="11"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -3293,8 +3378,9 @@
       <c r="X54" s="2"/>
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
-    </row>
-    <row r="55" spans="1:26">
+      <c r="AA54" s="2"/>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" s="11" t="s">
         <v>99</v>
       </c>
@@ -3303,10 +3389,10 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
+      <c r="E55" s="16"/>
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
-      <c r="H55" s="2"/>
+      <c r="H55" s="11"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -3325,8 +3411,9 @@
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
-    </row>
-    <row r="56" spans="1:26">
+      <c r="AA55" s="2"/>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" s="2" t="s">
         <v>19</v>
       </c>
@@ -3339,12 +3426,12 @@
       <c r="D56" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="2" t="s">
+      <c r="E56" s="16"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -3363,8 +3450,9 @@
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
-    </row>
-    <row r="57" spans="1:26">
+      <c r="AA56" s="2"/>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" s="2" t="s">
         <v>95</v>
       </c>
@@ -3377,7 +3465,7 @@
       <c r="D57" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" s="16"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -3399,8 +3487,9 @@
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
-    </row>
-    <row r="58" spans="1:26">
+      <c r="AA57" s="2"/>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" s="2" t="s">
         <v>95</v>
       </c>
@@ -3413,7 +3502,7 @@
       <c r="D58" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" s="16"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -3435,8 +3524,9 @@
       <c r="X58" s="2"/>
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
-    </row>
-    <row r="59" spans="1:26">
+      <c r="AA58" s="2"/>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" s="2" t="s">
         <v>95</v>
       </c>
@@ -3449,7 +3539,7 @@
       <c r="D59" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" s="16"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -3471,8 +3561,9 @@
       <c r="X59" s="2"/>
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
-    </row>
-    <row r="60" spans="1:26">
+      <c r="AA59" s="2"/>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" s="2" t="s">
         <v>95</v>
       </c>
@@ -3485,7 +3576,7 @@
       <c r="D60" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" s="16"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -3507,8 +3598,9 @@
       <c r="X60" s="2"/>
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
-    </row>
-    <row r="61" spans="1:26">
+      <c r="AA60" s="2"/>
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" s="2" t="s">
         <v>35</v>
       </c>
@@ -3517,7 +3609,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
+      <c r="E61" s="16"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -3539,8 +3631,9 @@
       <c r="X61" s="2"/>
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
-    </row>
-    <row r="62" spans="1:26">
+      <c r="AA61" s="2"/>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" s="16" t="s">
         <v>91</v>
       </c>
@@ -3548,7 +3641,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:26">
+    <row r="63" spans="1:27">
       <c r="A63" s="16" t="s">
         <v>95</v>
       </c>
@@ -3559,7 +3652,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:26">
+    <row r="64" spans="1:27">
       <c r="A64" s="16" t="s">
         <v>99</v>
       </c>
@@ -3567,699 +3660,718 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:26" s="28" customFormat="1" ht="39">
-      <c r="A65" s="31" t="s">
+    <row r="65" spans="1:27" s="28" customFormat="1" ht="39">
+      <c r="A65" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="31" t="s">
+      <c r="B65" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="C65" s="31" t="s">
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="30"/>
+      <c r="N65" s="30"/>
+      <c r="O65" s="30"/>
+      <c r="P65" s="30"/>
+      <c r="Q65" s="30"/>
+      <c r="R65" s="30"/>
+      <c r="S65" s="30"/>
+      <c r="T65" s="30"/>
+      <c r="U65" s="30"/>
+      <c r="V65" s="30"/>
+      <c r="W65" s="30"/>
+      <c r="X65" s="30"/>
+      <c r="Y65" s="30"/>
+      <c r="Z65" s="30"/>
+      <c r="AA65" s="30"/>
+    </row>
+    <row r="66" spans="1:27" s="28" customFormat="1">
+      <c r="A66" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="C66" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="E65" s="31"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="31"/>
-      <c r="T65" s="31"/>
-      <c r="U65" s="31"/>
-      <c r="V65" s="31"/>
-      <c r="W65" s="31"/>
-      <c r="X65" s="31"/>
-      <c r="Y65" s="31"/>
-      <c r="Z65" s="31"/>
-    </row>
-    <row r="66" spans="1:26" s="28" customFormat="1">
-      <c r="A66" s="31" t="s">
+      <c r="D66" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="E66" s="32"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="30"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
+      <c r="R66" s="30"/>
+      <c r="S66" s="30"/>
+      <c r="T66" s="30"/>
+      <c r="U66" s="30"/>
+      <c r="V66" s="30"/>
+      <c r="W66" s="30"/>
+      <c r="X66" s="30"/>
+      <c r="Y66" s="30"/>
+      <c r="Z66" s="30"/>
+      <c r="AA66" s="30"/>
+    </row>
+    <row r="67" spans="1:27" s="28" customFormat="1">
+      <c r="A67" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+    </row>
+    <row r="68" spans="1:27" s="28" customFormat="1" ht="29.5">
+      <c r="A68" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E68" s="33"/>
+      <c r="F68" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="30"/>
+      <c r="R68" s="30"/>
+      <c r="S68" s="30"/>
+      <c r="T68" s="30"/>
+      <c r="U68" s="30"/>
+      <c r="V68" s="30"/>
+      <c r="W68" s="30"/>
+      <c r="X68" s="30"/>
+      <c r="Y68" s="30"/>
+      <c r="Z68" s="30"/>
+      <c r="AA68" s="30"/>
+    </row>
+    <row r="69" spans="1:27" s="28" customFormat="1" ht="44.25">
+      <c r="A69" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C69" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E69" s="33"/>
+      <c r="F69" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="30"/>
+      <c r="S69" s="30"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="30"/>
+      <c r="Y69" s="30"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+    </row>
+    <row r="70" spans="1:27" s="28" customFormat="1" ht="39">
+      <c r="A70" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+    </row>
+    <row r="71" spans="1:27" s="28" customFormat="1" ht="29.5">
+      <c r="A71" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E71" s="33"/>
+      <c r="F71" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
+      <c r="N71" s="30"/>
+      <c r="O71" s="30"/>
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
+      <c r="R71" s="30"/>
+      <c r="S71" s="30"/>
+      <c r="T71" s="30"/>
+      <c r="U71" s="30"/>
+      <c r="V71" s="30"/>
+      <c r="W71" s="30"/>
+      <c r="X71" s="30"/>
+      <c r="Y71" s="30"/>
+      <c r="Z71" s="30"/>
+      <c r="AA71" s="30"/>
+    </row>
+    <row r="72" spans="1:27" s="28" customFormat="1">
+      <c r="A72" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C72" s="34"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
+      <c r="M72" s="30"/>
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
+      <c r="R72" s="30"/>
+      <c r="S72" s="30"/>
+      <c r="T72" s="30"/>
+      <c r="U72" s="30"/>
+      <c r="V72" s="30"/>
+      <c r="W72" s="30"/>
+      <c r="X72" s="30"/>
+      <c r="Y72" s="30"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
+    </row>
+    <row r="73" spans="1:27" s="28" customFormat="1">
+      <c r="A73" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="C66" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D66" s="33" t="s">
+      <c r="B73" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E73" s="32"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
+      <c r="M73" s="30"/>
+      <c r="N73" s="30"/>
+      <c r="O73" s="30"/>
+      <c r="P73" s="30"/>
+      <c r="Q73" s="30"/>
+      <c r="R73" s="30"/>
+      <c r="S73" s="30"/>
+      <c r="T73" s="30"/>
+      <c r="U73" s="30"/>
+      <c r="V73" s="30"/>
+      <c r="W73" s="30"/>
+      <c r="X73" s="30"/>
+      <c r="Y73" s="30"/>
+      <c r="Z73" s="30"/>
+      <c r="AA73" s="30"/>
+    </row>
+    <row r="74" spans="1:27" s="28" customFormat="1">
+      <c r="A74" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E74" s="32"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
+      <c r="M74" s="30"/>
+      <c r="N74" s="30"/>
+      <c r="O74" s="30"/>
+      <c r="P74" s="30"/>
+      <c r="Q74" s="30"/>
+      <c r="R74" s="30"/>
+      <c r="S74" s="30"/>
+      <c r="T74" s="30"/>
+      <c r="U74" s="30"/>
+      <c r="V74" s="30"/>
+      <c r="W74" s="30"/>
+      <c r="X74" s="30"/>
+      <c r="Y74" s="30"/>
+      <c r="Z74" s="30"/>
+      <c r="AA74" s="30"/>
+    </row>
+    <row r="75" spans="1:27" s="28" customFormat="1" ht="14.75">
+      <c r="A75" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
-      <c r="N66" s="31"/>
-      <c r="O66" s="31"/>
-      <c r="P66" s="31"/>
-      <c r="Q66" s="31"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="31"/>
-      <c r="T66" s="31"/>
-      <c r="U66" s="31"/>
-      <c r="V66" s="31"/>
-      <c r="W66" s="31"/>
-      <c r="X66" s="31"/>
-      <c r="Y66" s="31"/>
-      <c r="Z66" s="31"/>
-    </row>
-    <row r="67" spans="1:26" s="28" customFormat="1">
-      <c r="A67" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67" s="31" t="s">
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="30"/>
+      <c r="M75" s="30"/>
+      <c r="N75" s="30"/>
+      <c r="O75" s="30"/>
+      <c r="P75" s="30"/>
+      <c r="Q75" s="30"/>
+      <c r="R75" s="30"/>
+      <c r="S75" s="30"/>
+      <c r="T75" s="30"/>
+      <c r="U75" s="30"/>
+      <c r="V75" s="30"/>
+      <c r="W75" s="30"/>
+      <c r="X75" s="30"/>
+      <c r="Y75" s="30"/>
+      <c r="Z75" s="30"/>
+      <c r="AA75" s="30"/>
+    </row>
+    <row r="76" spans="1:27" s="28" customFormat="1" ht="29.5">
+      <c r="A76" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="C67" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
-      <c r="X67" s="31"/>
-      <c r="Y67" s="31"/>
-      <c r="Z67" s="31"/>
-    </row>
-    <row r="68" spans="1:26" s="28" customFormat="1" ht="29.5">
-      <c r="A68" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B68" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="C68" s="34" t="s">
+      <c r="B76" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E76" s="33"/>
+      <c r="F76" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D68" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="E68" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
-      <c r="N68" s="31"/>
-      <c r="O68" s="31"/>
-      <c r="P68" s="31"/>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="31"/>
-      <c r="T68" s="31"/>
-      <c r="U68" s="31"/>
-      <c r="V68" s="31"/>
-      <c r="W68" s="31"/>
-      <c r="X68" s="31"/>
-      <c r="Y68" s="31"/>
-      <c r="Z68" s="31"/>
-    </row>
-    <row r="69" spans="1:26" s="28" customFormat="1" ht="44.25">
-      <c r="A69" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="D69" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="E69" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
-      <c r="N69" s="31"/>
-      <c r="O69" s="31"/>
-      <c r="P69" s="31"/>
-      <c r="Q69" s="31"/>
-      <c r="R69" s="31"/>
-      <c r="S69" s="31"/>
-      <c r="T69" s="31"/>
-      <c r="U69" s="31"/>
-      <c r="V69" s="31"/>
-      <c r="W69" s="31"/>
-      <c r="X69" s="31"/>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
-    </row>
-    <row r="70" spans="1:26" s="28" customFormat="1" ht="39">
-      <c r="A70" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="C70" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D70" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
-      <c r="W70" s="31"/>
-      <c r="X70" s="31"/>
-      <c r="Y70" s="31"/>
-      <c r="Z70" s="31"/>
-    </row>
-    <row r="71" spans="1:26" s="28" customFormat="1" ht="29.5">
-      <c r="A71" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="C71" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="D71" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="E71" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-      <c r="N71" s="31"/>
-      <c r="O71" s="31"/>
-      <c r="P71" s="31"/>
-      <c r="Q71" s="31"/>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="31"/>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="31"/>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="31"/>
-      <c r="Z71" s="31"/>
-    </row>
-    <row r="72" spans="1:26" s="28" customFormat="1">
-      <c r="A72" s="31" t="s">
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="30"/>
+      <c r="R76" s="30"/>
+      <c r="S76" s="30"/>
+      <c r="T76" s="30"/>
+      <c r="U76" s="30"/>
+      <c r="V76" s="30"/>
+      <c r="W76" s="30"/>
+      <c r="X76" s="30"/>
+      <c r="Y76" s="30"/>
+      <c r="Z76" s="30"/>
+      <c r="AA76" s="30"/>
+    </row>
+    <row r="77" spans="1:27" s="28" customFormat="1" ht="59">
+      <c r="A77" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" s="33"/>
+      <c r="F77" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="30"/>
+      <c r="M77" s="30"/>
+      <c r="N77" s="30"/>
+      <c r="O77" s="30"/>
+      <c r="P77" s="30"/>
+      <c r="Q77" s="30"/>
+      <c r="R77" s="30"/>
+      <c r="S77" s="30"/>
+      <c r="T77" s="30"/>
+      <c r="U77" s="30"/>
+      <c r="V77" s="30"/>
+      <c r="W77" s="30"/>
+      <c r="X77" s="30"/>
+      <c r="Y77" s="30"/>
+      <c r="Z77" s="30"/>
+      <c r="AA77" s="30"/>
+    </row>
+    <row r="78" spans="1:27" s="28" customFormat="1" ht="26.75">
+      <c r="A78" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="D78" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
+      <c r="L78" s="30"/>
+      <c r="M78" s="30"/>
+      <c r="N78" s="30"/>
+      <c r="O78" s="30"/>
+      <c r="P78" s="30"/>
+      <c r="Q78" s="30"/>
+      <c r="R78" s="30"/>
+      <c r="S78" s="30"/>
+      <c r="T78" s="30"/>
+      <c r="U78" s="30"/>
+      <c r="V78" s="30"/>
+      <c r="W78" s="30"/>
+      <c r="X78" s="30"/>
+      <c r="Y78" s="30"/>
+      <c r="Z78" s="30"/>
+      <c r="AA78" s="30"/>
+    </row>
+    <row r="79" spans="1:27" s="28" customFormat="1" ht="14.75">
+      <c r="A79" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="31"/>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-    </row>
-    <row r="73" spans="1:26" s="28" customFormat="1">
-      <c r="A73" s="31" t="s">
+      <c r="B79" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" s="33"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="30"/>
+      <c r="R79" s="30"/>
+      <c r="S79" s="30"/>
+      <c r="T79" s="30"/>
+      <c r="U79" s="30"/>
+      <c r="V79" s="30"/>
+      <c r="W79" s="30"/>
+      <c r="X79" s="30"/>
+      <c r="Y79" s="30"/>
+      <c r="Z79" s="30"/>
+      <c r="AA79" s="30"/>
+    </row>
+    <row r="80" spans="1:27" s="28" customFormat="1" ht="15.5" customHeight="1">
+      <c r="A80" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="30"/>
+      <c r="M80" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="N80" s="30"/>
+      <c r="O80" s="30"/>
+      <c r="P80" s="30"/>
+      <c r="Q80" s="30"/>
+      <c r="R80" s="30"/>
+      <c r="S80" s="30"/>
+      <c r="T80" s="30"/>
+      <c r="U80" s="30"/>
+      <c r="V80" s="30"/>
+      <c r="W80" s="30"/>
+      <c r="X80" s="30"/>
+      <c r="Y80" s="30"/>
+      <c r="Z80" s="30"/>
+      <c r="AA80" s="30"/>
+    </row>
+    <row r="81" spans="1:27" s="28" customFormat="1" ht="13.75" customHeight="1">
+      <c r="A81" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="D73" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="31"/>
-      <c r="K73" s="31"/>
-      <c r="L73" s="31"/>
-      <c r="M73" s="31"/>
-      <c r="N73" s="31"/>
-      <c r="O73" s="31"/>
-      <c r="P73" s="31"/>
-      <c r="Q73" s="31"/>
-      <c r="R73" s="31"/>
-      <c r="S73" s="31"/>
-      <c r="T73" s="31"/>
-      <c r="U73" s="31"/>
-      <c r="V73" s="31"/>
-      <c r="W73" s="31"/>
-      <c r="X73" s="31"/>
-      <c r="Y73" s="31"/>
-      <c r="Z73" s="31"/>
-    </row>
-    <row r="74" spans="1:26" s="28" customFormat="1">
-      <c r="A74" s="31" t="s">
+      <c r="B81" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="E81" s="33"/>
+      <c r="F81" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G81" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
+      <c r="M81" s="30"/>
+      <c r="N81" s="30"/>
+      <c r="O81" s="30"/>
+      <c r="P81" s="30"/>
+      <c r="Q81" s="30"/>
+      <c r="R81" s="30"/>
+      <c r="S81" s="30"/>
+      <c r="T81" s="30"/>
+      <c r="U81" s="30"/>
+      <c r="V81" s="30"/>
+      <c r="W81" s="30"/>
+      <c r="X81" s="30"/>
+      <c r="Y81" s="30"/>
+      <c r="Z81" s="30"/>
+      <c r="AA81" s="30"/>
+    </row>
+    <row r="82" spans="1:27" s="28" customFormat="1" ht="24.5" customHeight="1">
+      <c r="A82" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="D74" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="E74" s="31"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="31"/>
-      <c r="L74" s="31"/>
-      <c r="M74" s="31"/>
-      <c r="N74" s="31"/>
-      <c r="O74" s="31"/>
-      <c r="P74" s="31"/>
-      <c r="Q74" s="31"/>
-      <c r="R74" s="31"/>
-      <c r="S74" s="31"/>
-      <c r="T74" s="31"/>
-      <c r="U74" s="31"/>
-      <c r="V74" s="31"/>
-      <c r="W74" s="31"/>
-      <c r="X74" s="31"/>
-      <c r="Y74" s="31"/>
-      <c r="Z74" s="31"/>
-    </row>
-    <row r="75" spans="1:26" s="28" customFormat="1" ht="14.75">
-      <c r="A75" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="34"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="31"/>
-      <c r="K75" s="31"/>
-      <c r="L75" s="31"/>
-      <c r="M75" s="31"/>
-      <c r="N75" s="31"/>
-      <c r="O75" s="31"/>
-      <c r="P75" s="31"/>
-      <c r="Q75" s="31"/>
-      <c r="R75" s="31"/>
-      <c r="S75" s="31"/>
-      <c r="T75" s="31"/>
-      <c r="U75" s="31"/>
-      <c r="V75" s="31"/>
-      <c r="W75" s="31"/>
-      <c r="X75" s="31"/>
-      <c r="Y75" s="31"/>
-      <c r="Z75" s="31"/>
-    </row>
-    <row r="76" spans="1:26" s="28" customFormat="1" ht="29.5">
-      <c r="A76" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="D76" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="E76" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F76" s="31"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="31"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="31"/>
-      <c r="K76" s="31"/>
-      <c r="L76" s="31"/>
-      <c r="M76" s="31"/>
-      <c r="N76" s="31"/>
-      <c r="O76" s="31"/>
-      <c r="P76" s="31"/>
-      <c r="Q76" s="31"/>
-      <c r="R76" s="31"/>
-      <c r="S76" s="31"/>
-      <c r="T76" s="31"/>
-      <c r="U76" s="31"/>
-      <c r="V76" s="31"/>
-      <c r="W76" s="31"/>
-      <c r="X76" s="31"/>
-      <c r="Y76" s="31"/>
-      <c r="Z76" s="31"/>
-    </row>
-    <row r="77" spans="1:26" s="28" customFormat="1" ht="59">
-      <c r="A77" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="C77" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="D77" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="E77" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
-      <c r="K77" s="31"/>
-      <c r="L77" s="31"/>
-      <c r="M77" s="31"/>
-      <c r="N77" s="31"/>
-      <c r="O77" s="31"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="31"/>
-      <c r="T77" s="31"/>
-      <c r="U77" s="31"/>
-      <c r="V77" s="31"/>
-      <c r="W77" s="31"/>
-      <c r="X77" s="31"/>
-      <c r="Y77" s="31"/>
-      <c r="Z77" s="31"/>
-    </row>
-    <row r="78" spans="1:26" s="28" customFormat="1" ht="26.75">
-      <c r="A78" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="C78" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D78" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="E78" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="31"/>
-      <c r="K78" s="31"/>
-      <c r="L78" s="31"/>
-      <c r="M78" s="31"/>
-      <c r="N78" s="31"/>
-      <c r="O78" s="31"/>
-      <c r="P78" s="31"/>
-      <c r="Q78" s="31"/>
-      <c r="R78" s="31"/>
-      <c r="S78" s="31"/>
-      <c r="T78" s="31"/>
-      <c r="U78" s="31"/>
-      <c r="V78" s="31"/>
-      <c r="W78" s="31"/>
-      <c r="X78" s="31"/>
-      <c r="Y78" s="31"/>
-      <c r="Z78" s="31"/>
-    </row>
-    <row r="79" spans="1:26" s="28" customFormat="1" ht="14.75">
-      <c r="A79" s="31" t="s">
+      <c r="B82" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="E82" s="32"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+      <c r="L82" s="30"/>
+      <c r="M82" s="30"/>
+      <c r="N82" s="30"/>
+      <c r="O82" s="30"/>
+      <c r="P82" s="30"/>
+      <c r="Q82" s="30"/>
+      <c r="R82" s="30"/>
+      <c r="S82" s="30"/>
+      <c r="T82" s="30"/>
+      <c r="U82" s="30"/>
+      <c r="V82" s="30"/>
+      <c r="W82" s="30"/>
+      <c r="X82" s="30"/>
+      <c r="Y82" s="30"/>
+      <c r="Z82" s="30"/>
+      <c r="AA82" s="30"/>
+    </row>
+    <row r="83" spans="1:27" s="28" customFormat="1">
+      <c r="A83" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B79" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="C79" s="34"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="31"/>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
-      <c r="M79" s="31"/>
-      <c r="N79" s="31"/>
-      <c r="O79" s="31"/>
-      <c r="P79" s="31"/>
-      <c r="Q79" s="31"/>
-      <c r="R79" s="31"/>
-      <c r="S79" s="31"/>
-      <c r="T79" s="31"/>
-      <c r="U79" s="31"/>
-      <c r="V79" s="31"/>
-      <c r="W79" s="31"/>
-      <c r="X79" s="31"/>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-    </row>
-    <row r="80" spans="1:26" s="28" customFormat="1" ht="15.5" customHeight="1">
-      <c r="A80" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="C80" s="31"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="31"/>
-      <c r="G80" s="31"/>
-      <c r="H80" s="31"/>
-      <c r="I80" s="31"/>
-      <c r="J80" s="31"/>
-      <c r="K80" s="31"/>
-      <c r="L80" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="M80" s="31"/>
-      <c r="N80" s="31"/>
-      <c r="O80" s="31"/>
-      <c r="P80" s="31"/>
-      <c r="Q80" s="31"/>
-      <c r="R80" s="31"/>
-      <c r="S80" s="31"/>
-      <c r="T80" s="31"/>
-      <c r="U80" s="31"/>
-      <c r="V80" s="31"/>
-      <c r="W80" s="31"/>
-      <c r="X80" s="31"/>
-      <c r="Y80" s="31"/>
-      <c r="Z80" s="31"/>
-    </row>
-    <row r="81" spans="1:26" s="28" customFormat="1" ht="13.75" customHeight="1">
-      <c r="A81" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="D81" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="G81" s="31"/>
-      <c r="H81" s="31"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="31"/>
-      <c r="K81" s="31"/>
-      <c r="L81" s="31"/>
-      <c r="M81" s="31"/>
-      <c r="N81" s="31"/>
-      <c r="O81" s="31"/>
-      <c r="P81" s="31"/>
-      <c r="Q81" s="31"/>
-      <c r="R81" s="31"/>
-      <c r="S81" s="31"/>
-      <c r="T81" s="31"/>
-      <c r="U81" s="31"/>
-      <c r="V81" s="31"/>
-      <c r="W81" s="31"/>
-      <c r="X81" s="31"/>
-      <c r="Y81" s="31"/>
-      <c r="Z81" s="31"/>
-    </row>
-    <row r="82" spans="1:26" s="28" customFormat="1" ht="24.5" customHeight="1">
-      <c r="A82" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E82" s="31"/>
-      <c r="F82" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G82" s="31"/>
-      <c r="H82" s="31"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="31"/>
-      <c r="K82" s="31"/>
-      <c r="L82" s="31"/>
-      <c r="M82" s="31"/>
-      <c r="N82" s="31"/>
-      <c r="O82" s="31"/>
-      <c r="P82" s="31"/>
-      <c r="Q82" s="31"/>
-      <c r="R82" s="31"/>
-      <c r="S82" s="31"/>
-      <c r="T82" s="31"/>
-      <c r="U82" s="31"/>
-      <c r="V82" s="31"/>
-      <c r="W82" s="31"/>
-      <c r="X82" s="31"/>
-      <c r="Y82" s="31"/>
-      <c r="Z82" s="31"/>
-    </row>
-    <row r="83" spans="1:26" s="28" customFormat="1">
-      <c r="A83" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="31"/>
-      <c r="K83" s="31"/>
-      <c r="L83" s="31"/>
-      <c r="M83" s="31"/>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="31"/>
-      <c r="R83" s="31"/>
-      <c r="S83" s="31"/>
-      <c r="T83" s="31"/>
-      <c r="U83" s="31"/>
-      <c r="V83" s="31"/>
-      <c r="W83" s="31"/>
-      <c r="X83" s="31"/>
-      <c r="Y83" s="31"/>
-      <c r="Z83" s="31"/>
-    </row>
-    <row r="84" spans="1:26">
+      <c r="B83" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
+      <c r="N83" s="30"/>
+      <c r="O83" s="30"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="30"/>
+      <c r="R83" s="30"/>
+      <c r="S83" s="30"/>
+      <c r="T83" s="30"/>
+      <c r="U83" s="30"/>
+      <c r="V83" s="30"/>
+      <c r="W83" s="30"/>
+      <c r="X83" s="30"/>
+      <c r="Y83" s="30"/>
+      <c r="Z83" s="30"/>
+      <c r="AA83" s="30"/>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" s="16" t="s">
         <v>91</v>
       </c>
@@ -4268,12 +4380,11 @@
       </c>
       <c r="C84" s="28"/>
       <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
       <c r="F84" s="28"/>
-      <c r="G84" s="16" t="s">
+      <c r="G84" s="28"/>
+      <c r="H84" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H84" s="28"/>
       <c r="I84" s="28"/>
       <c r="J84" s="28"/>
       <c r="K84" s="28"/>
@@ -4292,8 +4403,9 @@
       <c r="X84" s="28"/>
       <c r="Y84" s="28"/>
       <c r="Z84" s="28"/>
-    </row>
-    <row r="85" spans="1:26" ht="14.75">
+      <c r="AA84" s="28"/>
+    </row>
+    <row r="85" spans="1:27" ht="14.75">
       <c r="A85" s="16" t="s">
         <v>121</v>
       </c>
@@ -4304,22 +4416,21 @@
         <v>123</v>
       </c>
       <c r="D85" s="28"/>
-      <c r="E85" s="26" t="s">
-        <v>223</v>
-      </c>
       <c r="F85" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="G85" s="28"/>
+        <v>221</v>
+      </c>
+      <c r="G85" s="26" t="s">
+        <v>313</v>
+      </c>
       <c r="H85" s="28"/>
       <c r="I85" s="28"/>
       <c r="J85" s="28"/>
       <c r="K85" s="28"/>
       <c r="L85" s="28"/>
-      <c r="M85" s="26" t="s">
+      <c r="M85" s="28"/>
+      <c r="N85" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="N85" s="28"/>
       <c r="O85" s="28"/>
       <c r="P85" s="28"/>
       <c r="Q85" s="28"/>
@@ -4332,8 +4443,9 @@
       <c r="X85" s="28"/>
       <c r="Y85" s="28"/>
       <c r="Z85" s="28"/>
-    </row>
-    <row r="86" spans="1:26">
+      <c r="AA85" s="28"/>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" s="16" t="s">
         <v>99</v>
       </c>
@@ -4342,7 +4454,6 @@
       </c>
       <c r="C86" s="28"/>
       <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
       <c r="F86" s="28"/>
       <c r="G86" s="28"/>
       <c r="H86" s="28"/>
@@ -4364,8 +4475,9 @@
       <c r="X86" s="28"/>
       <c r="Y86" s="28"/>
       <c r="Z86" s="28"/>
-    </row>
-    <row r="87" spans="1:26">
+      <c r="AA86" s="28"/>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" s="16" t="s">
         <v>19</v>
       </c>
@@ -4374,14 +4486,13 @@
       </c>
       <c r="C87" s="28"/>
       <c r="D87" s="28"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="G87" s="16" t="s">
+      <c r="F87" s="28"/>
+      <c r="G87" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="H87" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="H87" s="28"/>
       <c r="I87" s="28"/>
       <c r="J87" s="28"/>
       <c r="K87" s="28"/>
@@ -4400,8 +4511,9 @@
       <c r="X87" s="28"/>
       <c r="Y87" s="28"/>
       <c r="Z87" s="28"/>
-    </row>
-    <row r="88" spans="1:26" ht="14.75">
+      <c r="AA87" s="28"/>
+    </row>
+    <row r="88" spans="1:27" ht="14.75">
       <c r="A88" s="16" t="s">
         <v>95</v>
       </c>
@@ -4412,11 +4524,10 @@
         <v>127</v>
       </c>
       <c r="D88" s="28"/>
-      <c r="E88" s="28"/>
-      <c r="F88" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="G88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="36" t="s">
+        <v>274</v>
+      </c>
       <c r="H88" s="28"/>
       <c r="I88" s="28"/>
       <c r="J88" s="28"/>
@@ -4436,23 +4547,23 @@
       <c r="X88" s="28"/>
       <c r="Y88" s="28"/>
       <c r="Z88" s="28"/>
-    </row>
-    <row r="89" spans="1:26">
+      <c r="AA88" s="28"/>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="31" t="s">
-        <v>268</v>
+      <c r="B89" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="C89" s="16" t="s">
         <v>128</v>
       </c>
       <c r="D89" s="28"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="G89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="36" t="s">
+        <v>276</v>
+      </c>
       <c r="H89" s="28"/>
       <c r="I89" s="28"/>
       <c r="J89" s="28"/>
@@ -4472,36 +4583,37 @@
       <c r="X89" s="28"/>
       <c r="Y89" s="28"/>
       <c r="Z89" s="28"/>
-    </row>
-    <row r="90" spans="1:26">
+      <c r="AA89" s="28"/>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="31" t="s">
-        <v>269</v>
+      <c r="B90" s="30" t="s">
+        <v>267</v>
       </c>
       <c r="C90" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="F90" s="37" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26">
+      <c r="G90" s="36" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B91" s="31" t="s">
-        <v>270</v>
+      <c r="B91" s="30" t="s">
+        <v>268</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F91" s="37" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="92" spans="1:26">
+      <c r="G91" s="36" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" s="16" t="s">
         <v>95</v>
       </c>
@@ -4511,25 +4623,25 @@
       <c r="C92" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="F92" s="37" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="93" spans="1:26">
+      <c r="G92" s="36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="31" t="s">
-        <v>271</v>
+      <c r="B93" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="C93" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="F93" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26">
+      <c r="G93" s="36" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" s="16" t="s">
         <v>95</v>
       </c>
@@ -4539,11 +4651,11 @@
       <c r="C94" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F94" s="37" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26">
+      <c r="G94" s="36" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" s="16" t="s">
         <v>95</v>
       </c>
@@ -4553,11 +4665,11 @@
       <c r="C95" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F95" s="37" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26">
+      <c r="G95" s="36" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" s="16" t="s">
         <v>95</v>
       </c>
@@ -4567,11 +4679,11 @@
       <c r="C96" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F96" s="37" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="36" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" s="16" t="s">
         <v>95</v>
       </c>
@@ -4581,11 +4693,11 @@
       <c r="C97" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="F97" s="37" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="G97" s="36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" s="16" t="s">
         <v>95</v>
       </c>
@@ -4595,25 +4707,25 @@
       <c r="C98" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="F98" s="37" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="31" t="s">
-        <v>265</v>
+      <c r="B99" s="30" t="s">
+        <v>263</v>
       </c>
       <c r="C99" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F99" s="37" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="36" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" s="16" t="s">
         <v>95</v>
       </c>
@@ -4623,11 +4735,11 @@
       <c r="C100" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F100" s="37" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="36" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" s="16" t="s">
         <v>95</v>
       </c>
@@ -4637,11 +4749,11 @@
       <c r="C101" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F101" s="37" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" s="16" t="s">
         <v>95</v>
       </c>
@@ -4651,11 +4763,11 @@
       <c r="C102" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F102" s="37" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" s="16" t="s">
         <v>95</v>
       </c>
@@ -4665,11 +4777,11 @@
       <c r="C103" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="F103" s="37" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="36" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="16" t="s">
         <v>95</v>
       </c>
@@ -4679,11 +4791,11 @@
       <c r="C104" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F104" s="37" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="36" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" s="16" t="s">
         <v>95</v>
       </c>
@@ -4693,11 +4805,11 @@
       <c r="C105" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="F105" s="37" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="G105" s="36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" s="16" t="s">
         <v>95</v>
       </c>
@@ -4707,11 +4819,11 @@
       <c r="C106" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F106" s="37" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="36" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" s="16" t="s">
         <v>95</v>
       </c>
@@ -4721,11 +4833,11 @@
       <c r="C107" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="F107" s="37" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="36" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" s="16" t="s">
         <v>95</v>
       </c>
@@ -4735,39 +4847,39 @@
       <c r="C108" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="F108" s="37" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="36" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C109" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="F109" s="37" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="36" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C110" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F110" s="37" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="36" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" s="18" t="s">
         <v>95</v>
       </c>
@@ -4777,11 +4889,11 @@
       <c r="C111" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="F111" s="37" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="36" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" s="16" t="s">
         <v>95</v>
       </c>
@@ -4791,11 +4903,11 @@
       <c r="C112" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="F112" s="37" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13">
+      <c r="G112" s="36" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" s="16" t="s">
         <v>35</v>
       </c>
@@ -4803,18 +4915,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:14">
       <c r="A114" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="G114" t="s">
+        <v>309</v>
+      </c>
+      <c r="H114" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:14">
       <c r="A115" s="16" t="s">
         <v>185</v>
       </c>
@@ -4824,14 +4936,14 @@
       <c r="C115" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="E115" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="M115" s="26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" s="25" customFormat="1">
+      <c r="F115" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="N115" s="26" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" s="25" customFormat="1">
       <c r="A116" s="16" t="s">
         <v>95</v>
       </c>
@@ -4841,8 +4953,9 @@
       <c r="C116" s="16" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="117" spans="1:13">
+      <c r="E116" s="29"/>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" s="16" t="s">
         <v>99</v>
       </c>
@@ -4850,21 +4963,22 @@
         <v>184</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="28" customFormat="1">
+    <row r="118" spans="1:14" s="28" customFormat="1">
       <c r="A118" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="G118" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="E118" s="29"/>
+      <c r="G118" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="H118" s="28" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="119" spans="1:13" s="28" customFormat="1">
+    <row r="119" spans="1:14" s="28" customFormat="1">
       <c r="A119" s="16" t="s">
         <v>185</v>
       </c>
@@ -4872,16 +4986,17 @@
         <v>186</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="E119" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="M119" s="26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" s="28" customFormat="1">
+        <v>311</v>
+      </c>
+      <c r="E119" s="29"/>
+      <c r="F119" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="N119" s="26" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" s="28" customFormat="1">
       <c r="A120" s="16" t="s">
         <v>95</v>
       </c>
@@ -4889,32 +5004,34 @@
         <v>200</v>
       </c>
       <c r="C120" s="27" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" s="28" customFormat="1">
+        <v>312</v>
+      </c>
+      <c r="E120" s="29"/>
+    </row>
+    <row r="121" spans="1:14" s="28" customFormat="1">
       <c r="A121" s="16" t="s">
         <v>99</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13">
+        <v>310</v>
+      </c>
+      <c r="E121" s="29"/>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B122" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F122" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G122" t="s">
+      <c r="G122" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="H122" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:14">
       <c r="A123" s="16" t="s">
         <v>95</v>
       </c>
@@ -4925,61 +5042,114 @@
         <v>204</v>
       </c>
     </row>
-    <row r="124" spans="1:13" s="25" customFormat="1">
+    <row r="124" spans="1:14" s="37" customFormat="1">
       <c r="A124" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="E124" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" s="37" customFormat="1">
+      <c r="A125" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="M125" s="37" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" s="37" customFormat="1">
+      <c r="A126" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" s="29" customFormat="1">
+      <c r="A127" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E127" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="H127" s="29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" s="29" customFormat="1">
+      <c r="A128" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="M128" s="26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="25" customFormat="1">
+      <c r="A129" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="E129" s="29"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B131" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C131" t="s">
+        <v>206</v>
+      </c>
+      <c r="H131" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B124" s="16" t="s">
+      <c r="B132" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C132" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B133" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="C124" s="25" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13">
-      <c r="A125" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B125" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13">
-      <c r="A126" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C126" t="s">
-        <v>208</v>
-      </c>
-      <c r="G126" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13">
-      <c r="A127" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B127" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="C127" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13">
-      <c r="A128" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B128" s="16" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L28:Q28"/>
+    <mergeCell ref="M28:R28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5036,854 +5206,854 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A3" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A4" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="C4" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A5" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="C5" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A6" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B6" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A7" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="C7" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A8" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="31"/>
-      <c r="Z5" s="31"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B8" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A9" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A7" s="31" t="s">
+      <c r="B9" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A10" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B10" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A11" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A12" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A13" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A14" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A15" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+    </row>
+    <row r="17" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A17" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A18" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A19" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+    </row>
+    <row r="20" spans="1:26" ht="13">
+      <c r="A20" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+    </row>
+    <row r="21" spans="1:26" ht="13">
+      <c r="A21" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+    </row>
+    <row r="22" spans="1:26" ht="13">
+      <c r="A22" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+    </row>
+    <row r="23" spans="1:26" ht="13">
+      <c r="A23" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+    </row>
+    <row r="24" spans="1:26" ht="13">
+      <c r="A24" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="C24" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+    </row>
+    <row r="25" spans="1:26" ht="13">
+      <c r="A25" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="B25" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+    </row>
+    <row r="26" spans="1:26" ht="13">
+      <c r="A26" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="31"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A14" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A15" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-    </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A17" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="31"/>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A19" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-    </row>
-    <row r="20" spans="1:26" ht="13">
-      <c r="A20" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-    </row>
-    <row r="21" spans="1:26" ht="13">
-      <c r="A21" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="31"/>
-    </row>
-    <row r="22" spans="1:26" ht="13">
-      <c r="A22" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-    </row>
-    <row r="23" spans="1:26" ht="13">
-      <c r="A23" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-    </row>
-    <row r="24" spans="1:26" ht="13">
-      <c r="A24" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-    </row>
-    <row r="25" spans="1:26" ht="13">
-      <c r="A25" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-    </row>
-    <row r="26" spans="1:26" ht="13">
-      <c r="A26" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="C26" s="33" t="s">
+      <c r="B26" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1">
       <c r="A27" s="16" t="s">
@@ -5953,30 +6123,30 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="27" t="s">
         <v>259</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B34" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="D34" s="27" t="s">
         <v>262</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -1000,12 +1000,6 @@
     <t>${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true"</t>
   </si>
   <si>
-    <t>${high_risk_manual}  = "true"  and ${is_high_risk_pregnancy_ML} = "true"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">begin repeat </t>
-  </si>
-  <si>
     <t xml:space="preserve">questions_to_client </t>
   </si>
   <si>
@@ -1021,9 +1015,6 @@
     <t>current_name</t>
   </si>
   <si>
-    <t xml:space="preserve">end repeat </t>
-  </si>
-  <si>
     <t>imran</t>
   </si>
   <si>
@@ -1034,6 +1025,15 @@
   </si>
   <si>
     <t>indexed-repeat(${esmail}, ${imran}, position(..))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin_repeat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_repeat </t>
+  </si>
+  <si>
+    <t>${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true"</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -5025,7 +5025,7 @@
         <v>202</v>
       </c>
       <c r="G122" s="26" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="H122" t="s">
         <v>125</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="124" spans="1:14" s="37" customFormat="1">
       <c r="A124" s="16" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E124" s="37">
         <v>1</v>
@@ -5058,55 +5058,54 @@
         <v>41</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="M125" s="37" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="126" spans="1:14" s="37" customFormat="1">
       <c r="A126" s="16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" s="29" customFormat="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" s="37" customFormat="1">
       <c r="A127" s="16" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E127" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="H127" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="H127" s="37" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:14" s="29" customFormat="1">
+    <row r="128" spans="1:14" s="37" customFormat="1">
       <c r="A128" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M128" s="26" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" s="25" customFormat="1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="37" customFormat="1">
       <c r="A129" s="16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="E129" s="29"/>
-    </row>
-    <row r="130" spans="1:8">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" s="37" customFormat="1">
       <c r="A130" s="16" t="s">
         <v>99</v>
       </c>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6185"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="438">
   <si>
     <t>type</t>
   </si>
@@ -610,9 +610,6 @@
     <t xml:space="preserve">mitigation_strategies </t>
   </si>
   <si>
-    <t>Considering these risk factors: [${nitu}] what can you do to continue in good health and have a safe pregnancy all the way through delivery?</t>
-  </si>
-  <si>
     <t>facility_delivery</t>
   </si>
   <si>
@@ -997,7 +994,7 @@
     <t xml:space="preserve">${high_risk_manual}  = "true" </t>
   </si>
   <si>
-    <t>${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true"</t>
+    <t xml:space="preserve">begin repeat </t>
   </si>
   <si>
     <t xml:space="preserve">questions_to_client </t>
@@ -1009,12 +1006,12 @@
     <t xml:space="preserve">repeat_count </t>
   </si>
   <si>
-    <t>count(${mitigation_list})</t>
-  </si>
-  <si>
     <t>current_name</t>
   </si>
   <si>
+    <t xml:space="preserve">end repeat </t>
+  </si>
+  <si>
     <t>imran</t>
   </si>
   <si>
@@ -1024,23 +1021,380 @@
     <t>${mitigation_list}</t>
   </si>
   <si>
-    <t>indexed-repeat(${esmail}, ${imran}, position(..))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">begin_repeat </t>
-  </si>
-  <si>
-    <t xml:space="preserve">end_repeat </t>
-  </si>
-  <si>
-    <t>${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true"</t>
+    <t>selected-at(${esmail},0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of ${current_name} ? </t>
+  </si>
+  <si>
+    <t>qn_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat </t>
+  </si>
+  <si>
+    <t>pregnancy_issues_group</t>
+  </si>
+  <si>
+    <t>Pregnancy Issues</t>
+  </si>
+  <si>
+    <t>Maswala ya ujauzito</t>
+  </si>
+  <si>
+    <t>subgroup_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>select_multiple pregnancy_issues</t>
+  </si>
+  <si>
+    <t>pregnancy_issues</t>
+  </si>
+  <si>
+    <t>Continue with the following questions. Indicate if the client has any of the following common pregnancy issues. 
+Have you experienced:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endelea na maswali yafuatayo. Angalia kama mteja ana moja kati ya matatizo haya yafuatayo yanayohusu ujauzito:
+</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
+  </si>
+  <si>
+    <t>Cannot select "None" with other options</t>
+  </si>
+  <si>
+    <t>Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
+  </si>
+  <si>
+    <t>refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>if(selected(${pregnancy_issues},"difficulty_breathing") or 
+selected(${pregnancy_issues},"fatigue") or 
+selected(${pregnancy_issues},"fever") or 
+selected(${pregnancy_issues},"tinnitus") or 
+selected(${pregnancy_issues},"dizziness") or 
+selected(${pregnancy_issues},"frontal_headache") or 
+selected(${pregnancy_issues},"blurred_vision") or 
+selected(${pregnancy_issues},"gastric_pain") or 
+selected(${pregnancy_issues},"swelling") or 
+selected(${pregnancy_issues},"early_labor") or 
+selected(${pregnancy_issues},"liquid_leaking") or 
+selected(${pregnancy_issues},"malaria_signs") or 
+selected(${pregnancy_issues},"foul_smelling")1,0)</t>
+  </si>
+  <si>
+    <t>refer_pregnancy_issues_note</t>
+  </si>
+  <si>
+    <t>I am referring you to a health facility because I have identified that you have danger sign(s)</t>
+  </si>
+  <si>
+    <t>Nakupa rufaa uende kituo cha afya kwasababu nimekugundua una dalili za hatari.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_issues}=1</t>
+  </si>
+  <si>
+    <t>difficulty_breathing</t>
+  </si>
+  <si>
+    <t>Difficulty Breathing</t>
+  </si>
+  <si>
+    <t>Anapumua kwa shida</t>
+  </si>
+  <si>
+    <t>fatigue</t>
+  </si>
+  <si>
+    <t>Fatigue, lethergy</t>
+  </si>
+  <si>
+    <t>Uchovu</t>
+  </si>
+  <si>
+    <t>fever</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>Homa</t>
+  </si>
+  <si>
+    <t>tinnitus</t>
+  </si>
+  <si>
+    <t>Tinnitus</t>
+  </si>
+  <si>
+    <t>Maskio kulia nyenje/kuvuma</t>
+  </si>
+  <si>
+    <t>dizziness</t>
+  </si>
+  <si>
+    <t>Dizziness</t>
+  </si>
+  <si>
+    <t>Kizunguzungu</t>
+  </si>
+  <si>
+    <t>frontal_headache</t>
+  </si>
+  <si>
+    <t>Severe Frontal Headache</t>
+  </si>
+  <si>
+    <t>Kichwa kuuma sana sehemu ya mbele</t>
+  </si>
+  <si>
+    <t>blurred_vision</t>
+  </si>
+  <si>
+    <t>Blurred vision</t>
+  </si>
+  <si>
+    <t>Kutokuona vizuri</t>
+  </si>
+  <si>
+    <t>gastric_pain</t>
+  </si>
+  <si>
+    <t>Severe gastric pain</t>
+  </si>
+  <si>
+    <t>Maumivu makali ya tumbo</t>
+  </si>
+  <si>
+    <t>swelling</t>
+  </si>
+  <si>
+    <t>Swelling of face, arms, fingers, or legs</t>
+  </si>
+  <si>
+    <t>Kuvimba uso,mikono, vidole au miguu</t>
+  </si>
+  <si>
+    <t>early_labor</t>
+  </si>
+  <si>
+    <t>Early labor pain before 9 months gestation</t>
+  </si>
+  <si>
+    <t>Uchungu wa mapema kabla ya miezi tisa</t>
+  </si>
+  <si>
+    <t>liquid_leaking</t>
+  </si>
+  <si>
+    <t>Liquid leaking from vagina</t>
+  </si>
+  <si>
+    <t>Kutoka maji sehemu za siri</t>
+  </si>
+  <si>
+    <t>malaria_signs</t>
+  </si>
+  <si>
+    <t>Signs of malaria (feeling cold, fever, vomiting)</t>
+  </si>
+  <si>
+    <t>Dalili za malaria(kuhisi baridi,homa na kutapika)</t>
+  </si>
+  <si>
+    <t>foul_smelling</t>
+  </si>
+  <si>
+    <t>Foul smelling vaginal discharge</t>
+  </si>
+  <si>
+    <t>kutoa uchafu wenye harufu mbaya sehemu za siri</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Hakuna mojawapo</t>
+  </si>
+  <si>
+    <t>pregnancy_and_pallor</t>
+  </si>
+  <si>
+    <t>baby_moving</t>
+  </si>
+  <si>
+    <t>Do you feel the baby moving on a daily basis, at least every six hours?</t>
+  </si>
+  <si>
+    <t>Je unahisi mtoto anacheza angalau kila baada ya masaa sita kila siku?</t>
+  </si>
+  <si>
+    <t>covid19_plam_pallor_note</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Now you are at the stage of comparing your palm with the client’s palm. Before doing this, please keep a 2 meters distance from your client as a precautionary measure to avoid the spread of Corona virus. Please ask your client to show you their palm while still keeping the distance. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Sasa upo kwenye hatua ya kulinganisha kiganja chako na cha mteja wako. Kabla ya kufanya hivyo, tafadhali hakikisha umekaa umbali wa mita mbili na mteja wako ili kujilinda na uwezekano wa kusambaza maambukizi ya Korona. Tafadhali mwambie mteja akuoneshe kiganja chake. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>pallor</t>
+  </si>
+  <si>
+    <t>Does the client have pallor? Compare your palm with client's palm. If client's palms are paler than yours, this is pallor.</t>
+  </si>
+  <si>
+    <t>Linganisha kiganja chako na cha mteja. Ikiwa kiganja cha mteja kimepauka sana kuliko chako hili ni tatizo. Iniashiria upungufu wa damu.</t>
+  </si>
+  <si>
+    <t>refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>if(selected(${baby_moving},"no") or selected(${pallor},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>has_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=1</t>
+  </si>
+  <si>
+    <t>no_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t>Based on our conversation, I did not identify any health issues, but if you develop any of the signs we discussed today, you should go to a health facility immediately</t>
+  </si>
+  <si>
+    <t>Huna dalili yoyote ya hatari lakini ikitokea ukapatwa na moja ya dalili tulizozijadili unapaswa kwenda kituo cha afya.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=0 and ${refer_pregnancy_issues}=0 and
+selected(${baby_moving},"yes") and selected(${pallor},"no")</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ${emergency_danger_sign_referral} = 0 
+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gestation_in_weeks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO_LABEL </t>
+  </si>
+  <si>
+    <t>gestation_in_weeks_c</t>
+  </si>
+  <si>
+    <t>../inputs/gestation_in_weeks</t>
+  </si>
+  <si>
+    <t>${gestation_in_weeks_c} &gt; 24</t>
+  </si>
+  <si>
+    <t>${high_risk_manual}  = "true"  and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true" and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>has_referral</t>
+  </si>
+  <si>
+    <t>if(${emergency_danger_sign_referral}=1 or
+${refer_pregnancy_issues}=1 or
+${refer_pregnancy_complications}=1
+1, 0)</t>
+  </si>
+  <si>
+    <t>needs_referral_note</t>
+  </si>
+  <si>
+    <t>You need to go to the health facility for the following reasons:</t>
+  </si>
+  <si>
+    <t>Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
+  </si>
+  <si>
+    <t>${has_referral}=1</t>
+  </si>
+  <si>
+    <t>needs_referral_danger_signs</t>
+  </si>
+  <si>
+    <t>To address emergency pregnancy danger signs</t>
+  </si>
+  <si>
+    <t>Ili kushughulikia dalili za hatari za dharura za mama mjamzito.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral}=1</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>needs_referral_neonatal_note</t>
+  </si>
+  <si>
+    <t>To address other pregnancy danger signs</t>
+  </si>
+  <si>
+    <t>Ili kushughulikia dalili nyengine za hatari.</t>
+  </si>
+  <si>
+    <t>${refer_pregnancy_issues}=1 or 
+${refer_pregnancy_complications}=1</t>
+  </si>
+  <si>
+    <t>refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>../danger_signs/emergency_danger_sign_referral</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>../pregnancy_issues_group/subgroup_pregnancy_issues/refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>../pregnancy_issues_group/pregnancy_and_pallor/refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>risk_factor_names</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/risk_factor_names</t>
+  </si>
+  <si>
+    <t>risk_factor_list</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
+[${risk_factor_names}]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1113,6 +1467,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1167,7 +1527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1221,6 +1581,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1442,12 +1813,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA133"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="32.7265625" customWidth="1"/>
     <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="265.54296875" customWidth="1"/>
+    <col min="4" max="4" width="255.58984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.40625" style="29"/>
   </cols>
   <sheetData>
@@ -1465,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1633,7 +2005,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>21</v>
@@ -1803,15 +2175,15 @@
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
     </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
+    <row r="10" spans="1:27" s="37" customFormat="1">
+      <c r="A10" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>406</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1828,25 +2200,25 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1878,10 +2250,10 @@
         <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1913,10 +2285,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1945,12 +2317,14 @@
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1977,30 +2351,28 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -2013,10 +2385,10 @@
     </row>
     <row r="16" spans="1:27">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -2025,9 +2397,7 @@
       <c r="E16" s="16"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2050,10 +2420,10 @@
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
@@ -2062,7 +2432,9 @@
       <c r="E17" s="16"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2084,13 +2456,13 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="2"/>
@@ -2119,13 +2491,15 @@
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="A19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="16"/>
       <c r="F19" s="2"/>
@@ -2152,28 +2526,28 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
+      <c r="B20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
@@ -2186,26 +2560,22 @@
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-      <c r="M21" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -2225,8 +2595,8 @@
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
+      <c r="B22" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2241,7 +2611,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -2262,8 +2632,8 @@
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>47</v>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2278,7 +2648,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -2296,30 +2666,32 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
@@ -2331,13 +2703,13 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2"/>
+      <c r="B25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="4"/>
       <c r="D25" s="2"/>
       <c r="E25" s="16"/>
       <c r="F25" s="2"/>
@@ -2347,11 +2719,11 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
+      <c r="M25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -2369,8 +2741,8 @@
       <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -2382,11 +2754,11 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-      <c r="M26" s="6" t="s">
-        <v>54</v>
+      <c r="M26" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="2"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
@@ -2405,7 +2777,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -2418,9 +2790,9 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="N27" s="6"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
@@ -2436,11 +2808,11 @@
       <c r="AA27" s="2"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -2452,14 +2824,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
-      <c r="M28" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
+      <c r="M28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
@@ -2471,11 +2843,11 @@
       <c r="AA28" s="2"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -2487,14 +2859,14 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
+      <c r="M29" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
@@ -2509,8 +2881,8 @@
       <c r="A30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>61</v>
+      <c r="B30" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2522,10 +2894,10 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="8">
-        <v>7</v>
-      </c>
-      <c r="N30" s="2"/>
+      <c r="M30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" s="6"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
@@ -2545,7 +2917,7 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -2558,7 +2930,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -2576,11 +2948,11 @@
       <c r="AA31" s="2"/>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>63</v>
+      <c r="B32" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2592,10 +2964,10 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-      <c r="M32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="N32" s="6"/>
+      <c r="M32" s="8">
+        <v>30</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
@@ -2615,7 +2987,7 @@
         <v>41</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -2628,7 +3000,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N33" s="6"/>
       <c r="O33" s="2"/>
@@ -2650,7 +3022,7 @@
         <v>41</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2663,7 +3035,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="2"/>
@@ -2685,7 +3057,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -2698,7 +3070,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="2"/>
@@ -2716,11 +3088,11 @@
       <c r="AA35" s="2"/>
     </row>
     <row r="36" spans="1:27">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>23</v>
+      <c r="B36" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2732,10 +3104,10 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="N36" s="2"/>
+      <c r="M36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N36" s="6"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
@@ -2755,7 +3127,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -2767,10 +3139,10 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
-      <c r="M37" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="N37" s="6"/>
+      <c r="M37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
@@ -2790,22 +3162,22 @@
         <v>41</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="16"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="10"/>
+      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="N38" s="6"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
@@ -2825,7 +3197,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -2837,8 +3209,8 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
-      <c r="M39" s="10" t="s">
-        <v>77</v>
+      <c r="M39" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -2860,7 +3232,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -2873,7 +3245,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -2895,7 +3267,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -2907,8 +3279,8 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
-      <c r="M41" s="2" t="s">
-        <v>81</v>
+      <c r="M41" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -2925,47 +3297,47 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" s="28" customFormat="1">
-      <c r="A42" s="27" t="s">
+    <row r="42" spans="1:27">
+      <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
+      <c r="B42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="10"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="16"/>
-      <c r="Y42" s="16"/>
-      <c r="Z42" s="16"/>
-      <c r="AA42" s="16"/>
-    </row>
-    <row r="43" spans="1:27" s="28" customFormat="1">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+    </row>
+    <row r="43" spans="1:27" s="37" customFormat="1">
       <c r="A43" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>307</v>
+        <v>407</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -2978,7 +3350,7 @@
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
       <c r="M43" s="27" t="s">
-        <v>308</v>
+        <v>408</v>
       </c>
       <c r="N43" s="16"/>
       <c r="O43" s="16"/>
@@ -2995,12 +3367,12 @@
       <c r="Z43" s="16"/>
       <c r="AA43" s="16"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" s="28" customFormat="1">
       <c r="A44" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -3013,7 +3385,7 @@
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="27" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="N44" s="16"/>
       <c r="O44" s="16"/>
@@ -3035,7 +3407,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
@@ -3048,7 +3420,7 @@
       <c r="K45" s="16"/>
       <c r="L45" s="16"/>
       <c r="M45" s="27" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="N45" s="16"/>
       <c r="O45" s="16"/>
@@ -3065,12 +3437,12 @@
       <c r="Z45" s="16"/>
       <c r="AA45" s="16"/>
     </row>
-    <row r="46" spans="1:27" s="28" customFormat="1">
+    <row r="46" spans="1:27">
       <c r="A46" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
@@ -3083,7 +3455,7 @@
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="27" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="N46" s="16"/>
       <c r="O46" s="16"/>
@@ -3100,117 +3472,117 @@
       <c r="Z46" s="16"/>
       <c r="AA46" s="16"/>
     </row>
-    <row r="47" spans="1:27">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:27" s="28" customFormat="1">
+      <c r="A47" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="B47" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
       <c r="E47" s="16"/>
-      <c r="F47" s="2"/>
+      <c r="F47" s="16"/>
       <c r="G47" s="10"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2"/>
-    </row>
-    <row r="48" spans="1:27">
-      <c r="A48" s="2" t="s">
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+    </row>
+    <row r="48" spans="1:27" s="42" customFormat="1">
+      <c r="A48" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="16"/>
-      <c r="F48" s="2"/>
+      <c r="F48" s="16"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="2"/>
-      <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="2"/>
-      <c r="AA48" s="2"/>
-    </row>
-    <row r="49" spans="1:27">
-      <c r="A49" s="2" t="s">
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+    </row>
+    <row r="49" spans="1:27" s="28" customFormat="1">
+      <c r="A49" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="B49" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="16"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
     </row>
     <row r="50" spans="1:27">
       <c r="A50" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -3222,8 +3594,8 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
-      <c r="M50" s="2" t="s">
-        <v>88</v>
+      <c r="M50" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -3241,23 +3613,25 @@
       <c r="AA50" s="2"/>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>89</v>
+      <c r="A51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="16"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="G51" s="10"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
-      <c r="M51" s="10"/>
+      <c r="M51" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -3274,11 +3648,11 @@
       <c r="AA51" s="2"/>
     </row>
     <row r="52" spans="1:27">
-      <c r="A52" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>90</v>
+      <c r="A52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -3290,7 +3664,9 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
-      <c r="M52" s="10"/>
+      <c r="M52" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -3307,27 +3683,25 @@
       <c r="AA52" s="2"/>
     </row>
     <row r="53" spans="1:27">
-      <c r="A53" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E53" s="12"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
+      <c r="A53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
+      <c r="M53" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -3344,27 +3718,23 @@
       <c r="AA53" s="2"/>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>98</v>
-      </c>
+      <c r="A54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="16"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" s="10"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
@@ -3381,23 +3751,23 @@
       <c r="AA54" s="2"/>
     </row>
     <row r="55" spans="1:27">
-      <c r="A55" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
+      <c r="A55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
       <c r="E55" s="16"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" s="10"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
@@ -3414,24 +3784,22 @@
       <c r="AA55" s="2"/>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="A56" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="12"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -3453,22 +3821,22 @@
       <c r="AA56" s="2"/>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>106</v>
+      <c r="B57" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E57" s="16"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -3490,22 +3858,18 @@
       <c r="AA57" s="2"/>
     </row>
     <row r="58" spans="1:27">
-      <c r="A58" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>109</v>
-      </c>
+      <c r="A58" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
       <c r="E58" s="16"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -3528,21 +3892,23 @@
     </row>
     <row r="59" spans="1:27">
       <c r="A59" s="2" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>112</v>
+        <v>101</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -3568,13 +3934,13 @@
         <v>95</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E60" s="16"/>
       <c r="F60" s="2"/>
@@ -3602,13 +3968,17 @@
     </row>
     <row r="61" spans="1:27">
       <c r="A61" s="2" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>109</v>
+      </c>
       <c r="E61" s="16"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -3634,164 +4004,158 @@
       <c r="AA61" s="2"/>
     </row>
     <row r="62" spans="1:27">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
+      <c r="AA62" s="2"/>
+    </row>
+    <row r="63" spans="1:27">
+      <c r="A63" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
+      <c r="Z63" s="2"/>
+      <c r="AA63" s="2"/>
+    </row>
+    <row r="64" spans="1:27">
+      <c r="A64" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
+      <c r="AA64" s="2"/>
+    </row>
+    <row r="65" spans="1:27">
+      <c r="A65" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B65" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:27">
-      <c r="A63" s="16" t="s">
+    <row r="66" spans="1:27">
+      <c r="A66" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B66" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C66" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:27">
-      <c r="A64" s="16" t="s">
+    <row r="67" spans="1:27">
+      <c r="A67" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B67" s="16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:27" s="28" customFormat="1" ht="39">
-      <c r="A65" s="30" t="s">
+    <row r="68" spans="1:27" s="28" customFormat="1">
+      <c r="A68" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="30" t="s">
+      <c r="B68" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="D68" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="D65" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="30" t="s">
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="I65" s="30"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
-      <c r="L65" s="30"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="30"/>
-      <c r="O65" s="30"/>
-      <c r="P65" s="30"/>
-      <c r="Q65" s="30"/>
-      <c r="R65" s="30"/>
-      <c r="S65" s="30"/>
-      <c r="T65" s="30"/>
-      <c r="U65" s="30"/>
-      <c r="V65" s="30"/>
-      <c r="W65" s="30"/>
-      <c r="X65" s="30"/>
-      <c r="Y65" s="30"/>
-      <c r="Z65" s="30"/>
-      <c r="AA65" s="30"/>
-    </row>
-    <row r="66" spans="1:27" s="28" customFormat="1">
-      <c r="A66" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B66" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="C66" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="E66" s="32"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
-      <c r="J66" s="30"/>
-      <c r="K66" s="30"/>
-      <c r="L66" s="30"/>
-      <c r="M66" s="30"/>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
-      <c r="P66" s="30"/>
-      <c r="Q66" s="30"/>
-      <c r="R66" s="30"/>
-      <c r="S66" s="30"/>
-      <c r="T66" s="30"/>
-      <c r="U66" s="30"/>
-      <c r="V66" s="30"/>
-      <c r="W66" s="30"/>
-      <c r="X66" s="30"/>
-      <c r="Y66" s="30"/>
-      <c r="Z66" s="30"/>
-      <c r="AA66" s="30"/>
-    </row>
-    <row r="67" spans="1:27" s="28" customFormat="1">
-      <c r="A67" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B67" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="C67" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
-      <c r="AA67" s="30"/>
-    </row>
-    <row r="68" spans="1:27" s="28" customFormat="1" ht="29.5">
-      <c r="A68" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="B68" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="C68" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="D68" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="E68" s="33"/>
-      <c r="F68" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
       <c r="I68" s="30"/>
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
@@ -3812,23 +4176,21 @@
       <c r="Z68" s="30"/>
       <c r="AA68" s="30"/>
     </row>
-    <row r="69" spans="1:27" s="28" customFormat="1" ht="44.25">
+    <row r="69" spans="1:27" s="28" customFormat="1">
       <c r="A69" s="30" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="C69" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="E69" s="33"/>
-      <c r="F69" s="30" t="s">
-        <v>221</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="E69" s="32"/>
+      <c r="F69" s="30"/>
       <c r="G69" s="30"/>
       <c r="H69" s="30"/>
       <c r="I69" s="30"/>
@@ -3851,25 +4213,23 @@
       <c r="Z69" s="30"/>
       <c r="AA69" s="30"/>
     </row>
-    <row r="70" spans="1:27" s="28" customFormat="1" ht="39">
+    <row r="70" spans="1:27" s="28" customFormat="1">
       <c r="A70" s="30" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>227</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D70" s="30"/>
       <c r="E70" s="30"/>
-      <c r="F70" s="30" t="s">
-        <v>221</v>
-      </c>
+      <c r="F70" s="30"/>
       <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
+      <c r="H70" s="30" t="s">
+        <v>215</v>
+      </c>
       <c r="I70" s="30"/>
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
@@ -3890,22 +4250,22 @@
       <c r="Z70" s="30"/>
       <c r="AA70" s="30"/>
     </row>
-    <row r="71" spans="1:27" s="28" customFormat="1" ht="29.5">
+    <row r="71" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A71" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="B71" s="30" t="s">
-        <v>228</v>
-      </c>
       <c r="C71" s="33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E71" s="33"/>
       <c r="F71" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G71" s="30"/>
       <c r="H71" s="30"/>
@@ -3929,17 +4289,23 @@
       <c r="Z71" s="30"/>
       <c r="AA71" s="30"/>
     </row>
-    <row r="72" spans="1:27" s="28" customFormat="1">
+    <row r="72" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A72" s="30" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="C72" s="34"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
+        <v>221</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" s="33"/>
+      <c r="F72" s="30" t="s">
+        <v>220</v>
+      </c>
       <c r="G72" s="30"/>
       <c r="H72" s="30"/>
       <c r="I72" s="30"/>
@@ -3964,19 +4330,21 @@
     </row>
     <row r="73" spans="1:27" s="28" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="D73" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="E73" s="32"/>
-      <c r="F73" s="30"/>
+        <v>224</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30" t="s">
+        <v>220</v>
+      </c>
       <c r="G73" s="30"/>
       <c r="H73" s="30"/>
       <c r="I73" s="30"/>
@@ -3999,21 +4367,23 @@
       <c r="Z73" s="30"/>
       <c r="AA73" s="30"/>
     </row>
-    <row r="74" spans="1:27" s="28" customFormat="1">
+    <row r="74" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A74" s="30" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="C74" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D74" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E74" s="32"/>
-      <c r="F74" s="30"/>
+        <v>227</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" s="33"/>
+      <c r="F74" s="30" t="s">
+        <v>220</v>
+      </c>
       <c r="G74" s="30"/>
       <c r="H74" s="30"/>
       <c r="I74" s="30"/>
@@ -4036,23 +4406,19 @@
       <c r="Z74" s="30"/>
       <c r="AA74" s="30"/>
     </row>
-    <row r="75" spans="1:27" s="28" customFormat="1" ht="14.75">
+    <row r="75" spans="1:27" s="28" customFormat="1">
       <c r="A75" s="30" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="C75" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
+        <v>214</v>
+      </c>
+      <c r="C75" s="34"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
       <c r="F75" s="30"/>
       <c r="G75" s="30"/>
-      <c r="H75" s="30" t="s">
-        <v>216</v>
-      </c>
+      <c r="H75" s="30"/>
       <c r="I75" s="30"/>
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
@@ -4073,23 +4439,21 @@
       <c r="Z75" s="30"/>
       <c r="AA75" s="30"/>
     </row>
-    <row r="76" spans="1:27" s="28" customFormat="1" ht="29.5">
+    <row r="76" spans="1:27" s="28" customFormat="1">
       <c r="A76" s="30" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="C76" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="D76" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="30" t="s">
-        <v>221</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C76" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E76" s="32"/>
+      <c r="F76" s="30"/>
       <c r="G76" s="30"/>
       <c r="H76" s="30"/>
       <c r="I76" s="30"/>
@@ -4112,23 +4476,21 @@
       <c r="Z76" s="30"/>
       <c r="AA76" s="30"/>
     </row>
-    <row r="77" spans="1:27" s="28" customFormat="1" ht="59">
+    <row r="77" spans="1:27" s="28" customFormat="1">
       <c r="A77" s="30" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="C77" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="D77" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="30" t="s">
-        <v>221</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="32"/>
+      <c r="F77" s="30"/>
       <c r="G77" s="30"/>
       <c r="H77" s="30"/>
       <c r="I77" s="30"/>
@@ -4151,25 +4513,23 @@
       <c r="Z77" s="30"/>
       <c r="AA77" s="30"/>
     </row>
-    <row r="78" spans="1:27" s="28" customFormat="1" ht="26.75">
+    <row r="78" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A78" s="30" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="D78" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30" t="s">
-        <v>221</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="30"/>
       <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
+      <c r="H78" s="30" t="s">
+        <v>215</v>
+      </c>
       <c r="I78" s="30"/>
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
@@ -4192,15 +4552,21 @@
     </row>
     <row r="79" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A79" s="30" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="C79" s="33"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
+      <c r="C79" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E79" s="33"/>
+      <c r="F79" s="30" t="s">
+        <v>220</v>
+      </c>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
       <c r="I79" s="30"/>
@@ -4223,26 +4589,30 @@
       <c r="Z79" s="30"/>
       <c r="AA79" s="30"/>
     </row>
-    <row r="80" spans="1:27" s="28" customFormat="1" ht="15.5" customHeight="1">
+    <row r="80" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A80" s="30" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
+        <v>240</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E80" s="33"/>
+      <c r="F80" s="30" t="s">
+        <v>220</v>
+      </c>
       <c r="G80" s="30"/>
       <c r="H80" s="30"/>
       <c r="I80" s="30"/>
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
       <c r="L80" s="30"/>
-      <c r="M80" s="31" t="s">
-        <v>248</v>
-      </c>
+      <c r="M80" s="30"/>
       <c r="N80" s="30"/>
       <c r="O80" s="30"/>
       <c r="P80" s="30"/>
@@ -4258,26 +4628,24 @@
       <c r="Z80" s="30"/>
       <c r="AA80" s="30"/>
     </row>
-    <row r="81" spans="1:27" s="28" customFormat="1" ht="13.75" customHeight="1">
+    <row r="81" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A81" s="30" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="E81" s="33"/>
+        <v>244</v>
+      </c>
+      <c r="D81" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E81" s="30"/>
       <c r="F81" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="G81" s="30" t="s">
-        <v>252</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G81" s="30"/>
       <c r="H81" s="30"/>
       <c r="I81" s="30"/>
       <c r="J81" s="30"/>
@@ -4299,24 +4667,18 @@
       <c r="Z81" s="30"/>
       <c r="AA81" s="30"/>
     </row>
-    <row r="82" spans="1:27" s="28" customFormat="1" ht="24.5" customHeight="1">
+    <row r="82" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A82" s="30" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="D82" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E82" s="32"/>
+        <v>236</v>
+      </c>
+      <c r="C82" s="33"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
       <c r="F82" s="30"/>
-      <c r="G82" s="30" t="s">
-        <v>256</v>
-      </c>
+      <c r="G82" s="30"/>
       <c r="H82" s="30"/>
       <c r="I82" s="30"/>
       <c r="J82" s="30"/>
@@ -4338,24 +4700,26 @@
       <c r="Z82" s="30"/>
       <c r="AA82" s="30"/>
     </row>
-    <row r="83" spans="1:27" s="28" customFormat="1">
+    <row r="83" spans="1:27" s="28" customFormat="1" ht="15.5" customHeight="1">
       <c r="A83" s="30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="C83" s="30"/>
       <c r="D83" s="30"/>
       <c r="E83" s="30"/>
       <c r="F83" s="30"/>
-      <c r="G83" s="34"/>
+      <c r="G83" s="30"/>
       <c r="H83" s="30"/>
       <c r="I83" s="30"/>
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
       <c r="L83" s="30"/>
-      <c r="M83" s="30"/>
+      <c r="M83" s="31" t="s">
+        <v>247</v>
+      </c>
       <c r="N83" s="30"/>
       <c r="O83" s="30"/>
       <c r="P83" s="30"/>
@@ -4371,784 +4735,1682 @@
       <c r="Z83" s="30"/>
       <c r="AA83" s="30"/>
     </row>
-    <row r="84" spans="1:27">
-      <c r="A84" s="16" t="s">
+    <row r="84" spans="1:27" s="28" customFormat="1" ht="13.75" customHeight="1">
+      <c r="A84" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84" s="33"/>
+      <c r="F84" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G84" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="H84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="30"/>
+      <c r="L84" s="30"/>
+      <c r="M84" s="30"/>
+      <c r="N84" s="30"/>
+      <c r="O84" s="30"/>
+      <c r="P84" s="30"/>
+      <c r="Q84" s="30"/>
+      <c r="R84" s="30"/>
+      <c r="S84" s="30"/>
+      <c r="T84" s="30"/>
+      <c r="U84" s="30"/>
+      <c r="V84" s="30"/>
+      <c r="W84" s="30"/>
+      <c r="X84" s="30"/>
+      <c r="Y84" s="30"/>
+      <c r="Z84" s="30"/>
+      <c r="AA84" s="30"/>
+    </row>
+    <row r="85" spans="1:27" s="28" customFormat="1" ht="24.5" customHeight="1">
+      <c r="A85" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E85" s="32"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="30"/>
+      <c r="M85" s="30"/>
+      <c r="N85" s="30"/>
+      <c r="O85" s="30"/>
+      <c r="P85" s="30"/>
+      <c r="Q85" s="30"/>
+      <c r="R85" s="30"/>
+      <c r="S85" s="30"/>
+      <c r="T85" s="30"/>
+      <c r="U85" s="30"/>
+      <c r="V85" s="30"/>
+      <c r="W85" s="30"/>
+      <c r="X85" s="30"/>
+      <c r="Y85" s="30"/>
+      <c r="Z85" s="30"/>
+      <c r="AA85" s="30"/>
+    </row>
+    <row r="86" spans="1:27" s="28" customFormat="1">
+      <c r="A86" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B86" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
+      <c r="M86" s="30"/>
+      <c r="N86" s="30"/>
+      <c r="O86" s="30"/>
+      <c r="P86" s="30"/>
+      <c r="Q86" s="30"/>
+      <c r="R86" s="30"/>
+      <c r="S86" s="30"/>
+      <c r="T86" s="30"/>
+      <c r="U86" s="30"/>
+      <c r="V86" s="30"/>
+      <c r="W86" s="30"/>
+      <c r="X86" s="30"/>
+      <c r="Y86" s="30"/>
+      <c r="Z86" s="30"/>
+      <c r="AA86" s="30"/>
+    </row>
+    <row r="87" spans="1:27" s="37" customFormat="1" ht="78">
+      <c r="A87" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D87" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E87" s="30"/>
+      <c r="G87" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="30"/>
+      <c r="K87" s="30"/>
+      <c r="L87" s="30"/>
+      <c r="M87" s="30"/>
+      <c r="N87" s="30"/>
+      <c r="O87" s="30"/>
+      <c r="P87" s="30"/>
+      <c r="Q87" s="30"/>
+      <c r="R87" s="30"/>
+      <c r="S87" s="30"/>
+      <c r="T87" s="30"/>
+      <c r="U87" s="30"/>
+      <c r="V87" s="30"/>
+      <c r="W87" s="30"/>
+      <c r="X87" s="30"/>
+      <c r="Y87" s="30"/>
+      <c r="Z87" s="30"/>
+      <c r="AA87" s="30"/>
+    </row>
+    <row r="88" spans="1:27" s="37" customFormat="1">
+      <c r="A88" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="34"/>
+      <c r="H88" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I88" s="30"/>
+      <c r="J88" s="30"/>
+      <c r="K88" s="30"/>
+      <c r="L88" s="30"/>
+      <c r="M88" s="30"/>
+      <c r="N88" s="30"/>
+      <c r="O88" s="30"/>
+      <c r="P88" s="30"/>
+      <c r="Q88" s="30"/>
+      <c r="R88" s="30"/>
+      <c r="S88" s="30"/>
+      <c r="T88" s="30"/>
+      <c r="U88" s="30"/>
+      <c r="V88" s="30"/>
+      <c r="W88" s="30"/>
+      <c r="X88" s="30"/>
+      <c r="Y88" s="30"/>
+      <c r="Z88" s="30"/>
+      <c r="AA88" s="30"/>
+    </row>
+    <row r="89" spans="1:27" s="37" customFormat="1" ht="34.25" customHeight="1">
+      <c r="A89" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="B89" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D89" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G89" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="H89" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="J89" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="K89" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="L89" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="M89" s="30"/>
+      <c r="N89" s="30"/>
+      <c r="O89" s="30"/>
+      <c r="P89" s="30"/>
+      <c r="Q89" s="30"/>
+      <c r="R89" s="30"/>
+      <c r="S89" s="30"/>
+      <c r="T89" s="30"/>
+      <c r="U89" s="30"/>
+      <c r="V89" s="30"/>
+      <c r="W89" s="30"/>
+      <c r="X89" s="30"/>
+      <c r="Y89" s="30"/>
+      <c r="Z89" s="30"/>
+      <c r="AA89" s="30"/>
+    </row>
+    <row r="90" spans="1:27" s="37" customFormat="1" ht="38" customHeight="1">
+      <c r="A90" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="C90" s="31"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
+      <c r="K90" s="30"/>
+      <c r="M90" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="N90" s="30"/>
+      <c r="O90" s="30"/>
+      <c r="P90" s="30"/>
+      <c r="Q90" s="30"/>
+      <c r="R90" s="30"/>
+      <c r="S90" s="30"/>
+      <c r="T90" s="30"/>
+      <c r="U90" s="30"/>
+      <c r="V90" s="30"/>
+      <c r="W90" s="30"/>
+      <c r="X90" s="30"/>
+      <c r="Y90" s="30"/>
+      <c r="Z90" s="30"/>
+      <c r="AA90" s="30"/>
+    </row>
+    <row r="91" spans="1:27" s="37" customFormat="1" ht="36.75" customHeight="1">
+      <c r="A91" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="E91" s="30"/>
+      <c r="G91" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="H91" s="30"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="30"/>
+      <c r="K91" s="30"/>
+      <c r="L91" s="30"/>
+      <c r="M91" s="30"/>
+      <c r="N91" s="30"/>
+      <c r="O91" s="30"/>
+      <c r="P91" s="30"/>
+      <c r="Q91" s="30"/>
+      <c r="R91" s="30"/>
+      <c r="S91" s="30"/>
+      <c r="T91" s="30"/>
+      <c r="U91" s="30"/>
+      <c r="V91" s="30"/>
+      <c r="W91" s="30"/>
+      <c r="X91" s="30"/>
+      <c r="Y91" s="30"/>
+      <c r="Z91" s="30"/>
+      <c r="AA91" s="30"/>
+    </row>
+    <row r="92" spans="1:27" s="37" customFormat="1">
+      <c r="A92" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="34"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="30"/>
+      <c r="K92" s="30"/>
+      <c r="L92" s="30"/>
+      <c r="M92" s="30"/>
+      <c r="N92" s="30"/>
+      <c r="O92" s="30"/>
+      <c r="P92" s="30"/>
+      <c r="Q92" s="30"/>
+      <c r="R92" s="30"/>
+      <c r="S92" s="30"/>
+      <c r="T92" s="30"/>
+      <c r="U92" s="30"/>
+      <c r="V92" s="30"/>
+      <c r="W92" s="30"/>
+      <c r="X92" s="30"/>
+      <c r="Y92" s="30"/>
+      <c r="Z92" s="30"/>
+      <c r="AA92" s="30"/>
+    </row>
+    <row r="93" spans="1:27" s="37" customFormat="1" ht="39">
+      <c r="A93" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C93" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="G93" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="H93" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I93" s="30"/>
+      <c r="J93" s="30"/>
+      <c r="K93" s="30"/>
+      <c r="L93" s="30"/>
+      <c r="M93" s="30"/>
+      <c r="N93" s="30"/>
+      <c r="O93" s="30"/>
+      <c r="P93" s="30"/>
+      <c r="Q93" s="30"/>
+      <c r="R93" s="30"/>
+      <c r="S93" s="30"/>
+      <c r="T93" s="30"/>
+      <c r="U93" s="30"/>
+      <c r="V93" s="30"/>
+      <c r="W93" s="30"/>
+      <c r="X93" s="30"/>
+      <c r="Y93" s="30"/>
+      <c r="Z93" s="30"/>
+      <c r="AA93" s="30"/>
+    </row>
+    <row r="94" spans="1:27" s="37" customFormat="1" ht="26">
+      <c r="A94" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="D94" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="H94" s="30"/>
+      <c r="I94" s="30"/>
+      <c r="J94" s="30"/>
+      <c r="K94" s="30"/>
+      <c r="L94" s="30"/>
+      <c r="M94" s="30"/>
+      <c r="N94" s="30"/>
+      <c r="O94" s="30"/>
+      <c r="P94" s="30"/>
+      <c r="Q94" s="30"/>
+      <c r="R94" s="30"/>
+      <c r="S94" s="30"/>
+      <c r="T94" s="30"/>
+      <c r="U94" s="30"/>
+      <c r="V94" s="30"/>
+      <c r="W94" s="30"/>
+      <c r="X94" s="30"/>
+      <c r="Y94" s="30"/>
+      <c r="Z94" s="30"/>
+      <c r="AA94" s="30"/>
+    </row>
+    <row r="95" spans="1:27" s="37" customFormat="1" ht="39">
+      <c r="A95" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="E95" s="30"/>
+      <c r="G95" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+      <c r="J95" s="30"/>
+      <c r="K95" s="30"/>
+      <c r="L95" s="30"/>
+      <c r="M95" s="30"/>
+      <c r="N95" s="30"/>
+      <c r="O95" s="30"/>
+      <c r="P95" s="30"/>
+      <c r="Q95" s="30"/>
+      <c r="R95" s="30"/>
+      <c r="S95" s="30"/>
+      <c r="T95" s="30"/>
+      <c r="U95" s="30"/>
+      <c r="V95" s="30"/>
+      <c r="W95" s="30"/>
+      <c r="X95" s="30"/>
+      <c r="Y95" s="30"/>
+      <c r="Z95" s="30"/>
+      <c r="AA95" s="30"/>
+    </row>
+    <row r="96" spans="1:27" s="37" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A96" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="C96" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="D96" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G96" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+      <c r="J96" s="30"/>
+      <c r="K96" s="30"/>
+      <c r="L96" s="30"/>
+      <c r="M96" s="30"/>
+      <c r="N96" s="30"/>
+      <c r="O96" s="30"/>
+      <c r="P96" s="30"/>
+      <c r="Q96" s="30"/>
+      <c r="R96" s="30"/>
+      <c r="S96" s="30"/>
+      <c r="T96" s="30"/>
+      <c r="U96" s="30"/>
+      <c r="V96" s="30"/>
+      <c r="W96" s="30"/>
+      <c r="X96" s="30"/>
+      <c r="Y96" s="30"/>
+      <c r="Z96" s="30"/>
+      <c r="AA96" s="30"/>
+    </row>
+    <row r="97" spans="1:27" s="37" customFormat="1" ht="23" customHeight="1">
+      <c r="A97" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
+      <c r="I97" s="30"/>
+      <c r="J97" s="30"/>
+      <c r="K97" s="30"/>
+      <c r="M97" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="N97" s="30"/>
+      <c r="O97" s="30"/>
+      <c r="P97" s="30"/>
+      <c r="Q97" s="30"/>
+      <c r="R97" s="30"/>
+      <c r="S97" s="30"/>
+      <c r="T97" s="30"/>
+      <c r="U97" s="30"/>
+      <c r="V97" s="30"/>
+      <c r="W97" s="30"/>
+      <c r="X97" s="30"/>
+      <c r="Y97" s="30"/>
+      <c r="Z97" s="30"/>
+      <c r="AA97" s="30"/>
+    </row>
+    <row r="98" spans="1:27" s="37" customFormat="1" ht="26">
+      <c r="A98" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B98" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="C98" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="D98" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="E98" s="30"/>
+      <c r="G98" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+      <c r="J98" s="30"/>
+      <c r="K98" s="30"/>
+      <c r="L98" s="30"/>
+      <c r="M98" s="30"/>
+      <c r="N98" s="30"/>
+      <c r="O98" s="30"/>
+      <c r="P98" s="30"/>
+      <c r="Q98" s="30"/>
+      <c r="R98" s="30"/>
+      <c r="S98" s="30"/>
+      <c r="T98" s="30"/>
+      <c r="U98" s="30"/>
+      <c r="V98" s="30"/>
+      <c r="W98" s="30"/>
+      <c r="X98" s="30"/>
+      <c r="Y98" s="30"/>
+      <c r="Z98" s="30"/>
+      <c r="AA98" s="30"/>
+    </row>
+    <row r="99" spans="1:27" s="37" customFormat="1">
+      <c r="A99" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="D99" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="E99" s="30"/>
+      <c r="G99" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="30"/>
+      <c r="K99" s="30"/>
+      <c r="L99" s="30"/>
+      <c r="M99" s="30"/>
+      <c r="N99" s="30"/>
+      <c r="O99" s="30"/>
+      <c r="P99" s="30"/>
+      <c r="Q99" s="30"/>
+      <c r="R99" s="30"/>
+      <c r="S99" s="30"/>
+      <c r="T99" s="30"/>
+      <c r="U99" s="30"/>
+      <c r="V99" s="30"/>
+      <c r="W99" s="30"/>
+      <c r="X99" s="30"/>
+      <c r="Y99" s="30"/>
+      <c r="Z99" s="30"/>
+      <c r="AA99" s="30"/>
+    </row>
+    <row r="100" spans="1:27" s="37" customFormat="1">
+      <c r="A100" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B100" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="30"/>
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
+      <c r="M100" s="30"/>
+      <c r="N100" s="30"/>
+      <c r="O100" s="30"/>
+      <c r="P100" s="30"/>
+      <c r="Q100" s="30"/>
+      <c r="R100" s="30"/>
+      <c r="S100" s="30"/>
+      <c r="T100" s="30"/>
+      <c r="U100" s="30"/>
+      <c r="V100" s="30"/>
+      <c r="W100" s="30"/>
+      <c r="X100" s="30"/>
+      <c r="Y100" s="30"/>
+      <c r="Z100" s="30"/>
+      <c r="AA100" s="30"/>
+    </row>
+    <row r="101" spans="1:27" s="37" customFormat="1">
+      <c r="A101" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="30"/>
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
+      <c r="M101" s="30"/>
+      <c r="N101" s="30"/>
+      <c r="O101" s="30"/>
+      <c r="P101" s="30"/>
+      <c r="Q101" s="30"/>
+      <c r="R101" s="30"/>
+      <c r="S101" s="30"/>
+      <c r="T101" s="30"/>
+      <c r="U101" s="30"/>
+      <c r="V101" s="30"/>
+      <c r="W101" s="30"/>
+      <c r="X101" s="30"/>
+      <c r="Y101" s="30"/>
+      <c r="Z101" s="30"/>
+      <c r="AA101" s="30"/>
+    </row>
+    <row r="102" spans="1:27">
+      <c r="A102" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B102" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="16" t="s">
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="H102" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="28"/>
-      <c r="L84" s="28"/>
-      <c r="M84" s="28"/>
-      <c r="N84" s="28"/>
-      <c r="O84" s="28"/>
-      <c r="P84" s="28"/>
-      <c r="Q84" s="28"/>
-      <c r="R84" s="28"/>
-      <c r="S84" s="28"/>
-      <c r="T84" s="28"/>
-      <c r="U84" s="28"/>
-      <c r="V84" s="28"/>
-      <c r="W84" s="28"/>
-      <c r="X84" s="28"/>
-      <c r="Y84" s="28"/>
-      <c r="Z84" s="28"/>
-      <c r="AA84" s="28"/>
-    </row>
-    <row r="85" spans="1:27" ht="14.75">
-      <c r="A85" s="16" t="s">
+      <c r="I102" s="28"/>
+      <c r="J102" s="28"/>
+      <c r="K102" s="28"/>
+      <c r="L102" s="28"/>
+      <c r="M102" s="28"/>
+      <c r="N102" s="28"/>
+      <c r="O102" s="28"/>
+      <c r="P102" s="28"/>
+      <c r="Q102" s="28"/>
+      <c r="R102" s="28"/>
+      <c r="S102" s="28"/>
+      <c r="T102" s="28"/>
+      <c r="U102" s="28"/>
+      <c r="V102" s="28"/>
+      <c r="W102" s="28"/>
+      <c r="X102" s="28"/>
+      <c r="Y102" s="28"/>
+      <c r="Z102" s="28"/>
+      <c r="AA102" s="28"/>
+    </row>
+    <row r="103" spans="1:27" ht="14.75">
+      <c r="A103" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B103" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C103" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D85" s="28"/>
-      <c r="F85" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="G85" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="H85" s="28"/>
-      <c r="I85" s="28"/>
-      <c r="J85" s="28"/>
-      <c r="K85" s="28"/>
-      <c r="L85" s="28"/>
-      <c r="M85" s="28"/>
-      <c r="N85" s="26" t="s">
+      <c r="D103" s="28"/>
+      <c r="F103" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="G103" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+      <c r="J103" s="28"/>
+      <c r="K103" s="28"/>
+      <c r="L103" s="28"/>
+      <c r="M103" s="28"/>
+      <c r="N103" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="O85" s="28"/>
-      <c r="P85" s="28"/>
-      <c r="Q85" s="28"/>
-      <c r="R85" s="28"/>
-      <c r="S85" s="28"/>
-      <c r="T85" s="28"/>
-      <c r="U85" s="28"/>
-      <c r="V85" s="28"/>
-      <c r="W85" s="28"/>
-      <c r="X85" s="28"/>
-      <c r="Y85" s="28"/>
-      <c r="Z85" s="28"/>
-      <c r="AA85" s="28"/>
-    </row>
-    <row r="86" spans="1:27">
-      <c r="A86" s="16" t="s">
+      <c r="O103" s="28"/>
+      <c r="P103" s="28"/>
+      <c r="Q103" s="28"/>
+      <c r="R103" s="28"/>
+      <c r="S103" s="28"/>
+      <c r="T103" s="28"/>
+      <c r="U103" s="28"/>
+      <c r="V103" s="28"/>
+      <c r="W103" s="28"/>
+      <c r="X103" s="28"/>
+      <c r="Y103" s="28"/>
+      <c r="Z103" s="28"/>
+      <c r="AA103" s="28"/>
+    </row>
+    <row r="104" spans="1:27">
+      <c r="A104" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B104" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="28"/>
-      <c r="D86" s="28"/>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="28"/>
-      <c r="J86" s="28"/>
-      <c r="K86" s="28"/>
-      <c r="L86" s="28"/>
-      <c r="M86" s="28"/>
-      <c r="N86" s="28"/>
-      <c r="O86" s="28"/>
-      <c r="P86" s="28"/>
-      <c r="Q86" s="28"/>
-      <c r="R86" s="28"/>
-      <c r="S86" s="28"/>
-      <c r="T86" s="28"/>
-      <c r="U86" s="28"/>
-      <c r="V86" s="28"/>
-      <c r="W86" s="28"/>
-      <c r="X86" s="28"/>
-      <c r="Y86" s="28"/>
-      <c r="Z86" s="28"/>
-      <c r="AA86" s="28"/>
-    </row>
-    <row r="87" spans="1:27">
-      <c r="A87" s="16" t="s">
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="28"/>
+      <c r="J104" s="28"/>
+      <c r="K104" s="28"/>
+      <c r="L104" s="28"/>
+      <c r="M104" s="28"/>
+      <c r="N104" s="28"/>
+      <c r="O104" s="28"/>
+      <c r="P104" s="28"/>
+      <c r="Q104" s="28"/>
+      <c r="R104" s="28"/>
+      <c r="S104" s="28"/>
+      <c r="T104" s="28"/>
+      <c r="U104" s="28"/>
+      <c r="V104" s="28"/>
+      <c r="W104" s="28"/>
+      <c r="X104" s="28"/>
+      <c r="Y104" s="28"/>
+      <c r="Z104" s="28"/>
+      <c r="AA104" s="28"/>
+    </row>
+    <row r="105" spans="1:27">
+      <c r="A105" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B105" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C87" s="28"/>
-      <c r="D87" s="28"/>
-      <c r="F87" s="28"/>
-      <c r="G87" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="H87" s="16" t="s">
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="H105" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="I87" s="28"/>
-      <c r="J87" s="28"/>
-      <c r="K87" s="28"/>
-      <c r="L87" s="28"/>
-      <c r="M87" s="28"/>
-      <c r="N87" s="28"/>
-      <c r="O87" s="28"/>
-      <c r="P87" s="28"/>
-      <c r="Q87" s="28"/>
-      <c r="R87" s="28"/>
-      <c r="S87" s="28"/>
-      <c r="T87" s="28"/>
-      <c r="U87" s="28"/>
-      <c r="V87" s="28"/>
-      <c r="W87" s="28"/>
-      <c r="X87" s="28"/>
-      <c r="Y87" s="28"/>
-      <c r="Z87" s="28"/>
-      <c r="AA87" s="28"/>
-    </row>
-    <row r="88" spans="1:27" ht="14.75">
-      <c r="A88" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="H88" s="28"/>
-      <c r="I88" s="28"/>
-      <c r="J88" s="28"/>
-      <c r="K88" s="28"/>
-      <c r="L88" s="28"/>
-      <c r="M88" s="28"/>
-      <c r="N88" s="28"/>
-      <c r="O88" s="28"/>
-      <c r="P88" s="28"/>
-      <c r="Q88" s="28"/>
-      <c r="R88" s="28"/>
-      <c r="S88" s="28"/>
-      <c r="T88" s="28"/>
-      <c r="U88" s="28"/>
-      <c r="V88" s="28"/>
-      <c r="W88" s="28"/>
-      <c r="X88" s="28"/>
-      <c r="Y88" s="28"/>
-      <c r="Z88" s="28"/>
-      <c r="AA88" s="28"/>
-    </row>
-    <row r="89" spans="1:27">
-      <c r="A89" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89" s="28"/>
-      <c r="F89" s="28"/>
-      <c r="G89" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="H89" s="28"/>
-      <c r="I89" s="28"/>
-      <c r="J89" s="28"/>
-      <c r="K89" s="28"/>
-      <c r="L89" s="28"/>
-      <c r="M89" s="28"/>
-      <c r="N89" s="28"/>
-      <c r="O89" s="28"/>
-      <c r="P89" s="28"/>
-      <c r="Q89" s="28"/>
-      <c r="R89" s="28"/>
-      <c r="S89" s="28"/>
-      <c r="T89" s="28"/>
-      <c r="U89" s="28"/>
-      <c r="V89" s="28"/>
-      <c r="W89" s="28"/>
-      <c r="X89" s="28"/>
-      <c r="Y89" s="28"/>
-      <c r="Z89" s="28"/>
-      <c r="AA89" s="28"/>
-    </row>
-    <row r="90" spans="1:27">
-      <c r="A90" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="G90" s="36" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27">
-      <c r="A91" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B91" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="G91" s="36" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27">
-      <c r="A92" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G92" s="36" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="93" spans="1:27">
-      <c r="A93" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B93" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G93" s="36" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27">
-      <c r="A94" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C94" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="G94" s="36" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27">
-      <c r="A95" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B95" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G95" s="36" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27">
-      <c r="A96" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B96" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C96" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="G96" s="36" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C97" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="G97" s="36" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B98" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="C98" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="G98" s="36" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B99" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="G99" s="36" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B100" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="G100" s="36" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="G101" s="36" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B102" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C102" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="G102" s="36" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B103" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C103" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="G103" s="36" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C104" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="G104" s="36" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B105" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C105" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="G105" s="36" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="I105" s="28"/>
+      <c r="J105" s="28"/>
+      <c r="K105" s="28"/>
+      <c r="L105" s="28"/>
+      <c r="M105" s="28"/>
+      <c r="N105" s="28"/>
+      <c r="O105" s="28"/>
+      <c r="P105" s="28"/>
+      <c r="Q105" s="28"/>
+      <c r="R105" s="28"/>
+      <c r="S105" s="28"/>
+      <c r="T105" s="28"/>
+      <c r="U105" s="28"/>
+      <c r="V105" s="28"/>
+      <c r="W105" s="28"/>
+      <c r="X105" s="28"/>
+      <c r="Y105" s="28"/>
+      <c r="Z105" s="28"/>
+      <c r="AA105" s="28"/>
+    </row>
+    <row r="106" spans="1:27" ht="14.75">
       <c r="A106" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B106" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C106" s="16" t="s">
-        <v>158</v>
-      </c>
+      <c r="B106" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D106" s="28"/>
+      <c r="F106" s="28"/>
       <c r="G106" s="36" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>273</v>
+      </c>
+      <c r="H106" s="28"/>
+      <c r="I106" s="28"/>
+      <c r="J106" s="28"/>
+      <c r="K106" s="28"/>
+      <c r="L106" s="28"/>
+      <c r="M106" s="28"/>
+      <c r="N106" s="28"/>
+      <c r="O106" s="28"/>
+      <c r="P106" s="28"/>
+      <c r="Q106" s="28"/>
+      <c r="R106" s="28"/>
+      <c r="S106" s="28"/>
+      <c r="T106" s="28"/>
+      <c r="U106" s="28"/>
+      <c r="V106" s="28"/>
+      <c r="W106" s="28"/>
+      <c r="X106" s="28"/>
+      <c r="Y106" s="28"/>
+      <c r="Z106" s="28"/>
+      <c r="AA106" s="28"/>
+    </row>
+    <row r="107" spans="1:27">
       <c r="A107" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>159</v>
+      <c r="B107" s="30" t="s">
+        <v>265</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>160</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D107" s="28"/>
+      <c r="F107" s="28"/>
       <c r="G107" s="36" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>275</v>
+      </c>
+      <c r="H107" s="28"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="28"/>
+      <c r="K107" s="28"/>
+      <c r="L107" s="28"/>
+      <c r="M107" s="28"/>
+      <c r="N107" s="28"/>
+      <c r="O107" s="28"/>
+      <c r="P107" s="28"/>
+      <c r="Q107" s="28"/>
+      <c r="R107" s="28"/>
+      <c r="S107" s="28"/>
+      <c r="T107" s="28"/>
+      <c r="U107" s="28"/>
+      <c r="V107" s="28"/>
+      <c r="W107" s="28"/>
+      <c r="X107" s="28"/>
+      <c r="Y107" s="28"/>
+      <c r="Z107" s="28"/>
+      <c r="AA107" s="28"/>
+    </row>
+    <row r="108" spans="1:27">
       <c r="A108" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B108" s="27" t="s">
-        <v>161</v>
+      <c r="B108" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="G108" s="36" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27">
       <c r="A109" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B109" s="26" t="s">
-        <v>273</v>
+      <c r="B109" s="30" t="s">
+        <v>267</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27">
       <c r="A110" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>271</v>
+        <v>131</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27">
+      <c r="A111" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B111" s="27" t="s">
-        <v>165</v>
+      <c r="B111" s="30" t="s">
+        <v>268</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27">
       <c r="A112" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="G112" s="36" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="16" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
+        <v>136</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G113" s="36" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="H114" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
+        <v>138</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G114" s="36" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B115" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="F115" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="N115" s="26" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" s="25" customFormat="1">
+        <v>95</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="G115" s="36" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B116" s="16" t="s">
-        <v>200</v>
+      <c r="B116" s="27" t="s">
+        <v>142</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E116" s="29"/>
-    </row>
-    <row r="117" spans="1:14">
+        <v>143</v>
+      </c>
+      <c r="G116" s="36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B117" s="16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" s="28" customFormat="1">
+        <v>95</v>
+      </c>
+      <c r="B117" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G117" s="36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E118" s="29"/>
-      <c r="G118" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="H118" s="28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" s="28" customFormat="1">
+        <v>145</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G118" s="36" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B119" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C119" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="E119" s="29"/>
-      <c r="F119" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="N119" s="26" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" s="28" customFormat="1">
+        <v>95</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G119" s="36" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B120" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C120" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="E120" s="29"/>
-    </row>
-    <row r="121" spans="1:14" s="28" customFormat="1">
+      <c r="B120" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G120" s="36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E121" s="29"/>
-    </row>
-    <row r="122" spans="1:14">
+        <v>151</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B122" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="G122" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="H122" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
+        <v>95</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="G122" s="36" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B123" s="16" t="s">
+      <c r="B123" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G123" s="36" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G124" s="36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G125" s="36" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G126" s="36" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G127" s="36" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G128" s="36" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="G129" s="36" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
+      <c r="A130" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G130" s="36" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="A131" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
+      <c r="A132" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="G132" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="H132" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" s="42" customFormat="1" ht="26">
+      <c r="A133" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B133" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="C133" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="G133" s="36"/>
+    </row>
+    <row r="134" spans="1:14">
+      <c r="A134" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C134" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="F134" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="N134" s="26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" s="25" customFormat="1">
+      <c r="A135" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B135" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E135" s="29"/>
+    </row>
+    <row r="136" spans="1:14">
+      <c r="A136" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" s="28" customFormat="1">
+      <c r="A137" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B137" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="E137" s="29"/>
+      <c r="G137" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="H137" s="28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" s="28" customFormat="1">
+      <c r="A138" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B138" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C138" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="E138" s="29"/>
+      <c r="F138" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="N138" s="26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" s="28" customFormat="1">
+      <c r="A139" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B139" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C139" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="E139" s="29"/>
+    </row>
+    <row r="140" spans="1:14" s="28" customFormat="1">
+      <c r="A140" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B140" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="E140" s="29"/>
+    </row>
+    <row r="141" spans="1:14">
+      <c r="A141" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B141" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="G141" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="H141" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
+      <c r="A142" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B142" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C142" t="s">
         <v>203</v>
       </c>
-      <c r="C123" t="s">
+    </row>
+    <row r="143" spans="1:14" s="37" customFormat="1">
+      <c r="A143" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B143" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E143" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" s="37" customFormat="1">
+      <c r="A144" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="M144" s="37" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27" s="37" customFormat="1">
+      <c r="A145" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B145" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="146" spans="1:27" s="37" customFormat="1">
+      <c r="A146" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B146" s="16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="147" spans="1:27" s="37" customFormat="1">
+      <c r="A147" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E147" s="26">
+        <v>2</v>
+      </c>
+      <c r="H147" s="37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="148" spans="1:27" s="37" customFormat="1">
+      <c r="A148" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B148" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="M148" s="26" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="149" spans="1:27" s="37" customFormat="1">
+      <c r="A149" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B149" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C149" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="M149" s="26"/>
+    </row>
+    <row r="150" spans="1:27" s="37" customFormat="1">
+      <c r="A150" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B150" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="151" spans="1:27" s="37" customFormat="1">
+      <c r="A151" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B151" s="16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="152" spans="1:27" s="37" customFormat="1">
+      <c r="A152" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="153" spans="1:27">
+      <c r="A153" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B153" s="16" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" s="37" customFormat="1">
-      <c r="A124" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B124" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="E124" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" s="37" customFormat="1">
-      <c r="A125" s="16" t="s">
+      <c r="C153" t="s">
+        <v>205</v>
+      </c>
+      <c r="H153" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="154" spans="1:27" s="37" customFormat="1" ht="26">
+      <c r="A154" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B154" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="C154" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="D154" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="E154" s="30"/>
+      <c r="G154" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="H154" s="30"/>
+      <c r="I154" s="30"/>
+      <c r="J154" s="30"/>
+      <c r="K154" s="30"/>
+      <c r="L154" s="30"/>
+      <c r="M154" s="30"/>
+      <c r="N154" s="30"/>
+      <c r="O154" s="30"/>
+      <c r="P154" s="30"/>
+      <c r="Q154" s="30"/>
+      <c r="R154" s="30"/>
+      <c r="S154" s="30"/>
+      <c r="T154" s="30"/>
+      <c r="U154" s="30"/>
+      <c r="V154" s="30"/>
+      <c r="W154" s="30"/>
+      <c r="X154" s="30"/>
+      <c r="Y154" s="30"/>
+      <c r="Z154" s="30"/>
+    </row>
+    <row r="155" spans="1:27" s="37" customFormat="1" ht="39">
+      <c r="A155" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B155" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="C155" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="D155" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="E155" s="30"/>
+      <c r="G155" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="H155" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="I155" s="30"/>
+      <c r="J155" s="30"/>
+      <c r="K155" s="30"/>
+      <c r="L155" s="30"/>
+      <c r="M155" s="30"/>
+      <c r="N155" s="30"/>
+      <c r="O155" s="30"/>
+      <c r="P155" s="30"/>
+      <c r="Q155" s="30"/>
+      <c r="R155" s="30"/>
+      <c r="S155" s="30"/>
+      <c r="T155" s="30"/>
+      <c r="U155" s="30"/>
+      <c r="V155" s="30"/>
+      <c r="W155" s="30"/>
+      <c r="X155" s="30"/>
+      <c r="Y155" s="30"/>
+      <c r="Z155" s="30"/>
+    </row>
+    <row r="156" spans="1:27" s="37" customFormat="1" ht="85.5">
+      <c r="A156" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B156" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="C156" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="D156" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="E156" s="30"/>
+      <c r="G156" s="41" t="s">
+        <v>427</v>
+      </c>
+      <c r="H156" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="I156" s="30"/>
+      <c r="J156" s="30"/>
+      <c r="K156" s="30"/>
+      <c r="L156" s="30"/>
+      <c r="M156" s="30"/>
+      <c r="N156" s="30"/>
+      <c r="O156" s="30"/>
+      <c r="P156" s="30"/>
+      <c r="Q156" s="30"/>
+      <c r="R156" s="30"/>
+      <c r="S156" s="30"/>
+      <c r="T156" s="30"/>
+      <c r="U156" s="30"/>
+      <c r="V156" s="30"/>
+      <c r="W156" s="30"/>
+      <c r="X156" s="30"/>
+      <c r="Y156" s="30"/>
+      <c r="Z156" s="30"/>
+    </row>
+    <row r="157" spans="1:27">
+      <c r="A157" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B157" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C157" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="158" spans="1:27">
+      <c r="A158" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B158" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="159" spans="1:27" s="37" customFormat="1" ht="31" customHeight="1">
+      <c r="A159" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="M125" s="37" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" s="37" customFormat="1">
-      <c r="A126" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" s="37" customFormat="1">
-      <c r="A127" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B127" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E127" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="H127" s="37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" s="37" customFormat="1">
-      <c r="A128" s="27" t="s">
+      <c r="B159" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="C159" s="30"/>
+      <c r="D159" s="30"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="30"/>
+      <c r="G159" s="30"/>
+      <c r="H159" s="30"/>
+      <c r="I159" s="30"/>
+      <c r="J159" s="30"/>
+      <c r="K159" s="30"/>
+      <c r="M159" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="N159" s="30"/>
+      <c r="O159" s="30"/>
+      <c r="P159" s="30"/>
+      <c r="Q159" s="30"/>
+      <c r="R159" s="30"/>
+      <c r="S159" s="30"/>
+      <c r="T159" s="30"/>
+      <c r="U159" s="30"/>
+      <c r="V159" s="30"/>
+      <c r="W159" s="30"/>
+      <c r="X159" s="30"/>
+      <c r="Y159" s="30"/>
+      <c r="Z159" s="30"/>
+      <c r="AA159" s="30"/>
+    </row>
+    <row r="160" spans="1:27" s="38" customFormat="1">
+      <c r="A160" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="M128" s="26" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" s="37" customFormat="1">
-      <c r="A129" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" s="37" customFormat="1">
-      <c r="A130" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="A131" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B131" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C131" t="s">
-        <v>206</v>
-      </c>
-      <c r="H131" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C132" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>205</v>
+      <c r="B160" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="M160" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" s="38" customFormat="1">
+      <c r="A161" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="M161" s="18" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" s="38" customFormat="1">
+      <c r="A162" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B162" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="M162" s="18" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="M28:R28"/>
+    <mergeCell ref="M29:R29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5160,9 +6422,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z48"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
+    <col min="1" max="1" width="17.04296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5209,7 +6472,7 @@
         <v>122</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>127</v>
@@ -5243,7 +6506,7 @@
         <v>122</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>128</v>
@@ -5277,7 +6540,7 @@
         <v>122</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>129</v>
@@ -5311,7 +6574,7 @@
         <v>122</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>130</v>
@@ -5379,7 +6642,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>133</v>
@@ -5583,7 +6846,7 @@
         <v>122</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>144</v>
@@ -5889,7 +7152,7 @@
         <v>122</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>162</v>
@@ -5923,7 +7186,7 @@
         <v>122</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>163</v>
@@ -5957,7 +7220,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C24" s="32" t="s">
         <v>164</v>
@@ -6025,7 +7288,7 @@
         <v>122</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>168</v>
@@ -6056,97 +7319,601 @@
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B30" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B33" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C33" s="27" t="s">
+      <c r="D33" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="D33" s="27" t="s">
+    </row>
+    <row r="34" spans="1:26" ht="13">
+      <c r="A34" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="B34" s="27" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A34" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="B34" s="27" t="s">
+      <c r="C34" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="D34" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="D34" s="27" t="s">
-        <v>262</v>
-      </c>
+    </row>
+    <row r="35" spans="1:26" ht="26">
+      <c r="A35" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+    </row>
+    <row r="36" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A36" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+    </row>
+    <row r="37" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A37" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+    </row>
+    <row r="38" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A38" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+    </row>
+    <row r="39" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A39" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+    </row>
+    <row r="40" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A40" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+    </row>
+    <row r="41" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A41" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="30"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="30"/>
+      <c r="U41" s="30"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="30"/>
+      <c r="X41" s="30"/>
+      <c r="Y41" s="30"/>
+      <c r="Z41" s="30"/>
+    </row>
+    <row r="42" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A42" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="30"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+    </row>
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A43" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+    </row>
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A44" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="30"/>
+      <c r="X44" s="30"/>
+      <c r="Y44" s="30"/>
+      <c r="Z44" s="30"/>
+    </row>
+    <row r="45" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A45" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>375</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="30"/>
+      <c r="X45" s="30"/>
+      <c r="Y45" s="30"/>
+      <c r="Z45" s="30"/>
+    </row>
+    <row r="46" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A46" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+    </row>
+    <row r="47" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A47" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30"/>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+    </row>
+    <row r="48" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A48" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -16,12 +16,12 @@
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="508">
   <si>
     <t>type</t>
   </si>
@@ -652,13 +652,7 @@
     <t>I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery</t>
   </si>
   <si>
-    <t>mitigation_strategy_questions</t>
-  </si>
-  <si>
     <t xml:space="preserve">note_to_chv </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have the mother explain first and if she cannot then explain it to her. </t>
   </si>
   <si>
     <t xml:space="preserve">visit_summary </t>
@@ -994,43 +988,7 @@
     <t xml:space="preserve">${high_risk_manual}  = "true" </t>
   </si>
   <si>
-    <t xml:space="preserve">begin repeat </t>
-  </si>
-  <si>
-    <t xml:space="preserve">questions_to_client </t>
-  </si>
-  <si>
-    <t>questions_to_client</t>
-  </si>
-  <si>
     <t xml:space="preserve">repeat_count </t>
-  </si>
-  <si>
-    <t>current_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end repeat </t>
-  </si>
-  <si>
-    <t>imran</t>
-  </si>
-  <si>
-    <t>esmail</t>
-  </si>
-  <si>
-    <t>${mitigation_list}</t>
-  </si>
-  <si>
-    <t>selected-at(${esmail},0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you understand the importance of ${current_name} ? </t>
-  </si>
-  <si>
-    <t>qn_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repeat </t>
   </si>
   <si>
     <t>pregnancy_issues_group</t>
@@ -1389,12 +1347,265 @@
     <t>&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
 [${risk_factor_names}]</t>
   </si>
+  <si>
+    <t>Kupata mimba zaidi ya mara 5</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa kupasuliwa</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa kusaidiwa kuvutwa na mashine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupoteza mtoto wakati wa kujifungua </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
+  </si>
+  <si>
+    <t>Kuchanika njia ya uzazi(karibia ya njia ya choo kikubwa)</t>
+  </si>
+  <si>
+    <t>Kondo la nyuma kukataa kutoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutokwa na damu nyingi kabla ya kujifungua </t>
+  </si>
+  <si>
+    <t>Kutokwa damu nyingi baada ya kujifungua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kujifungua mtoto mkubwa ( zaidi ya kilo 4) (mimba hii au kabla) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mimba kuharibika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutarajia kuwa na mapacha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtoto kutanguliza makalio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shinikizo la damu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kisukari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seli mundu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maradhi ya moyo </t>
+  </si>
+  <si>
+    <t>Upungufu wa damu mwilini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kushauriwa kujifungua katika kituo cha afya kikubwa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mwenwa hajatoa ruhusa ya kujifungua kituo cha afya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mimba iliyopita ilikuwa miaka kumi ilopita au zaidi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutumia dawa za mitishamba </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuepuka kula baadhi ya vyakula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitigation Strategy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito </t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Ukizingatia sababu zifuatazo za hatari za ujauzito:&lt;/strong&gt;
+[${risk_factor_names_swahili}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unaweza kufanya mambo gani ili uweze kuendelea na mimba yako vizuri hadi utakapojifungua? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sasa, nitakufahamisha mambo ambayo yatakuwezesha kuendelea na mimba yako vizuri hadi utakapojifungua. </t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Have the mother explain first and if she cannot then explain it to her. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Mpe nafasi mama aeleze kwanza. Ikiwa hawezi kueleza basi mfahamishe. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>risk_factor_names_swahili</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/risk_factor_names_swahili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wakati wa usajili, tulizungumza kuhusu sababu za hatari za ujauzito. Nataka nihakikishe kwamba unazijua sababu hizo ili kuwe na uwezekano mdogo sana wa kuja kuzipata.  Kwahiyo, nitakuja kukutembela kila baada ya wiki mbili ili kuhakikisha unaendelea vizuri na mimba yako hadi utakapojifungua. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unakumbuka sababu zipi za hatari za ujauzito? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nitakutembelea tena baada ya wiki mbili. </t>
+  </si>
+  <si>
+    <t>Kujifungulia kituo cha afya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuhudhuria kliniki wakati wa ujauzito </t>
+  </si>
+  <si>
+    <t>Kupumzika</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kula vyakula vyenye virutubisho </t>
+  </si>
+  <si>
+    <t>Kutokufanya kazi ngumu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutumia uzazi wa mpango </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhtasari wa tembeleo </t>
+  </si>
+  <si>
+    <t>Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
+  </si>
+  <si>
+    <t>mitigation_qn</t>
+  </si>
+  <si>
+    <t>mitigation_index_1</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=1</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},0)</t>
+  </si>
+  <si>
+    <t>mitigation_note_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_1}? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>mitigation_index_2</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=2</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},1)</t>
+  </si>
+  <si>
+    <t>mitigation_note_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_2}? </t>
+  </si>
+  <si>
+    <t>mitigation_index_3</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=3</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},2)</t>
+  </si>
+  <si>
+    <t>mitigation_note_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_3}? </t>
+  </si>
+  <si>
+    <t>mitigation_index_4</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=4</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},3)</t>
+  </si>
+  <si>
+    <t>mitigation_note_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_4}? </t>
+  </si>
+  <si>
+    <t>mitigation_index_5</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=5</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},4)</t>
+  </si>
+  <si>
+    <t>mitigation_note_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_5}? </t>
+  </si>
+  <si>
+    <t>mitigation_index_6</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=6</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},5)</t>
+  </si>
+  <si>
+    <t>mitigation_note_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_6}? </t>
+  </si>
+  <si>
+    <t>mitigation_index_7</t>
+  </si>
+  <si>
+    <t>${mitigation_list_length}&gt;=7</t>
+  </si>
+  <si>
+    <t>selected-at(${mitigation_list},6)</t>
+  </si>
+  <si>
+    <t>mitigation_note_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of  ${mitigation_index_7}? </t>
+  </si>
+  <si>
+    <t>mitigation_list_length</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/mitigation_list_length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je, unaelewa umuhimu wa  ${mitigation_index_1} ? </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1473,8 +1684,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1497,6 +1715,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -1527,7 +1757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1593,8 +1823,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1813,7 +2050,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA162"/>
+  <dimension ref="A1:AA169"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="1"/>
@@ -1837,7 +2074,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -2005,7 +2242,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>21</v>
@@ -2180,10 +2417,10 @@
         <v>25</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -2859,14 +3096,14 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="43" t="s">
+      <c r="M29" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
@@ -3337,7 +3574,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -3350,7 +3587,7 @@
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
       <c r="M43" s="27" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="N43" s="16"/>
       <c r="O43" s="16"/>
@@ -3372,7 +3609,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -3385,7 +3622,7 @@
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="27" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N44" s="16"/>
       <c r="O44" s="16"/>
@@ -3407,7 +3644,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
@@ -3420,7 +3657,7 @@
       <c r="K45" s="16"/>
       <c r="L45" s="16"/>
       <c r="M45" s="27" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N45" s="16"/>
       <c r="O45" s="16"/>
@@ -3455,7 +3692,7 @@
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N46" s="16"/>
       <c r="O46" s="16"/>
@@ -3477,7 +3714,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
@@ -3490,7 +3727,7 @@
       <c r="K47" s="16"/>
       <c r="L47" s="16"/>
       <c r="M47" s="27" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N47" s="16"/>
       <c r="O47" s="16"/>
@@ -3507,47 +3744,24 @@
       <c r="Z47" s="16"/>
       <c r="AA47" s="16"/>
     </row>
-    <row r="48" spans="1:27" s="42" customFormat="1">
-      <c r="A48" s="27" t="s">
+    <row r="48" spans="1:27" s="45" customFormat="1">
+      <c r="A48" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="27" t="s">
-        <v>435</v>
-      </c>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
-      <c r="AA48" s="16"/>
-    </row>
-    <row r="49" spans="1:27" s="28" customFormat="1">
+      <c r="B48" s="50" t="s">
+        <v>505</v>
+      </c>
+      <c r="G48" s="51"/>
+      <c r="M48" s="50" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" s="42" customFormat="1">
       <c r="A49" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>301</v>
+        <v>420</v>
       </c>
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
@@ -3560,7 +3774,7 @@
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="27" t="s">
-        <v>302</v>
+        <v>421</v>
       </c>
       <c r="N49" s="16"/>
       <c r="O49" s="16"/>
@@ -3577,95 +3791,95 @@
       <c r="Z49" s="16"/>
       <c r="AA49" s="16"/>
     </row>
-    <row r="50" spans="1:27">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:27" s="42" customFormat="1">
+      <c r="A50" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
       <c r="E50" s="16"/>
-      <c r="F50" s="2"/>
+      <c r="F50" s="16"/>
       <c r="G50" s="10"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
-      <c r="AA50" s="2"/>
-    </row>
-    <row r="51" spans="1:27">
-      <c r="A51" s="2" t="s">
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+    </row>
+    <row r="51" spans="1:27" s="28" customFormat="1">
+      <c r="A51" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="B51" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
       <c r="E51" s="16"/>
-      <c r="F51" s="2"/>
+      <c r="F51" s="16"/>
       <c r="G51" s="10"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
     </row>
     <row r="52" spans="1:27">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="16"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+      <c r="G52" s="10"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
-      <c r="M52" s="2" t="s">
-        <v>87</v>
+      <c r="M52" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -3687,7 +3901,7 @@
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -3700,7 +3914,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -3718,11 +3932,11 @@
       <c r="AA53" s="2"/>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>89</v>
+      <c r="A54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -3734,7 +3948,9 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
-      <c r="M54" s="10"/>
+      <c r="M54" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
@@ -3751,23 +3967,25 @@
       <c r="AA54" s="2"/>
     </row>
     <row r="55" spans="1:27">
-      <c r="A55" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>90</v>
+      <c r="A55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="16"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
+      <c r="G55" s="10"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
-      <c r="M55" s="10"/>
+      <c r="M55" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
@@ -3784,27 +4002,23 @@
       <c r="AA55" s="2"/>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
+      <c r="A56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" s="10"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -3821,27 +4035,23 @@
       <c r="AA56" s="2"/>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>98</v>
-      </c>
+      <c r="A57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
       <c r="E57" s="16"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" s="10"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -3859,14 +4069,18 @@
     </row>
     <row r="58" spans="1:27">
       <c r="A58" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="16"/>
+      <c r="C58" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="12"/>
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
       <c r="H58" s="11"/>
@@ -3891,24 +4105,22 @@
       <c r="AA58" s="2"/>
     </row>
     <row r="59" spans="1:27">
-      <c r="A59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>102</v>
+      <c r="A59" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="E59" s="16"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -3930,22 +4142,18 @@
       <c r="AA59" s="2"/>
     </row>
     <row r="60" spans="1:27">
-      <c r="A60" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>106</v>
-      </c>
+      <c r="A60" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
       <c r="E60" s="16"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -3968,21 +4176,23 @@
     </row>
     <row r="61" spans="1:27">
       <c r="A61" s="2" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -4008,13 +4218,13 @@
         <v>95</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="2"/>
@@ -4045,13 +4255,13 @@
         <v>95</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="2"/>
@@ -4079,13 +4289,17 @@
     </row>
     <row r="64" spans="1:27">
       <c r="A64" s="2" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="E64" s="16"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -4111,124 +4325,123 @@
       <c r="AA64" s="2"/>
     </row>
     <row r="65" spans="1:27">
-      <c r="A65" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>116</v>
-      </c>
+      <c r="A65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
+      <c r="AA65" s="2"/>
     </row>
     <row r="66" spans="1:27">
-      <c r="A66" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>117</v>
-      </c>
+      <c r="A66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="2"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
+      <c r="Y66" s="2"/>
+      <c r="Z66" s="2"/>
+      <c r="AA66" s="2"/>
     </row>
     <row r="67" spans="1:27">
       <c r="A67" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
+      <c r="A68" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
+      <c r="A69" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B69" s="16" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="68" spans="1:27" s="28" customFormat="1">
-      <c r="A68" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B68" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="D68" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="I68" s="30"/>
-      <c r="J68" s="30"/>
-      <c r="K68" s="30"/>
-      <c r="L68" s="30"/>
-      <c r="M68" s="30"/>
-      <c r="N68" s="30"/>
-      <c r="O68" s="30"/>
-      <c r="P68" s="30"/>
-      <c r="Q68" s="30"/>
-      <c r="R68" s="30"/>
-      <c r="S68" s="30"/>
-      <c r="T68" s="30"/>
-      <c r="U68" s="30"/>
-      <c r="V68" s="30"/>
-      <c r="W68" s="30"/>
-      <c r="X68" s="30"/>
-      <c r="Y68" s="30"/>
-      <c r="Z68" s="30"/>
-      <c r="AA68" s="30"/>
-    </row>
-    <row r="69" spans="1:27" s="28" customFormat="1">
-      <c r="A69" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B69" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="D69" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="E69" s="32"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="30"/>
-      <c r="K69" s="30"/>
-      <c r="L69" s="30"/>
-      <c r="M69" s="30"/>
-      <c r="N69" s="30"/>
-      <c r="O69" s="30"/>
-      <c r="P69" s="30"/>
-      <c r="Q69" s="30"/>
-      <c r="R69" s="30"/>
-      <c r="S69" s="30"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
-      <c r="V69" s="30"/>
-      <c r="W69" s="30"/>
-      <c r="X69" s="30"/>
-      <c r="Y69" s="30"/>
-      <c r="Z69" s="30"/>
-      <c r="AA69" s="30"/>
     </row>
     <row r="70" spans="1:27" s="28" customFormat="1">
       <c r="A70" s="30" t="s">
         <v>19</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="30"/>
+        <v>207</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>208</v>
+      </c>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
+      <c r="G70" s="31"/>
       <c r="H70" s="30" t="s">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="I70" s="30"/>
       <c r="J70" s="30"/>
@@ -4250,23 +4463,21 @@
       <c r="Z70" s="30"/>
       <c r="AA70" s="30"/>
     </row>
-    <row r="71" spans="1:27" s="28" customFormat="1" ht="14.75">
+    <row r="71" spans="1:27" s="28" customFormat="1">
       <c r="A71" s="30" t="s">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="E71" s="33"/>
-      <c r="F71" s="30" t="s">
-        <v>220</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E71" s="32"/>
+      <c r="F71" s="30"/>
       <c r="G71" s="30"/>
       <c r="H71" s="30"/>
       <c r="I71" s="30"/>
@@ -4289,25 +4500,23 @@
       <c r="Z71" s="30"/>
       <c r="AA71" s="30"/>
     </row>
-    <row r="72" spans="1:27" s="28" customFormat="1" ht="14.75">
+    <row r="72" spans="1:27" s="28" customFormat="1">
       <c r="A72" s="30" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C72" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="D72" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E72" s="33"/>
-      <c r="F72" s="30" t="s">
-        <v>220</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
       <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
+      <c r="H72" s="30" t="s">
+        <v>213</v>
+      </c>
       <c r="I72" s="30"/>
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
@@ -4328,22 +4537,22 @@
       <c r="Z72" s="30"/>
       <c r="AA72" s="30"/>
     </row>
-    <row r="73" spans="1:27" s="28" customFormat="1">
+    <row r="73" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A73" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="B73" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="C73" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E73" s="30"/>
+      <c r="D73" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E73" s="33"/>
       <c r="F73" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G73" s="30"/>
       <c r="H73" s="30"/>
@@ -4369,20 +4578,20 @@
     </row>
     <row r="74" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A74" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E74" s="33"/>
       <c r="F74" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G74" s="30"/>
       <c r="H74" s="30"/>
@@ -4408,15 +4617,21 @@
     </row>
     <row r="75" spans="1:27" s="28" customFormat="1">
       <c r="A75" s="30" t="s">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="C75" s="34"/>
-      <c r="D75" s="30"/>
+        <v>222</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" s="30" t="s">
+        <v>224</v>
+      </c>
       <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
+      <c r="F75" s="30" t="s">
+        <v>218</v>
+      </c>
       <c r="G75" s="30"/>
       <c r="H75" s="30"/>
       <c r="I75" s="30"/>
@@ -4439,21 +4654,23 @@
       <c r="Z75" s="30"/>
       <c r="AA75" s="30"/>
     </row>
-    <row r="76" spans="1:27" s="28" customFormat="1">
+    <row r="76" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A76" s="30" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="D76" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E76" s="32"/>
-      <c r="F76" s="30"/>
+        <v>225</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="E76" s="33"/>
+      <c r="F76" s="30" t="s">
+        <v>218</v>
+      </c>
       <c r="G76" s="30"/>
       <c r="H76" s="30"/>
       <c r="I76" s="30"/>
@@ -4478,18 +4695,14 @@
     </row>
     <row r="77" spans="1:27" s="28" customFormat="1">
       <c r="A77" s="30" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="C77" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="D77" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E77" s="32"/>
+        <v>212</v>
+      </c>
+      <c r="C77" s="34"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
       <c r="F77" s="30"/>
       <c r="G77" s="30"/>
       <c r="H77" s="30"/>
@@ -4513,23 +4726,23 @@
       <c r="Z77" s="30"/>
       <c r="AA77" s="30"/>
     </row>
-    <row r="78" spans="1:27" s="28" customFormat="1" ht="14.75">
+    <row r="78" spans="1:27" s="28" customFormat="1">
       <c r="A78" s="30" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="C78" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
+        <v>228</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="D78" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E78" s="32"/>
       <c r="F78" s="30"/>
       <c r="G78" s="30"/>
-      <c r="H78" s="30" t="s">
-        <v>215</v>
-      </c>
+      <c r="H78" s="30"/>
       <c r="I78" s="30"/>
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
@@ -4550,23 +4763,21 @@
       <c r="Z78" s="30"/>
       <c r="AA78" s="30"/>
     </row>
-    <row r="79" spans="1:27" s="28" customFormat="1" ht="14.75">
+    <row r="79" spans="1:27" s="28" customFormat="1">
       <c r="A79" s="30" t="s">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="C79" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="D79" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E79" s="33"/>
-      <c r="F79" s="30" t="s">
-        <v>220</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E79" s="32"/>
+      <c r="F79" s="30"/>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
       <c r="I79" s="30"/>
@@ -4591,23 +4802,21 @@
     </row>
     <row r="80" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A80" s="30" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>242</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D80" s="33"/>
       <c r="E80" s="33"/>
-      <c r="F80" s="30" t="s">
-        <v>220</v>
-      </c>
+      <c r="F80" s="30"/>
       <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
+      <c r="H80" s="30" t="s">
+        <v>213</v>
+      </c>
       <c r="I80" s="30"/>
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
@@ -4630,20 +4839,20 @@
     </row>
     <row r="81" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A81" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="D81" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="E81" s="30"/>
+        <v>236</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E81" s="33"/>
       <c r="F81" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G81" s="30"/>
       <c r="H81" s="30"/>
@@ -4669,15 +4878,21 @@
     </row>
     <row r="82" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A82" s="30" t="s">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="C82" s="33"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
+        <v>238</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E82" s="33"/>
+      <c r="F82" s="30" t="s">
+        <v>218</v>
+      </c>
       <c r="G82" s="30"/>
       <c r="H82" s="30"/>
       <c r="I82" s="30"/>
@@ -4700,26 +4915,30 @@
       <c r="Z82" s="30"/>
       <c r="AA82" s="30"/>
     </row>
-    <row r="83" spans="1:27" s="28" customFormat="1" ht="15.5" customHeight="1">
+    <row r="83" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A83" s="30" t="s">
-        <v>41</v>
+        <v>214</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
+        <v>241</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="D83" s="30" t="s">
+        <v>243</v>
+      </c>
       <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
+      <c r="F83" s="30" t="s">
+        <v>218</v>
+      </c>
       <c r="G83" s="30"/>
       <c r="H83" s="30"/>
       <c r="I83" s="30"/>
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
       <c r="L83" s="30"/>
-      <c r="M83" s="31" t="s">
-        <v>247</v>
-      </c>
+      <c r="M83" s="30"/>
       <c r="N83" s="30"/>
       <c r="O83" s="30"/>
       <c r="P83" s="30"/>
@@ -4735,26 +4954,18 @@
       <c r="Z83" s="30"/>
       <c r="AA83" s="30"/>
     </row>
-    <row r="84" spans="1:27" s="28" customFormat="1" ht="13.75" customHeight="1">
+    <row r="84" spans="1:27" s="28" customFormat="1" ht="14.75">
       <c r="A84" s="30" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="C84" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="E84" s="33"/>
-      <c r="F84" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G84" s="30" t="s">
-        <v>251</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C84" s="33"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
       <c r="H84" s="30"/>
       <c r="I84" s="30"/>
       <c r="J84" s="30"/>
@@ -4776,30 +4987,26 @@
       <c r="Z84" s="30"/>
       <c r="AA84" s="30"/>
     </row>
-    <row r="85" spans="1:27" s="28" customFormat="1" ht="24.5" customHeight="1">
+    <row r="85" spans="1:27" s="28" customFormat="1" ht="15.5" customHeight="1">
       <c r="A85" s="30" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="D85" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="E85" s="32"/>
+        <v>244</v>
+      </c>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
       <c r="F85" s="30"/>
-      <c r="G85" s="30" t="s">
-        <v>255</v>
-      </c>
+      <c r="G85" s="30"/>
       <c r="H85" s="30"/>
       <c r="I85" s="30"/>
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
       <c r="L85" s="30"/>
-      <c r="M85" s="30"/>
+      <c r="M85" s="31" t="s">
+        <v>245</v>
+      </c>
       <c r="N85" s="30"/>
       <c r="O85" s="30"/>
       <c r="P85" s="30"/>
@@ -4815,18 +5022,26 @@
       <c r="Z85" s="30"/>
       <c r="AA85" s="30"/>
     </row>
-    <row r="86" spans="1:27" s="28" customFormat="1">
+    <row r="86" spans="1:27" s="28" customFormat="1" ht="13.75" customHeight="1">
       <c r="A86" s="30" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="34"/>
+        <v>246</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="E86" s="33"/>
+      <c r="F86" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>249</v>
+      </c>
       <c r="H86" s="30"/>
       <c r="I86" s="30"/>
       <c r="J86" s="30"/>
@@ -4848,22 +5063,23 @@
       <c r="Z86" s="30"/>
       <c r="AA86" s="30"/>
     </row>
-    <row r="87" spans="1:27" s="37" customFormat="1" ht="78">
+    <row r="87" spans="1:27" s="28" customFormat="1" ht="24.5" customHeight="1">
       <c r="A87" s="30" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="D87" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="E87" s="30"/>
-      <c r="G87" s="40" t="s">
-        <v>404</v>
+        <v>251</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="E87" s="32"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30" t="s">
+        <v>253</v>
       </c>
       <c r="H87" s="30"/>
       <c r="I87" s="30"/>
@@ -4886,22 +5102,19 @@
       <c r="Z87" s="30"/>
       <c r="AA87" s="30"/>
     </row>
-    <row r="88" spans="1:27" s="37" customFormat="1">
+    <row r="88" spans="1:27" s="28" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="C88" s="30" t="s">
-        <v>21</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C88" s="30"/>
       <c r="D88" s="30"/>
       <c r="E88" s="30"/>
-      <c r="F88" s="34"/>
-      <c r="H88" s="30" t="s">
-        <v>103</v>
-      </c>
+      <c r="F88" s="30"/>
+      <c r="G88" s="34"/>
+      <c r="H88" s="30"/>
       <c r="I88" s="30"/>
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
@@ -4922,37 +5135,28 @@
       <c r="Z88" s="30"/>
       <c r="AA88" s="30"/>
     </row>
-    <row r="89" spans="1:27" s="37" customFormat="1" ht="34.25" customHeight="1">
+    <row r="89" spans="1:27" s="37" customFormat="1" ht="78">
       <c r="A89" s="30" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G89" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="H89" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="J89" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="K89" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="L89" s="30" t="s">
-        <v>337</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="E89" s="30"/>
+      <c r="G89" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="H89" s="30"/>
+      <c r="I89" s="30"/>
+      <c r="J89" s="30"/>
+      <c r="K89" s="30"/>
+      <c r="L89" s="30"/>
       <c r="M89" s="30"/>
       <c r="N89" s="30"/>
       <c r="O89" s="30"/>
@@ -4969,25 +5173,27 @@
       <c r="Z89" s="30"/>
       <c r="AA89" s="30"/>
     </row>
-    <row r="90" spans="1:27" s="37" customFormat="1" ht="38" customHeight="1">
+    <row r="90" spans="1:27" s="37" customFormat="1">
       <c r="A90" s="30" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C90" s="31"/>
+        <v>315</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>21</v>
+      </c>
       <c r="D90" s="30"/>
       <c r="E90" s="30"/>
       <c r="F90" s="34"/>
-      <c r="G90" s="30"/>
-      <c r="H90" s="30"/>
+      <c r="H90" s="30" t="s">
+        <v>103</v>
+      </c>
       <c r="I90" s="30"/>
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
-      <c r="M90" s="30" t="s">
-        <v>339</v>
-      </c>
+      <c r="L90" s="30"/>
+      <c r="M90" s="30"/>
       <c r="N90" s="30"/>
       <c r="O90" s="30"/>
       <c r="P90" s="30"/>
@@ -5003,28 +5209,37 @@
       <c r="Z90" s="30"/>
       <c r="AA90" s="30"/>
     </row>
-    <row r="91" spans="1:27" s="37" customFormat="1" ht="36.75" customHeight="1">
+    <row r="91" spans="1:27" s="37" customFormat="1" ht="34.25" customHeight="1">
       <c r="A91" s="30" t="s">
-        <v>95</v>
+        <v>316</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="E91" s="30"/>
-      <c r="G91" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="H91" s="30"/>
-      <c r="I91" s="30"/>
-      <c r="J91" s="30"/>
-      <c r="K91" s="30"/>
-      <c r="L91" s="30"/>
+        <v>317</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D91" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G91" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="H91" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="J91" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="K91" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="L91" s="30" t="s">
+        <v>323</v>
+      </c>
       <c r="M91" s="30"/>
       <c r="N91" s="30"/>
       <c r="O91" s="30"/>
@@ -5041,14 +5256,14 @@
       <c r="Z91" s="30"/>
       <c r="AA91" s="30"/>
     </row>
-    <row r="92" spans="1:27" s="37" customFormat="1">
+    <row r="92" spans="1:27" s="37" customFormat="1" ht="38" customHeight="1">
       <c r="A92" s="30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="C92" s="30"/>
+        <v>324</v>
+      </c>
+      <c r="C92" s="31"/>
       <c r="D92" s="30"/>
       <c r="E92" s="30"/>
       <c r="F92" s="34"/>
@@ -5057,8 +5272,9 @@
       <c r="I92" s="30"/>
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
-      <c r="L92" s="30"/>
-      <c r="M92" s="30"/>
+      <c r="M92" s="30" t="s">
+        <v>325</v>
+      </c>
       <c r="N92" s="30"/>
       <c r="O92" s="30"/>
       <c r="P92" s="30"/>
@@ -5074,24 +5290,24 @@
       <c r="Z92" s="30"/>
       <c r="AA92" s="30"/>
     </row>
-    <row r="93" spans="1:27" s="37" customFormat="1" ht="39">
+    <row r="93" spans="1:27" s="37" customFormat="1" ht="36.75" customHeight="1">
       <c r="A93" s="30" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B93" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="C93" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="30"/>
+        <v>326</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="D93" s="32" t="s">
+        <v>328</v>
+      </c>
       <c r="E93" s="30"/>
-      <c r="G93" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="H93" s="30" t="s">
-        <v>103</v>
-      </c>
+      <c r="G93" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="H93" s="30"/>
       <c r="I93" s="30"/>
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
@@ -5112,25 +5328,18 @@
       <c r="Z93" s="30"/>
       <c r="AA93" s="30"/>
     </row>
-    <row r="94" spans="1:27" s="37" customFormat="1" ht="26">
+    <row r="94" spans="1:27" s="37" customFormat="1">
       <c r="A94" s="30" t="s">
-        <v>216</v>
+        <v>35</v>
       </c>
       <c r="B94" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="C94" s="30" t="s">
-        <v>388</v>
-      </c>
-      <c r="D94" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="F94" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G94" s="31" t="s">
-        <v>409</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="34"/>
+      <c r="G94" s="30"/>
       <c r="H94" s="30"/>
       <c r="I94" s="30"/>
       <c r="J94" s="30"/>
@@ -5154,22 +5363,22 @@
     </row>
     <row r="95" spans="1:27" s="37" customFormat="1" ht="39">
       <c r="A95" s="30" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="D95" s="32" t="s">
-        <v>392</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D95" s="30"/>
       <c r="E95" s="30"/>
       <c r="G95" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="H95" s="30"/>
+        <v>320</v>
+      </c>
+      <c r="H95" s="30" t="s">
+        <v>103</v>
+      </c>
       <c r="I95" s="30"/>
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
@@ -5190,24 +5399,24 @@
       <c r="Z95" s="30"/>
       <c r="AA95" s="30"/>
     </row>
-    <row r="96" spans="1:27" s="37" customFormat="1" ht="24.75" customHeight="1">
+    <row r="96" spans="1:27" s="37" customFormat="1" ht="26">
       <c r="A96" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B96" s="30" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="D96" s="30" t="s">
+        <v>375</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G96" s="31" t="s">
         <v>395</v>
-      </c>
-      <c r="F96" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G96" s="31" t="s">
-        <v>334</v>
       </c>
       <c r="H96" s="30"/>
       <c r="I96" s="30"/>
@@ -5230,25 +5439,29 @@
       <c r="Z96" s="30"/>
       <c r="AA96" s="30"/>
     </row>
-    <row r="97" spans="1:27" s="37" customFormat="1" ht="23" customHeight="1">
+    <row r="97" spans="1:27" s="37" customFormat="1" ht="39">
       <c r="A97" s="30" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
+        <v>376</v>
+      </c>
+      <c r="C97" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="D97" s="32" t="s">
+        <v>378</v>
+      </c>
       <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
+      <c r="G97" s="31" t="s">
+        <v>320</v>
+      </c>
       <c r="H97" s="30"/>
       <c r="I97" s="30"/>
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
-      <c r="M97" s="31" t="s">
-        <v>397</v>
-      </c>
+      <c r="L97" s="30"/>
+      <c r="M97" s="30"/>
       <c r="N97" s="30"/>
       <c r="O97" s="30"/>
       <c r="P97" s="30"/>
@@ -5264,22 +5477,24 @@
       <c r="Z97" s="30"/>
       <c r="AA97" s="30"/>
     </row>
-    <row r="98" spans="1:27" s="37" customFormat="1" ht="26">
+    <row r="98" spans="1:27" s="37" customFormat="1" ht="24.75" customHeight="1">
       <c r="A98" s="30" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="B98" s="30" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="D98" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="E98" s="30"/>
-      <c r="G98" s="32" t="s">
-        <v>399</v>
+        <v>380</v>
+      </c>
+      <c r="D98" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>320</v>
       </c>
       <c r="H98" s="30"/>
       <c r="I98" s="30"/>
@@ -5302,29 +5517,25 @@
       <c r="Z98" s="30"/>
       <c r="AA98" s="30"/>
     </row>
-    <row r="99" spans="1:27" s="37" customFormat="1">
+    <row r="99" spans="1:27" s="37" customFormat="1" ht="23" customHeight="1">
       <c r="A99" s="30" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="C99" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="D99" s="32" t="s">
-        <v>402</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
       <c r="E99" s="30"/>
-      <c r="G99" s="32" t="s">
-        <v>403</v>
-      </c>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
       <c r="H99" s="30"/>
       <c r="I99" s="30"/>
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
-      <c r="L99" s="30"/>
-      <c r="M99" s="30"/>
+      <c r="M99" s="31" t="s">
+        <v>383</v>
+      </c>
       <c r="N99" s="30"/>
       <c r="O99" s="30"/>
       <c r="P99" s="30"/>
@@ -5340,18 +5551,23 @@
       <c r="Z99" s="30"/>
       <c r="AA99" s="30"/>
     </row>
-    <row r="100" spans="1:27" s="37" customFormat="1">
+    <row r="100" spans="1:27" s="37" customFormat="1" ht="26">
       <c r="A100" s="30" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
+        <v>384</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>328</v>
+      </c>
       <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
+      <c r="G100" s="32" t="s">
+        <v>385</v>
+      </c>
       <c r="H100" s="30"/>
       <c r="I100" s="30"/>
       <c r="J100" s="30"/>
@@ -5375,16 +5591,21 @@
     </row>
     <row r="101" spans="1:27" s="37" customFormat="1">
       <c r="A101" s="30" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B101" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="C101" s="30"/>
-      <c r="D101" s="30"/>
+        <v>386</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D101" s="32" t="s">
+        <v>388</v>
+      </c>
       <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
+      <c r="G101" s="32" t="s">
+        <v>389</v>
+      </c>
       <c r="H101" s="30"/>
       <c r="I101" s="30"/>
       <c r="J101" s="30"/>
@@ -5406,85 +5627,75 @@
       <c r="Z101" s="30"/>
       <c r="AA101" s="30"/>
     </row>
-    <row r="102" spans="1:27">
-      <c r="A102" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B102" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C102" s="28"/>
-      <c r="D102" s="28"/>
-      <c r="F102" s="28"/>
-      <c r="G102" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="H102" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I102" s="28"/>
-      <c r="J102" s="28"/>
-      <c r="K102" s="28"/>
-      <c r="L102" s="28"/>
-      <c r="M102" s="28"/>
-      <c r="N102" s="28"/>
-      <c r="O102" s="28"/>
-      <c r="P102" s="28"/>
-      <c r="Q102" s="28"/>
-      <c r="R102" s="28"/>
-      <c r="S102" s="28"/>
-      <c r="T102" s="28"/>
-      <c r="U102" s="28"/>
-      <c r="V102" s="28"/>
-      <c r="W102" s="28"/>
-      <c r="X102" s="28"/>
-      <c r="Y102" s="28"/>
-      <c r="Z102" s="28"/>
-      <c r="AA102" s="28"/>
-    </row>
-    <row r="103" spans="1:27" ht="14.75">
-      <c r="A103" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B103" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C103" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D103" s="28"/>
-      <c r="F103" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="G103" s="26" t="s">
+    <row r="102" spans="1:27" s="37" customFormat="1">
+      <c r="A102" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B102" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+      <c r="H102" s="30"/>
+      <c r="I102" s="30"/>
+      <c r="J102" s="30"/>
+      <c r="K102" s="30"/>
+      <c r="L102" s="30"/>
+      <c r="M102" s="30"/>
+      <c r="N102" s="30"/>
+      <c r="O102" s="30"/>
+      <c r="P102" s="30"/>
+      <c r="Q102" s="30"/>
+      <c r="R102" s="30"/>
+      <c r="S102" s="30"/>
+      <c r="T102" s="30"/>
+      <c r="U102" s="30"/>
+      <c r="V102" s="30"/>
+      <c r="W102" s="30"/>
+      <c r="X102" s="30"/>
+      <c r="Y102" s="30"/>
+      <c r="Z102" s="30"/>
+      <c r="AA102" s="30"/>
+    </row>
+    <row r="103" spans="1:27" s="37" customFormat="1">
+      <c r="A103" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="H103" s="28"/>
-      <c r="I103" s="28"/>
-      <c r="J103" s="28"/>
-      <c r="K103" s="28"/>
-      <c r="L103" s="28"/>
-      <c r="M103" s="28"/>
-      <c r="N103" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="O103" s="28"/>
-      <c r="P103" s="28"/>
-      <c r="Q103" s="28"/>
-      <c r="R103" s="28"/>
-      <c r="S103" s="28"/>
-      <c r="T103" s="28"/>
-      <c r="U103" s="28"/>
-      <c r="V103" s="28"/>
-      <c r="W103" s="28"/>
-      <c r="X103" s="28"/>
-      <c r="Y103" s="28"/>
-      <c r="Z103" s="28"/>
-      <c r="AA103" s="28"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
+      <c r="I103" s="30"/>
+      <c r="J103" s="30"/>
+      <c r="K103" s="30"/>
+      <c r="L103" s="30"/>
+      <c r="M103" s="30"/>
+      <c r="N103" s="30"/>
+      <c r="O103" s="30"/>
+      <c r="P103" s="30"/>
+      <c r="Q103" s="30"/>
+      <c r="R103" s="30"/>
+      <c r="S103" s="30"/>
+      <c r="T103" s="30"/>
+      <c r="U103" s="30"/>
+      <c r="V103" s="30"/>
+      <c r="W103" s="30"/>
+      <c r="X103" s="30"/>
+      <c r="Y103" s="30"/>
+      <c r="Z103" s="30"/>
+      <c r="AA103" s="30"/>
     </row>
     <row r="104" spans="1:27">
       <c r="A104" s="16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B104" s="16" t="s">
         <v>119</v>
@@ -5492,8 +5703,12 @@
       <c r="C104" s="28"/>
       <c r="D104" s="28"/>
       <c r="F104" s="28"/>
-      <c r="G104" s="28"/>
-      <c r="H104" s="28"/>
+      <c r="G104" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="H104" s="16" t="s">
+        <v>120</v>
+      </c>
       <c r="I104" s="28"/>
       <c r="J104" s="28"/>
       <c r="K104" s="28"/>
@@ -5514,28 +5729,34 @@
       <c r="Z104" s="28"/>
       <c r="AA104" s="28"/>
     </row>
-    <row r="105" spans="1:27">
+    <row r="105" spans="1:27" ht="14.75">
       <c r="A105" s="16" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C105" s="28"/>
-      <c r="D105" s="28"/>
-      <c r="F105" s="28"/>
+        <v>122</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D105" s="46" t="s">
+        <v>457</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>218</v>
+      </c>
       <c r="G105" s="26" t="s">
-        <v>410</v>
-      </c>
-      <c r="H105" s="16" t="s">
-        <v>125</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="H105" s="28"/>
       <c r="I105" s="28"/>
       <c r="J105" s="28"/>
       <c r="K105" s="28"/>
       <c r="L105" s="28"/>
       <c r="M105" s="28"/>
-      <c r="N105" s="28"/>
+      <c r="N105" s="26" t="s">
+        <v>183</v>
+      </c>
       <c r="O105" s="28"/>
       <c r="P105" s="28"/>
       <c r="Q105" s="28"/>
@@ -5550,21 +5771,17 @@
       <c r="Z105" s="28"/>
       <c r="AA105" s="28"/>
     </row>
-    <row r="106" spans="1:27" ht="14.75">
+    <row r="106" spans="1:27">
       <c r="A106" s="16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C106" s="17" t="s">
-        <v>127</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C106" s="28"/>
       <c r="D106" s="28"/>
       <c r="F106" s="28"/>
-      <c r="G106" s="36" t="s">
-        <v>273</v>
-      </c>
+      <c r="G106" s="28"/>
       <c r="H106" s="28"/>
       <c r="I106" s="28"/>
       <c r="J106" s="28"/>
@@ -5588,20 +5805,20 @@
     </row>
     <row r="107" spans="1:27">
       <c r="A107" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B107" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C107" s="16" t="s">
-        <v>128</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C107" s="28"/>
       <c r="D107" s="28"/>
       <c r="F107" s="28"/>
-      <c r="G107" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="H107" s="28"/>
+      <c r="G107" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="H107" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="I107" s="28"/>
       <c r="J107" s="28"/>
       <c r="K107" s="28"/>
@@ -5622,46 +5839,97 @@
       <c r="Z107" s="28"/>
       <c r="AA107" s="28"/>
     </row>
-    <row r="108" spans="1:27">
+    <row r="108" spans="1:27" ht="14.75">
       <c r="A108" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B108" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="C108" s="16" t="s">
-        <v>129</v>
-      </c>
+      <c r="B108" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="F108" s="28"/>
       <c r="G108" s="36" t="s">
-        <v>274</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="28"/>
+      <c r="K108" s="28"/>
+      <c r="L108" s="28"/>
+      <c r="M108" s="28"/>
+      <c r="N108" s="28"/>
+      <c r="O108" s="28"/>
+      <c r="P108" s="28"/>
+      <c r="Q108" s="28"/>
+      <c r="R108" s="28"/>
+      <c r="S108" s="28"/>
+      <c r="T108" s="28"/>
+      <c r="U108" s="28"/>
+      <c r="V108" s="28"/>
+      <c r="W108" s="28"/>
+      <c r="X108" s="28"/>
+      <c r="Y108" s="28"/>
+      <c r="Z108" s="28"/>
+      <c r="AA108" s="28"/>
     </row>
     <row r="109" spans="1:27">
       <c r="A109" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>130</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D109" s="26" t="s">
+        <v>425</v>
+      </c>
+      <c r="F109" s="28"/>
       <c r="G109" s="36" t="s">
-        <v>276</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="28"/>
+      <c r="L109" s="28"/>
+      <c r="M109" s="28"/>
+      <c r="N109" s="28"/>
+      <c r="O109" s="28"/>
+      <c r="P109" s="28"/>
+      <c r="Q109" s="28"/>
+      <c r="R109" s="28"/>
+      <c r="S109" s="28"/>
+      <c r="T109" s="28"/>
+      <c r="U109" s="28"/>
+      <c r="V109" s="28"/>
+      <c r="W109" s="28"/>
+      <c r="X109" s="28"/>
+      <c r="Y109" s="28"/>
+      <c r="Z109" s="28"/>
+      <c r="AA109" s="28"/>
     </row>
     <row r="110" spans="1:27">
       <c r="A110" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B110" s="27" t="s">
-        <v>131</v>
+      <c r="B110" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="D110" s="26" t="s">
+        <v>426</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:27">
@@ -5669,13 +5937,16 @@
         <v>95</v>
       </c>
       <c r="B111" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="D111" s="26" t="s">
+        <v>427</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="112" spans="1:27">
@@ -5683,27 +5954,33 @@
         <v>95</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="D112" s="27" t="s">
+        <v>428</v>
       </c>
       <c r="G112" s="36" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="27" t="s">
-        <v>136</v>
+      <c r="B113" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="D113" s="26" t="s">
+        <v>429</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5711,13 +5988,16 @@
         <v>95</v>
       </c>
       <c r="B114" s="27" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="D114" s="27" t="s">
+        <v>430</v>
       </c>
       <c r="G114" s="36" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5725,13 +6005,16 @@
         <v>95</v>
       </c>
       <c r="B115" s="27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="D115" s="27" t="s">
+        <v>431</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5739,27 +6022,33 @@
         <v>95</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>432</v>
       </c>
       <c r="G116" s="36" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B117" s="30" t="s">
-        <v>262</v>
+      <c r="B117" s="27" t="s">
+        <v>140</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
+      </c>
+      <c r="D117" s="27" t="s">
+        <v>243</v>
       </c>
       <c r="G117" s="36" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5767,27 +6056,33 @@
         <v>95</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>146</v>
+        <v>143</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>433</v>
       </c>
       <c r="G118" s="36" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B119" s="27" t="s">
-        <v>147</v>
+      <c r="B119" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>434</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5795,13 +6090,16 @@
         <v>95</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
+      </c>
+      <c r="D120" s="27" t="s">
+        <v>435</v>
       </c>
       <c r="G120" s="36" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5809,13 +6107,13 @@
         <v>95</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G121" s="36" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5823,13 +6121,16 @@
         <v>95</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>436</v>
       </c>
       <c r="G122" s="36" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5837,13 +6138,16 @@
         <v>95</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="D123" s="27" t="s">
+        <v>437</v>
       </c>
       <c r="G123" s="36" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5851,13 +6155,16 @@
         <v>95</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>158</v>
+        <v>154</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="G124" s="36" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -5865,13 +6172,16 @@
         <v>95</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
+      </c>
+      <c r="D125" s="27" t="s">
+        <v>439</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5879,27 +6189,33 @@
         <v>95</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="D126" s="27" t="s">
+        <v>440</v>
       </c>
       <c r="G126" s="36" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B127" s="26" t="s">
-        <v>272</v>
+      <c r="B127" s="27" t="s">
+        <v>159</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="D127" s="27" t="s">
+        <v>441</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -5907,27 +6223,33 @@
         <v>95</v>
       </c>
       <c r="B128" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D128" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="G128" s="36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B129" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C128" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="G128" s="36" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
-      <c r="A129" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B129" s="27" t="s">
-        <v>165</v>
-      </c>
       <c r="C129" s="16" t="s">
-        <v>166</v>
+        <v>163</v>
+      </c>
+      <c r="D129" s="27" t="s">
+        <v>443</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -5935,477 +6257,679 @@
         <v>95</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>167</v>
+        <v>268</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>168</v>
+        <v>164</v>
+      </c>
+      <c r="D130" s="27" t="s">
+        <v>444</v>
       </c>
       <c r="G130" s="36" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="16" t="s">
-        <v>35</v>
+      <c r="A131" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>124</v>
+        <v>165</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D131" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="G131" s="36" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>308</v>
+        <v>167</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D132" s="27" t="s">
+        <v>446</v>
       </c>
       <c r="G132" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="H132" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" s="42" customFormat="1" ht="26">
-      <c r="A133" s="27" t="s">
-        <v>95</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
+      <c r="A133" s="16" t="s">
+        <v>35</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>436</v>
-      </c>
-      <c r="C133" s="30" t="s">
-        <v>437</v>
-      </c>
-      <c r="G133" s="36"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>186</v>
+        <v>91</v>
+      </c>
+      <c r="B134" s="27" t="s">
+        <v>306</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="F134" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="N134" s="26" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14" s="25" customFormat="1">
-      <c r="A135" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="D134" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="G134" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="H134" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" s="42" customFormat="1" ht="26">
+      <c r="A135" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C135" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="E135" s="29"/>
+      <c r="B135" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="C135" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="D135" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="F136" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="N136" s="26" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" s="25" customFormat="1">
+      <c r="A137" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B137" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="D137" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="E137" s="29"/>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="A138" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B136" s="16" t="s">
+      <c r="B138" s="16" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14" s="28" customFormat="1">
-      <c r="A137" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B137" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="E137" s="29"/>
-      <c r="G137" s="26" t="s">
-        <v>411</v>
-      </c>
-      <c r="H137" s="28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14" s="28" customFormat="1">
-      <c r="A138" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B138" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C138" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E138" s="29"/>
-      <c r="F138" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="N138" s="26" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="139" spans="1:14" s="28" customFormat="1">
       <c r="A139" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>199</v>
+        <v>91</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>307</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>311</v>
+        <v>447</v>
+      </c>
+      <c r="D139" s="27" t="s">
+        <v>448</v>
       </c>
       <c r="E139" s="29"/>
+      <c r="G139" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="H139" s="28" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="140" spans="1:14" s="28" customFormat="1">
       <c r="A140" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B140" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C140" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="D140" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="E140" s="29"/>
+      <c r="F140" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="N140" s="26" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" s="28" customFormat="1">
+      <c r="A141" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B141" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C141" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="D141" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="E141" s="29"/>
+    </row>
+    <row r="142" spans="1:14" s="28" customFormat="1">
+      <c r="A142" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B140" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="E140" s="29"/>
-    </row>
-    <row r="141" spans="1:14">
-      <c r="A141" s="16" t="s">
+      <c r="B142" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E142" s="29"/>
+    </row>
+    <row r="143" spans="1:14" s="45" customFormat="1">
+      <c r="A143" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="C143" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="D143" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="G143" s="26" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" s="45" customFormat="1">
+      <c r="A144" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C144" s="26" t="s">
+        <v>452</v>
+      </c>
+      <c r="D144" s="27" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" s="49" customFormat="1">
+      <c r="A145" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="G145" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="M145" s="49" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" s="49" customFormat="1">
+      <c r="A146" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B146" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="C146" s="49" t="s">
+        <v>473</v>
+      </c>
+      <c r="D146" s="49" t="s">
+        <v>507</v>
+      </c>
+      <c r="G146" s="49" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" s="49" customFormat="1">
+      <c r="A147" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" s="49" t="s">
+        <v>475</v>
+      </c>
+      <c r="G147" s="49" t="s">
+        <v>476</v>
+      </c>
+      <c r="M147" s="49" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" s="49" customFormat="1">
+      <c r="A148" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" s="49" t="s">
+        <v>478</v>
+      </c>
+      <c r="C148" s="49" t="s">
+        <v>479</v>
+      </c>
+      <c r="D148" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G148" s="49" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" s="49" customFormat="1">
+      <c r="A149" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" s="49" t="s">
+        <v>480</v>
+      </c>
+      <c r="G149" s="49" t="s">
+        <v>481</v>
+      </c>
+      <c r="M149" s="49" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" s="49" customFormat="1">
+      <c r="A150" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B150" s="49" t="s">
+        <v>483</v>
+      </c>
+      <c r="C150" s="49" t="s">
+        <v>484</v>
+      </c>
+      <c r="D150" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G150" s="49" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" s="49" customFormat="1">
+      <c r="A151" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B151" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="G151" s="49" t="s">
+        <v>486</v>
+      </c>
+      <c r="M151" s="49" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" s="49" customFormat="1">
+      <c r="A152" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B152" s="49" t="s">
+        <v>488</v>
+      </c>
+      <c r="C152" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="D152" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G152" s="49" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" s="49" customFormat="1">
+      <c r="A153" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B153" s="49" t="s">
+        <v>490</v>
+      </c>
+      <c r="G153" s="49" t="s">
+        <v>491</v>
+      </c>
+      <c r="M153" s="49" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" s="49" customFormat="1">
+      <c r="A154" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B154" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="C154" s="49" t="s">
+        <v>494</v>
+      </c>
+      <c r="D154" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G154" s="49" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" s="49" customFormat="1">
+      <c r="A155" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" s="49" t="s">
+        <v>495</v>
+      </c>
+      <c r="G155" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="M155" s="49" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" s="49" customFormat="1">
+      <c r="A156" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B156" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C156" s="49" t="s">
+        <v>499</v>
+      </c>
+      <c r="D156" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G156" s="49" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" s="49" customFormat="1">
+      <c r="A157" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="G157" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="M157" s="49" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" s="49" customFormat="1">
+      <c r="A158" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B158" s="49" t="s">
+        <v>503</v>
+      </c>
+      <c r="C158" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="D158" s="49" t="s">
+        <v>474</v>
+      </c>
+      <c r="G158" s="49" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" s="45" customFormat="1">
+      <c r="A159" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B159" s="45" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13">
+      <c r="A160" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B141" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="G141" s="26" t="s">
+      <c r="B160" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C160" t="s">
+        <v>203</v>
+      </c>
+      <c r="D160" t="s">
+        <v>466</v>
+      </c>
+      <c r="H160" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27" s="37" customFormat="1" ht="26">
+      <c r="A161" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B161" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="C161" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="D161" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="E161" s="30"/>
+      <c r="G161" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="H161" s="30"/>
+      <c r="I161" s="30"/>
+      <c r="J161" s="30"/>
+      <c r="K161" s="30"/>
+      <c r="L161" s="30"/>
+      <c r="M161" s="30"/>
+      <c r="N161" s="30"/>
+      <c r="O161" s="30"/>
+      <c r="P161" s="30"/>
+      <c r="Q161" s="30"/>
+      <c r="R161" s="30"/>
+      <c r="S161" s="30"/>
+      <c r="T161" s="30"/>
+      <c r="U161" s="30"/>
+      <c r="V161" s="30"/>
+      <c r="W161" s="30"/>
+      <c r="X161" s="30"/>
+      <c r="Y161" s="30"/>
+      <c r="Z161" s="30"/>
+    </row>
+    <row r="162" spans="1:27" s="37" customFormat="1" ht="39">
+      <c r="A162" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B162" s="30" t="s">
+        <v>405</v>
+      </c>
+      <c r="C162" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="D162" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E162" s="30"/>
+      <c r="G162" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="H162" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="I162" s="30"/>
+      <c r="J162" s="30"/>
+      <c r="K162" s="30"/>
+      <c r="L162" s="30"/>
+      <c r="M162" s="30"/>
+      <c r="N162" s="30"/>
+      <c r="O162" s="30"/>
+      <c r="P162" s="30"/>
+      <c r="Q162" s="30"/>
+      <c r="R162" s="30"/>
+      <c r="S162" s="30"/>
+      <c r="T162" s="30"/>
+      <c r="U162" s="30"/>
+      <c r="V162" s="30"/>
+      <c r="W162" s="30"/>
+      <c r="X162" s="30"/>
+      <c r="Y162" s="30"/>
+      <c r="Z162" s="30"/>
+    </row>
+    <row r="163" spans="1:27" s="37" customFormat="1" ht="85.5">
+      <c r="A163" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B163" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="C163" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="D163" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="H141" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
-      <c r="A142" s="16" t="s">
+      <c r="E163" s="30"/>
+      <c r="G163" s="41" t="s">
+        <v>413</v>
+      </c>
+      <c r="H163" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="I163" s="30"/>
+      <c r="J163" s="30"/>
+      <c r="K163" s="30"/>
+      <c r="L163" s="30"/>
+      <c r="M163" s="30"/>
+      <c r="N163" s="30"/>
+      <c r="O163" s="30"/>
+      <c r="P163" s="30"/>
+      <c r="Q163" s="30"/>
+      <c r="R163" s="30"/>
+      <c r="S163" s="30"/>
+      <c r="T163" s="30"/>
+      <c r="U163" s="30"/>
+      <c r="V163" s="30"/>
+      <c r="W163" s="30"/>
+      <c r="X163" s="30"/>
+      <c r="Y163" s="30"/>
+      <c r="Z163" s="30"/>
+    </row>
+    <row r="164" spans="1:27">
+      <c r="A164" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B164" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C164" t="s">
+        <v>205</v>
+      </c>
+      <c r="D164" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27">
+      <c r="A165" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B165" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C142" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" s="37" customFormat="1">
-      <c r="A143" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B143" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="E143" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" s="37" customFormat="1">
-      <c r="A144" s="16" t="s">
+    </row>
+    <row r="166" spans="1:27" s="37" customFormat="1" ht="31" customHeight="1">
+      <c r="A166" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B144" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="M144" s="37" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="145" spans="1:27" s="37" customFormat="1">
-      <c r="A145" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B145" s="16" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="146" spans="1:27" s="37" customFormat="1">
-      <c r="A146" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B146" s="16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="147" spans="1:27" s="37" customFormat="1">
-      <c r="A147" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B147" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="E147" s="26">
-        <v>2</v>
-      </c>
-      <c r="H147" s="37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="148" spans="1:27" s="37" customFormat="1">
-      <c r="A148" s="27" t="s">
+      <c r="B166" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="C166" s="30"/>
+      <c r="D166" s="30"/>
+      <c r="E166" s="30"/>
+      <c r="F166" s="30"/>
+      <c r="G166" s="30"/>
+      <c r="H166" s="30"/>
+      <c r="I166" s="30"/>
+      <c r="J166" s="30"/>
+      <c r="K166" s="30"/>
+      <c r="M166" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="N166" s="30"/>
+      <c r="O166" s="30"/>
+      <c r="P166" s="30"/>
+      <c r="Q166" s="30"/>
+      <c r="R166" s="30"/>
+      <c r="S166" s="30"/>
+      <c r="T166" s="30"/>
+      <c r="U166" s="30"/>
+      <c r="V166" s="30"/>
+      <c r="W166" s="30"/>
+      <c r="X166" s="30"/>
+      <c r="Y166" s="30"/>
+      <c r="Z166" s="30"/>
+      <c r="AA166" s="30"/>
+    </row>
+    <row r="167" spans="1:27" s="38" customFormat="1">
+      <c r="A167" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B148" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="M148" s="26" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="149" spans="1:27" s="37" customFormat="1">
-      <c r="A149" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B149" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="C149" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="M149" s="26"/>
-    </row>
-    <row r="150" spans="1:27" s="37" customFormat="1">
-      <c r="A150" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="151" spans="1:27" s="37" customFormat="1">
-      <c r="A151" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B151" s="16" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="152" spans="1:27" s="37" customFormat="1">
-      <c r="A152" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B152" s="16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="153" spans="1:27">
-      <c r="A153" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B153" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C153" t="s">
-        <v>205</v>
-      </c>
-      <c r="H153" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="154" spans="1:27" s="37" customFormat="1" ht="26">
-      <c r="A154" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B154" s="30" t="s">
+      <c r="B167" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="M167" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="C154" s="30" t="s">
+    </row>
+    <row r="168" spans="1:27" s="38" customFormat="1">
+      <c r="A168" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B168" s="18" t="s">
         <v>416</v>
       </c>
-      <c r="D154" s="32" t="s">
+      <c r="M168" s="18" t="s">
         <v>417</v>
       </c>
-      <c r="E154" s="30"/>
-      <c r="G154" s="30" t="s">
+    </row>
+    <row r="169" spans="1:27" s="38" customFormat="1">
+      <c r="A169" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B169" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="H154" s="30"/>
-      <c r="I154" s="30"/>
-      <c r="J154" s="30"/>
-      <c r="K154" s="30"/>
-      <c r="L154" s="30"/>
-      <c r="M154" s="30"/>
-      <c r="N154" s="30"/>
-      <c r="O154" s="30"/>
-      <c r="P154" s="30"/>
-      <c r="Q154" s="30"/>
-      <c r="R154" s="30"/>
-      <c r="S154" s="30"/>
-      <c r="T154" s="30"/>
-      <c r="U154" s="30"/>
-      <c r="V154" s="30"/>
-      <c r="W154" s="30"/>
-      <c r="X154" s="30"/>
-      <c r="Y154" s="30"/>
-      <c r="Z154" s="30"/>
-    </row>
-    <row r="155" spans="1:27" s="37" customFormat="1" ht="39">
-      <c r="A155" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B155" s="30" t="s">
+      <c r="M169" s="18" t="s">
         <v>419</v>
-      </c>
-      <c r="C155" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="D155" s="39" t="s">
-        <v>421</v>
-      </c>
-      <c r="E155" s="30"/>
-      <c r="G155" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="H155" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="I155" s="30"/>
-      <c r="J155" s="30"/>
-      <c r="K155" s="30"/>
-      <c r="L155" s="30"/>
-      <c r="M155" s="30"/>
-      <c r="N155" s="30"/>
-      <c r="O155" s="30"/>
-      <c r="P155" s="30"/>
-      <c r="Q155" s="30"/>
-      <c r="R155" s="30"/>
-      <c r="S155" s="30"/>
-      <c r="T155" s="30"/>
-      <c r="U155" s="30"/>
-      <c r="V155" s="30"/>
-      <c r="W155" s="30"/>
-      <c r="X155" s="30"/>
-      <c r="Y155" s="30"/>
-      <c r="Z155" s="30"/>
-    </row>
-    <row r="156" spans="1:27" s="37" customFormat="1" ht="85.5">
-      <c r="A156" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B156" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="C156" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="D156" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="E156" s="30"/>
-      <c r="G156" s="41" t="s">
-        <v>427</v>
-      </c>
-      <c r="H156" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="I156" s="30"/>
-      <c r="J156" s="30"/>
-      <c r="K156" s="30"/>
-      <c r="L156" s="30"/>
-      <c r="M156" s="30"/>
-      <c r="N156" s="30"/>
-      <c r="O156" s="30"/>
-      <c r="P156" s="30"/>
-      <c r="Q156" s="30"/>
-      <c r="R156" s="30"/>
-      <c r="S156" s="30"/>
-      <c r="T156" s="30"/>
-      <c r="U156" s="30"/>
-      <c r="V156" s="30"/>
-      <c r="W156" s="30"/>
-      <c r="X156" s="30"/>
-      <c r="Y156" s="30"/>
-      <c r="Z156" s="30"/>
-    </row>
-    <row r="157" spans="1:27">
-      <c r="A157" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B157" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C157" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="158" spans="1:27">
-      <c r="A158" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B158" s="16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="159" spans="1:27" s="37" customFormat="1" ht="31" customHeight="1">
-      <c r="A159" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B159" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="C159" s="30"/>
-      <c r="D159" s="30"/>
-      <c r="E159" s="30"/>
-      <c r="F159" s="30"/>
-      <c r="G159" s="30"/>
-      <c r="H159" s="30"/>
-      <c r="I159" s="30"/>
-      <c r="J159" s="30"/>
-      <c r="K159" s="30"/>
-      <c r="M159" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="N159" s="30"/>
-      <c r="O159" s="30"/>
-      <c r="P159" s="30"/>
-      <c r="Q159" s="30"/>
-      <c r="R159" s="30"/>
-      <c r="S159" s="30"/>
-      <c r="T159" s="30"/>
-      <c r="U159" s="30"/>
-      <c r="V159" s="30"/>
-      <c r="W159" s="30"/>
-      <c r="X159" s="30"/>
-      <c r="Y159" s="30"/>
-      <c r="Z159" s="30"/>
-      <c r="AA159" s="30"/>
-    </row>
-    <row r="160" spans="1:27" s="38" customFormat="1">
-      <c r="A160" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B160" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="M160" s="18" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" s="38" customFormat="1">
-      <c r="A161" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B161" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="M161" s="18" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" s="38" customFormat="1">
-      <c r="A162" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B162" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="M162" s="18" t="s">
-        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6427,6 +6951,7 @@
   <cols>
     <col min="1" max="1" width="17.04296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -6472,12 +6997,14 @@
         <v>122</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="30"/>
+      <c r="D2" s="26" t="s">
+        <v>424</v>
+      </c>
       <c r="E2" s="30"/>
       <c r="F2" s="30"/>
       <c r="G2" s="30"/>
@@ -6506,12 +7033,14 @@
         <v>122</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="26" t="s">
+        <v>425</v>
+      </c>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -6540,12 +7069,14 @@
         <v>122</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="30"/>
+      <c r="D4" s="26" t="s">
+        <v>426</v>
+      </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -6574,12 +7105,14 @@
         <v>122</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="D5" s="30"/>
+      <c r="D5" s="26" t="s">
+        <v>427</v>
+      </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -6613,7 +7146,9 @@
       <c r="C6" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="30"/>
+      <c r="D6" s="27" t="s">
+        <v>467</v>
+      </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
@@ -6642,12 +7177,14 @@
         <v>122</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="D7" s="30"/>
+      <c r="D7" s="26" t="s">
+        <v>429</v>
+      </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
@@ -6681,7 +7218,9 @@
       <c r="C8" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="30"/>
+      <c r="D8" s="27" t="s">
+        <v>430</v>
+      </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
       <c r="G8" s="30"/>
@@ -6715,7 +7254,9 @@
       <c r="C9" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="30"/>
+      <c r="D9" s="27" t="s">
+        <v>431</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
@@ -6749,7 +7290,9 @@
       <c r="C10" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="30"/>
+      <c r="D10" s="27" t="s">
+        <v>432</v>
+      </c>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="30"/>
@@ -6783,7 +7326,9 @@
       <c r="C11" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="30"/>
+      <c r="D11" s="27" t="s">
+        <v>243</v>
+      </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
@@ -6817,7 +7362,9 @@
       <c r="C12" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="30"/>
+      <c r="D12" s="27" t="s">
+        <v>433</v>
+      </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
@@ -6846,12 +7393,14 @@
         <v>122</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="30"/>
+      <c r="D13" s="27" t="s">
+        <v>434</v>
+      </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
@@ -6885,7 +7434,9 @@
       <c r="C14" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="30"/>
+      <c r="D14" s="27" t="s">
+        <v>435</v>
+      </c>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
@@ -6919,7 +7470,7 @@
       <c r="C15" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="30"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="30"/>
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
@@ -6953,7 +7504,9 @@
       <c r="C16" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="30"/>
+      <c r="D16" s="27" t="s">
+        <v>436</v>
+      </c>
       <c r="E16" s="30"/>
       <c r="F16" s="30"/>
       <c r="G16" s="30"/>
@@ -6987,7 +7540,9 @@
       <c r="C17" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="D17" s="30"/>
+      <c r="D17" s="27" t="s">
+        <v>437</v>
+      </c>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>
       <c r="G17" s="30"/>
@@ -7021,7 +7576,9 @@
       <c r="C18" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="30"/>
+      <c r="D18" s="27" t="s">
+        <v>438</v>
+      </c>
       <c r="E18" s="30"/>
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
@@ -7055,7 +7612,9 @@
       <c r="C19" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="D19" s="30"/>
+      <c r="D19" s="27" t="s">
+        <v>439</v>
+      </c>
       <c r="E19" s="30"/>
       <c r="F19" s="30"/>
       <c r="G19" s="30"/>
@@ -7089,7 +7648,9 @@
       <c r="C20" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="30"/>
+      <c r="D20" s="27" t="s">
+        <v>440</v>
+      </c>
       <c r="E20" s="30"/>
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
@@ -7123,7 +7684,9 @@
       <c r="C21" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="30"/>
+      <c r="D21" s="27" t="s">
+        <v>441</v>
+      </c>
       <c r="E21" s="30"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -7152,12 +7715,14 @@
         <v>122</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="27" t="s">
+        <v>442</v>
+      </c>
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
@@ -7186,12 +7751,14 @@
         <v>122</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="27" t="s">
+        <v>443</v>
+      </c>
       <c r="E23" s="30"/>
       <c r="F23" s="30"/>
       <c r="G23" s="30"/>
@@ -7220,12 +7787,14 @@
         <v>122</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C24" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="27" t="s">
+        <v>444</v>
+      </c>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="30"/>
@@ -7259,7 +7828,9 @@
       <c r="C25" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="27" t="s">
+        <v>445</v>
+      </c>
       <c r="E25" s="30"/>
       <c r="F25" s="30"/>
       <c r="G25" s="30"/>
@@ -7288,12 +7859,14 @@
         <v>122</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="30"/>
+      <c r="D26" s="27" t="s">
+        <v>446</v>
+      </c>
       <c r="E26" s="30"/>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
@@ -7327,6 +7900,9 @@
       <c r="C27" s="16" t="s">
         <v>188</v>
       </c>
+      <c r="D27" s="27" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="16" t="s">
@@ -7338,6 +7914,9 @@
       <c r="C28" s="16" t="s">
         <v>190</v>
       </c>
+      <c r="D28" s="27" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="16" t="s">
@@ -7347,7 +7926,10 @@
         <v>191</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>191</v>
+        <v>462</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
@@ -7360,6 +7942,9 @@
       <c r="C30" s="16" t="s">
         <v>193</v>
       </c>
+      <c r="D30" s="27" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="16" t="s">
@@ -7371,6 +7956,9 @@
       <c r="C31" s="16" t="s">
         <v>194</v>
       </c>
+      <c r="D31" s="27" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="16" t="s">
@@ -7382,47 +7970,50 @@
       <c r="C32" s="16" t="s">
         <v>197</v>
       </c>
+      <c r="D32" s="27" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="27" t="s">
         <v>256</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="13">
       <c r="A34" s="27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B34" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="D34" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="C34" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="26">
+    </row>
+    <row r="35" spans="1:26" ht="13">
       <c r="A35" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="C35" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="B35" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>345</v>
-      </c>
       <c r="D35" s="32" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="E35" s="30"/>
       <c r="F35" s="30"/>
@@ -7449,16 +8040,16 @@
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
@@ -7485,16 +8076,16 @@
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
@@ -7521,16 +8112,16 @@
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E38" s="30"/>
       <c r="F38" s="30"/>
@@ -7557,16 +8148,16 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="30"/>
@@ -7593,16 +8184,16 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
@@ -7629,16 +8220,16 @@
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="30"/>
@@ -7665,16 +8256,16 @@
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="E42" s="30"/>
       <c r="F42" s="30"/>
@@ -7701,16 +8292,16 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E43" s="30"/>
       <c r="F43" s="30"/>
@@ -7737,16 +8328,16 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
@@ -7773,16 +8364,16 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -7809,16 +8400,16 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
@@ -7845,16 +8436,16 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
@@ -7881,16 +8472,16 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="499">
   <si>
     <t>type</t>
   </si>
@@ -1149,82 +1149,40 @@
     <t>mitigation_note_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you understand the importance of Facility Delivery </t>
-  </si>
-  <si>
-    <t>Je unaelewa umuhimu wa Kujifungulia kituo cha afya</t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”facility_delivery“)</t>
   </si>
   <si>
     <t>mitigation_note_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you understand the importance of ANC Visits </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unaelewa umuhimu wa Kuhudhuria kliniki wakati wa ujauzito </t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”anc_visits“)</t>
   </si>
   <si>
     <t>mitigation_note_3</t>
   </si>
   <si>
-    <t>Do you understand the importance of Rest</t>
-  </si>
-  <si>
-    <t>Je unaelewa umuhimu wa Kupumzika</t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”rest“)</t>
   </si>
   <si>
     <t>mitigation_note_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you understand the importance of Balanced Diet/Good Nutrition Practices </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unaelewa umuhimu wa Kula vyakula vyenye virutubisho </t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”balanced_diet“)</t>
   </si>
   <si>
     <t>mitigation_note_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you understand the importance of No heavy work </t>
-  </si>
-  <si>
-    <t>Je unaelewa umuhimu wa Kutokufanya kazi ngumu</t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”no_heavy_work “)</t>
   </si>
   <si>
     <t>mitigation_note_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you understand the importance of Family Planning </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unaelewa umuhimu wa Kutumia uzazi wa mpango </t>
-  </si>
-  <si>
     <t>contains(${mitigation_list},”family_planning“)</t>
   </si>
   <si>
     <t>mitigation_note_7</t>
-  </si>
-  <si>
-    <t>Do you understand the importance of Risks of using herbs</t>
-  </si>
-  <si>
-    <t>Je unaelewa umuhimu wa Hatari za kutumia dawa za mitishamba</t>
   </si>
   <si>
     <t>contains(${mitigation_list},”local_herbs_risks“)</t>
@@ -1574,13 +1532,58 @@
   </si>
   <si>
     <t>Milalo mibaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of Facility Delivery ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of ANC Visits ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of Rest ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of Balanced Diet/Good Nutrition Practices  ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of No heavy work  ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of Family Planning  ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you understand the importance of Risks of using herbs ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kujifungulia kituo cha afya ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kuhudhuria kliniki wakati wa ujauzito  ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kupumzika ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kula vyakula vyenye virutubisho  ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kutokufanya kazi ngumu ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Kutumia uzazi wa mpango ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unaelewa umuhimu wa Hatari za kutumia dawa za mitishamba ? </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1649,6 +1652,12 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1697,7 +1706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1753,6 +1762,7 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5921,7 +5931,7 @@
         <v>290</v>
       </c>
       <c r="D120" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="G120" s="21" t="s">
         <v>291</v>
@@ -6272,7 +6282,7 @@
         <v>337</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>355</v>
@@ -6285,15 +6295,15 @@
       <c r="B143" t="s">
         <v>356</v>
       </c>
-      <c r="C143" t="s">
-        <v>357</v>
-      </c>
-      <c r="D143" t="s">
-        <v>358</v>
+      <c r="C143" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="D143" s="29" t="s">
+        <v>492</v>
       </c>
       <c r="E143"/>
       <c r="G143" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -6301,17 +6311,17 @@
         <v>116</v>
       </c>
       <c r="B144" t="s">
-        <v>360</v>
-      </c>
-      <c r="C144" t="s">
-        <v>361</v>
-      </c>
-      <c r="D144" t="s">
-        <v>362</v>
+        <v>358</v>
+      </c>
+      <c r="C144" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="D144" s="29" t="s">
+        <v>493</v>
       </c>
       <c r="E144"/>
       <c r="G144" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145" spans="1:27">
@@ -6319,17 +6329,17 @@
         <v>116</v>
       </c>
       <c r="B145" t="s">
-        <v>364</v>
-      </c>
-      <c r="C145" t="s">
-        <v>365</v>
-      </c>
-      <c r="D145" t="s">
-        <v>366</v>
+        <v>360</v>
+      </c>
+      <c r="C145" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="D145" s="29" t="s">
+        <v>494</v>
       </c>
       <c r="E145"/>
       <c r="G145" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="146" spans="1:27">
@@ -6337,17 +6347,17 @@
         <v>116</v>
       </c>
       <c r="B146" t="s">
-        <v>368</v>
-      </c>
-      <c r="C146" t="s">
-        <v>369</v>
-      </c>
-      <c r="D146" t="s">
-        <v>370</v>
+        <v>362</v>
+      </c>
+      <c r="C146" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="D146" s="29" t="s">
+        <v>495</v>
       </c>
       <c r="E146"/>
       <c r="G146" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="147" spans="1:27">
@@ -6355,17 +6365,17 @@
         <v>116</v>
       </c>
       <c r="B147" t="s">
-        <v>372</v>
-      </c>
-      <c r="C147" t="s">
-        <v>373</v>
-      </c>
-      <c r="D147" t="s">
-        <v>374</v>
+        <v>364</v>
+      </c>
+      <c r="C147" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="D147" s="29" t="s">
+        <v>496</v>
       </c>
       <c r="E147"/>
       <c r="G147" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:27">
@@ -6373,17 +6383,17 @@
         <v>116</v>
       </c>
       <c r="B148" t="s">
-        <v>376</v>
-      </c>
-      <c r="C148" t="s">
-        <v>377</v>
-      </c>
-      <c r="D148" t="s">
-        <v>378</v>
+        <v>366</v>
+      </c>
+      <c r="C148" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="D148" s="29" t="s">
+        <v>497</v>
       </c>
       <c r="E148"/>
       <c r="G148" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:27">
@@ -6391,17 +6401,17 @@
         <v>116</v>
       </c>
       <c r="B149" t="s">
-        <v>380</v>
-      </c>
-      <c r="C149" t="s">
-        <v>381</v>
-      </c>
-      <c r="D149" t="s">
-        <v>382</v>
+        <v>368</v>
+      </c>
+      <c r="C149" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="D149" s="29" t="s">
+        <v>498</v>
       </c>
       <c r="E149"/>
       <c r="G149" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:27" s="2" customFormat="1">
@@ -6418,13 +6428,13 @@
         <v>112</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C151" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D151" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="H151" t="s">
         <v>237</v>
@@ -6436,17 +6446,17 @@
         <v>116</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="E152" s="13"/>
       <c r="G152" s="13" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="H152" s="13"/>
       <c r="I152" s="13"/>
@@ -6473,20 +6483,20 @@
         <v>116</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="D153" s="23" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="E153" s="13"/>
       <c r="G153" s="14" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="I153" s="13"/>
       <c r="J153" s="13"/>
@@ -6512,20 +6522,20 @@
         <v>116</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="E154" s="13"/>
       <c r="G154" s="24" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="I154" s="13"/>
       <c r="J154" s="13"/>
@@ -6551,13 +6561,13 @@
         <v>116</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C155" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:27">
@@ -6565,7 +6575,7 @@
         <v>120</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="K156" s="13"/>
     </row>
@@ -6574,7 +6584,7 @@
         <v>46</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C157" s="13"/>
       <c r="D157" s="13"/>
@@ -6585,7 +6595,7 @@
       <c r="I157" s="13"/>
       <c r="J157" s="13"/>
       <c r="M157" s="13" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="N157" s="13"/>
       <c r="O157" s="13"/>
@@ -6607,10 +6617,10 @@
         <v>46</v>
       </c>
       <c r="B158" s="22" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="M158" s="22" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
     </row>
     <row r="159" spans="1:27" s="2" customFormat="1">
@@ -6618,10 +6628,10 @@
         <v>46</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="M159" s="22" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
     </row>
     <row r="160" spans="1:27" s="2" customFormat="1">
@@ -6629,11 +6639,11 @@
         <v>46</v>
       </c>
       <c r="B160" s="22" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="K160"/>
       <c r="M160" s="22" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -6659,7 +6669,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>1</v>
@@ -6700,7 +6710,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>239</v>
@@ -6850,7 +6860,7 @@
         <v>255</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
@@ -7174,7 +7184,7 @@
         <v>290</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
@@ -7420,7 +7430,7 @@
         <v>230</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>317</v>
@@ -7564,7 +7574,7 @@
         <v>230</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>333</v>
@@ -7597,128 +7607,128 @@
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>153</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="5" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="1:26">
@@ -7726,13 +7736,13 @@
         <v>195</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
@@ -7762,13 +7772,13 @@
         <v>195</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
@@ -7798,13 +7808,13 @@
         <v>195</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
@@ -7834,13 +7844,13 @@
         <v>195</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
@@ -7870,13 +7880,13 @@
         <v>195</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -7906,13 +7916,13 @@
         <v>195</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -7942,13 +7952,13 @@
         <v>195</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -7978,13 +7988,13 @@
         <v>195</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
@@ -8014,13 +8024,13 @@
         <v>195</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
@@ -8050,13 +8060,13 @@
         <v>195</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
@@ -8086,13 +8096,13 @@
         <v>195</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
@@ -8122,13 +8132,13 @@
         <v>195</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="13"/>
@@ -8158,13 +8168,13 @@
         <v>195</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
@@ -8194,13 +8204,13 @@
         <v>195</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
@@ -8243,22 +8253,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -8283,19 +8293,19 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="2"/>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,342 +26,342 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="508">
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relevant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">read_only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repeat_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::image::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::image::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">begin group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO_LABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due_date_human_readable</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="509">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>due_date</t>
+  </si>
+  <si>
+    <t>due_date_human_readable</t>
   </si>
   <si>
     <t xml:space="preserve">string </t>
   </si>
   <si>
-    <t xml:space="preserve">client_EDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visit_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_high_risk_pregnancy_ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_EDD_human_readable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facility_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db:person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db-object</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/contact/name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/enabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_pregnancy_visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/n_pregnancy_visits,'')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_previous_anc_visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/n_previous_anc_visits,'')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_hiv_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/previous_hiv_status,'false')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_rchcard_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/previous_rchcard_status,"false")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">show_research_questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/show_research_questions,"false")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patient_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/contact/_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">created_by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/user/name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">created_by_person_uuid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/user/contact_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">created_by_place_uuid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/user/facility_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_birth_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/contact/date_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int(decimal-date-time(now())-decimal-date-time(${date_of_birth_c}))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int(${age_days} div (30 *12),0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_in_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">round((decimal-date-time(today()) - decimal-date-time(${date_of_birth_c})) div 365,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_days_display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household_head</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/household_head</t>
-  </si>
-  <si>
-    <t xml:space="preserve">house_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/house_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kitongoji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/kitongoji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/due_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due_date_pretty_print_english</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Unknown")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due_date_pretty_print_swahili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Haijulikani")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_EDD_pretty_print_english</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Unknown")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_EDD_pretty_print_swahili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Haijulikani")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_EDD_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/client_EDD</t>
+    <t>client_EDD</t>
+  </si>
+  <si>
+    <t>visit_id</t>
+  </si>
+  <si>
+    <t>is_high_risk_pregnancy_ML</t>
+  </si>
+  <si>
+    <t>client_EDD_human_readable</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>db:person</t>
+  </si>
+  <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>db-object</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>../inputs/contact/name</t>
+  </si>
+  <si>
+    <t>enabel</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/enabel</t>
+  </si>
+  <si>
+    <t>n_pregnancy_visits</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/n_pregnancy_visits,'')</t>
+  </si>
+  <si>
+    <t>n_previous_anc_visits</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/n_previous_anc_visits,'')</t>
+  </si>
+  <si>
+    <t>previous_hiv_status</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/previous_hiv_status,'false')</t>
+  </si>
+  <si>
+    <t>previous_rchcard_status</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/previous_rchcard_status,"false")</t>
+  </si>
+  <si>
+    <t>show_research_questions</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/show_research_questions,"false")</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>../inputs/user/name</t>
+  </si>
+  <si>
+    <t>created_by_person_uuid</t>
+  </si>
+  <si>
+    <t>../inputs/user/contact_id</t>
+  </si>
+  <si>
+    <t>created_by_place_uuid</t>
+  </si>
+  <si>
+    <t>../inputs/user/facility_id</t>
+  </si>
+  <si>
+    <t>date_of_birth_c</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t>age_days</t>
+  </si>
+  <si>
+    <t>int(decimal-date-time(now())-decimal-date-time(${date_of_birth_c}))</t>
+  </si>
+  <si>
+    <t>age_months</t>
+  </si>
+  <si>
+    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
+  </si>
+  <si>
+    <t>age_years</t>
+  </si>
+  <si>
+    <t>int(${age_days} div (30 *12),0)</t>
+  </si>
+  <si>
+    <t>age_in_years</t>
+  </si>
+  <si>
+    <t>round((decimal-date-time(today()) - decimal-date-time(${date_of_birth_c})) div 365,0)</t>
+  </si>
+  <si>
+    <t>age_days_display</t>
+  </si>
+  <si>
+    <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>household_head</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/household_head</t>
+  </si>
+  <si>
+    <t>house_number</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/house_number</t>
+  </si>
+  <si>
+    <t>kitongoji</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/kitongoji</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/phone</t>
+  </si>
+  <si>
+    <t>../inputs/due_date</t>
+  </si>
+  <si>
+    <t>due_date_pretty_print_english</t>
+  </si>
+  <si>
+    <t>if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Unknown")</t>
+  </si>
+  <si>
+    <t>due_date_pretty_print_swahili</t>
+  </si>
+  <si>
+    <t>if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Haijulikani")</t>
+  </si>
+  <si>
+    <t>client_EDD_pretty_print_english</t>
+  </si>
+  <si>
+    <t>if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Unknown")</t>
+  </si>
+  <si>
+    <t>client_EDD_pretty_print_swahili</t>
+  </si>
+  <si>
+    <t>if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Haijulikani")</t>
+  </si>
+  <si>
+    <t>client_EDD_c</t>
+  </si>
+  <si>
+    <t>../inputs/client_EDD</t>
   </si>
   <si>
     <t xml:space="preserve">currently_pregnant </t>
   </si>
   <si>
-    <t xml:space="preserve">instance('contact-summary')/context/currently_pregnant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide_lmp_or_months_pregnant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/hide_lmp_or_months_pregnant,"false")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(../inputs/visit_id != "", ../inputs/visit_id, "pregnancy_consent_visit")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
+    <t>instance('contact-summary')/context/currently_pregnant</t>
+  </si>
+  <si>
+    <t>hide_lmp_or_months_pregnant</t>
+  </si>
+  <si>
+    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/hide_lmp_or_months_pregnant,"false")</t>
+  </si>
+  <si>
+    <t>if(../inputs/visit_id != "", ../inputs/visit_id, "pregnancy_consent_visit")</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
   </si>
   <si>
     <t xml:space="preserve">begin group </t>
   </si>
   <si>
-    <t xml:space="preserve">covid19_intro</t>
+    <t>covid19_intro</t>
   </si>
   <si>
     <t xml:space="preserve">Precautionary measures when visiting a client  </t>
   </si>
   <si>
-    <t xml:space="preserve">Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">covid19_intro_note</t>
+    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>covid19_intro_note</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
@@ -387,70 +391,70 @@
     <t xml:space="preserve">end group </t>
   </si>
   <si>
-    <t xml:space="preserve">gestation_in_weeks_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“true”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_high_risk_pregnancy_ML_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/is_high_risk_pregnancy_ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high_risk_manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/high_risk_manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk_factor_names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/mitigation_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk_factor_labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk_factor_labels_swahili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_labels_swahili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_information</t>
+    <t>gestation_in_weeks_c</t>
+  </si>
+  <si>
+    <t>“true”</t>
+  </si>
+  <si>
+    <t>is_high_risk_pregnancy_ML_c</t>
+  </si>
+  <si>
+    <t>../inputs/is_high_risk_pregnancy_ML</t>
+  </si>
+  <si>
+    <t>high_risk_manual</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/high_risk_manual</t>
+  </si>
+  <si>
+    <t>risk_factor_names</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/risk_factor_names</t>
+  </si>
+  <si>
+    <t>mitigation_list</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/mitigation_list</t>
+  </si>
+  <si>
+    <t>risk_factor_labels</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/risk_factor_labels</t>
+  </si>
+  <si>
+    <t>risk_factor_labels_swahili</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/risk_factor_labels_swahili</t>
+  </si>
+  <si>
+    <t>client_information</t>
   </si>
   <si>
     <t xml:space="preserve">Client Information </t>
   </si>
   <si>
-    <t xml:space="preserve">Taarifa za mteja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intro_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visit type: &lt;span style="font-weight:bold"&gt;Pregnancy Counselling&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Ujauzito&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household_note</t>
+    <t>Taarifa za mteja</t>
+  </si>
+  <si>
+    <t>field-list</t>
+  </si>
+  <si>
+    <t>intro_note</t>
+  </si>
+  <si>
+    <t>Visit type: &lt;span style="font-weight:bold"&gt;Pregnancy Counselling&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Ujauzito&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>household_note</t>
   </si>
   <si>
     <t xml:space="preserve">Name: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
@@ -461,35 +465,35 @@
 IPO futa: &lt;span style="font-weight:bold"&gt;${is_high_risk_pregnancy_ML_c}&lt;/span&gt; </t>
   </si>
   <si>
-    <t xml:space="preserve">Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
+    <t>Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
 Umri: &lt;span style=""font-weight:bold""&gt;miaka ${age_years}&lt;/span&gt;
 Mtu wa karibu kwa mawasiliano: &lt;span style=""font-weight:bold""&gt;${household_head}&lt;/span&gt; 
 Namba ya nyumba: &lt;span style=""font-weight:bold""&gt;${house_number}&lt;/span&gt;
 Kitongoji: &lt;span style=""font-weight:bold""&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">phone_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due_date_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_english}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_swahili}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intro_message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">During the enrolment we talked about pregnancy risk factors. I want to make sure that you are aware of these factors and know what to do to lower your risk if you identify any. Therefore, I will visit you every two weeks, in addition to the regular pregnancy visits, to make sure you continue in good health and have a safe pregnancy all the way through delivery.</t>
+    <t>phone_note</t>
+  </si>
+  <si>
+    <t>Phone: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>due_date_note</t>
+  </si>
+  <si>
+    <t>Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_english}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_swahili}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>intro_message</t>
+  </si>
+  <si>
+    <t>During the enrolment we talked about pregnancy risk factors. I want to make sure that you are aware of these factors and know what to do to lower your risk if you identify any. Therefore, I will visit you every two weeks, in addition to the regular pregnancy visits, to make sure you continue in good health and have a safe pregnancy all the way through delivery.</t>
   </si>
   <si>
     <t xml:space="preserve">Wakati wa usajili, tulizungumza kuhusu sababu za hatari za ujauzito. Nataka nihakikishe kwamba unazijua sababu hizo ili kuwe na uwezekano mdogo sana wa kuja kuzipata.  Kwahiyo, nitakuja kukutembela kila baada ya wiki mbili ili kuhakikisha unaendelea vizuri na mimba yako hadi utakapojifungua. </t>
@@ -498,148 +502,148 @@
     <t xml:space="preserve">intro_message </t>
   </si>
   <si>
-    <t xml:space="preserve">danger_signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pregnancy Danger Signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalili Hatari Kwa Mama Wajawazito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_intro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Now I will ask you some questions about pregnancy danger signs. Have you experienced any of these symptoms?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahivi naomba kukuliza maswali yanayohusiana na dalili za hatari kwa ujauzito. Je una dalizi za hatari kati ya hizi zifuatazo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_table_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_vaginal_bleeding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaginal Bleeding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unatokwa na damu ukeni?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_abdominal_pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severe abdoninal pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una maumivu makali ya tumbo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_severe_headache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severe Headache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una maumivu makali ya kichwa ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fever and being too weak to get out of bed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una homa au umedhoofika ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_note_to_chv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">observe_danger_signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f;font-weight: bold"&gt;OBSERVE: &lt;/span&gt;&lt;span style="color:#f58a1f"&gt; if the client has the following pregnancy danger signs.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f;font-weight: bold"&gt;ANGALIA: &lt;/span&gt; &lt;span style="color:#f58a1f"&gt;kama mteja ana dalili za hatari kwa wajawazito hizi zifuatazo.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_table_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_unconsciouss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unconsciousness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupoteza fahamu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_difficult_breathing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast or difficult breathing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupumua kwa haraka au ugumu katika kupumua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danger_sign_convulsions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convulsions/fits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kifafa cha mimba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emergency_danger_sign_referral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(selected(${danger_sign_vaginal_bleeding},"yes") or selected(${danger_sign_convulsions},"yes") or selected(${danger_sign_unconsciouss},"yes") or selected(${danger_sign_severe_headache},"yes") or selected(${danger_sign_fever},"yes") or selected(${danger_sign_abdominal_pain},"yes") or selected(${danger_sign_difficult_breathing},"yes"),1,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emergency_danger_sign_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;This woman is experiencing or has experienced an emergency danger sign. Urge the woman and her family to get the woman medical help as the lives of the mother and her baby are potentially in danger.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Mwanamke huyu anadalili za hatari au aliwahi kupata dalili za hatari za ghafla. Mtake Mama na familia yake kupata msaada wa kimatibabu kwasababu maisha ya mama na mtoto wake yapo katika hatari.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral} = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_danger_sign_note_to_chv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No emergency referral condition was identified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwa sasa, hauna dalili yoyote ya hatari iliyogundulika. Lakini ukipata dalili yote kati ya hizi tulizozijadili, tafadhali nenda kituo cha afya haraka iwezakanavyo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${danger_sign_convulsions},'no') and 
+    <t>danger_signs</t>
+  </si>
+  <si>
+    <t>Pregnancy Danger Signs</t>
+  </si>
+  <si>
+    <t>Dalili Hatari Kwa Mama Wajawazito</t>
+  </si>
+  <si>
+    <t>danger_sign_intro</t>
+  </si>
+  <si>
+    <t>Now I will ask you some questions about pregnancy danger signs. Have you experienced any of these symptoms?</t>
+  </si>
+  <si>
+    <t>Sahivi naomba kukuliza maswali yanayohusiana na dalili za hatari kwa ujauzito. Je una dalizi za hatari kati ya hizi zifuatazo?</t>
+  </si>
+  <si>
+    <t>danger_sign_table_1</t>
+  </si>
+  <si>
+    <t>table-list</t>
+  </si>
+  <si>
+    <t>select_one yes_no</t>
+  </si>
+  <si>
+    <t>danger_sign_vaginal_bleeding</t>
+  </si>
+  <si>
+    <t>Vaginal Bleeding</t>
+  </si>
+  <si>
+    <t>Unatokwa na damu ukeni?</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>danger_sign_abdominal_pain</t>
+  </si>
+  <si>
+    <t>Severe abdoninal pain</t>
+  </si>
+  <si>
+    <t>Una maumivu makali ya tumbo?</t>
+  </si>
+  <si>
+    <t>danger_sign_severe_headache</t>
+  </si>
+  <si>
+    <t>Severe Headache</t>
+  </si>
+  <si>
+    <t>Una maumivu makali ya kichwa ?</t>
+  </si>
+  <si>
+    <t>danger_sign_fever</t>
+  </si>
+  <si>
+    <t>Fever and being too weak to get out of bed</t>
+  </si>
+  <si>
+    <t>Una homa au umedhoofika ?</t>
+  </si>
+  <si>
+    <t>danger_sign_note_to_chv</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>observe_danger_signs</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;OBSERVE: &lt;/span&gt;&lt;span style="color:#f58a1f"&gt; if the client has the following pregnancy danger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;ANGALIA: &lt;/span&gt; &lt;span style="color:#f58a1f"&gt;kama mteja ana dalili za hatari kwa wajawazito hizi zifuatazo.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>danger_sign_table_2</t>
+  </si>
+  <si>
+    <t>danger_sign_unconsciouss</t>
+  </si>
+  <si>
+    <t>Unconsciousness</t>
+  </si>
+  <si>
+    <t>Kupoteza fahamu</t>
+  </si>
+  <si>
+    <t>danger_sign_difficult_breathing</t>
+  </si>
+  <si>
+    <t>Fast or difficult breathing</t>
+  </si>
+  <si>
+    <t>Kupumua kwa haraka au ugumu katika kupumua</t>
+  </si>
+  <si>
+    <t>danger_sign_convulsions</t>
+  </si>
+  <si>
+    <t>Convulsions/fits</t>
+  </si>
+  <si>
+    <t>Kifafa cha mimba</t>
+  </si>
+  <si>
+    <t>emergency_danger_sign_referral</t>
+  </si>
+  <si>
+    <t>if(selected(${danger_sign_vaginal_bleeding},"yes") or selected(${danger_sign_convulsions},"yes") or selected(${danger_sign_unconsciouss},"yes") or selected(${danger_sign_severe_headache},"yes") or selected(${danger_sign_fever},"yes") or selected(${danger_sign_abdominal_pain},"yes") or selected(${danger_sign_difficult_breathing},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>emergency_danger_sign_note</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;This woman is experiencing or has experienced an emergency danger sign. Urge the woman and her family to get the woman medical help as the lives of the mother and her baby are potentially in danger.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Mwanamke huyu anadalili za hatari au aliwahi kupata dalili za hatari za ghafla. Mtake Mama na familia yake kupata msaada wa kimatibabu kwasababu maisha ya mama na mtoto wake yapo katika hatari.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 1</t>
+  </si>
+  <si>
+    <t>no_danger_sign_note_to_chv</t>
+  </si>
+  <si>
+    <t>No emergency referral condition was identified.</t>
+  </si>
+  <si>
+    <t>Kwa sasa, hauna dalili yoyote ya hatari iliyogundulika. Lakini ukipata dalili yote kati ya hizi tulizozijadili, tafadhali nenda kituo cha afya haraka iwezakanavyo.</t>
+  </si>
+  <si>
+    <t>selected(${danger_sign_convulsions},'no') and 
 selected(${danger_sign_unconsciouss},'no') and 
 selected(${danger_sign_severe_headache},'no') and 
 selected(${danger_sign_fever},'no') and 
@@ -648,29 +652,29 @@
 selected(${danger_sign_vaginal_bleeding},'no')</t>
   </si>
   <si>
-    <t xml:space="preserve">pregnancy_issues_group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pregnancy Issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maswala ya ujauzito</t>
+    <t>pregnancy_issues_group</t>
+  </si>
+  <si>
+    <t>Pregnancy Issues</t>
+  </si>
+  <si>
+    <t>Maswala ya ujauzito</t>
   </si>
   <si>
     <t xml:space="preserve"> ${emergency_danger_sign_referral} = 0 
  </t>
   </si>
   <si>
-    <t xml:space="preserve">subgroup_pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_multiple pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continue with the following questions. Indicate if the client has any of the following common pregnancy issues. 
+    <t>subgroup_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>select_multiple pregnancy_issues</t>
+  </si>
+  <si>
+    <t>pregnancy_issues</t>
+  </si>
+  <si>
+    <t>Continue with the following questions. Indicate if the client has any of the following common pregnancy issues. 
 Have you experienced:</t>
   </si>
   <si>
@@ -678,22 +682,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannot select "None" with other options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(selected(${pregnancy_issues},"difficulty_breathing") or 
+    <t>${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
+  </si>
+  <si>
+    <t>Cannot select "None" with other options</t>
+  </si>
+  <si>
+    <t>Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
+  </si>
+  <si>
+    <t>refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>if(selected(${pregnancy_issues},"difficulty_breathing") or 
 selected(${pregnancy_issues},"fatigue") or 
 selected(${pregnancy_issues},"fever") or 
 selected(${pregnancy_issues},"tinrisk_factor_namess") or 
@@ -708,73 +712,73 @@
 selected(${pregnancy_issues},"foul_smelling")1,0)</t>
   </si>
   <si>
-    <t xml:space="preserve">refer_pregnancy_issues_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am referring you to a health facility because I have identified that you have danger sign(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakupa rufaa uende kituo cha afya kwasababu nimekugundua una dalili za hatari.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_issues}=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pregnancy_and_pallor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baby_moving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you feel the baby moving on a daily basis, at least every six hours?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unahisi mtoto anacheza angalau kila baada ya masaa sita kila siku?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${gestation_in_weeks_c} &gt; 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">covid19_plam_pallor_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Now you are at the stage of comparing your palm with the client’s palm. Before doing this, please keep a 2 meters distance from your client as a precautionary measure to avoid the spread of Corona virus. Please ask your client to show you their palm while still keeping the distance. &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Sasa upo kwenye hatua ya kulinganisha kiganja chako na cha mteja wako. Kabla ya kufanya hivyo, tafadhali hakikisha umekaa umbali wa mita mbili na mteja wako ili kujilinda na uwezekano wa kusambaza maambukizi ya Korona. Tafadhali mwambie mteja akuoneshe kiganja chake. &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pallor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does the client have pallor? Compare your palm with client's palm. If client's palms are paler than yours, this is pallor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linganisha kiganja chako na cha mteja. Ikiwa kiganja cha mteja kimepauka sana kuliko chako hili ni tatizo. Iniashiria upungufu wa damu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_pregnancy_complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(selected(${baby_moving},"no") or selected(${pallor},"yes"),1,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_pregnancy_complication_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_pregnancy_complication_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on our conversation, I did not identify any health issues, but if you develop any of the signs we discussed today, you should go to a health facility immediately</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huna dalili yoyote ya hatari lakini ikitokea ukapatwa na moja ya dalili tulizozijadili unapaswa kwenda kituo cha afya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=0 and ${refer_pregnancy_issues}=0 and
+    <t>refer_pregnancy_issues_note</t>
+  </si>
+  <si>
+    <t>I am referring you to a health facility because I have identified that you have danger sign(s)</t>
+  </si>
+  <si>
+    <t>Nakupa rufaa uende kituo cha afya kwasababu nimekugundua una dalili za hatari.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_issues}=1</t>
+  </si>
+  <si>
+    <t>pregnancy_and_pallor</t>
+  </si>
+  <si>
+    <t>baby_moving</t>
+  </si>
+  <si>
+    <t>Do you feel the baby moving on a daily basis, at least every six hours?</t>
+  </si>
+  <si>
+    <t>Je unahisi mtoto anacheza angalau kila baada ya masaa sita kila siku?</t>
+  </si>
+  <si>
+    <t>${gestation_in_weeks_c} &gt; 24</t>
+  </si>
+  <si>
+    <t>covid19_plam_pallor_note</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Now you are at the stage of comparing your palm with the client’s palm. Before doing this, please keep a 2 meters distance from your client as a precautionary measure to avoid the spread of Corona virus. Please ask your client to show you their palm while still keeping the distance. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Sasa upo kwenye hatua ya kulinganisha kiganja chako na cha mteja wako. Kabla ya kufanya hivyo, tafadhali hakikisha umekaa umbali wa mita mbili na mteja wako ili kujilinda na uwezekano wa kusambaza maambukizi ya Korona. Tafadhali mwambie mteja akuoneshe kiganja chake. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>pallor</t>
+  </si>
+  <si>
+    <t>Does the client have pallor? Compare your palm with client's palm. If client's palms are paler than yours, this is pallor.</t>
+  </si>
+  <si>
+    <t>Linganisha kiganja chako na cha mteja. Ikiwa kiganja cha mteja kimepauka sana kuliko chako hili ni tatizo. Iniashiria upungufu wa damu.</t>
+  </si>
+  <si>
+    <t>refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>if(selected(${baby_moving},"no") or selected(${pallor},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>has_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=1</t>
+  </si>
+  <si>
+    <t>no_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t>Based on our conversation, I did not identify any health issues, but if you develop any of the signs we discussed today, you should go to a health facility immediately</t>
+  </si>
+  <si>
+    <t>Huna dalili yoyote ya hatari lakini ikitokea ukapatwa na moja ya dalili tulizozijadili unapaswa kwenda kituo cha afya.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=0 and ${refer_pregnancy_issues}=0 and
 selected(${baby_moving},"yes") and selected(${pallor},"no")</t>
   </si>
   <si>
@@ -784,13 +788,13 @@
     <t xml:space="preserve">fiel-list </t>
   </si>
   <si>
-    <t xml:space="preserve">select_multiple risk_factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk_factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which pregnancy risk factors do you remember?</t>
+    <t>select_multiple risk_factors</t>
+  </si>
+  <si>
+    <t>risk_factors</t>
+  </si>
+  <si>
+    <t>Which pregnancy risk factors do you remember?</t>
   </si>
   <si>
     <t xml:space="preserve">Je unakumbuka sababu zipi za hatari za ujauzito? </t>
@@ -802,13 +806,13 @@
     <t xml:space="preserve">Cannot select "None" with other options </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${risk_factor_names}, name) or name = 'none'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short_explanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${high_risk_manual}  = "true"  and ${emergency_danger_sign_referral} = 0</t>
+    <t>contains(${risk_factor_names}, name) or name = 'none'</t>
+  </si>
+  <si>
+    <t>short_explanation</t>
+  </si>
+  <si>
+    <t>${high_risk_manual}  = "true"  and ${emergency_danger_sign_referral} = 0</t>
   </si>
   <si>
     <t xml:space="preserve">field-list </t>
@@ -817,301 +821,301 @@
     <t xml:space="preserve">previous_pregnancies </t>
   </si>
   <si>
-    <t xml:space="preserve">More than 5 previous pregnancies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupata mimba zaidi ya mara 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'previous_pregnancies')) and contains(${risk_factor_names}, 'previous_pregnancies')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_delivery_by_c_section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarean section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kujifungua kwa kupasuliwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'previous_delivery_by_c_section')) and contains(${risk_factor_names}, 'previous_delivery_by_c_section')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_delivery_by_vacuum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery by vacuum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kujifungua kwa kusaidiwa kuvutwa na mashine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'previous_delivery_by_vacuum')) and contains(${risk_factor_names}, 'previous_delivery_by_vacuum')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_stillbirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stillbirth</t>
+    <t>More than 5 previous pregnancies</t>
+  </si>
+  <si>
+    <t>Kupata mimba zaidi ya mara 5</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'previous_pregnancies')) and contains(${risk_factor_names}, 'previous_pregnancies')</t>
+  </si>
+  <si>
+    <t>previous_delivery_by_c_section</t>
+  </si>
+  <si>
+    <t>Caesarean section</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa kupasuliwa</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'previous_delivery_by_c_section')) and contains(${risk_factor_names}, 'previous_delivery_by_c_section')</t>
+  </si>
+  <si>
+    <t>previous_delivery_by_vacuum</t>
+  </si>
+  <si>
+    <t>Delivery by vacuum</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa kusaidiwa kuvutwa na mashine</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'previous_delivery_by_vacuum')) and contains(${risk_factor_names}, 'previous_delivery_by_vacuum')</t>
+  </si>
+  <si>
+    <t>previous_stillbirth</t>
+  </si>
+  <si>
+    <t>Stillbirth</t>
   </si>
   <si>
     <t xml:space="preserve">Kupoteza mtoto wakati wa kujifungua </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'previous_stillbirth')) and contains(${risk_factor_names}, 'previous_stillbirth')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolonged_labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prolonged labor (12 hours or more)</t>
+    <t>not(selected(${risk_factors},'previous_stillbirth')) and contains(${risk_factor_names}, 'previous_stillbirth')</t>
+  </si>
+  <si>
+    <t>prolonged_labor</t>
+  </si>
+  <si>
+    <t>Prolonged labor (12 hours or more)</t>
   </si>
   <si>
     <t xml:space="preserve"> Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'prolonged_labor')) and contains(${risk_factor_names}, 'prolonged_labor')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">large_perineal_tear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large perineal tear (close to anus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuchanika njia ya uzazi(karibia ya njia ya choo kikubwa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'large_perineal_tear')) and contains(${risk_factor_names}, 'large_perineal_tear')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retained_placenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retained placenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kondo la nyuma kukataa kutoka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'retained_placenta')) and contains(${risk_factor_names}, 'retained_placenta')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APH</t>
+    <t>not(selected(${risk_factors},'prolonged_labor')) and contains(${risk_factor_names}, 'prolonged_labor')</t>
+  </si>
+  <si>
+    <t>large_perineal_tear</t>
+  </si>
+  <si>
+    <t>Large perineal tear (close to anus)</t>
+  </si>
+  <si>
+    <t>Kuchanika njia ya uzazi(karibia ya njia ya choo kikubwa)</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'large_perineal_tear')) and contains(${risk_factor_names}, 'large_perineal_tear')</t>
+  </si>
+  <si>
+    <t>retained_placenta</t>
+  </si>
+  <si>
+    <t>Retained placenta</t>
+  </si>
+  <si>
+    <t>Kondo la nyuma kukataa kutoka</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'retained_placenta')) and contains(${risk_factor_names}, 'retained_placenta')</t>
+  </si>
+  <si>
+    <t>aph</t>
+  </si>
+  <si>
+    <t>APH</t>
   </si>
   <si>
     <t xml:space="preserve">Kutokwa na damu nyingi kabla ya kujifungua </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'aph')) and contains(${risk_factor_names}, 'aph')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">postpartum_hemorrage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postpartum hemorrhage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kutokwa damu nyingi baada ya kujifungua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'postpartum_hemorrage')) and contains(${risk_factor_names}, 'postpartum_hemorrage')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enclampsia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eclampsia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'enclampsia')) and contains(${risk_factor_names}, 'enclampsia')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">big_baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big baby in previous or current (more than 4 kg)</t>
+    <t>not(selected(${risk_factors},'aph')) and contains(${risk_factor_names}, 'aph')</t>
+  </si>
+  <si>
+    <t>postpartum_hemorrage</t>
+  </si>
+  <si>
+    <t>Postpartum hemorrhage</t>
+  </si>
+  <si>
+    <t>Kutokwa damu nyingi baada ya kujifungua</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'postpartum_hemorrage')) and contains(${risk_factor_names}, 'postpartum_hemorrage')</t>
+  </si>
+  <si>
+    <t>enclampsia</t>
+  </si>
+  <si>
+    <t>Eclampsia</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'enclampsia')) and contains(${risk_factor_names}, 'enclampsia')</t>
+  </si>
+  <si>
+    <t>big_baby</t>
+  </si>
+  <si>
+    <t>Big baby in previous or current (more than 4 kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Kujifungua mtoto mkubwa ( zaidi ya kilo 4) (mimba hii au kabla) </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'big_baby')) and contains(${risk_factor_names}, 'big_baby')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_miscarriages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miscarriage/abortion</t>
+    <t>not(selected(${risk_factors},'big_baby')) and contains(${risk_factor_names}, 'big_baby')</t>
+  </si>
+  <si>
+    <t>previous_miscarriages</t>
+  </si>
+  <si>
+    <t>Miscarriage/abortion</t>
   </si>
   <si>
     <t xml:space="preserve">Mimba kuharibika </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'previous_miscarriages')) and contains(${risk_factor_names}, 'previous_miscarriages')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">multiple_pregnancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple pregnancy</t>
+    <t>not(selected(${risk_factors},'previous_miscarriages')) and contains(${risk_factor_names}, 'previous_miscarriages')</t>
+  </si>
+  <si>
+    <t>multiple_pregnancy</t>
+  </si>
+  <si>
+    <t>Multiple pregnancy</t>
   </si>
   <si>
     <t xml:space="preserve">Kutarajia kuwa na mapacha </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'multiple_pregnancy')) and contains(${risk_factor_names}, 'multiple_pregnancy')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malpresentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malpresentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milalo mibaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'malpresentation')) and contains(${risk_factor_names}, 'malpresentation')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breech_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breech position</t>
+    <t>not(selected(${risk_factors},'multiple_pregnancy')) and contains(${risk_factor_names}, 'multiple_pregnancy')</t>
+  </si>
+  <si>
+    <t>malpresentation</t>
+  </si>
+  <si>
+    <t>Malpresentation</t>
+  </si>
+  <si>
+    <t>Milalo mibaya</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'malpresentation')) and contains(${risk_factor_names}, 'malpresentation')</t>
+  </si>
+  <si>
+    <t>breech_position</t>
+  </si>
+  <si>
+    <t>Breech position</t>
   </si>
   <si>
     <t xml:space="preserve">Mtoto kutanguliza makalio </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'breech_position')) and contains(${risk_factor_names}, 'breech_position')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high_blood_pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High blood pressure</t>
+    <t>not(selected(${risk_factors},'breech_position')) and contains(${risk_factor_names}, 'breech_position')</t>
+  </si>
+  <si>
+    <t>high_blood_pressure</t>
+  </si>
+  <si>
+    <t>High blood pressure</t>
   </si>
   <si>
     <t xml:space="preserve">Shinikizo la damu </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'high_blood_pressure')) and contains(${risk_factor_names}, 'high_blood_pressure')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diabetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diabetes</t>
+    <t>not(selected(${risk_factors},'high_blood_pressure')) and contains(${risk_factor_names}, 'high_blood_pressure')</t>
+  </si>
+  <si>
+    <t>diabetes</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Kisukari </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'diabetes')) and contains(${risk_factor_names}, 'diabetes')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sicke_cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sickle cell</t>
+    <t>not(selected(${risk_factors},'diabetes')) and contains(${risk_factor_names}, 'diabetes')</t>
+  </si>
+  <si>
+    <t>sicke_cell</t>
+  </si>
+  <si>
+    <t>Sickle cell</t>
   </si>
   <si>
     <t xml:space="preserve">Seli mundu </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'sicke_cell')) and contains(${risk_factor_names}, 'sicke_cell')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardiac_disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardiac disease</t>
+    <t>not(selected(${risk_factors},'sicke_cell')) and contains(${risk_factor_names}, 'sicke_cell')</t>
+  </si>
+  <si>
+    <t>cardiac_disease</t>
+  </si>
+  <si>
+    <t>Cardiac disease</t>
   </si>
   <si>
     <t xml:space="preserve">Maradhi ya moyo </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'cardiac_disease')) and contains(${risk_factor_names}, 'cardiac_disease')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anemia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anemia [received tablets, or didn’t receive because out of stock/too expensive/don’t know]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upungufu wa damu mwilini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'anemia')) and contains(${risk_factor_names}, 'anemia')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">higher_level_facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advise to deliver at higher-level facility</t>
+    <t>not(selected(${risk_factors},'cardiac_disease')) and contains(${risk_factor_names}, 'cardiac_disease')</t>
+  </si>
+  <si>
+    <t>anemia</t>
+  </si>
+  <si>
+    <t>Anemia [received tablets, or didn’t receive because out of stock/too expensive/don’t know]</t>
+  </si>
+  <si>
+    <t>Upungufu wa damu mwilini</t>
+  </si>
+  <si>
+    <t>not(selected(${risk_factors},'anemia')) and contains(${risk_factor_names}, 'anemia')</t>
+  </si>
+  <si>
+    <t>higher_level_facility</t>
+  </si>
+  <si>
+    <t>Advise to deliver at higher-level facility</t>
   </si>
   <si>
     <t xml:space="preserve">Kushauriwa kujifungua katika kituo cha afya kikubwa </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'higher_level_facility')) and contains(${risk_factor_names}, 'higher_level_facility')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allow_partner_to_deliver_facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner permission not given</t>
+    <t>not(selected(${risk_factors},'higher_level_facility')) and contains(${risk_factor_names}, 'higher_level_facility')</t>
+  </si>
+  <si>
+    <t>allow_partner_to_deliver_facility</t>
+  </si>
+  <si>
+    <t>Partner permission not given</t>
   </si>
   <si>
     <t xml:space="preserve">Mwenwa hajatoa ruhusa ya kujifungua kituo cha afya </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'allow_partner_to_deliver_facility')) and contains(${risk_factor_names}, 'allow_partner_to_deliver_facility')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ten_or_more_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last pregnancy 10 or more years ago</t>
+    <t>not(selected(${risk_factors},'allow_partner_to_deliver_facility')) and contains(${risk_factor_names}, 'allow_partner_to_deliver_facility')</t>
+  </si>
+  <si>
+    <t>ten_or_more_years</t>
+  </si>
+  <si>
+    <t>Last pregnancy 10 or more years ago</t>
   </si>
   <si>
     <t xml:space="preserve">Mimba iliyopita ilikuwa miaka kumi ilopita au zaidi </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'ten_or_more_years')) and contains(${risk_factor_names}, 'ten_or_more_years')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">local_herbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use of local herbs</t>
+    <t>not(selected(${risk_factors},'ten_or_more_years')) and contains(${risk_factor_names}, 'ten_or_more_years')</t>
+  </si>
+  <si>
+    <t>local_herbs</t>
+  </si>
+  <si>
+    <t>Use of local herbs</t>
   </si>
   <si>
     <t xml:space="preserve">Kutumia dawa za mitishamba </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'local_herbs')) and contains(${risk_factor_names}, 'local_herbs')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follows nutrition restrictions</t>
+    <t>not(selected(${risk_factors},'local_herbs')) and contains(${risk_factor_names}, 'local_herbs')</t>
+  </si>
+  <si>
+    <t>nutrition</t>
+  </si>
+  <si>
+    <t>Follows nutrition restrictions</t>
   </si>
   <si>
     <t xml:space="preserve">Kuepuka kula baadhi ya vyakula </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'nutrition')) and contains(${risk_factor_names}, 'nutrition')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_strategy</t>
+    <t>not(selected(${risk_factors},'nutrition')) and contains(${risk_factor_names}, 'nutrition')</t>
+  </si>
+  <si>
+    <t>mitigation_strategy</t>
   </si>
   <si>
     <t xml:space="preserve">Mitigation Strategy </t>
@@ -1120,36 +1124,36 @@
     <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito </t>
   </si>
   <si>
-    <t xml:space="preserve">risk_factor_list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
+    <t>risk_factor_list</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
 [${risk_factor_labels}]</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;strong&gt;Ukizingatia sababu zifuatazo za hatari za ujauzito:&lt;/strong&gt;
+    <t>&lt;strong&gt;Ukizingatia sababu zifuatazo za hatari za ujauzito:&lt;/strong&gt;
 [${risk_factor_labels_swahili}]</t>
   </si>
   <si>
-    <t xml:space="preserve">select_multiple mitigation_strategies</t>
+    <t>select_multiple mitigation_strategies</t>
   </si>
   <si>
     <t xml:space="preserve">mitigation_strategies </t>
   </si>
   <si>
-    <t xml:space="preserve">What can you do to continue in good health and have a safe pregnancy all the way through delivery?</t>
+    <t>What can you do to continue in good health and have a safe pregnancy all the way through delivery?</t>
   </si>
   <si>
     <t xml:space="preserve">Unaweza kufanya mambo gani ili uweze kuendelea na mimba yako vizuri hadi utakapojifungua? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list}, name) or name = 'none'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_strategy_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery</t>
+    <t>contains(${mitigation_list}, name) or name = 'none'</t>
+  </si>
+  <si>
+    <t>mitigation_strategy_note</t>
+  </si>
+  <si>
+    <t>I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Sasa, nitakufahamisha mambo ambayo yatakuwezesha kuendelea na mimba yako vizuri hadi utakapojifungua. </t>
@@ -1158,25 +1162,25 @@
     <t xml:space="preserve">mitigation_strategy </t>
   </si>
   <si>
-    <t xml:space="preserve">mitigation_strategy_ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true" and ${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_qn</t>
+    <t>mitigation_strategy_ml</t>
+  </si>
+  <si>
+    <t>${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true" and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery.</t>
+  </si>
+  <si>
+    <t>mitigation_qn</t>
   </si>
   <si>
     <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito ? </t>
   </si>
   <si>
-    <t xml:space="preserve">(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_1</t>
+    <t>(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t>mitigation_note_1</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Facility Delivery ? </t>
@@ -1185,10 +1189,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kujifungulia kituo cha afya ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”facility_delivery“)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_2</t>
+    <t>contains(${mitigation_list},”facility_delivery“)</t>
+  </si>
+  <si>
+    <t>mitigation_note_2</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of ANC Visits ? </t>
@@ -1197,10 +1201,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kuhudhuria kliniki wakati wa ujauzito  ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”anc_visits“)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_3</t>
+    <t>contains(${mitigation_list},”anc_visits“)</t>
+  </si>
+  <si>
+    <t>mitigation_note_3</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Rest ? </t>
@@ -1209,10 +1213,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kupumzika ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”rest“)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_4</t>
+    <t>contains(${mitigation_list},”rest“)</t>
+  </si>
+  <si>
+    <t>mitigation_note_4</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Balanced Diet/Good Nutrition Practices  ? </t>
@@ -1221,10 +1225,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kula vyakula vyenye virutubisho  ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”balanced_diet“)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_5</t>
+    <t>contains(${mitigation_list},”balanced_diet“)</t>
+  </si>
+  <si>
+    <t>mitigation_note_5</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of No heavy work  ? </t>
@@ -1233,10 +1237,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kutokufanya kazi ngumu ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”no_heavy_work “)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_6</t>
+    <t>contains(${mitigation_list},”no_heavy_work “)</t>
+  </si>
+  <si>
+    <t>mitigation_note_6</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Family Planning  ? </t>
@@ -1245,10 +1249,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kutumia uzazi wa mpango ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”family_planning“)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_note_7</t>
+    <t>contains(${mitigation_list},”family_planning“)</t>
+  </si>
+  <si>
+    <t>mitigation_note_7</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Risks of using herbs ? </t>
@@ -1257,7 +1261,7 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Hatari za kutumia dawa za mitishamba ? </t>
   </si>
   <si>
-    <t xml:space="preserve">contains(${mitigation_list},”local_herbs_risks“)</t>
+    <t>contains(${mitigation_list},”local_herbs_risks“)</t>
   </si>
   <si>
     <t xml:space="preserve">visit_summary </t>
@@ -1269,47 +1273,47 @@
     <t xml:space="preserve">Muhtasari wa tembeleo </t>
   </si>
   <si>
-    <t xml:space="preserve">needs_referral_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You need to go to the health facility for the following reasons:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${has_referral}=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">needs_referral_danger_signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To address emergency pregnancy danger signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ili kushughulikia dalili za hatari za dharura za mama mjamzito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${emergency_danger_sign_referral}=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">li</t>
-  </si>
-  <si>
-    <t xml:space="preserve">needs_referral_neonatal_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To address other pregnancy danger signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ili kushughulikia dalili nyengine za hatari.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${refer_pregnancy_issues}=1 or 
+    <t>needs_referral_note</t>
+  </si>
+  <si>
+    <t>You need to go to the health facility for the following reasons:</t>
+  </si>
+  <si>
+    <t>Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
+  </si>
+  <si>
+    <t>${has_referral}=1</t>
+  </si>
+  <si>
+    <t>needs_referral_danger_signs</t>
+  </si>
+  <si>
+    <t>To address emergency pregnancy danger signs</t>
+  </si>
+  <si>
+    <t>Ili kushughulikia dalili za hatari za dharura za mama mjamzito.</t>
+  </si>
+  <si>
+    <t>${emergency_danger_sign_referral}=1</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>needs_referral_neonatal_note</t>
+  </si>
+  <si>
+    <t>To address other pregnancy danger signs</t>
+  </si>
+  <si>
+    <t>Ili kushughulikia dalili nyengine za hatari.</t>
+  </si>
+  <si>
+    <t>${refer_pregnancy_issues}=1 or 
 ${refer_pregnancy_complications}=1</t>
   </si>
   <si>
-    <t xml:space="preserve">next_visit</t>
+    <t>next_visit</t>
   </si>
   <si>
     <t xml:space="preserve">I will visit you again in two weeks. </t>
@@ -1318,70 +1322,70 @@
     <t xml:space="preserve">Nitakutembelea tena baada ya wiki mbili. </t>
   </si>
   <si>
-    <t xml:space="preserve">has_referral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${emergency_danger_sign_referral}=1 or
+    <t>has_referral</t>
+  </si>
+  <si>
+    <t>if(${emergency_danger_sign_referral}=1 or
 ${refer_pregnancy_issues}=1 or
 ${refer_pregnancy_complications}=1
 1, 0)</t>
   </si>
   <si>
-    <t xml:space="preserve">refer_flag_emergency_danger_sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../danger_signs/emergency_danger_sign_referral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_flag_pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../pregnancy_issues_group/subgroup_pregnancy_issues/refer_pregnancy_issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_flag_pregnancy_complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../pregnancy_issues_group/pregnancy_and_pallor/refer_pregnancy_complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">previous_pregnancies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">higher_facility_delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nutrition_restrictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hakuna mojawapo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mitigation_strategies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facility_delivery</t>
+    <t>refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>../danger_signs/emergency_danger_sign_referral</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>../pregnancy_issues_group/subgroup_pregnancy_issues/refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>../pregnancy_issues_group/pregnancy_and_pallor/refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>previous_pregnancies</t>
+  </si>
+  <si>
+    <t>Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
+  </si>
+  <si>
+    <t>higher_facility_delivery</t>
+  </si>
+  <si>
+    <t>nutrition_restrictions</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Hakuna mojawapo</t>
+  </si>
+  <si>
+    <t>mitigation_strategies</t>
+  </si>
+  <si>
+    <t>facility_delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Facility Delivery </t>
   </si>
   <si>
-    <t xml:space="preserve">Kujifungulia kituo cha afya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anc_visits</t>
+    <t>Kujifungulia kituo cha afya</t>
+  </si>
+  <si>
+    <t>anc_visits</t>
   </si>
   <si>
     <t xml:space="preserve">ANC Visits </t>
@@ -1390,16 +1394,16 @@
     <t xml:space="preserve">Kuhudhuria kliniki wakati wa ujauzito </t>
   </si>
   <si>
-    <t xml:space="preserve">rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupumzika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">balanced_diet</t>
+    <t>rest</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Kupumzika</t>
+  </si>
+  <si>
+    <t>balanced_diet</t>
   </si>
   <si>
     <t xml:space="preserve">Balanced Diet/Good Nutrition Practices </t>
@@ -1414,10 +1418,10 @@
     <t xml:space="preserve">No heavy work </t>
   </si>
   <si>
-    <t xml:space="preserve">Kutokufanya kazi ngumu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">family_planning</t>
+    <t>Kutokufanya kazi ngumu</t>
+  </si>
+  <si>
+    <t>family_planning</t>
   </si>
   <si>
     <t xml:space="preserve">Family Planning </t>
@@ -1426,252 +1430,229 @@
     <t xml:space="preserve">Kutumia uzazi wa mpango </t>
   </si>
   <si>
-    <t xml:space="preserve">local_herb_risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risks of using herbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hatari za kutumia dawa za mitishamba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hapana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">difficulty_breathing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difficulty Breathing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anapumua kwa shida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fatigue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatigue, lethergy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uchovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tinnitus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tinnitus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maskio kulia nyenje/kuvuma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dizziness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dizziness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kizunguzungu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frontal_headache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severe Frontal Headache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kichwa kuuma sana sehemu ya mbele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blurred_vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blurred vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kutokuona vizuri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gastric_pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severe gastric pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maumivu makali ya tumbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swelling of face, arms, fingers, or legs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuvimba uso,mikono, vidole au miguu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">early_labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early labor pain before 9 months gestation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uchungu wa mapema kabla ya miezi tisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liquid_leaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquid leaking from vagina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kutoka maji sehemu za siri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malaria_signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signs of malaria (feeling cold, fever, vomiting)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalili za malaria(kuhisi baridi,homa na kutapika)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foul_smelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foul smelling vaginal discharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kutoa uchafu wenye harufu mbaya sehemu za siri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">futa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
+    <t>local_herb_risks</t>
+  </si>
+  <si>
+    <t>Risks of using herbs</t>
+  </si>
+  <si>
+    <t>Hatari za kutumia dawa za mitishamba</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndio</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>difficulty_breathing</t>
+  </si>
+  <si>
+    <t>Difficulty Breathing</t>
+  </si>
+  <si>
+    <t>Anapumua kwa shida</t>
+  </si>
+  <si>
+    <t>fatigue</t>
+  </si>
+  <si>
+    <t>Fatigue, lethergy</t>
+  </si>
+  <si>
+    <t>Uchovu</t>
+  </si>
+  <si>
+    <t>fever</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>Homa</t>
+  </si>
+  <si>
+    <t>tinnitus</t>
+  </si>
+  <si>
+    <t>Tinnitus</t>
+  </si>
+  <si>
+    <t>Maskio kulia nyenje/kuvuma</t>
+  </si>
+  <si>
+    <t>dizziness</t>
+  </si>
+  <si>
+    <t>Dizziness</t>
+  </si>
+  <si>
+    <t>Kizunguzungu</t>
+  </si>
+  <si>
+    <t>frontal_headache</t>
+  </si>
+  <si>
+    <t>Severe Frontal Headache</t>
+  </si>
+  <si>
+    <t>Kichwa kuuma sana sehemu ya mbele</t>
+  </si>
+  <si>
+    <t>blurred_vision</t>
+  </si>
+  <si>
+    <t>Blurred vision</t>
+  </si>
+  <si>
+    <t>Kutokuona vizuri</t>
+  </si>
+  <si>
+    <t>gastric_pain</t>
+  </si>
+  <si>
+    <t>Severe gastric pain</t>
+  </si>
+  <si>
+    <t>Maumivu makali ya tumbo</t>
+  </si>
+  <si>
+    <t>swelling</t>
+  </si>
+  <si>
+    <t>Swelling of face, arms, fingers, or legs</t>
+  </si>
+  <si>
+    <t>Kuvimba uso,mikono, vidole au miguu</t>
+  </si>
+  <si>
+    <t>early_labor</t>
+  </si>
+  <si>
+    <t>Early labor pain before 9 months gestation</t>
+  </si>
+  <si>
+    <t>Uchungu wa mapema kabla ya miezi tisa</t>
+  </si>
+  <si>
+    <t>liquid_leaking</t>
+  </si>
+  <si>
+    <t>Liquid leaking from vagina</t>
+  </si>
+  <si>
+    <t>Kutoka maji sehemu za siri</t>
+  </si>
+  <si>
+    <t>malaria_signs</t>
+  </si>
+  <si>
+    <t>Signs of malaria (feeling cold, fever, vomiting)</t>
+  </si>
+  <si>
+    <t>Dalili za malaria(kuhisi baridi,homa na kutapika)</t>
+  </si>
+  <si>
+    <t>foul_smelling</t>
+  </si>
+  <si>
+    <t>Foul smelling vaginal discharge</t>
+  </si>
+  <si>
+    <t>kutoa uchafu wenye harufu mbaya sehemu za siri</t>
+  </si>
+  <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>21/12/2020</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamna mojawapo </t>
+  </si>
+  <si>
+    <t>Pregnancy Counselling</t>
+  </si>
+  <si>
+    <t>pregnancy_counselling</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1685,7 +1666,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1699,7 +1679,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1711,7 +1690,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1725,7 +1703,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1750,7 +1727,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1758,177 +1735,79 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1987,30 +1866,304 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1D1C1D"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AMJ164"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="23.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="7" style="0" width="14.41"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1023" style="0" width="11.52"/>
+    <col min="1" max="1" width="30.86328125" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="62.76953125" customWidth="1"/>
+    <col min="4" max="4" width="50.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.40625" customWidth="1"/>
+    <col min="6" max="6" width="23.6328125" customWidth="1"/>
+    <col min="7" max="1022" width="14.40625" customWidth="1"/>
+    <col min="1023" max="1025" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:26" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2069,7 +2222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:26" ht="14.25">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -2081,8 +2234,8 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="3" t="n">
-        <f aca="false">FALSE()</f>
+      <c r="F2" s="3" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="G2" s="1"/>
@@ -2097,7 +2250,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:26" ht="14.25">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2131,7 +2284,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:26" ht="14.25">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
@@ -2165,7 +2318,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:26" ht="14.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
@@ -2190,7 +2343,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:26" ht="14.25">
       <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
@@ -2215,18 +2368,18 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:26" ht="14.25">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:26" ht="14.25">
       <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
@@ -2251,7 +2404,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:26" ht="14.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2276,7 +2429,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:26" ht="14.25">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -2301,7 +2454,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:26" ht="14.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -2326,7 +2479,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:26" ht="14.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2351,7 +2504,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:26" ht="14.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -2374,7 +2527,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:26" ht="14.25">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
@@ -2408,7 +2561,7 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:26" ht="14.25">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
@@ -2444,7 +2597,7 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:26" ht="14.25">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -2478,7 +2631,7 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:26" ht="14.25">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -2512,7 +2665,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:26" ht="14.25">
       <c r="A18" s="4" t="s">
         <v>36</v>
       </c>
@@ -2544,7 +2697,7 @@
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:26" ht="14.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2567,7 +2720,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:26" ht="14.25">
       <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
@@ -2601,7 +2754,7 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:26" ht="14.25">
       <c r="A21" s="4" t="s">
         <v>42</v>
       </c>
@@ -2635,7 +2788,7 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:26" ht="14.25">
       <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
@@ -2669,7 +2822,7 @@
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:26" ht="14.25">
       <c r="A23" s="4" t="s">
         <v>42</v>
       </c>
@@ -2703,7 +2856,7 @@
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:26" ht="14.25">
       <c r="A24" s="4" t="s">
         <v>42</v>
       </c>
@@ -2737,7 +2890,7 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:26" ht="14.25">
       <c r="A25" s="4" t="s">
         <v>42</v>
       </c>
@@ -2771,7 +2924,7 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:26" ht="14.25">
       <c r="A26" s="4" t="s">
         <v>42</v>
       </c>
@@ -2805,7 +2958,7 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:26" ht="14.25">
       <c r="A27" s="4" t="s">
         <v>42</v>
       </c>
@@ -2839,7 +2992,7 @@
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:26" ht="14.25">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
@@ -2866,7 +3019,7 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:26" ht="14.25">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -2893,7 +3046,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:26" ht="14.25">
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
@@ -2920,7 +3073,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:26" ht="14.25">
       <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
@@ -2954,7 +3107,7 @@
       <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:26" ht="14.25">
       <c r="A32" s="4" t="s">
         <v>42</v>
       </c>
@@ -2988,7 +3141,7 @@
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:26" ht="14.25">
       <c r="A33" s="4" t="s">
         <v>42</v>
       </c>
@@ -3022,7 +3175,7 @@
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:26" ht="14.25">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
@@ -3056,7 +3209,7 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:26" ht="14.25">
       <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
@@ -3072,14 +3225,14 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="8" t="s">
+      <c r="L35" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
@@ -3090,7 +3243,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:26" ht="14.25">
       <c r="A36" s="4" t="s">
         <v>42</v>
       </c>
@@ -3124,7 +3277,7 @@
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:26" ht="14.25">
       <c r="A37" s="4" t="s">
         <v>42</v>
       </c>
@@ -3140,7 +3293,7 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="9">
         <v>7</v>
       </c>
       <c r="M37" s="4"/>
@@ -3158,7 +3311,7 @@
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:26" ht="14.25">
       <c r="A38" s="4" t="s">
         <v>42</v>
       </c>
@@ -3174,7 +3327,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="9">
         <v>30</v>
       </c>
       <c r="M38" s="4"/>
@@ -3192,7 +3345,7 @@
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:26" ht="14.25">
       <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
@@ -3226,7 +3379,7 @@
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:26" ht="14.25">
       <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
@@ -3260,7 +3413,7 @@
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:26" ht="14.25">
       <c r="A41" s="5" t="s">
         <v>42</v>
       </c>
@@ -3294,7 +3447,7 @@
       <c r="Y41" s="4"/>
       <c r="Z41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:26" ht="14.25">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -3328,7 +3481,7 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:26" ht="14.25">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
@@ -3362,7 +3515,7 @@
       <c r="Y43" s="4"/>
       <c r="Z43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:26" ht="14.25">
       <c r="A44" s="4" t="s">
         <v>42</v>
       </c>
@@ -3396,7 +3549,7 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:26" ht="14.25">
       <c r="A45" s="4" t="s">
         <v>42</v>
       </c>
@@ -3430,7 +3583,7 @@
       <c r="Y45" s="4"/>
       <c r="Z45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:26" ht="14.25">
       <c r="A46" s="4" t="s">
         <v>42</v>
       </c>
@@ -3464,7 +3617,7 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:26" ht="14.25">
       <c r="A47" s="4" t="s">
         <v>42</v>
       </c>
@@ -3498,7 +3651,7 @@
       <c r="Y47" s="4"/>
       <c r="Z47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:26" ht="14.25">
       <c r="A48" s="4" t="s">
         <v>42</v>
       </c>
@@ -3532,7 +3685,7 @@
       <c r="Y48" s="4"/>
       <c r="Z48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:26" ht="14.25">
       <c r="A49" s="4" t="s">
         <v>42</v>
       </c>
@@ -3566,7 +3719,7 @@
       <c r="Y49" s="4"/>
       <c r="Z49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:26" ht="14.25">
       <c r="A50" s="4" t="s">
         <v>42</v>
       </c>
@@ -3600,7 +3753,7 @@
       <c r="Y50" s="4"/>
       <c r="Z50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:26" ht="14.25">
       <c r="A51" s="4" t="s">
         <v>42</v>
       </c>
@@ -3634,7 +3787,7 @@
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:26" ht="14.25">
       <c r="A52" s="5" t="s">
         <v>104</v>
       </c>
@@ -3666,7 +3819,7 @@
       <c r="Y52" s="4"/>
       <c r="Z52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:26" ht="14.25">
       <c r="A53" s="5" t="s">
         <v>105</v>
       </c>
@@ -3698,7 +3851,7 @@
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:26" ht="14.25">
       <c r="A54" s="4" t="s">
         <v>106</v>
       </c>
@@ -3734,7 +3887,7 @@
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:26" ht="409.5">
       <c r="A55" s="4" t="s">
         <v>110</v>
       </c>
@@ -3770,7 +3923,7 @@
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:26" ht="14.25">
       <c r="A56" s="4" t="s">
         <v>114</v>
       </c>
@@ -3802,84 +3955,84 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+    <row r="57" spans="1:26">
+      <c r="A57" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" t="s">
         <v>115</v>
       </c>
-      <c r="L57" s="0" t="s">
+      <c r="L57" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="58" spans="1:26">
+      <c r="A58" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" t="s">
         <v>117</v>
       </c>
       <c r="L58" s="14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+    <row r="59" spans="1:26">
+      <c r="A59" t="s">
         <v>42</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" t="s">
         <v>119</v>
       </c>
-      <c r="L59" s="0" t="s">
+      <c r="L59" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="60" spans="1:26">
+      <c r="A60" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" t="s">
         <v>121</v>
       </c>
-      <c r="L60" s="0" t="s">
+      <c r="L60" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+    <row r="61" spans="1:26">
+      <c r="A61" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" t="s">
         <v>123</v>
       </c>
-      <c r="L61" s="0" t="s">
+      <c r="L61" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="62" spans="1:26">
+      <c r="A62" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" t="s">
         <v>125</v>
       </c>
-      <c r="L62" s="0" t="s">
+      <c r="L62" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+    <row r="63" spans="1:26">
+      <c r="A63" t="s">
         <v>42</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
-      <c r="L63" s="0" t="s">
+      <c r="L63" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:26">
       <c r="A64" s="15" t="s">
         <v>19</v>
       </c>
@@ -3917,7 +4070,7 @@
       <c r="Y64" s="15"/>
       <c r="Z64" s="15"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:1024">
       <c r="A65" s="15" t="s">
         <v>110</v>
       </c>
@@ -3953,7 +4106,7 @@
       <c r="Y65" s="15"/>
       <c r="Z65" s="15"/>
     </row>
-    <row r="66" customFormat="false" ht="117.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:1024" ht="130">
       <c r="A66" s="15" t="s">
         <v>110</v>
       </c>
@@ -3989,7 +4142,7 @@
       <c r="Y66" s="15"/>
       <c r="Z66" s="15"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:1024">
       <c r="A67" s="15" t="s">
         <v>110</v>
       </c>
@@ -4025,7 +4178,7 @@
       <c r="Y67" s="15"/>
       <c r="Z67" s="15"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:1024">
       <c r="A68" s="15" t="s">
         <v>110</v>
       </c>
@@ -4061,7 +4214,7 @@
       <c r="Y68" s="15"/>
       <c r="Z68" s="15"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:1024">
       <c r="A69" s="15" t="s">
         <v>36</v>
       </c>
@@ -4093,7 +4246,7 @@
       <c r="Y69" s="15"/>
       <c r="Z69" s="15"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:1024">
       <c r="A70" s="15" t="s">
         <v>106</v>
       </c>
@@ -4101,7 +4254,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:1024">
       <c r="A71" s="15" t="s">
         <v>110</v>
       </c>
@@ -4115,7 +4268,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:1024">
       <c r="A72" s="15" t="s">
         <v>114</v>
       </c>
@@ -4123,7 +4276,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="73" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:1024" s="15" customFormat="1">
       <c r="A73" s="18" t="s">
         <v>19</v>
       </c>
@@ -4160,9 +4313,9 @@
       <c r="X73" s="18"/>
       <c r="Y73" s="18"/>
       <c r="Z73" s="18"/>
-      <c r="AMJ73" s="0"/>
-    </row>
-    <row r="74" s="15" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ73"/>
+    </row>
+    <row r="74" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A74" s="18" t="s">
         <v>110</v>
       </c>
@@ -4197,9 +4350,9 @@
       <c r="X74" s="18"/>
       <c r="Y74" s="18"/>
       <c r="Z74" s="18"/>
-      <c r="AMJ74" s="0"/>
-    </row>
-    <row r="75" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ74"/>
+    </row>
+    <row r="75" spans="1:1024" s="15" customFormat="1">
       <c r="A75" s="18" t="s">
         <v>19</v>
       </c>
@@ -4234,9 +4387,9 @@
       <c r="X75" s="18"/>
       <c r="Y75" s="18"/>
       <c r="Z75" s="18"/>
-      <c r="AMJ75" s="0"/>
-    </row>
-    <row r="76" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ75"/>
+    </row>
+    <row r="76" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A76" s="18" t="s">
         <v>157</v>
       </c>
@@ -4273,9 +4426,9 @@
       <c r="X76" s="18"/>
       <c r="Y76" s="18"/>
       <c r="Z76" s="18"/>
-      <c r="AMJ76" s="0"/>
-    </row>
-    <row r="77" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ76"/>
+    </row>
+    <row r="77" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A77" s="18" t="s">
         <v>157</v>
       </c>
@@ -4312,9 +4465,9 @@
       <c r="X77" s="18"/>
       <c r="Y77" s="18"/>
       <c r="Z77" s="18"/>
-      <c r="AMJ77" s="0"/>
-    </row>
-    <row r="78" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ77"/>
+    </row>
+    <row r="78" spans="1:1024" s="15" customFormat="1">
       <c r="A78" s="18" t="s">
         <v>157</v>
       </c>
@@ -4351,9 +4504,9 @@
       <c r="X78" s="18"/>
       <c r="Y78" s="18"/>
       <c r="Z78" s="18"/>
-      <c r="AMJ78" s="0"/>
-    </row>
-    <row r="79" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ78"/>
+    </row>
+    <row r="79" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A79" s="18" t="s">
         <v>157</v>
       </c>
@@ -4390,9 +4543,9 @@
       <c r="X79" s="18"/>
       <c r="Y79" s="18"/>
       <c r="Z79" s="18"/>
-      <c r="AMJ79" s="0"/>
-    </row>
-    <row r="80" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ79"/>
+    </row>
+    <row r="80" spans="1:1024" s="15" customFormat="1">
       <c r="A80" s="18" t="s">
         <v>36</v>
       </c>
@@ -4423,9 +4576,9 @@
       <c r="X80" s="18"/>
       <c r="Y80" s="18"/>
       <c r="Z80" s="18"/>
-      <c r="AMJ80" s="0"/>
-    </row>
-    <row r="81" s="15" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ80"/>
+    </row>
+    <row r="81" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A81" s="18" t="s">
         <v>110</v>
       </c>
@@ -4460,9 +4613,9 @@
       <c r="X81" s="18"/>
       <c r="Y81" s="18"/>
       <c r="Z81" s="18"/>
-      <c r="AMJ81" s="0"/>
-    </row>
-    <row r="82" s="15" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ81"/>
+    </row>
+    <row r="82" spans="1:1024" s="15" customFormat="1" ht="39">
       <c r="A82" s="18" t="s">
         <v>110</v>
       </c>
@@ -4497,9 +4650,9 @@
       <c r="X82" s="18"/>
       <c r="Y82" s="18"/>
       <c r="Z82" s="18"/>
-      <c r="AMJ82" s="0"/>
-    </row>
-    <row r="83" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ82"/>
+    </row>
+    <row r="83" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A83" s="18" t="s">
         <v>19</v>
       </c>
@@ -4534,9 +4687,9 @@
       <c r="X83" s="18"/>
       <c r="Y83" s="18"/>
       <c r="Z83" s="18"/>
-      <c r="AMJ83" s="0"/>
-    </row>
-    <row r="84" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ83"/>
+    </row>
+    <row r="84" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A84" s="18" t="s">
         <v>157</v>
       </c>
@@ -4573,9 +4726,9 @@
       <c r="X84" s="18"/>
       <c r="Y84" s="18"/>
       <c r="Z84" s="18"/>
-      <c r="AMJ84" s="0"/>
-    </row>
-    <row r="85" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ84"/>
+    </row>
+    <row r="85" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A85" s="18" t="s">
         <v>157</v>
       </c>
@@ -4612,9 +4765,9 @@
       <c r="X85" s="18"/>
       <c r="Y85" s="18"/>
       <c r="Z85" s="18"/>
-      <c r="AMJ85" s="0"/>
-    </row>
-    <row r="86" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ85"/>
+    </row>
+    <row r="86" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A86" s="18" t="s">
         <v>157</v>
       </c>
@@ -4651,9 +4804,9 @@
       <c r="X86" s="18"/>
       <c r="Y86" s="18"/>
       <c r="Z86" s="18"/>
-      <c r="AMJ86" s="0"/>
-    </row>
-    <row r="87" s="15" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ86"/>
+    </row>
+    <row r="87" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A87" s="18" t="s">
         <v>36</v>
       </c>
@@ -4684,9 +4837,9 @@
       <c r="X87" s="18"/>
       <c r="Y87" s="18"/>
       <c r="Z87" s="18"/>
-      <c r="AMJ87" s="0"/>
-    </row>
-    <row r="88" s="15" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ87"/>
+    </row>
+    <row r="88" spans="1:1024" s="15" customFormat="1" ht="15.5" customHeight="1">
       <c r="A88" s="18" t="s">
         <v>42</v>
       </c>
@@ -4719,9 +4872,9 @@
       <c r="X88" s="18"/>
       <c r="Y88" s="18"/>
       <c r="Z88" s="18"/>
-      <c r="AMJ88" s="0"/>
-    </row>
-    <row r="89" s="15" customFormat="true" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ88"/>
+    </row>
+    <row r="89" spans="1:1024" s="15" customFormat="1" ht="13.75" customHeight="1">
       <c r="A89" s="18" t="s">
         <v>110</v>
       </c>
@@ -4760,9 +4913,9 @@
       <c r="X89" s="18"/>
       <c r="Y89" s="18"/>
       <c r="Z89" s="18"/>
-      <c r="AMJ89" s="0"/>
-    </row>
-    <row r="90" s="15" customFormat="true" ht="24.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ89"/>
+    </row>
+    <row r="90" spans="1:1024" s="15" customFormat="1" ht="24.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>110</v>
       </c>
@@ -4799,9 +4952,9 @@
       <c r="X90" s="18"/>
       <c r="Y90" s="18"/>
       <c r="Z90" s="18"/>
-      <c r="AMJ90" s="0"/>
-    </row>
-    <row r="91" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ90"/>
+    </row>
+    <row r="91" spans="1:1024" s="15" customFormat="1">
       <c r="A91" s="18" t="s">
         <v>36</v>
       </c>
@@ -4832,9 +4985,9 @@
       <c r="X91" s="18"/>
       <c r="Y91" s="18"/>
       <c r="Z91" s="18"/>
-      <c r="AMJ91" s="0"/>
-    </row>
-    <row r="92" s="15" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ91"/>
+    </row>
+    <row r="92" spans="1:1024" s="15" customFormat="1" ht="65">
       <c r="A92" s="18" t="s">
         <v>19</v>
       </c>
@@ -4870,9 +5023,9 @@
       <c r="X92" s="18"/>
       <c r="Y92" s="18"/>
       <c r="Z92" s="18"/>
-      <c r="AMJ92" s="0"/>
-    </row>
-    <row r="93" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ92"/>
+    </row>
+    <row r="93" spans="1:1024" s="15" customFormat="1">
       <c r="A93" s="18" t="s">
         <v>19</v>
       </c>
@@ -4906,9 +5059,9 @@
       <c r="X93" s="18"/>
       <c r="Y93" s="18"/>
       <c r="Z93" s="18"/>
-      <c r="AMJ93" s="0"/>
-    </row>
-    <row r="94" s="15" customFormat="true" ht="34.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ93"/>
+    </row>
+    <row r="94" spans="1:1024" s="15" customFormat="1" ht="34.25" customHeight="1">
       <c r="A94" s="18" t="s">
         <v>202</v>
       </c>
@@ -4954,9 +5107,9 @@
       <c r="X94" s="18"/>
       <c r="Y94" s="18"/>
       <c r="Z94" s="18"/>
-      <c r="AMJ94" s="0"/>
-    </row>
-    <row r="95" s="15" customFormat="true" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ94"/>
+    </row>
+    <row r="95" spans="1:1024" s="15" customFormat="1" ht="38" customHeight="1">
       <c r="A95" s="18" t="s">
         <v>42</v>
       </c>
@@ -4988,9 +5141,9 @@
       <c r="X95" s="18"/>
       <c r="Y95" s="18"/>
       <c r="Z95" s="18"/>
-      <c r="AMJ95" s="0"/>
-    </row>
-    <row r="96" s="15" customFormat="true" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ95"/>
+    </row>
+    <row r="96" spans="1:1024" s="15" customFormat="1" ht="36.75" customHeight="1">
       <c r="A96" s="18" t="s">
         <v>110</v>
       </c>
@@ -5026,9 +5179,9 @@
       <c r="X96" s="18"/>
       <c r="Y96" s="18"/>
       <c r="Z96" s="18"/>
-      <c r="AMJ96" s="0"/>
-    </row>
-    <row r="97" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ96"/>
+    </row>
+    <row r="97" spans="1:1024" s="15" customFormat="1">
       <c r="A97" s="18" t="s">
         <v>36</v>
       </c>
@@ -5059,9 +5212,9 @@
       <c r="X97" s="18"/>
       <c r="Y97" s="18"/>
       <c r="Z97" s="18"/>
-      <c r="AMJ97" s="0"/>
-    </row>
-    <row r="98" s="15" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ97"/>
+    </row>
+    <row r="98" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A98" s="18" t="s">
         <v>19</v>
       </c>
@@ -5097,9 +5250,9 @@
       <c r="X98" s="18"/>
       <c r="Y98" s="18"/>
       <c r="Z98" s="18"/>
-      <c r="AMJ98" s="0"/>
-    </row>
-    <row r="99" s="15" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ98"/>
+    </row>
+    <row r="99" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A99" s="18" t="s">
         <v>157</v>
       </c>
@@ -5138,9 +5291,9 @@
       <c r="X99" s="18"/>
       <c r="Y99" s="18"/>
       <c r="Z99" s="18"/>
-      <c r="AMJ99" s="0"/>
-    </row>
-    <row r="100" s="15" customFormat="true" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ99"/>
+    </row>
+    <row r="100" spans="1:1024" s="15" customFormat="1" ht="65">
       <c r="A100" s="18" t="s">
         <v>110</v>
       </c>
@@ -5176,9 +5329,9 @@
       <c r="X100" s="18"/>
       <c r="Y100" s="18"/>
       <c r="Z100" s="18"/>
-      <c r="AMJ100" s="0"/>
-    </row>
-    <row r="101" s="15" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ100"/>
+    </row>
+    <row r="101" spans="1:1024" s="15" customFormat="1" ht="24.75" customHeight="1">
       <c r="A101" s="18" t="s">
         <v>157</v>
       </c>
@@ -5217,9 +5370,9 @@
       <c r="X101" s="18"/>
       <c r="Y101" s="18"/>
       <c r="Z101" s="18"/>
-      <c r="AMJ101" s="0"/>
-    </row>
-    <row r="102" s="15" customFormat="true" ht="23" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AMJ101"/>
+    </row>
+    <row r="102" spans="1:1024" s="15" customFormat="1" ht="23" customHeight="1">
       <c r="A102" s="18" t="s">
         <v>42</v>
       </c>
@@ -5251,9 +5404,9 @@
       <c r="X102" s="18"/>
       <c r="Y102" s="18"/>
       <c r="Z102" s="18"/>
-      <c r="AMJ102" s="0"/>
-    </row>
-    <row r="103" s="15" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ102"/>
+    </row>
+    <row r="103" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A103" s="18" t="s">
         <v>110</v>
       </c>
@@ -5289,9 +5442,9 @@
       <c r="X103" s="18"/>
       <c r="Y103" s="18"/>
       <c r="Z103" s="18"/>
-      <c r="AMJ103" s="0"/>
-    </row>
-    <row r="104" s="15" customFormat="true" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ103"/>
+    </row>
+    <row r="104" spans="1:1024" s="15" customFormat="1" ht="117">
       <c r="A104" s="18" t="s">
         <v>110</v>
       </c>
@@ -5327,9 +5480,9 @@
       <c r="X104" s="18"/>
       <c r="Y104" s="18"/>
       <c r="Z104" s="18"/>
-      <c r="AMJ104" s="0"/>
-    </row>
-    <row r="105" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ104"/>
+    </row>
+    <row r="105" spans="1:1024" s="15" customFormat="1">
       <c r="A105" s="18" t="s">
         <v>36</v>
       </c>
@@ -5360,9 +5513,9 @@
       <c r="X105" s="18"/>
       <c r="Y105" s="18"/>
       <c r="Z105" s="18"/>
-      <c r="AMJ105" s="0"/>
-    </row>
-    <row r="106" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ105"/>
+    </row>
+    <row r="106" spans="1:1024" s="15" customFormat="1">
       <c r="A106" s="18" t="s">
         <v>36</v>
       </c>
@@ -5393,9 +5546,9 @@
       <c r="X106" s="18"/>
       <c r="Y106" s="18"/>
       <c r="Z106" s="18"/>
-      <c r="AMJ106" s="0"/>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ106"/>
+    </row>
+    <row r="107" spans="1:1024">
       <c r="A107" s="15" t="s">
         <v>106</v>
       </c>
@@ -5431,7 +5584,7 @@
       <c r="Y107" s="15"/>
       <c r="Z107" s="15"/>
     </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:1024" ht="14.75">
       <c r="A108" s="15" t="s">
         <v>237</v>
       </c>
@@ -5479,7 +5632,7 @@
       <c r="Y108" s="15"/>
       <c r="Z108" s="15"/>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:1024">
       <c r="A109" s="15" t="s">
         <v>114</v>
       </c>
@@ -5511,7 +5664,7 @@
       <c r="Y109" s="15"/>
       <c r="Z109" s="15"/>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:1024">
       <c r="A110" s="15" t="s">
         <v>19</v>
       </c>
@@ -5547,7 +5700,7 @@
       <c r="Y110" s="15"/>
       <c r="Z110" s="15"/>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:1024" ht="14.75">
       <c r="A111" s="15" t="s">
         <v>110</v>
       </c>
@@ -5585,7 +5738,7 @@
       <c r="Y111" s="15"/>
       <c r="Z111" s="15"/>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:1024">
       <c r="A112" s="15" t="s">
         <v>110</v>
       </c>
@@ -5623,7 +5776,7 @@
       <c r="Y112" s="15"/>
       <c r="Z112" s="15"/>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:6">
       <c r="A113" s="15" t="s">
         <v>110</v>
       </c>
@@ -5640,7 +5793,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:6">
       <c r="A114" s="15" t="s">
         <v>110</v>
       </c>
@@ -5657,7 +5810,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:6">
       <c r="A115" s="15" t="s">
         <v>110</v>
       </c>
@@ -5674,7 +5827,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:6">
       <c r="A116" s="15" t="s">
         <v>110</v>
       </c>
@@ -5691,7 +5844,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:6">
       <c r="A117" s="15" t="s">
         <v>110</v>
       </c>
@@ -5708,7 +5861,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:6">
       <c r="A118" s="15" t="s">
         <v>110</v>
       </c>
@@ -5725,7 +5878,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:6">
       <c r="A119" s="15" t="s">
         <v>110</v>
       </c>
@@ -5742,7 +5895,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:6">
       <c r="A120" s="15" t="s">
         <v>110</v>
       </c>
@@ -5759,7 +5912,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:6">
       <c r="A121" s="15" t="s">
         <v>110</v>
       </c>
@@ -5776,7 +5929,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:6">
       <c r="A122" s="15" t="s">
         <v>110</v>
       </c>
@@ -5793,7 +5946,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:6">
       <c r="A123" s="15" t="s">
         <v>110</v>
       </c>
@@ -5810,7 +5963,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:6">
       <c r="A124" s="15" t="s">
         <v>110</v>
       </c>
@@ -5820,14 +5973,14 @@
       <c r="C124" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="D124" s="0" t="s">
+      <c r="D124" t="s">
         <v>300</v>
       </c>
       <c r="F124" s="27" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:6">
       <c r="A125" s="15" t="s">
         <v>110</v>
       </c>
@@ -5844,7 +5997,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:6">
       <c r="A126" s="15" t="s">
         <v>110</v>
       </c>
@@ -5861,7 +6014,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:6">
       <c r="A127" s="15" t="s">
         <v>110</v>
       </c>
@@ -5878,7 +6031,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:6">
       <c r="A128" s="15" t="s">
         <v>110</v>
       </c>
@@ -5895,7 +6048,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:1024">
       <c r="A129" s="15" t="s">
         <v>110</v>
       </c>
@@ -5912,7 +6065,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:1024">
       <c r="A130" s="15" t="s">
         <v>110</v>
       </c>
@@ -5929,7 +6082,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:1024">
       <c r="A131" s="15" t="s">
         <v>110</v>
       </c>
@@ -5946,7 +6099,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:1024">
       <c r="A132" s="15" t="s">
         <v>110</v>
       </c>
@@ -5963,7 +6116,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:1024">
       <c r="A133" s="15" t="s">
         <v>110</v>
       </c>
@@ -5980,7 +6133,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:1024">
       <c r="A134" s="28" t="s">
         <v>110</v>
       </c>
@@ -5997,7 +6150,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:1024">
       <c r="A135" s="15" t="s">
         <v>110</v>
       </c>
@@ -6014,7 +6167,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:1024">
       <c r="A136" s="15" t="s">
         <v>36</v>
       </c>
@@ -6022,7 +6175,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:1024">
       <c r="A137" s="15" t="s">
         <v>106</v>
       </c>
@@ -6038,11 +6191,11 @@
       <c r="F137" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="G137" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="138" s="15" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:1024" s="15" customFormat="1" ht="39">
       <c r="A138" s="14" t="s">
         <v>110</v>
       </c>
@@ -6056,9 +6209,9 @@
         <v>351</v>
       </c>
       <c r="F138" s="27"/>
-      <c r="AMJ138" s="0"/>
-    </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ138"/>
+    </row>
+    <row r="139" spans="1:1024">
       <c r="A139" s="15" t="s">
         <v>352</v>
       </c>
@@ -6087,7 +6240,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="140" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:1024" s="15" customFormat="1">
       <c r="A140" s="15" t="s">
         <v>110</v>
       </c>
@@ -6100,9 +6253,9 @@
       <c r="D140" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="AMJ140" s="0"/>
-    </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ140"/>
+    </row>
+    <row r="141" spans="1:1024">
       <c r="A141" s="15" t="s">
         <v>114</v>
       </c>
@@ -6110,7 +6263,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="142" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:1024" s="15" customFormat="1">
       <c r="A142" s="15" t="s">
         <v>106</v>
       </c>
@@ -6129,9 +6282,9 @@
       <c r="G142" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="AMJ142" s="0"/>
-    </row>
-    <row r="143" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ142"/>
+    </row>
+    <row r="143" spans="1:1024" s="15" customFormat="1">
       <c r="A143" s="15" t="s">
         <v>352</v>
       </c>
@@ -6147,12 +6300,15 @@
       <c r="E143" s="14" t="s">
         <v>161</v>
       </c>
+      <c r="I143" s="26" t="s">
+        <v>207</v>
+      </c>
       <c r="M143" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="AMJ143" s="0"/>
-    </row>
-    <row r="144" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ143"/>
+    </row>
+    <row r="144" spans="1:1024" s="15" customFormat="1">
       <c r="A144" s="15" t="s">
         <v>110</v>
       </c>
@@ -6165,18 +6321,18 @@
       <c r="D144" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="AMJ144" s="0"/>
-    </row>
-    <row r="145" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ144"/>
+    </row>
+    <row r="145" spans="1:1024" s="15" customFormat="1">
       <c r="A145" s="15" t="s">
         <v>114</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="AMJ145" s="0"/>
-    </row>
-    <row r="146" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ145"/>
+    </row>
+    <row r="146" spans="1:1024" s="15" customFormat="1">
       <c r="A146" s="15" t="s">
         <v>19</v>
       </c>
@@ -6192,13 +6348,13 @@
       <c r="F146" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="AMJ146" s="0"/>
-    </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="AMJ146"/>
+    </row>
+    <row r="147" spans="1:1024">
+      <c r="A147" t="s">
         <v>110</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" t="s">
         <v>367</v>
       </c>
       <c r="C147" s="26" t="s">
@@ -6207,15 +6363,15 @@
       <c r="D147" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="F147" s="0" t="s">
+      <c r="F147" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+    <row r="148" spans="1:1024">
+      <c r="A148" t="s">
         <v>110</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" t="s">
         <v>371</v>
       </c>
       <c r="C148" s="26" t="s">
@@ -6224,15 +6380,15 @@
       <c r="D148" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="F148" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+    <row r="149" spans="1:1024">
+      <c r="A149" t="s">
         <v>110</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" t="s">
         <v>375</v>
       </c>
       <c r="C149" s="26" t="s">
@@ -6241,15 +6397,15 @@
       <c r="D149" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="F149" s="0" t="s">
+      <c r="F149" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
+    <row r="150" spans="1:1024">
+      <c r="A150" t="s">
         <v>110</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B150" t="s">
         <v>379</v>
       </c>
       <c r="C150" s="26" t="s">
@@ -6258,15 +6414,15 @@
       <c r="D150" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="F150" s="0" t="s">
+      <c r="F150" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
+    <row r="151" spans="1:1024">
+      <c r="A151" t="s">
         <v>110</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" t="s">
         <v>383</v>
       </c>
       <c r="C151" s="26" t="s">
@@ -6275,15 +6431,15 @@
       <c r="D151" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="F151" s="0" t="s">
+      <c r="F151" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
+    <row r="152" spans="1:1024">
+      <c r="A152" t="s">
         <v>110</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" t="s">
         <v>387</v>
       </c>
       <c r="C152" s="26" t="s">
@@ -6292,15 +6448,15 @@
       <c r="D152" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="F152" s="0" t="s">
+      <c r="F152" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+    <row r="153" spans="1:1024">
+      <c r="A153" t="s">
         <v>110</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B153" t="s">
         <v>391</v>
       </c>
       <c r="C153" s="26" t="s">
@@ -6309,38 +6465,38 @@
       <c r="D153" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="F153" s="0" t="s">
+      <c r="F153" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="154" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:1024" s="15" customFormat="1">
       <c r="A154" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B154" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="AMJ154" s="0"/>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ154"/>
+    </row>
+    <row r="155" spans="1:1024">
       <c r="A155" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B155" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C155" t="s">
         <v>396</v>
       </c>
-      <c r="D155" s="0" t="s">
+      <c r="D155" t="s">
         <v>397</v>
       </c>
-      <c r="G155" s="0" t="s">
+      <c r="G155" t="s">
         <v>246</v>
       </c>
       <c r="J155" s="18"/>
     </row>
-    <row r="156" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:1024" s="15" customFormat="1">
       <c r="A156" s="18" t="s">
         <v>110</v>
       </c>
@@ -6375,9 +6531,9 @@
       <c r="W156" s="18"/>
       <c r="X156" s="18"/>
       <c r="Y156" s="18"/>
-      <c r="AMJ156" s="0"/>
-    </row>
-    <row r="157" s="15" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ156"/>
+    </row>
+    <row r="157" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A157" s="18" t="s">
         <v>110</v>
       </c>
@@ -6414,9 +6570,9 @@
       <c r="W157" s="18"/>
       <c r="X157" s="18"/>
       <c r="Y157" s="18"/>
-      <c r="AMJ157" s="0"/>
-    </row>
-    <row r="158" s="15" customFormat="true" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ157"/>
+    </row>
+    <row r="158" spans="1:1024" s="15" customFormat="1" ht="57">
       <c r="A158" s="18" t="s">
         <v>110</v>
       </c>
@@ -6452,23 +6608,23 @@
       <c r="W158" s="18"/>
       <c r="X158" s="18"/>
       <c r="Y158" s="18"/>
-      <c r="AMJ158" s="0"/>
-    </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ158"/>
+    </row>
+    <row r="159" spans="1:1024">
       <c r="A159" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B159" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="C159" s="0" t="s">
+      <c r="C159" t="s">
         <v>412</v>
       </c>
-      <c r="D159" s="0" t="s">
+      <c r="D159" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:1024">
       <c r="A160" s="15" t="s">
         <v>114</v>
       </c>
@@ -6477,7 +6633,7 @@
       </c>
       <c r="J160" s="18"/>
     </row>
-    <row r="161" s="15" customFormat="true" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:1024" s="15" customFormat="1" ht="31" customHeight="1">
       <c r="A161" s="18" t="s">
         <v>42</v>
       </c>
@@ -6508,9 +6664,9 @@
       <c r="X161" s="18"/>
       <c r="Y161" s="18"/>
       <c r="Z161" s="18"/>
-      <c r="AMJ161" s="0"/>
-    </row>
-    <row r="162" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ161"/>
+    </row>
+    <row r="162" spans="1:1024" s="15" customFormat="1">
       <c r="A162" s="28" t="s">
         <v>42</v>
       </c>
@@ -6520,9 +6676,9 @@
       <c r="L162" s="28" t="s">
         <v>417</v>
       </c>
-      <c r="AMJ162" s="0"/>
-    </row>
-    <row r="163" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ162"/>
+    </row>
+    <row r="163" spans="1:1024" s="15" customFormat="1">
       <c r="A163" s="28" t="s">
         <v>42</v>
       </c>
@@ -6532,9 +6688,9 @@
       <c r="L163" s="28" t="s">
         <v>419</v>
       </c>
-      <c r="AMJ163" s="0"/>
-    </row>
-    <row r="164" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMJ163"/>
+    </row>
+    <row r="164" spans="1:1024" s="15" customFormat="1">
       <c r="A164" s="28" t="s">
         <v>42</v>
       </c>
@@ -6544,38 +6700,30 @@
       <c r="L164" s="28" t="s">
         <v>421</v>
       </c>
-      <c r="AMJ164" s="0"/>
+      <c r="AMJ164"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L35:Q35"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:Z50"/>
-  <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z51"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="72.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="53.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="14.41"/>
+    <col min="1" max="1" width="17.04296875" customWidth="1"/>
+    <col min="2" max="2" width="25.90625" customWidth="1"/>
+    <col min="3" max="3" width="72.26953125" customWidth="1"/>
+    <col min="4" max="4" width="53.08984375" customWidth="1"/>
+    <col min="5" max="1025" width="14.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
         <v>422</v>
       </c>
@@ -6613,7 +6761,7 @@
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="18" t="s">
         <v>238</v>
       </c>
@@ -6649,7 +6797,7 @@
       <c r="Y2" s="18"/>
       <c r="Z2" s="18"/>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>238</v>
       </c>
@@ -6685,7 +6833,7 @@
       <c r="Y3" s="18"/>
       <c r="Z3" s="18"/>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>238</v>
       </c>
@@ -6721,7 +6869,7 @@
       <c r="Y4" s="18"/>
       <c r="Z4" s="18"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>238</v>
       </c>
@@ -6757,7 +6905,7 @@
       <c r="Y5" s="18"/>
       <c r="Z5" s="18"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>238</v>
       </c>
@@ -6793,7 +6941,7 @@
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>238</v>
       </c>
@@ -6829,7 +6977,7 @@
       <c r="Y7" s="18"/>
       <c r="Z7" s="18"/>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>238</v>
       </c>
@@ -6865,7 +7013,7 @@
       <c r="Y8" s="18"/>
       <c r="Z8" s="18"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="18" t="s">
         <v>238</v>
       </c>
@@ -6901,7 +7049,7 @@
       <c r="Y9" s="18"/>
       <c r="Z9" s="18"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="18" t="s">
         <v>238</v>
       </c>
@@ -6937,7 +7085,7 @@
       <c r="Y10" s="18"/>
       <c r="Z10" s="18"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>238</v>
       </c>
@@ -6973,7 +7121,7 @@
       <c r="Y11" s="18"/>
       <c r="Z11" s="18"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="18" t="s">
         <v>238</v>
       </c>
@@ -7009,7 +7157,7 @@
       <c r="Y12" s="18"/>
       <c r="Z12" s="18"/>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="18" t="s">
         <v>238</v>
       </c>
@@ -7045,7 +7193,7 @@
       <c r="Y13" s="18"/>
       <c r="Z13" s="18"/>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="18" t="s">
         <v>238</v>
       </c>
@@ -7081,7 +7229,7 @@
       <c r="Y14" s="18"/>
       <c r="Z14" s="18"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="18" t="s">
         <v>238</v>
       </c>
@@ -7117,7 +7265,7 @@
       <c r="Y15" s="18"/>
       <c r="Z15" s="18"/>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="18" t="s">
         <v>238</v>
       </c>
@@ -7153,7 +7301,7 @@
       <c r="Y16" s="18"/>
       <c r="Z16" s="18"/>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>238</v>
       </c>
@@ -7189,7 +7337,7 @@
       <c r="Y17" s="18"/>
       <c r="Z17" s="18"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>238</v>
       </c>
@@ -7225,7 +7373,7 @@
       <c r="Y18" s="18"/>
       <c r="Z18" s="18"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="18" t="s">
         <v>238</v>
       </c>
@@ -7261,7 +7409,7 @@
       <c r="Y19" s="18"/>
       <c r="Z19" s="18"/>
     </row>
-    <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:26">
       <c r="A20" s="18" t="s">
         <v>238</v>
       </c>
@@ -7297,7 +7445,7 @@
       <c r="Y20" s="18"/>
       <c r="Z20" s="18"/>
     </row>
-    <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:26">
       <c r="A21" s="18" t="s">
         <v>238</v>
       </c>
@@ -7333,7 +7481,7 @@
       <c r="Y21" s="18"/>
       <c r="Z21" s="18"/>
     </row>
-    <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:26">
       <c r="A22" s="18" t="s">
         <v>238</v>
       </c>
@@ -7369,7 +7517,7 @@
       <c r="Y22" s="18"/>
       <c r="Z22" s="18"/>
     </row>
-    <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:26">
       <c r="A23" s="18" t="s">
         <v>238</v>
       </c>
@@ -7405,7 +7553,7 @@
       <c r="Y23" s="18"/>
       <c r="Z23" s="18"/>
     </row>
-    <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:26">
       <c r="A24" s="18" t="s">
         <v>238</v>
       </c>
@@ -7441,7 +7589,7 @@
       <c r="Y24" s="18"/>
       <c r="Z24" s="18"/>
     </row>
-    <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:26">
       <c r="A25" s="18" t="s">
         <v>238</v>
       </c>
@@ -7477,7 +7625,7 @@
       <c r="Y25" s="18"/>
       <c r="Z25" s="18"/>
     </row>
-    <row r="26" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:26">
       <c r="A26" s="18" t="s">
         <v>238</v>
       </c>
@@ -7513,7 +7661,7 @@
       <c r="Y26" s="18"/>
       <c r="Z26" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:26">
       <c r="A27" s="18" t="s">
         <v>238</v>
       </c>
@@ -7549,7 +7697,7 @@
       <c r="Y27" s="18"/>
       <c r="Z27" s="18"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>430</v>
       </c>
@@ -7563,7 +7711,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
         <v>430</v>
       </c>
@@ -7577,7 +7725,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>430</v>
       </c>
@@ -7591,7 +7739,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="15" t="s">
         <v>430</v>
       </c>
@@ -7605,7 +7753,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="15" t="s">
         <v>430</v>
       </c>
@@ -7619,7 +7767,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>430</v>
       </c>
@@ -7633,7 +7781,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>430</v>
       </c>
@@ -7647,82 +7795,60 @@
         <v>451</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>452</v>
+    <row r="35" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>430</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>427</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="14" t="s">
         <v>452</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26">
+      <c r="A37" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C37" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:26">
       <c r="A38" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>463</v>
+        <v>459</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>460</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
@@ -7747,18 +7873,18 @@
       <c r="Y38" s="18"/>
       <c r="Z38" s="18"/>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
@@ -7783,18 +7909,18 @@
       <c r="Y39" s="18"/>
       <c r="Z39" s="18"/>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>468</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>469</v>
+        <v>465</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>466</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
@@ -7819,18 +7945,18 @@
       <c r="Y40" s="18"/>
       <c r="Z40" s="18"/>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>472</v>
+        <v>468</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>469</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
@@ -7855,18 +7981,18 @@
       <c r="Y41" s="18"/>
       <c r="Z41" s="18"/>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>475</v>
+        <v>471</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>472</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -7891,18 +8017,18 @@
       <c r="Y42" s="18"/>
       <c r="Z42" s="18"/>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
@@ -7927,18 +8053,18 @@
       <c r="Y43" s="18"/>
       <c r="Z43" s="18"/>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -7963,18 +8089,18 @@
       <c r="Y44" s="18"/>
       <c r="Z44" s="18"/>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -7999,18 +8125,18 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="18"/>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
@@ -8035,18 +8161,18 @@
       <c r="Y46" s="18"/>
       <c r="Z46" s="18"/>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
@@ -8071,18 +8197,18 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="18"/>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
@@ -8107,18 +8233,18 @@
       <c r="Y48" s="18"/>
       <c r="Z48" s="18"/>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1">
       <c r="A49" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -8143,18 +8269,18 @@
       <c r="Y49" s="18"/>
       <c r="Z49" s="18"/>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1">
       <c r="A50" s="18" t="s">
         <v>203</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>427</v>
+        <v>494</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -8179,31 +8305,59 @@
       <c r="Y50" s="18"/>
       <c r="Z50" s="18"/>
     </row>
+    <row r="51" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A51" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="18"/>
+      <c r="X51" s="18"/>
+      <c r="Y51" s="18"/>
+      <c r="Z51" s="18"/>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="14.41"/>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="3" max="1025" width="14.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
         <v>497</v>
       </c>
@@ -8243,21 +8397,21 @@
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>503</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="D2" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="E2" s="25" t="s">
         <v>505</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>507</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="15"/>
@@ -8282,12 +8436,7 @@
       <c r="Z2" s="15"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="511">
   <si>
     <t>type</t>
   </si>
@@ -392,9 +392,6 @@
   </si>
   <si>
     <t>gestation_in_weeks_c</t>
-  </si>
-  <si>
-    <t>“true”</t>
   </si>
   <si>
     <t>is_high_risk_pregnancy_ML_c</t>
@@ -1609,12 +1606,21 @@
   <si>
     <t>pregnancy_counselling</t>
   </si>
+  <si>
+    <t>gestation_in_weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO_LABEL </t>
+  </si>
+  <si>
+    <t>../inputs/gestation_in_weeks</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1705,6 +1711,11 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1738,7 +1749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1802,6 +1813,7 @@
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2150,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMJ164"/>
+  <dimension ref="A1:AMJ165"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="30.86328125" customWidth="1"/>
@@ -2158,7 +2170,7 @@
     <col min="3" max="3" width="62.76953125" customWidth="1"/>
     <col min="4" max="4" width="50.54296875" customWidth="1"/>
     <col min="5" max="5" width="14.40625" customWidth="1"/>
-    <col min="6" max="6" width="23.6328125" customWidth="1"/>
+    <col min="6" max="6" width="31.76953125" customWidth="1"/>
     <col min="7" max="1022" width="14.40625" customWidth="1"/>
     <col min="1023" max="1025" width="11.5"/>
   </cols>
@@ -2286,13 +2298,13 @@
     </row>
     <row r="4" spans="1:26" ht="14.25">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>508</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>509</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2319,36 +2331,45 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="14.25">
-      <c r="A5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="14.25">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>21</v>
@@ -2369,49 +2390,49 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="14.25">
-      <c r="A7" t="s">
+      <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="14.25">
-      <c r="A8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="14.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="1"/>
@@ -2431,13 +2452,13 @@
     </row>
     <row r="10" spans="1:26" ht="14.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -2459,10 +2480,10 @@
         <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2484,10 +2505,10 @@
         <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -2506,12 +2527,14 @@
     </row>
     <row r="13" spans="1:26" ht="14.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2528,45 +2551,34 @@
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="14.25">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
+      <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="14.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>21</v>
@@ -2574,9 +2586,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -2599,10 +2609,10 @@
     </row>
     <row r="16" spans="1:26" ht="14.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>21</v>
@@ -2610,7 +2620,9 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -2636,7 +2648,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>21</v>
@@ -2655,24 +2667,26 @@
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
     </row>
     <row r="18" spans="1:26" ht="14.25">
       <c r="A18" s="4" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -2687,79 +2701,77 @@
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
     </row>
     <row r="19" spans="1:26" ht="14.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+    </row>
+    <row r="20" spans="1:26" ht="14.25">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:26" ht="14.25">
-      <c r="A20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="14.25">
       <c r="A21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -2770,8 +2782,8 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
-        <v>46</v>
+      <c r="L21" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
@@ -2793,7 +2805,7 @@
         <v>42</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -2804,8 +2816,8 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="7" t="s">
-        <v>48</v>
+      <c r="L22" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
@@ -2827,7 +2839,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2838,8 +2850,8 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="6" t="s">
-        <v>50</v>
+      <c r="L23" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -2861,7 +2873,7 @@
         <v>42</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -2873,7 +2885,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -2895,7 +2907,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -2906,8 +2918,8 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="7" t="s">
-        <v>54</v>
+      <c r="L25" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -2929,7 +2941,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -2941,7 +2953,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
@@ -2963,7 +2975,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -2974,8 +2986,8 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="6" t="s">
-        <v>58</v>
+      <c r="L27" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -2993,38 +3005,45 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" spans="1:26" ht="14.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
+      <c r="B28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
     </row>
     <row r="29" spans="1:26" ht="14.25">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>62</v>
+      <c r="B29" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -3038,7 +3057,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -3050,8 +3069,8 @@
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>64</v>
+      <c r="B30" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -3065,7 +3084,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3074,60 +3093,53 @@
       <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="14.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:26" ht="14.25">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-    </row>
-    <row r="32" spans="1:26" ht="14.25">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="4"/>
+      <c r="C32" s="5"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="L32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
@@ -3146,7 +3158,7 @@
         <v>42</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3157,11 +3169,11 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="6" t="s">
-        <v>71</v>
+      <c r="L33" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="M33" s="6"/>
-      <c r="N33" s="4"/>
+      <c r="N33" s="6"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
@@ -3180,7 +3192,7 @@
         <v>42</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3192,9 +3204,9 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M34" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="M34" s="6"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
@@ -3214,7 +3226,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3225,30 +3237,30 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
-      <c r="V35" s="5"/>
-      <c r="W35" s="5"/>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5"/>
-      <c r="Z35" s="5"/>
+      <c r="L35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
     </row>
     <row r="36" spans="1:26" ht="14.25">
       <c r="A36" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3259,30 +3271,30 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
+      <c r="L36" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
     </row>
     <row r="37" spans="1:26" ht="14.25">
       <c r="A37" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3293,10 +3305,10 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="9">
-        <v>7</v>
-      </c>
-      <c r="M37" s="4"/>
+      <c r="L37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M37" s="6"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
@@ -3316,7 +3328,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3328,7 +3340,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="9">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
@@ -3346,11 +3358,11 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" spans="1:26" ht="14.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>80</v>
+      <c r="B39" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3361,10 +3373,10 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="M39" s="6"/>
+      <c r="L39" s="9">
+        <v>30</v>
+      </c>
+      <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
       <c r="P39" s="4"/>
@@ -3384,7 +3396,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3396,7 +3408,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M40" s="6"/>
       <c r="N40" s="4"/>
@@ -3418,7 +3430,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3430,7 +3442,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M41" s="6"/>
       <c r="N41" s="4"/>
@@ -3452,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3464,7 +3476,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M42" s="6"/>
       <c r="N42" s="4"/>
@@ -3482,11 +3494,11 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" spans="1:26" ht="14.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>23</v>
+      <c r="B43" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3497,10 +3509,10 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M43" s="4"/>
+      <c r="L43" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M43" s="6"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="4"/>
@@ -3520,7 +3532,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3531,10 +3543,10 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="L44" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M44" s="6"/>
+      <c r="L44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="4"/>
@@ -3554,21 +3566,21 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="7"/>
+      <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="M45" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="M45" s="6"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
@@ -3588,7 +3600,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3599,8 +3611,8 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
-      <c r="L46" s="7" t="s">
-        <v>94</v>
+      <c r="L46" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -3622,7 +3634,7 @@
         <v>42</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -3634,7 +3646,7 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -3656,7 +3668,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -3667,8 +3679,8 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="4" t="s">
-        <v>98</v>
+      <c r="L48" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -3690,7 +3702,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -3701,8 +3713,8 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="7" t="s">
-        <v>100</v>
+      <c r="L49" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -3724,7 +3736,7 @@
         <v>42</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -3735,8 +3747,8 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="4" t="s">
-        <v>102</v>
+      <c r="L50" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -3758,7 +3770,7 @@
         <v>42</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -3770,7 +3782,7 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -3788,22 +3800,24 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" spans="1:26" ht="14.25">
-      <c r="A52" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>104</v>
+      <c r="A52" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="F52" s="7"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="11"/>
+      <c r="L52" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
@@ -3821,10 +3835,10 @@
     </row>
     <row r="53" spans="1:26" ht="14.25">
       <c r="A53" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -3852,18 +3866,14 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" spans="1:26" ht="14.25">
-      <c r="A54" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>109</v>
-      </c>
+      <c r="A54" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -3871,7 +3881,7 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
+      <c r="L54" s="11"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
@@ -3887,18 +3897,18 @@
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
     </row>
-    <row r="55" spans="1:26" ht="409.5">
+    <row r="55" spans="1:26" ht="14.25">
       <c r="A55" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -3923,15 +3933,19 @@
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
     </row>
-    <row r="56" spans="1:26" ht="14.25">
+    <row r="56" spans="1:26" ht="409.5">
       <c r="A56" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>113</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -3955,26 +3969,47 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26">
-      <c r="A57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" t="s">
-        <v>115</v>
-      </c>
-      <c r="L57" t="s">
-        <v>116</v>
-      </c>
+    <row r="57" spans="1:26" ht="14.25">
+      <c r="A57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
     </row>
     <row r="58" spans="1:26">
       <c r="A58" t="s">
         <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>118</v>
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:26">
@@ -3982,10 +4017,10 @@
         <v>42</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
-      </c>
-      <c r="L59" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="L59" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:26">
@@ -3993,10 +4028,10 @@
         <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L60" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:26">
@@ -4004,10 +4039,10 @@
         <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L61" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:26">
@@ -4015,10 +4050,10 @@
         <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L62" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:26">
@@ -4026,66 +4061,41 @@
         <v>42</v>
       </c>
       <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="L63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26">
+      <c r="A64" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" t="s">
+        <v>126</v>
+      </c>
+      <c r="L64" t="s">
         <v>127</v>
       </c>
-      <c r="L63" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" s="15"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-      <c r="N64" s="15"/>
-      <c r="O64" s="15"/>
-      <c r="P64" s="15"/>
-      <c r="Q64" s="15"/>
-      <c r="R64" s="15"/>
-      <c r="S64" s="15"/>
-      <c r="T64" s="15"/>
-      <c r="U64" s="15"/>
-      <c r="V64" s="15"/>
-      <c r="W64" s="15"/>
-      <c r="X64" s="15"/>
-      <c r="Y64" s="15"/>
-      <c r="Z64" s="15"/>
     </row>
     <row r="65" spans="1:1024">
       <c r="A65" s="15" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="15" t="s">
+        <v>131</v>
+      </c>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
@@ -4106,18 +4116,18 @@
       <c r="Y65" s="15"/>
       <c r="Z65" s="15"/>
     </row>
-    <row r="66" spans="1:1024" ht="130">
+    <row r="66" spans="1:1024">
       <c r="A66" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="15"/>
@@ -4142,18 +4152,18 @@
       <c r="Y66" s="15"/>
       <c r="Z66" s="15"/>
     </row>
-    <row r="67" spans="1:1024">
+    <row r="67" spans="1:1024" ht="130">
       <c r="A67" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>137</v>
       </c>
       <c r="E67" s="15"/>
       <c r="F67" s="15"/>
@@ -4183,13 +4193,13 @@
         <v>110</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
@@ -4216,13 +4226,17 @@
     </row>
     <row r="69" spans="1:1024">
       <c r="A69" s="15" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
+        <v>141</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
       <c r="G69" s="15"/>
@@ -4248,89 +4262,84 @@
     </row>
     <row r="70" spans="1:1024">
       <c r="A70" s="15" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>145</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
+      <c r="T70" s="15"/>
+      <c r="U70" s="15"/>
+      <c r="V70" s="15"/>
+      <c r="W70" s="15"/>
+      <c r="X70" s="15"/>
+      <c r="Y70" s="15"/>
+      <c r="Z70" s="15"/>
     </row>
     <row r="71" spans="1:1024">
       <c r="A71" s="15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:1024">
       <c r="A72" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1024">
+      <c r="A73" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B73" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1024" s="15" customFormat="1">
+      <c r="A74" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" s="18" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="73" spans="1:1024" s="15" customFormat="1">
-      <c r="A73" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B73" s="18" t="s">
+      <c r="C74" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="D74" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D73" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E73" s="18"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="18"/>
-      <c r="Q73" s="18"/>
-      <c r="R73" s="18"/>
-      <c r="S73" s="18"/>
-      <c r="T73" s="18"/>
-      <c r="U73" s="18"/>
-      <c r="V73" s="18"/>
-      <c r="W73" s="18"/>
-      <c r="X73" s="18"/>
-      <c r="Y73" s="18"/>
-      <c r="Z73" s="18"/>
-      <c r="AMJ73"/>
-    </row>
-    <row r="74" spans="1:1024" s="15" customFormat="1" ht="26">
-      <c r="A74" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B74" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C74" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>154</v>
-      </c>
       <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="18" t="s">
+        <v>131</v>
+      </c>
       <c r="H74" s="18"/>
       <c r="I74" s="18"/>
       <c r="J74" s="18"/>
@@ -4352,22 +4361,22 @@
       <c r="Z74" s="18"/>
       <c r="AMJ74"/>
     </row>
-    <row r="75" spans="1:1024" s="15" customFormat="1">
+    <row r="75" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A75" s="18" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>153</v>
+      </c>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
-      <c r="G75" s="18" t="s">
-        <v>156</v>
-      </c>
+      <c r="G75" s="18"/>
       <c r="H75" s="18"/>
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
@@ -4389,24 +4398,22 @@
       <c r="Z75" s="18"/>
       <c r="AMJ75"/>
     </row>
-    <row r="76" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    <row r="76" spans="1:1024" s="15" customFormat="1">
       <c r="A76" s="18" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>161</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
       <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
+      <c r="G76" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="H76" s="18"/>
       <c r="I76" s="18"/>
       <c r="J76" s="18"/>
@@ -4430,19 +4437,19 @@
     </row>
     <row r="77" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A77" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B77" s="18" t="s">
-        <v>162</v>
-      </c>
       <c r="C77" s="21" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="18"/>
@@ -4467,21 +4474,21 @@
       <c r="Z77" s="18"/>
       <c r="AMJ77"/>
     </row>
-    <row r="78" spans="1:1024" s="15" customFormat="1">
+    <row r="78" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A78" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>167</v>
+        <v>161</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>163</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18"/>
@@ -4506,21 +4513,21 @@
       <c r="Z78" s="18"/>
       <c r="AMJ78"/>
     </row>
-    <row r="79" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    <row r="79" spans="1:1024" s="15" customFormat="1">
       <c r="A79" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>170</v>
+        <v>164</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="18"/>
@@ -4545,16 +4552,22 @@
       <c r="Z79" s="18"/>
       <c r="AMJ79"/>
     </row>
-    <row r="80" spans="1:1024" s="15" customFormat="1">
+    <row r="80" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A80" s="18" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C80" s="22"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
+        <v>167</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>160</v>
+      </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18"/>
       <c r="H80" s="18"/>
@@ -4578,19 +4591,15 @@
       <c r="Z80" s="18"/>
       <c r="AMJ80"/>
     </row>
-    <row r="81" spans="1:1024" s="15" customFormat="1" ht="26">
+    <row r="81" spans="1:1024" s="15" customFormat="1">
       <c r="A81" s="18" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>173</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C81" s="22"/>
+      <c r="D81" s="18"/>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
       <c r="G81" s="18"/>
@@ -4615,18 +4624,18 @@
       <c r="Z81" s="18"/>
       <c r="AMJ81"/>
     </row>
-    <row r="82" spans="1:1024" s="15" customFormat="1" ht="39">
+    <row r="82" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A82" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>175</v>
+        <v>170</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
@@ -4652,22 +4661,22 @@
       <c r="Z82" s="18"/>
       <c r="AMJ82"/>
     </row>
-    <row r="83" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    <row r="83" spans="1:1024" s="15" customFormat="1" ht="39">
       <c r="A83" s="18" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" s="21"/>
+        <v>173</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>175</v>
+      </c>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
-      <c r="G83" s="18" t="s">
-        <v>156</v>
-      </c>
+      <c r="G83" s="18"/>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
@@ -4691,22 +4700,20 @@
     </row>
     <row r="84" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A84" s="18" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>161</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D84" s="21"/>
+      <c r="E84" s="18"/>
       <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
+      <c r="G84" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="H84" s="18"/>
       <c r="I84" s="18"/>
       <c r="J84" s="18"/>
@@ -4730,19 +4737,19 @@
     </row>
     <row r="85" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A85" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
@@ -4769,19 +4776,19 @@
     </row>
     <row r="86" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A86" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>186</v>
+        <v>181</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>182</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F86" s="18"/>
       <c r="G86" s="18"/>
@@ -4808,14 +4815,20 @@
     </row>
     <row r="87" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A87" s="18" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C87" s="21"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+        <v>183</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>160</v>
+      </c>
       <c r="F87" s="18"/>
       <c r="G87" s="18"/>
       <c r="H87" s="18"/>
@@ -4839,14 +4852,14 @@
       <c r="Z87" s="18"/>
       <c r="AMJ87"/>
     </row>
-    <row r="88" spans="1:1024" s="15" customFormat="1" ht="15.5" customHeight="1">
+    <row r="88" spans="1:1024" s="15" customFormat="1" ht="14.75">
       <c r="A88" s="18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C88" s="18"/>
+        <v>176</v>
+      </c>
+      <c r="C88" s="21"/>
       <c r="D88" s="18"/>
       <c r="E88" s="18"/>
       <c r="F88" s="18"/>
@@ -4855,9 +4868,7 @@
       <c r="I88" s="18"/>
       <c r="J88" s="18"/>
       <c r="K88" s="18"/>
-      <c r="L88" s="19" t="s">
-        <v>188</v>
-      </c>
+      <c r="L88" s="18"/>
       <c r="M88" s="18"/>
       <c r="N88" s="18"/>
       <c r="O88" s="18"/>
@@ -4874,31 +4885,25 @@
       <c r="Z88" s="18"/>
       <c r="AMJ88"/>
     </row>
-    <row r="89" spans="1:1024" s="15" customFormat="1" ht="13.75" customHeight="1">
+    <row r="89" spans="1:1024" s="15" customFormat="1" ht="15.5" customHeight="1">
       <c r="A89" s="18" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>192</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
       <c r="G89" s="18"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18"/>
       <c r="J89" s="18"/>
       <c r="K89" s="18"/>
-      <c r="L89" s="18"/>
+      <c r="L89" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="M89" s="18"/>
       <c r="N89" s="18"/>
       <c r="O89" s="18"/>
@@ -4915,22 +4920,24 @@
       <c r="Z89" s="18"/>
       <c r="AMJ89"/>
     </row>
-    <row r="90" spans="1:1024" s="15" customFormat="1" ht="24.5" customHeight="1">
+    <row r="90" spans="1:1024" s="15" customFormat="1" ht="13.75" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C90" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D90" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E90" s="18"/>
+        <v>188</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>160</v>
+      </c>
       <c r="F90" s="18" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G90" s="18"/>
       <c r="H90" s="18"/>
@@ -4954,17 +4961,23 @@
       <c r="Z90" s="18"/>
       <c r="AMJ90"/>
     </row>
-    <row r="91" spans="1:1024" s="15" customFormat="1">
+    <row r="91" spans="1:1024" s="15" customFormat="1" ht="24.5" customHeight="1">
       <c r="A91" s="18" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
+        <v>192</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>194</v>
+      </c>
       <c r="E91" s="18"/>
-      <c r="F91" s="22"/>
+      <c r="F91" s="18" t="s">
+        <v>195</v>
+      </c>
       <c r="G91" s="18"/>
       <c r="H91" s="18"/>
       <c r="I91" s="18"/>
@@ -4987,22 +5000,17 @@
       <c r="Z91" s="18"/>
       <c r="AMJ91"/>
     </row>
-    <row r="92" spans="1:1024" s="15" customFormat="1" ht="65">
+    <row r="92" spans="1:1024" s="15" customFormat="1">
       <c r="A92" s="18" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C92" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="F92" s="23" t="s">
-        <v>200</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="22"/>
       <c r="G92" s="18"/>
       <c r="H92" s="18"/>
       <c r="I92" s="18"/>
@@ -5025,21 +5033,23 @@
       <c r="Z92" s="18"/>
       <c r="AMJ92"/>
     </row>
-    <row r="93" spans="1:1024" s="15" customFormat="1">
+    <row r="93" spans="1:1024" s="15" customFormat="1" ht="65">
       <c r="A93" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="18"/>
-      <c r="E93" s="22"/>
-      <c r="G93" s="18" t="s">
-        <v>132</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="F93" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="G93" s="18"/>
       <c r="H93" s="18"/>
       <c r="I93" s="18"/>
       <c r="J93" s="18"/>
@@ -5061,37 +5071,25 @@
       <c r="Z93" s="18"/>
       <c r="AMJ93"/>
     </row>
-    <row r="94" spans="1:1024" s="15" customFormat="1" ht="34.25" customHeight="1">
+    <row r="94" spans="1:1024" s="15" customFormat="1">
       <c r="A94" s="18" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F94" s="22" t="s">
-        <v>206</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D94" s="18"/>
+      <c r="E94" s="22"/>
       <c r="G94" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I94" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="J94" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="K94" s="18" t="s">
-        <v>209</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
       <c r="L94" s="18"/>
       <c r="M94" s="18"/>
       <c r="N94" s="18"/>
@@ -5109,24 +5107,38 @@
       <c r="Z94" s="18"/>
       <c r="AMJ94"/>
     </row>
-    <row r="95" spans="1:1024" s="15" customFormat="1" ht="38" customHeight="1">
+    <row r="95" spans="1:1024" s="15" customFormat="1" ht="34.25" customHeight="1">
       <c r="A95" s="18" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C95" s="19"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="22"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-      <c r="H95" s="18"/>
-      <c r="I95" s="18"/>
-      <c r="J95" s="18"/>
-      <c r="L95" s="18" t="s">
-        <v>211</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="G95" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="I95" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="J95" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="K95" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="L95" s="18"/>
       <c r="M95" s="18"/>
       <c r="N95" s="18"/>
       <c r="O95" s="18"/>
@@ -5143,28 +5155,24 @@
       <c r="Z95" s="18"/>
       <c r="AMJ95"/>
     </row>
-    <row r="96" spans="1:1024" s="15" customFormat="1" ht="36.75" customHeight="1">
+    <row r="96" spans="1:1024" s="15" customFormat="1" ht="38" customHeight="1">
       <c r="A96" s="18" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="D96" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="F96" s="18" t="s">
-        <v>215</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C96" s="19"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="18"/>
       <c r="G96" s="18"/>
       <c r="H96" s="18"/>
       <c r="I96" s="18"/>
       <c r="J96" s="18"/>
-      <c r="K96" s="18"/>
-      <c r="L96" s="18"/>
+      <c r="L96" s="18" t="s">
+        <v>210</v>
+      </c>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
       <c r="O96" s="18"/>
@@ -5181,17 +5189,22 @@
       <c r="Z96" s="18"/>
       <c r="AMJ96"/>
     </row>
-    <row r="97" spans="1:1024" s="15" customFormat="1">
+    <row r="97" spans="1:1024" s="15" customFormat="1" ht="36.75" customHeight="1">
       <c r="A97" s="18" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="22"/>
-      <c r="F97" s="18"/>
+        <v>211</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>214</v>
+      </c>
       <c r="G97" s="18"/>
       <c r="H97" s="18"/>
       <c r="I97" s="18"/>
@@ -5214,23 +5227,18 @@
       <c r="Z97" s="18"/>
       <c r="AMJ97"/>
     </row>
-    <row r="98" spans="1:1024" s="15" customFormat="1" ht="26">
+    <row r="98" spans="1:1024" s="15" customFormat="1">
       <c r="A98" s="18" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>21</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C98" s="18"/>
       <c r="D98" s="18"/>
-      <c r="F98" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="G98" s="18" t="s">
-        <v>132</v>
-      </c>
+      <c r="E98" s="22"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
       <c r="H98" s="18"/>
       <c r="I98" s="18"/>
       <c r="J98" s="18"/>
@@ -5254,24 +5262,21 @@
     </row>
     <row r="99" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A99" s="18" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>161</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D99" s="18"/>
       <c r="F99" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="G99" s="18"/>
+        <v>205</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>131</v>
+      </c>
       <c r="H99" s="18"/>
       <c r="I99" s="18"/>
       <c r="J99" s="18"/>
@@ -5293,21 +5298,24 @@
       <c r="Z99" s="18"/>
       <c r="AMJ99"/>
     </row>
-    <row r="100" spans="1:1024" s="15" customFormat="1" ht="65">
+    <row r="100" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A100" s="18" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D100" s="20" t="s">
-        <v>223</v>
+        <v>217</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>160</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G100" s="18"/>
       <c r="H100" s="18"/>
@@ -5331,24 +5339,21 @@
       <c r="Z100" s="18"/>
       <c r="AMJ100"/>
     </row>
-    <row r="101" spans="1:1024" s="15" customFormat="1" ht="24.75" customHeight="1">
+    <row r="101" spans="1:1024" s="15" customFormat="1" ht="65">
       <c r="A101" s="18" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="D101" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="E101" s="18" t="s">
-        <v>161</v>
+        <v>221</v>
+      </c>
+      <c r="D101" s="20" t="s">
+        <v>222</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G101" s="18"/>
       <c r="H101" s="18"/>
@@ -5372,24 +5377,31 @@
       <c r="Z101" s="18"/>
       <c r="AMJ101"/>
     </row>
-    <row r="102" spans="1:1024" s="15" customFormat="1" ht="23" customHeight="1">
+    <row r="102" spans="1:1024" s="15" customFormat="1" ht="24.75" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
+        <v>223</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>205</v>
+      </c>
       <c r="G102" s="18"/>
       <c r="H102" s="18"/>
       <c r="I102" s="18"/>
       <c r="J102" s="18"/>
-      <c r="L102" s="19" t="s">
-        <v>228</v>
-      </c>
+      <c r="K102" s="18"/>
+      <c r="L102" s="18"/>
       <c r="M102" s="18"/>
       <c r="N102" s="18"/>
       <c r="O102" s="18"/>
@@ -5406,28 +5418,24 @@
       <c r="Z102" s="18"/>
       <c r="AMJ102"/>
     </row>
-    <row r="103" spans="1:1024" s="15" customFormat="1" ht="26">
+    <row r="103" spans="1:1024" s="15" customFormat="1" ht="23" customHeight="1">
       <c r="A103" s="18" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C103" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D103" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="F103" s="20" t="s">
-        <v>230</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
       <c r="G103" s="18"/>
       <c r="H103" s="18"/>
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
-      <c r="K103" s="18"/>
-      <c r="L103" s="18"/>
+      <c r="L103" s="19" t="s">
+        <v>227</v>
+      </c>
       <c r="M103" s="18"/>
       <c r="N103" s="18"/>
       <c r="O103" s="18"/>
@@ -5444,21 +5452,21 @@
       <c r="Z103" s="18"/>
       <c r="AMJ103"/>
     </row>
-    <row r="104" spans="1:1024" s="15" customFormat="1" ht="117">
+    <row r="104" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A104" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="F104" s="24" t="s">
-        <v>234</v>
+        <v>213</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>229</v>
       </c>
       <c r="G104" s="18"/>
       <c r="H104" s="18"/>
@@ -5482,17 +5490,22 @@
       <c r="Z104" s="18"/>
       <c r="AMJ104"/>
     </row>
-    <row r="105" spans="1:1024" s="15" customFormat="1">
+    <row r="105" spans="1:1024" s="15" customFormat="1" ht="117">
       <c r="A105" s="18" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
+        <v>230</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F105" s="24" t="s">
+        <v>233</v>
+      </c>
       <c r="G105" s="18"/>
       <c r="H105" s="18"/>
       <c r="I105" s="18"/>
@@ -5520,7 +5533,7 @@
         <v>36</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -5548,76 +5561,61 @@
       <c r="Z106" s="18"/>
       <c r="AMJ106"/>
     </row>
-    <row r="107" spans="1:1024">
-      <c r="A107" s="15" t="s">
+    <row r="107" spans="1:1024" s="15" customFormat="1">
+      <c r="A107" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18"/>
+      <c r="I107" s="18"/>
+      <c r="J107" s="18"/>
+      <c r="K107" s="18"/>
+      <c r="L107" s="18"/>
+      <c r="M107" s="18"/>
+      <c r="N107" s="18"/>
+      <c r="O107" s="18"/>
+      <c r="P107" s="18"/>
+      <c r="Q107" s="18"/>
+      <c r="R107" s="18"/>
+      <c r="S107" s="18"/>
+      <c r="T107" s="18"/>
+      <c r="U107" s="18"/>
+      <c r="V107" s="18"/>
+      <c r="W107" s="18"/>
+      <c r="X107" s="18"/>
+      <c r="Y107" s="18"/>
+      <c r="Z107" s="18"/>
+      <c r="AMJ107"/>
+    </row>
+    <row r="108" spans="1:1024">
+      <c r="A108" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B108" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G108" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="H107" s="15"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15"/>
-      <c r="L107" s="15"/>
-      <c r="M107" s="15"/>
-      <c r="N107" s="15"/>
-      <c r="O107" s="15"/>
-      <c r="P107" s="15"/>
-      <c r="Q107" s="15"/>
-      <c r="R107" s="15"/>
-      <c r="S107" s="15"/>
-      <c r="T107" s="15"/>
-      <c r="U107" s="15"/>
-      <c r="V107" s="15"/>
-      <c r="W107" s="15"/>
-      <c r="X107" s="15"/>
-      <c r="Y107" s="15"/>
-      <c r="Z107" s="15"/>
-    </row>
-    <row r="108" spans="1:1024" ht="14.75">
-      <c r="A108" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="E108" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F108" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="G108" s="15"/>
       <c r="H108" s="15"/>
-      <c r="I108" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="J108" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="K108" s="26" t="s">
-        <v>209</v>
-      </c>
+      <c r="I108" s="15"/>
+      <c r="J108" s="15"/>
+      <c r="K108" s="15"/>
       <c r="L108" s="15"/>
-      <c r="M108" s="14" t="s">
-        <v>243</v>
-      </c>
+      <c r="M108" s="15"/>
       <c r="N108" s="15"/>
       <c r="O108" s="15"/>
       <c r="P108" s="15"/>
@@ -5632,24 +5630,40 @@
       <c r="Y108" s="15"/>
       <c r="Z108" s="15"/>
     </row>
-    <row r="109" spans="1:1024">
+    <row r="109" spans="1:1024" ht="14.75">
       <c r="A109" s="15" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
+        <v>237</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>240</v>
+      </c>
       <c r="G109" s="15"/>
       <c r="H109" s="15"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="15"/>
-      <c r="K109" s="15"/>
+      <c r="I109" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="J109" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="K109" s="26" t="s">
+        <v>208</v>
+      </c>
       <c r="L109" s="15"/>
-      <c r="M109" s="15"/>
+      <c r="M109" s="14" t="s">
+        <v>242</v>
+      </c>
       <c r="N109" s="15"/>
       <c r="O109" s="15"/>
       <c r="P109" s="15"/>
@@ -5666,20 +5680,16 @@
     </row>
     <row r="110" spans="1:1024">
       <c r="A110" s="15" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C110" s="15"/>
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
-      <c r="F110" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="G110" s="15" t="s">
-        <v>246</v>
-      </c>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
       <c r="H110" s="15"/>
       <c r="I110" s="15"/>
       <c r="J110" s="15"/>
@@ -5700,24 +5710,22 @@
       <c r="Y110" s="15"/>
       <c r="Z110" s="15"/>
     </row>
-    <row r="111" spans="1:1024" ht="14.75">
+    <row r="111" spans="1:1024">
       <c r="A111" s="15" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>249</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
       <c r="E111" s="15"/>
-      <c r="F111" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="G111" s="15"/>
+      <c r="F111" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>245</v>
+      </c>
       <c r="H111" s="15"/>
       <c r="I111" s="15"/>
       <c r="J111" s="15"/>
@@ -5738,22 +5746,22 @@
       <c r="Y111" s="15"/>
       <c r="Z111" s="15"/>
     </row>
-    <row r="112" spans="1:1024">
+    <row r="112" spans="1:1024" ht="14.75">
       <c r="A112" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>252</v>
+      <c r="B112" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>247</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="27" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15"/>
@@ -5776,276 +5784,297 @@
       <c r="Y112" s="15"/>
       <c r="Z112" s="15"/>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:26">
       <c r="A113" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>257</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="E113" s="15"/>
       <c r="F113" s="27" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>253</v>
+      </c>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15"/>
+      <c r="L113" s="15"/>
+      <c r="M113" s="15"/>
+      <c r="N113" s="15"/>
+      <c r="O113" s="15"/>
+      <c r="P113" s="15"/>
+      <c r="Q113" s="15"/>
+      <c r="R113" s="15"/>
+      <c r="S113" s="15"/>
+      <c r="T113" s="15"/>
+      <c r="U113" s="15"/>
+      <c r="V113" s="15"/>
+      <c r="W113" s="15"/>
+      <c r="X113" s="15"/>
+      <c r="Y113" s="15"/>
+      <c r="Z113" s="15"/>
+    </row>
+    <row r="114" spans="1:26">
       <c r="A114" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F114" s="27" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26">
       <c r="A115" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B115" s="14" t="s">
-        <v>263</v>
+      <c r="B115" s="18" t="s">
+        <v>258</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26">
       <c r="A116" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B116" s="18" t="s">
-        <v>267</v>
+      <c r="B116" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F116" s="27" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26">
       <c r="A117" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B117" s="14" t="s">
-        <v>271</v>
+      <c r="B117" s="18" t="s">
+        <v>266</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F117" s="27" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26">
       <c r="A118" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F118" s="27" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26">
       <c r="A119" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F119" s="27" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26">
       <c r="A120" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="F120" s="27" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26">
       <c r="A121" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="F121" s="27" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26">
       <c r="A122" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B122" s="18" t="s">
-        <v>290</v>
+      <c r="B122" s="14" t="s">
+        <v>285</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26">
       <c r="A123" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B123" s="14" t="s">
-        <v>294</v>
+      <c r="B123" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26">
       <c r="A124" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="D124" t="s">
-        <v>300</v>
+        <v>294</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26">
       <c r="A125" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
+      </c>
+      <c r="D125" t="s">
+        <v>299</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26">
       <c r="A126" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F126" s="27" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26">
       <c r="A127" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F127" s="27" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26">
       <c r="A128" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F128" s="27" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" spans="1:1024">
@@ -6053,16 +6082,16 @@
         <v>110</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F129" s="27" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130" spans="1:1024">
@@ -6070,16 +6099,16 @@
         <v>110</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F130" s="27" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="131" spans="1:1024">
@@ -6087,16 +6116,16 @@
         <v>110</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F131" s="27" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="132" spans="1:1024">
@@ -6104,16 +6133,16 @@
         <v>110</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F132" s="27" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="133" spans="1:1024">
@@ -6121,267 +6150,267 @@
         <v>110</v>
       </c>
       <c r="B133" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D133" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="F133" s="27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1024">
+      <c r="A134" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C134" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C133" s="15" t="s">
+      <c r="D134" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="D133" s="14" t="s">
+      <c r="F134" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="F133" s="27" t="s">
+    </row>
+    <row r="135" spans="1:1024">
+      <c r="A135" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B135" s="14" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="134" spans="1:1024">
-      <c r="A134" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B134" s="14" t="s">
+      <c r="C135" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C134" s="15" t="s">
+      <c r="D135" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="D134" s="14" t="s">
+      <c r="F135" s="27" t="s">
         <v>340</v>
-      </c>
-      <c r="F134" s="27" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1024">
-      <c r="A135" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="D135" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="F135" s="27" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="136" spans="1:1024">
       <c r="A136" s="15" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>244</v>
+        <v>341</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="F136" s="27" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="137" spans="1:1024">
       <c r="A137" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1024">
+      <c r="A138" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B137" s="14" t="s">
+      <c r="B138" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="C138" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="C137" s="14" t="s">
+      <c r="D138" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="D137" s="14" t="s">
+      <c r="F138" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G138" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1024" s="15" customFormat="1" ht="39">
+      <c r="A139" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B139" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="F137" s="27" t="s">
+      <c r="C139" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="F139" s="27"/>
+      <c r="AMJ139"/>
+    </row>
+    <row r="140" spans="1:1024">
+      <c r="A140" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="E140" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I140" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="G137" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1024" s="15" customFormat="1" ht="39">
-      <c r="A138" s="14" t="s">
+      <c r="J140" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="K140" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="M140" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1024" s="15" customFormat="1">
+      <c r="A141" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B138" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C138" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="F138" s="27"/>
-      <c r="AMJ138"/>
-    </row>
-    <row r="139" spans="1:1024">
-      <c r="A139" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="B139" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C139" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="I139" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="J139" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="K139" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="M139" s="14" t="s">
+      <c r="B141" s="15" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="140" spans="1:1024" s="15" customFormat="1">
-      <c r="A140" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B140" s="15" t="s">
+      <c r="C141" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C140" s="15" t="s">
+      <c r="D141" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D140" s="14" t="s">
+      <c r="AMJ141"/>
+    </row>
+    <row r="142" spans="1:1024">
+      <c r="A142" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B142" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="AMJ140"/>
-    </row>
-    <row r="141" spans="1:1024">
-      <c r="A141" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B141" s="15" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1024" s="15" customFormat="1">
-      <c r="A142" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B142" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="D142" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="F142" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="G142" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="AMJ142"/>
     </row>
     <row r="143" spans="1:1024" s="15" customFormat="1">
       <c r="A143" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="B143" s="15" t="s">
-        <v>353</v>
+        <v>106</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>360</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="E143" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="I143" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="M143" s="14" t="s">
-        <v>356</v>
+        <v>347</v>
+      </c>
+      <c r="F143" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="G143" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="AMJ143"/>
     </row>
     <row r="144" spans="1:1024" s="15" customFormat="1">
       <c r="A144" s="15" t="s">
-        <v>110</v>
+        <v>351</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>359</v>
+        <v>354</v>
+      </c>
+      <c r="E144" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I144" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="M144" s="14" t="s">
+        <v>355</v>
       </c>
       <c r="AMJ144"/>
     </row>
     <row r="145" spans="1:1024" s="15" customFormat="1">
       <c r="A145" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>361</v>
+        <v>110</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D145" s="14" t="s">
+        <v>358</v>
       </c>
       <c r="AMJ145"/>
     </row>
     <row r="146" spans="1:1024" s="15" customFormat="1">
       <c r="A146" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="AMJ146"/>
+    </row>
+    <row r="147" spans="1:1024" s="15" customFormat="1">
+      <c r="A147" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B146" s="15" t="s">
+      <c r="B147" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="D147" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="C146" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="D146" s="14" t="s">
+      <c r="F147" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="F146" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="AMJ146"/>
-    </row>
-    <row r="147" spans="1:1024">
-      <c r="A147" t="s">
-        <v>110</v>
-      </c>
-      <c r="B147" t="s">
-        <v>367</v>
-      </c>
-      <c r="C147" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="D147" s="26" t="s">
-        <v>369</v>
-      </c>
-      <c r="F147" t="s">
-        <v>370</v>
-      </c>
+      <c r="AMJ147"/>
     </row>
     <row r="148" spans="1:1024">
       <c r="A148" t="s">
         <v>110</v>
       </c>
       <c r="B148" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C148" s="26" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D148" s="26" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F148" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="149" spans="1:1024">
@@ -6389,16 +6418,16 @@
         <v>110</v>
       </c>
       <c r="B149" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C149" s="26" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D149" s="26" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F149" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="150" spans="1:1024">
@@ -6406,16 +6435,16 @@
         <v>110</v>
       </c>
       <c r="B150" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C150" s="26" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D150" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F150" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="151" spans="1:1024">
@@ -6423,16 +6452,16 @@
         <v>110</v>
       </c>
       <c r="B151" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C151" s="26" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F151" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="152" spans="1:1024">
@@ -6440,16 +6469,16 @@
         <v>110</v>
       </c>
       <c r="B152" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C152" s="26" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F152" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:1024">
@@ -6457,101 +6486,79 @@
         <v>110</v>
       </c>
       <c r="B153" t="s">
+        <v>386</v>
+      </c>
+      <c r="C153" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="D153" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="F153" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1024">
+      <c r="A154" t="s">
+        <v>110</v>
+      </c>
+      <c r="B154" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="D154" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="D153" s="26" t="s">
+      <c r="F154" t="s">
         <v>393</v>
       </c>
-      <c r="F153" t="s">
+    </row>
+    <row r="155" spans="1:1024" s="15" customFormat="1">
+      <c r="A155" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="AMJ155"/>
+    </row>
+    <row r="156" spans="1:1024">
+      <c r="A156" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B156" s="15" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="154" spans="1:1024" s="15" customFormat="1">
-      <c r="A154" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="AMJ154"/>
-    </row>
-    <row r="155" spans="1:1024">
-      <c r="A155" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B155" s="15" t="s">
+      <c r="C156" t="s">
         <v>395</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D156" t="s">
         <v>396</v>
       </c>
-      <c r="D155" t="s">
-        <v>397</v>
-      </c>
-      <c r="G155" t="s">
-        <v>246</v>
-      </c>
-      <c r="J155" s="18"/>
-    </row>
-    <row r="156" spans="1:1024" s="15" customFormat="1">
-      <c r="A156" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B156" s="18" t="s">
-        <v>398</v>
-      </c>
-      <c r="C156" s="18" t="s">
-        <v>399</v>
-      </c>
-      <c r="D156" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="F156" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="G156" s="18"/>
-      <c r="H156" s="18"/>
-      <c r="I156" s="18"/>
+      <c r="G156" t="s">
+        <v>245</v>
+      </c>
       <c r="J156" s="18"/>
-      <c r="K156" s="18"/>
-      <c r="L156" s="18"/>
-      <c r="M156" s="18"/>
-      <c r="N156" s="18"/>
-      <c r="O156" s="18"/>
-      <c r="P156" s="18"/>
-      <c r="Q156" s="18"/>
-      <c r="R156" s="18"/>
-      <c r="S156" s="18"/>
-      <c r="T156" s="18"/>
-      <c r="U156" s="18"/>
-      <c r="V156" s="18"/>
-      <c r="W156" s="18"/>
-      <c r="X156" s="18"/>
-      <c r="Y156" s="18"/>
-      <c r="AMJ156"/>
-    </row>
-    <row r="157" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="157" spans="1:1024" s="15" customFormat="1">
       <c r="A157" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="D157" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="F157" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="G157" s="18" t="s">
-        <v>406</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="D157" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="F157" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="G157" s="18"/>
       <c r="H157" s="18"/>
       <c r="I157" s="18"/>
       <c r="J157" s="18"/>
@@ -6572,27 +6579,28 @@
       <c r="Y157" s="18"/>
       <c r="AMJ157"/>
     </row>
-    <row r="158" spans="1:1024" s="15" customFormat="1" ht="57">
+    <row r="158" spans="1:1024" s="15" customFormat="1" ht="26">
       <c r="A158" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="D158" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="F158" s="30" t="s">
-        <v>410</v>
+        <v>402</v>
+      </c>
+      <c r="D158" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="F158" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H158" s="18"/>
       <c r="I158" s="18"/>
+      <c r="J158" s="18"/>
       <c r="K158" s="18"/>
       <c r="L158" s="18"/>
       <c r="M158" s="18"/>
@@ -6610,72 +6618,98 @@
       <c r="Y158" s="18"/>
       <c r="AMJ158"/>
     </row>
-    <row r="159" spans="1:1024">
-      <c r="A159" s="15" t="s">
+    <row r="159" spans="1:1024" s="15" customFormat="1" ht="57">
+      <c r="A159" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C159" t="s">
-        <v>412</v>
-      </c>
-      <c r="D159" t="s">
-        <v>413</v>
-      </c>
+      <c r="B159" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C159" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="D159" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="F159" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="G159" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="H159" s="18"/>
+      <c r="I159" s="18"/>
+      <c r="K159" s="18"/>
+      <c r="L159" s="18"/>
+      <c r="M159" s="18"/>
+      <c r="N159" s="18"/>
+      <c r="O159" s="18"/>
+      <c r="P159" s="18"/>
+      <c r="Q159" s="18"/>
+      <c r="R159" s="18"/>
+      <c r="S159" s="18"/>
+      <c r="T159" s="18"/>
+      <c r="U159" s="18"/>
+      <c r="V159" s="18"/>
+      <c r="W159" s="18"/>
+      <c r="X159" s="18"/>
+      <c r="Y159" s="18"/>
+      <c r="AMJ159"/>
     </row>
     <row r="160" spans="1:1024">
       <c r="A160" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C160" t="s">
+        <v>411</v>
+      </c>
+      <c r="D160" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1024">
+      <c r="A161" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="J160" s="18"/>
-    </row>
-    <row r="161" spans="1:1024" s="15" customFormat="1" ht="31" customHeight="1">
-      <c r="A161" s="18" t="s">
+      <c r="B161" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="J161" s="18"/>
+    </row>
+    <row r="162" spans="1:1024" s="15" customFormat="1" ht="31" customHeight="1">
+      <c r="A162" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B161" s="18" t="s">
+      <c r="B162" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="C162" s="18"/>
+      <c r="D162" s="18"/>
+      <c r="E162" s="18"/>
+      <c r="F162" s="18"/>
+      <c r="G162" s="18"/>
+      <c r="H162" s="18"/>
+      <c r="I162" s="18"/>
+      <c r="L162" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="C161" s="18"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="18"/>
-      <c r="F161" s="18"/>
-      <c r="G161" s="18"/>
-      <c r="H161" s="18"/>
-      <c r="I161" s="18"/>
-      <c r="L161" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="M161" s="18"/>
-      <c r="N161" s="18"/>
-      <c r="O161" s="18"/>
-      <c r="P161" s="18"/>
-      <c r="Q161" s="18"/>
-      <c r="R161" s="18"/>
-      <c r="S161" s="18"/>
-      <c r="T161" s="18"/>
-      <c r="U161" s="18"/>
-      <c r="V161" s="18"/>
-      <c r="W161" s="18"/>
-      <c r="X161" s="18"/>
-      <c r="Y161" s="18"/>
-      <c r="Z161" s="18"/>
-      <c r="AMJ161"/>
-    </row>
-    <row r="162" spans="1:1024" s="15" customFormat="1">
-      <c r="A162" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B162" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="L162" s="28" t="s">
-        <v>417</v>
-      </c>
+      <c r="M162" s="18"/>
+      <c r="N162" s="18"/>
+      <c r="O162" s="18"/>
+      <c r="P162" s="18"/>
+      <c r="Q162" s="18"/>
+      <c r="R162" s="18"/>
+      <c r="S162" s="18"/>
+      <c r="T162" s="18"/>
+      <c r="U162" s="18"/>
+      <c r="V162" s="18"/>
+      <c r="W162" s="18"/>
+      <c r="X162" s="18"/>
+      <c r="Y162" s="18"/>
+      <c r="Z162" s="18"/>
       <c r="AMJ162"/>
     </row>
     <row r="163" spans="1:1024" s="15" customFormat="1">
@@ -6683,10 +6717,10 @@
         <v>42</v>
       </c>
       <c r="B163" s="28" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AMJ163"/>
     </row>
@@ -6695,19 +6729,31 @@
         <v>42</v>
       </c>
       <c r="B164" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="L164" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="AMJ164"/>
+    </row>
+    <row r="165" spans="1:1024" s="15" customFormat="1">
+      <c r="A165" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B165" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="L165" s="28" t="s">
         <v>420</v>
       </c>
-      <c r="L164" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="AMJ164"/>
+      <c r="AMJ165"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L35:Q35"/>
+    <mergeCell ref="L36:Q36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6725,7 +6771,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>1</v>
@@ -6763,16 +6809,16 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C2" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>249</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
@@ -6799,16 +6845,16 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="14" t="s">
         <v>252</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>253</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -6835,16 +6881,16 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="14" t="s">
         <v>256</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>257</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
@@ -6871,16 +6917,16 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B5" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D5" s="14" t="s">
         <v>260</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>261</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
@@ -6907,16 +6953,16 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>264</v>
-      </c>
       <c r="D6" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
@@ -6943,16 +6989,16 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>269</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
@@ -6979,16 +7025,16 @@
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="14" t="s">
         <v>272</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>273</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
@@ -7015,16 +7061,16 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>277</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
@@ -7051,16 +7097,16 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="D10" s="14" t="s">
         <v>280</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>281</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
@@ -7087,16 +7133,16 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B11" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>284</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
@@ -7123,16 +7169,16 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="D12" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>288</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -7159,16 +7205,16 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="D13" s="14" t="s">
         <v>291</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>292</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
@@ -7195,16 +7241,16 @@
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="14" t="s">
         <v>295</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>296</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
@@ -7231,16 +7277,16 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="D15" s="14" t="s">
         <v>299</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>300</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
@@ -7267,16 +7313,16 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="D16" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>304</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
@@ -7303,16 +7349,16 @@
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="D17" s="14" t="s">
         <v>307</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>308</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
@@ -7339,16 +7385,16 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="D18" s="14" t="s">
         <v>311</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>312</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -7375,16 +7421,16 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="D19" s="14" t="s">
         <v>315</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>316</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
@@ -7411,16 +7457,16 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="D20" s="14" t="s">
         <v>319</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>320</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -7447,16 +7493,16 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="D21" s="14" t="s">
         <v>323</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>324</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -7483,16 +7529,16 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>327</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>328</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
@@ -7519,16 +7565,16 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="D23" s="14" t="s">
         <v>331</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>332</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -7555,16 +7601,16 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="D24" s="14" t="s">
         <v>335</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>336</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
@@ -7591,16 +7637,16 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="D25" s="14" t="s">
         <v>339</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>340</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
@@ -7627,16 +7673,16 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C26" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>344</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
@@ -7663,16 +7709,16 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="D27" s="14" t="s">
         <v>428</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>429</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
@@ -7699,156 +7745,156 @@
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>432</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>435</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>438</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B31" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>441</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B32" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>444</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>447</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>450</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B35" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>428</v>
-      </c>
       <c r="D35" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="D36" s="14" t="s">
         <v>453</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>456</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B38" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="D38" s="20" t="s">
         <v>459</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>460</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
@@ -7875,16 +7921,16 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="D39" s="18" t="s">
         <v>462</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>463</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
@@ -7911,16 +7957,16 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B40" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="D40" s="18" t="s">
         <v>465</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>466</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
@@ -7947,16 +7993,16 @@
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B41" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="D41" s="20" t="s">
         <v>468</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>469</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
@@ -7983,16 +8029,16 @@
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B42" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="C42" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="D42" s="18" t="s">
         <v>471</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>472</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -8019,16 +8065,16 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="D43" s="20" t="s">
         <v>474</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>475</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
@@ -8055,16 +8101,16 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B44" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="C44" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="D44" s="20" t="s">
         <v>477</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>478</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -8091,16 +8137,16 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B45" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="C45" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="D45" s="20" t="s">
         <v>480</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>481</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -8127,16 +8173,16 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B46" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="D46" s="20" t="s">
         <v>483</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>484</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
@@ -8163,16 +8209,16 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B47" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="D47" s="20" t="s">
         <v>486</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>487</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
@@ -8199,16 +8245,16 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B48" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="C48" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="D48" s="20" t="s">
         <v>489</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>490</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
@@ -8235,16 +8281,16 @@
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B49" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="C49" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="D49" s="20" t="s">
         <v>492</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>493</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -8271,16 +8317,16 @@
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B50" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="C50" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>495</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>496</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -8307,16 +8353,16 @@
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1">
       <c r="A51" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B51" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="D51" s="20" t="s">
         <v>428</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>429</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
@@ -8359,22 +8405,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>497</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="C1" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>500</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="31" t="s">
         <v>501</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>502</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
@@ -8399,19 +8445,19 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>508</v>
-      </c>
       <c r="C2" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>503</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="E2" s="25" t="s">
         <v>504</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>505</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="15"/>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5300" tabRatio="384"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="516">
   <si>
     <t>type</t>
   </si>
@@ -1171,9 +1171,6 @@
     <t>mitigation_qn</t>
   </si>
   <si>
-    <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito ? </t>
-  </si>
-  <si>
     <t>(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
   </si>
   <si>
@@ -1614,13 +1611,37 @@
   </si>
   <si>
     <t>../inputs/gestation_in_weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kifafa cha mimba
+Mama akipata tatizo hili hukutika mfano wa homa ya mdudu na kupoteza faham, kifafa cha mimba hutokea kabla au baada ya mama kujifungua. 
+</t>
+  </si>
+  <si>
+    <t>Milalo mibaya
+Kutokea akiwa na mlalo usio wa kawaida wakati wa mtoto kuzaliwa</t>
+  </si>
+  <si>
+    <t>Mtoto kutanguliza makalio 
+Mtoto kutokeza makalio wakati wa kuzaliwa kawaida atokee kichwa ili azae salama.</t>
+  </si>
+  <si>
+    <t>Seli mundu 
+Maradhi ya homa ya mifupa/seli nundu, mwenye maradhi haya chembe chembe nyekundu za damu huwa kidogo na hazikukamilika, hupekelea kuwa na ukosefu wa damu mara kwa mara</t>
+  </si>
+  <si>
+    <t>Maradhi ya moyo 
+Haya ni maradhi sugu ambapo moyo hushindwa kufanya kazi vizuri na tujuwe kwamba moyo ni kiungo kinacho sambaza damu safi kwenda sehemu zote za mwili</t>
+  </si>
+  <si>
+    <t>Mkakati wa kuepuka sababu za hatari za ujauzito</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1636,18 +1657,18 @@
     <font>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1685,7 +1706,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1696,7 +1717,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1709,10 +1730,16 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1749,7 +1776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1812,8 +1839,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2301,10 +2331,10 @@
         <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>508</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>509</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -3271,14 +3301,14 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="34" t="s">
+      <c r="L36" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
@@ -4009,7 +4039,7 @@
         <v>115</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="59" spans="1:26">
@@ -5033,7 +5063,7 @@
       <c r="Z92" s="18"/>
       <c r="AMJ92"/>
     </row>
-    <row r="93" spans="1:1024" s="15" customFormat="1" ht="65">
+    <row r="93" spans="1:1024" s="15" customFormat="1" ht="52">
       <c r="A93" s="18" t="s">
         <v>19</v>
       </c>
@@ -5490,7 +5520,7 @@
       <c r="Z104" s="18"/>
       <c r="AMJ104"/>
     </row>
-    <row r="105" spans="1:1024" s="15" customFormat="1" ht="117">
+    <row r="105" spans="1:1024" s="15" customFormat="1" ht="78">
       <c r="A105" s="18" t="s">
         <v>110</v>
       </c>
@@ -5941,7 +5971,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="121" spans="1:26">
+    <row r="121" spans="1:26" ht="65">
       <c r="A121" s="15" t="s">
         <v>110</v>
       </c>
@@ -5951,8 +5981,8 @@
       <c r="C121" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="D121" s="14" t="s">
-        <v>185</v>
+      <c r="D121" s="18" t="s">
+        <v>510</v>
       </c>
       <c r="F121" s="27" t="s">
         <v>284</v>
@@ -6009,7 +6039,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="125" spans="1:26">
+    <row r="125" spans="1:26" ht="39">
       <c r="A125" s="15" t="s">
         <v>110</v>
       </c>
@@ -6019,14 +6049,14 @@
       <c r="C125" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="D125" t="s">
-        <v>299</v>
+      <c r="D125" s="36" t="s">
+        <v>511</v>
       </c>
       <c r="F125" s="27" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="126" spans="1:26">
+    <row r="126" spans="1:26" ht="39">
       <c r="A126" s="15" t="s">
         <v>110</v>
       </c>
@@ -6036,8 +6066,8 @@
       <c r="C126" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="D126" s="14" t="s">
-        <v>303</v>
+      <c r="D126" s="18" t="s">
+        <v>512</v>
       </c>
       <c r="F126" s="27" t="s">
         <v>304</v>
@@ -6077,7 +6107,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="129" spans="1:1024">
+    <row r="129" spans="1:1024" ht="65">
       <c r="A129" s="15" t="s">
         <v>110</v>
       </c>
@@ -6087,14 +6117,14 @@
       <c r="C129" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="D129" s="14" t="s">
-        <v>315</v>
+      <c r="D129" s="18" t="s">
+        <v>513</v>
       </c>
       <c r="F129" s="27" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="130" spans="1:1024">
+    <row r="130" spans="1:1024" ht="52">
       <c r="A130" s="15" t="s">
         <v>110</v>
       </c>
@@ -6104,8 +6134,8 @@
       <c r="C130" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="D130" s="14" t="s">
-        <v>319</v>
+      <c r="D130" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="F130" s="27" t="s">
         <v>320</v>
@@ -6389,10 +6419,10 @@
         <v>346</v>
       </c>
       <c r="D147" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="F147" s="14" t="s">
         <v>364</v>
-      </c>
-      <c r="F147" s="14" t="s">
-        <v>365</v>
       </c>
       <c r="AMJ147"/>
     </row>
@@ -6401,16 +6431,16 @@
         <v>110</v>
       </c>
       <c r="B148" t="s">
+        <v>365</v>
+      </c>
+      <c r="C148" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="C148" s="26" t="s">
+      <c r="D148" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="D148" s="26" t="s">
+      <c r="F148" t="s">
         <v>368</v>
-      </c>
-      <c r="F148" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="149" spans="1:1024">
@@ -6418,16 +6448,16 @@
         <v>110</v>
       </c>
       <c r="B149" t="s">
+        <v>369</v>
+      </c>
+      <c r="C149" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="D149" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="F149" t="s">
         <v>372</v>
-      </c>
-      <c r="F149" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="150" spans="1:1024">
@@ -6435,16 +6465,16 @@
         <v>110</v>
       </c>
       <c r="B150" t="s">
+        <v>373</v>
+      </c>
+      <c r="C150" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="D150" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="D150" s="26" t="s">
+      <c r="F150" t="s">
         <v>376</v>
-      </c>
-      <c r="F150" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="151" spans="1:1024">
@@ -6452,16 +6482,16 @@
         <v>110</v>
       </c>
       <c r="B151" t="s">
+        <v>377</v>
+      </c>
+      <c r="C151" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="D151" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="D151" s="26" t="s">
+      <c r="F151" t="s">
         <v>380</v>
-      </c>
-      <c r="F151" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="152" spans="1:1024">
@@ -6469,16 +6499,16 @@
         <v>110</v>
       </c>
       <c r="B152" t="s">
+        <v>381</v>
+      </c>
+      <c r="C152" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="D152" s="26" t="s">
         <v>383</v>
       </c>
-      <c r="D152" s="26" t="s">
+      <c r="F152" t="s">
         <v>384</v>
-      </c>
-      <c r="F152" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:1024">
@@ -6486,16 +6516,16 @@
         <v>110</v>
       </c>
       <c r="B153" t="s">
+        <v>385</v>
+      </c>
+      <c r="C153" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="D153" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="D153" s="26" t="s">
+      <c r="F153" t="s">
         <v>388</v>
-      </c>
-      <c r="F153" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="154" spans="1:1024">
@@ -6503,16 +6533,16 @@
         <v>110</v>
       </c>
       <c r="B154" t="s">
+        <v>389</v>
+      </c>
+      <c r="C154" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="D154" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="D154" s="26" t="s">
+      <c r="F154" t="s">
         <v>392</v>
-      </c>
-      <c r="F154" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:1024" s="15" customFormat="1">
@@ -6529,13 +6559,13 @@
         <v>106</v>
       </c>
       <c r="B156" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" t="s">
         <v>394</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>395</v>
-      </c>
-      <c r="D156" t="s">
-        <v>396</v>
       </c>
       <c r="G156" t="s">
         <v>245</v>
@@ -6547,16 +6577,16 @@
         <v>110</v>
       </c>
       <c r="B157" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C157" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C157" s="18" t="s">
+      <c r="D157" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="D157" s="20" t="s">
+      <c r="F157" s="18" t="s">
         <v>399</v>
-      </c>
-      <c r="F157" s="18" t="s">
-        <v>400</v>
       </c>
       <c r="G157" s="18"/>
       <c r="H157" s="18"/>
@@ -6584,19 +6614,19 @@
         <v>110</v>
       </c>
       <c r="B158" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C158" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="C158" s="18" t="s">
+      <c r="D158" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="D158" s="29" t="s">
+      <c r="F158" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="F158" s="19" t="s">
+      <c r="G158" s="18" t="s">
         <v>404</v>
-      </c>
-      <c r="G158" s="18" t="s">
-        <v>405</v>
       </c>
       <c r="H158" s="18"/>
       <c r="I158" s="18"/>
@@ -6618,24 +6648,24 @@
       <c r="Y158" s="18"/>
       <c r="AMJ158"/>
     </row>
-    <row r="159" spans="1:1024" s="15" customFormat="1" ht="57">
+    <row r="159" spans="1:1024" s="15" customFormat="1" ht="42.75">
       <c r="A159" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B159" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C159" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="C159" s="18" t="s">
+      <c r="D159" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="D159" s="18" t="s">
+      <c r="F159" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="F159" s="30" t="s">
-        <v>409</v>
-      </c>
       <c r="G159" s="18" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H159" s="18"/>
       <c r="I159" s="18"/>
@@ -6661,13 +6691,13 @@
         <v>110</v>
       </c>
       <c r="B160" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C160" t="s">
         <v>410</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>411</v>
-      </c>
-      <c r="D160" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:1024">
@@ -6675,7 +6705,7 @@
         <v>114</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J161" s="18"/>
     </row>
@@ -6684,7 +6714,7 @@
         <v>42</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C162" s="18"/>
       <c r="D162" s="18"/>
@@ -6694,7 +6724,7 @@
       <c r="H162" s="18"/>
       <c r="I162" s="18"/>
       <c r="L162" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M162" s="18"/>
       <c r="N162" s="18"/>
@@ -6717,10 +6747,10 @@
         <v>42</v>
       </c>
       <c r="B163" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="L163" s="28" t="s">
         <v>415</v>
-      </c>
-      <c r="L163" s="28" t="s">
-        <v>416</v>
       </c>
       <c r="AMJ163"/>
     </row>
@@ -6729,10 +6759,10 @@
         <v>42</v>
       </c>
       <c r="B164" s="28" t="s">
+        <v>416</v>
+      </c>
+      <c r="L164" s="28" t="s">
         <v>417</v>
-      </c>
-      <c r="L164" s="28" t="s">
-        <v>418</v>
       </c>
       <c r="AMJ164"/>
     </row>
@@ -6741,10 +6771,10 @@
         <v>42</v>
       </c>
       <c r="B165" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="L165" s="28" t="s">
         <v>419</v>
-      </c>
-      <c r="L165" s="28" t="s">
-        <v>420</v>
       </c>
       <c r="AMJ165"/>
     </row>
@@ -6771,7 +6801,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>1</v>
@@ -6812,7 +6842,7 @@
         <v>237</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>247</v>
@@ -6962,7 +6992,7 @@
         <v>263</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
@@ -7532,7 +7562,7 @@
         <v>237</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>326</v>
@@ -7676,7 +7706,7 @@
         <v>237</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>342</v>
@@ -7712,13 +7742,13 @@
         <v>237</v>
       </c>
       <c r="B27" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="D27" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>428</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
@@ -7745,142 +7775,142 @@
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>431</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>434</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>437</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B31" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>440</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B32" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>443</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>446</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>449</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B35" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>427</v>
-      </c>
       <c r="D35" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>160</v>
       </c>
       <c r="C36" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>452</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>455</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:26">
@@ -7888,13 +7918,13 @@
         <v>202</v>
       </c>
       <c r="B38" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>457</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="D38" s="20" t="s">
         <v>458</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>459</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
@@ -7924,13 +7954,13 @@
         <v>202</v>
       </c>
       <c r="B39" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>460</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="D39" s="18" t="s">
         <v>461</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>462</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
@@ -7960,13 +7990,13 @@
         <v>202</v>
       </c>
       <c r="B40" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>463</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="D40" s="18" t="s">
         <v>464</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>465</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
@@ -7996,13 +8026,13 @@
         <v>202</v>
       </c>
       <c r="B41" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="D41" s="20" t="s">
         <v>467</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>468</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
@@ -8032,13 +8062,13 @@
         <v>202</v>
       </c>
       <c r="B42" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="C42" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="D42" s="18" t="s">
         <v>470</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>471</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -8068,13 +8098,13 @@
         <v>202</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="D43" s="20" t="s">
         <v>473</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>474</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
@@ -8104,13 +8134,13 @@
         <v>202</v>
       </c>
       <c r="B44" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="C44" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="D44" s="20" t="s">
         <v>476</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>477</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -8140,13 +8170,13 @@
         <v>202</v>
       </c>
       <c r="B45" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="C45" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="D45" s="20" t="s">
         <v>479</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>480</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -8176,13 +8206,13 @@
         <v>202</v>
       </c>
       <c r="B46" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="D46" s="20" t="s">
         <v>482</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>483</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
@@ -8212,13 +8242,13 @@
         <v>202</v>
       </c>
       <c r="B47" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="D47" s="20" t="s">
         <v>485</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>486</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
@@ -8248,13 +8278,13 @@
         <v>202</v>
       </c>
       <c r="B48" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C48" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="D48" s="20" t="s">
         <v>488</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>489</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
@@ -8284,13 +8314,13 @@
         <v>202</v>
       </c>
       <c r="B49" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="C49" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="D49" s="20" t="s">
         <v>491</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>492</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -8320,13 +8350,13 @@
         <v>202</v>
       </c>
       <c r="B50" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="C50" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -8356,13 +8386,13 @@
         <v>202</v>
       </c>
       <c r="B51" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="C51" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="D51" s="20" t="s">
         <v>427</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>428</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
@@ -8405,22 +8435,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>496</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="C1" s="31" t="s">
         <v>497</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="31" t="s">
         <v>500</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>501</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
@@ -8445,19 +8475,19 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>507</v>
-      </c>
       <c r="C2" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="E2" s="25" t="s">
         <v>503</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>504</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="15"/>

--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5300" tabRatio="384"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -28,340 +24,346 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="516">
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>media::image::en</t>
-  </si>
-  <si>
-    <t>media::image::sw</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>due_date</t>
-  </si>
-  <si>
-    <t>due_date_human_readable</t>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relevant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">appearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">read_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice_filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::image::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::image::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO_LABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due_date</t>
   </si>
   <si>
     <t xml:space="preserve">string </t>
   </si>
   <si>
-    <t>client_EDD</t>
-  </si>
-  <si>
-    <t>visit_id</t>
-  </si>
-  <si>
-    <t>is_high_risk_pregnancy_ML</t>
-  </si>
-  <si>
-    <t>client_EDD_human_readable</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
-    <t>end group</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>db:person</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>client_name</t>
-  </si>
-  <si>
-    <t>../inputs/contact/name</t>
-  </si>
-  <si>
-    <t>enabel</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/enabel</t>
-  </si>
-  <si>
-    <t>n_pregnancy_visits</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/n_pregnancy_visits,'')</t>
-  </si>
-  <si>
-    <t>n_previous_anc_visits</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/n_previous_anc_visits,'')</t>
-  </si>
-  <si>
-    <t>previous_hiv_status</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/previous_hiv_status,'false')</t>
-  </si>
-  <si>
-    <t>previous_rchcard_status</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/previous_rchcard_status,"false")</t>
-  </si>
-  <si>
-    <t>show_research_questions</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/show_research_questions,"false")</t>
-  </si>
-  <si>
-    <t>patient_id</t>
-  </si>
-  <si>
-    <t>../inputs/contact/_id</t>
-  </si>
-  <si>
-    <t>created_by</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>../inputs/user/name</t>
-  </si>
-  <si>
-    <t>created_by_person_uuid</t>
-  </si>
-  <si>
-    <t>../inputs/user/contact_id</t>
-  </si>
-  <si>
-    <t>created_by_place_uuid</t>
-  </si>
-  <si>
-    <t>../inputs/user/facility_id</t>
-  </si>
-  <si>
-    <t>date_of_birth_c</t>
-  </si>
-  <si>
-    <t>../inputs/contact/date_of_birth</t>
-  </si>
-  <si>
-    <t>age_days</t>
-  </si>
-  <si>
-    <t>int(decimal-date-time(now())-decimal-date-time(${date_of_birth_c}))</t>
-  </si>
-  <si>
-    <t>age_months</t>
-  </si>
-  <si>
-    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
-  </si>
-  <si>
-    <t>age_years</t>
-  </si>
-  <si>
-    <t>int(${age_days} div (30 *12),0)</t>
-  </si>
-  <si>
-    <t>age_in_years</t>
-  </si>
-  <si>
-    <t>round((decimal-date-time(today()) - decimal-date-time(${date_of_birth_c})) div 365,0)</t>
-  </si>
-  <si>
-    <t>age_days_display</t>
-  </si>
-  <si>
-    <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
-  </si>
-  <si>
-    <t>week</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>household_head</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/household_head</t>
-  </si>
-  <si>
-    <t>house_number</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/house_number</t>
-  </si>
-  <si>
-    <t>kitongoji</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/kitongoji</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/phone</t>
-  </si>
-  <si>
-    <t>../inputs/due_date</t>
-  </si>
-  <si>
-    <t>due_date_pretty_print_english</t>
-  </si>
-  <si>
-    <t>if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Unknown")</t>
-  </si>
-  <si>
-    <t>due_date_pretty_print_swahili</t>
-  </si>
-  <si>
-    <t>if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Haijulikani")</t>
-  </si>
-  <si>
-    <t>client_EDD_pretty_print_english</t>
-  </si>
-  <si>
-    <t>if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Unknown")</t>
-  </si>
-  <si>
-    <t>client_EDD_pretty_print_swahili</t>
-  </si>
-  <si>
-    <t>if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Haijulikani")</t>
-  </si>
-  <si>
-    <t>client_EDD_c</t>
-  </si>
-  <si>
-    <t>../inputs/client_EDD</t>
+    <t xml:space="preserve">gestation_in_weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO_LABEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">due_date_human_readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_EDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visit_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_high_risk_pregnancy_ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_EDD_human_readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facility_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the logged in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db:person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db-object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_of_birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/contact/name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/enabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_pregnancy_visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/n_pregnancy_visits,'')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_previous_anc_visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/n_previous_anc_visits,'')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_hiv_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/previous_hiv_status,'false')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_rchcard_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/previous_rchcard_status,"false")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_research_questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/show_research_questions,"false")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/user/name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created_by_person_uuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/user/contact_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created_by_place_uuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/user/facility_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_of_birth_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int(decimal-date-time(now())-decimal-date-time(${date_of_birth_c}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int(${age_days} div (30 *12),0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_in_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round((decimal-date-time(today()) - decimal-date-time(${date_of_birth_c})) div 365,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_days_display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household_head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/household_head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">house_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/house_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitongoji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/kitongoji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/due_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due_date_pretty_print_english</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Unknown")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due_date_pretty_print_swahili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(../inputs/due_date_human_readable != "", ../inputs/due_date_human_readable, "Haijulikani")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_EDD_pretty_print_english</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Unknown")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_EDD_pretty_print_swahili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(../inputs/client_EDD_human_readable != "", ../inputs/client_EDD_human_readable, "Haijulikani")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_EDD_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/client_EDD</t>
   </si>
   <si>
     <t xml:space="preserve">currently_pregnant </t>
   </si>
   <si>
-    <t>instance('contact-summary')/context/currently_pregnant</t>
-  </si>
-  <si>
-    <t>hide_lmp_or_months_pregnant</t>
-  </si>
-  <si>
-    <t>if(${currently_pregnant}="true",instance('contact-summary')/context/hide_lmp_or_months_pregnant,"false")</t>
-  </si>
-  <si>
-    <t>if(../inputs/visit_id != "", ../inputs/visit_id, "pregnancy_consent_visit")</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>end</t>
+    <t xml:space="preserve">instance('contact-summary')/context/currently_pregnant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide_lmp_or_months_pregnant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${currently_pregnant}="true",instance('contact-summary')/context/hide_lmp_or_months_pregnant,"false")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(../inputs/visit_id != "", ../inputs/visit_id, "pregnancy_consent_visit")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end</t>
   </si>
   <si>
     <t xml:space="preserve">begin group </t>
   </si>
   <si>
-    <t>covid19_intro</t>
+    <t xml:space="preserve">covid19_intro</t>
   </si>
   <si>
     <t xml:space="preserve">Precautionary measures when visiting a client  </t>
   </si>
   <si>
-    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>covid19_intro_note</t>
+    <t xml:space="preserve">Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">covid19_intro_note</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
@@ -391,67 +393,70 @@
     <t xml:space="preserve">end group </t>
   </si>
   <si>
-    <t>gestation_in_weeks_c</t>
-  </si>
-  <si>
-    <t>is_high_risk_pregnancy_ML_c</t>
-  </si>
-  <si>
-    <t>../inputs/is_high_risk_pregnancy_ML</t>
-  </si>
-  <si>
-    <t>high_risk_manual</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/high_risk_manual</t>
-  </si>
-  <si>
-    <t>risk_factor_names</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/risk_factor_names</t>
-  </si>
-  <si>
-    <t>mitigation_list</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/mitigation_list</t>
-  </si>
-  <si>
-    <t>risk_factor_labels</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/risk_factor_labels</t>
-  </si>
-  <si>
-    <t>risk_factor_labels_swahili</t>
-  </si>
-  <si>
-    <t>instance('contact-summary')/context/risk_factor_labels_swahili</t>
-  </si>
-  <si>
-    <t>client_information</t>
+    <t xml:space="preserve">gestation_in_weeks_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/gestation_in_weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_high_risk_pregnancy_ML_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/is_high_risk_pregnancy_ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high_risk_manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/high_risk_manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk_factor_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/mitigation_list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk_factor_labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk_factor_labels_swahili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance('contact-summary')/context/risk_factor_labels_swahili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_information</t>
   </si>
   <si>
     <t xml:space="preserve">Client Information </t>
   </si>
   <si>
-    <t>Taarifa za mteja</t>
-  </si>
-  <si>
-    <t>field-list</t>
-  </si>
-  <si>
-    <t>intro_note</t>
-  </si>
-  <si>
-    <t>Visit type: &lt;span style="font-weight:bold"&gt;Pregnancy Counselling&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Ujauzito&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>household_note</t>
+    <t xml:space="preserve">Taarifa za mteja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit type: &lt;span style="font-weight:bold"&gt;Pregnancy Counselling&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Ujauzito&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household_note</t>
   </si>
   <si>
     <t xml:space="preserve">Name: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
@@ -462,35 +467,35 @@
 IPO futa: &lt;span style="font-weight:bold"&gt;${is_high_risk_pregnancy_ML_c}&lt;/span&gt; </t>
   </si>
   <si>
-    <t>Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
+    <t xml:space="preserve">Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
 Umri: &lt;span style=""font-weight:bold""&gt;miaka ${age_years}&lt;/span&gt;
 Mtu wa karibu kwa mawasiliano: &lt;span style=""font-weight:bold""&gt;${household_head}&lt;/span&gt; 
 Namba ya nyumba: &lt;span style=""font-weight:bold""&gt;${house_number}&lt;/span&gt;
 Kitongoji: &lt;span style=""font-weight:bold""&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
-    <t>phone_note</t>
-  </si>
-  <si>
-    <t>Phone: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>due_date_note</t>
-  </si>
-  <si>
-    <t>Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_english}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_swahili}&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>intro_message</t>
-  </si>
-  <si>
-    <t>During the enrolment we talked about pregnancy risk factors. I want to make sure that you are aware of these factors and know what to do to lower your risk if you identify any. Therefore, I will visit you every two weeks, in addition to the regular pregnancy visits, to make sure you continue in good health and have a safe pregnancy all the way through delivery.</t>
+    <t xml:space="preserve">phone_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due_date_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_english}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print_swahili}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro_message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During the enrolment we talked about pregnancy risk factors. I want to make sure that you are aware of these factors and know what to do to lower your risk if you identify any. Therefore, I will visit you every two weeks, in addition to the regular pregnancy visits, to make sure you continue in good health and have a safe pregnancy all the way through delivery.</t>
   </si>
   <si>
     <t xml:space="preserve">Wakati wa usajili, tulizungumza kuhusu sababu za hatari za ujauzito. Nataka nihakikishe kwamba unazijua sababu hizo ili kuwe na uwezekano mdogo sana wa kuja kuzipata.  Kwahiyo, nitakuja kukutembela kila baada ya wiki mbili ili kuhakikisha unaendelea vizuri na mimba yako hadi utakapojifungua. </t>
@@ -499,148 +504,148 @@
     <t xml:space="preserve">intro_message </t>
   </si>
   <si>
-    <t>danger_signs</t>
-  </si>
-  <si>
-    <t>Pregnancy Danger Signs</t>
-  </si>
-  <si>
-    <t>Dalili Hatari Kwa Mama Wajawazito</t>
-  </si>
-  <si>
-    <t>danger_sign_intro</t>
-  </si>
-  <si>
-    <t>Now I will ask you some questions about pregnancy danger signs. Have you experienced any of these symptoms?</t>
-  </si>
-  <si>
-    <t>Sahivi naomba kukuliza maswali yanayohusiana na dalili za hatari kwa ujauzito. Je una dalizi za hatari kati ya hizi zifuatazo?</t>
-  </si>
-  <si>
-    <t>danger_sign_table_1</t>
-  </si>
-  <si>
-    <t>table-list</t>
-  </si>
-  <si>
-    <t>select_one yes_no</t>
-  </si>
-  <si>
-    <t>danger_sign_vaginal_bleeding</t>
-  </si>
-  <si>
-    <t>Vaginal Bleeding</t>
-  </si>
-  <si>
-    <t>Unatokwa na damu ukeni?</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>danger_sign_abdominal_pain</t>
-  </si>
-  <si>
-    <t>Severe abdoninal pain</t>
-  </si>
-  <si>
-    <t>Una maumivu makali ya tumbo?</t>
-  </si>
-  <si>
-    <t>danger_sign_severe_headache</t>
-  </si>
-  <si>
-    <t>Severe Headache</t>
-  </si>
-  <si>
-    <t>Una maumivu makali ya kichwa ?</t>
-  </si>
-  <si>
-    <t>danger_sign_fever</t>
-  </si>
-  <si>
-    <t>Fever and being too weak to get out of bed</t>
-  </si>
-  <si>
-    <t>Una homa au umedhoofika ?</t>
-  </si>
-  <si>
-    <t>danger_sign_note_to_chv</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>observe_danger_signs</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;OBSERVE: &lt;/span&gt;&lt;span style="color:#f58a1f"&gt; if the client has the following pregnancy danger signs.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;ANGALIA: &lt;/span&gt; &lt;span style="color:#f58a1f"&gt;kama mteja ana dalili za hatari kwa wajawazito hizi zifuatazo.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>danger_sign_table_2</t>
-  </si>
-  <si>
-    <t>danger_sign_unconsciouss</t>
-  </si>
-  <si>
-    <t>Unconsciousness</t>
-  </si>
-  <si>
-    <t>Kupoteza fahamu</t>
-  </si>
-  <si>
-    <t>danger_sign_difficult_breathing</t>
-  </si>
-  <si>
-    <t>Fast or difficult breathing</t>
-  </si>
-  <si>
-    <t>Kupumua kwa haraka au ugumu katika kupumua</t>
-  </si>
-  <si>
-    <t>danger_sign_convulsions</t>
-  </si>
-  <si>
-    <t>Convulsions/fits</t>
-  </si>
-  <si>
-    <t>Kifafa cha mimba</t>
-  </si>
-  <si>
-    <t>emergency_danger_sign_referral</t>
-  </si>
-  <si>
-    <t>if(selected(${danger_sign_vaginal_bleeding},"yes") or selected(${danger_sign_convulsions},"yes") or selected(${danger_sign_unconsciouss},"yes") or selected(${danger_sign_severe_headache},"yes") or selected(${danger_sign_fever},"yes") or selected(${danger_sign_abdominal_pain},"yes") or selected(${danger_sign_difficult_breathing},"yes"),1,0)</t>
-  </si>
-  <si>
-    <t>emergency_danger_sign_note</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;This woman is experiencing or has experienced an emergency danger sign. Urge the woman and her family to get the woman medical help as the lives of the mother and her baby are potentially in danger.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Mwanamke huyu anadalili za hatari au aliwahi kupata dalili za hatari za ghafla. Mtake Mama na familia yake kupata msaada wa kimatibabu kwasababu maisha ya mama na mtoto wake yapo katika hatari.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>${emergency_danger_sign_referral} = 1</t>
-  </si>
-  <si>
-    <t>no_danger_sign_note_to_chv</t>
-  </si>
-  <si>
-    <t>No emergency referral condition was identified.</t>
-  </si>
-  <si>
-    <t>Kwa sasa, hauna dalili yoyote ya hatari iliyogundulika. Lakini ukipata dalili yote kati ya hizi tulizozijadili, tafadhali nenda kituo cha afya haraka iwezakanavyo.</t>
-  </si>
-  <si>
-    <t>selected(${danger_sign_convulsions},'no') and 
+    <t xml:space="preserve">danger_signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregnancy Danger Signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalili Hatari Kwa Mama Wajawazito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now I will ask you some questions about pregnancy danger signs. Have you experienced any of these symptoms?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahivi naomba kukuliza maswali yanayohusiana na dalili za hatari kwa ujauzito. Je una dalizi za hatari kati ya hizi zifuatazo?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_table_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_one yes_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_vaginal_bleeding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaginal Bleeding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unatokwa na damu ukeni?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_abdominal_pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe abdoninal pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una maumivu makali ya tumbo?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_severe_headache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe Headache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una maumivu makali ya kichwa ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fever and being too weak to get out of bed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una homa au umedhoofika ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_note_to_chv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observe_danger_signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f;font-weight: bold"&gt;OBSERVE: &lt;/span&gt;&lt;span style="color:#f58a1f"&gt; if the client has the following pregnancy danger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f;font-weight: bold"&gt;ANGALIA: &lt;/span&gt; &lt;span style="color:#f58a1f"&gt;kama mteja ana dalili za hatari kwa wajawazito hizi zifuatazo.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_table_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_unconsciouss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unconsciousness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupoteza fahamu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_difficult_breathing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast or difficult breathing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupumua kwa haraka au ugumu katika kupumua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">danger_sign_convulsions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convulsions/fits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kifafa cha mimba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emergency_danger_sign_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(selected(${danger_sign_vaginal_bleeding},"yes") or selected(${danger_sign_convulsions},"yes") or selected(${danger_sign_unconsciouss},"yes") or selected(${danger_sign_severe_headache},"yes") or selected(${danger_sign_fever},"yes") or selected(${danger_sign_abdominal_pain},"yes") or selected(${danger_sign_difficult_breathing},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emergency_danger_sign_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;This woman is experiencing or has experienced an emergency danger sign. Urge the woman and her family to get the woman medical help as the lives of the mother and her baby are potentially in danger.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Mwanamke huyu anadalili za hatari au aliwahi kupata dalili za hatari za ghafla. Mtake Mama na familia yake kupata msaada wa kimatibabu kwasababu maisha ya mama na mtoto wake yapo katika hatari.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${emergency_danger_sign_referral} = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_danger_sign_note_to_chv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No emergency referral condition was identified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwa sasa, hauna dalili yoyote ya hatari iliyogundulika. Lakini ukipata dalili yote kati ya hizi tulizozijadili, tafadhali nenda kituo cha afya haraka iwezakanavyo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${danger_sign_convulsions},'no') and 
 selected(${danger_sign_unconsciouss},'no') and 
 selected(${danger_sign_severe_headache},'no') and 
 selected(${danger_sign_fever},'no') and 
@@ -649,29 +654,29 @@
 selected(${danger_sign_vaginal_bleeding},'no')</t>
   </si>
   <si>
-    <t>pregnancy_issues_group</t>
-  </si>
-  <si>
-    <t>Pregnancy Issues</t>
-  </si>
-  <si>
-    <t>Maswala ya ujauzito</t>
+    <t xml:space="preserve">pregnancy_issues_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregnancy Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maswala ya ujauzito</t>
   </si>
   <si>
     <t xml:space="preserve"> ${emergency_danger_sign_referral} = 0 
  </t>
   </si>
   <si>
-    <t>subgroup_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>select_multiple pregnancy_issues</t>
-  </si>
-  <si>
-    <t>pregnancy_issues</t>
-  </si>
-  <si>
-    <t>Continue with the following questions. Indicate if the client has any of the following common pregnancy issues. 
+    <t xml:space="preserve">subgroup_pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_multiple pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue with the following questions. Indicate if the client has any of the following common pregnancy issues. 
 Have you experienced:</t>
   </si>
   <si>
@@ -679,22 +684,22 @@
 </t>
   </si>
   <si>
-    <t>${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
-  </si>
-  <si>
-    <t>Cannot select "None" with other options</t>
-  </si>
-  <si>
-    <t>Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
-  </si>
-  <si>
-    <t>refer_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>if(selected(${pregnancy_issues},"difficulty_breathing") or 
+    <t xml:space="preserve">${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannot select "None" with other options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(selected(${pregnancy_issues},"difficulty_breathing") or 
 selected(${pregnancy_issues},"fatigue") or 
 selected(${pregnancy_issues},"fever") or 
 selected(${pregnancy_issues},"tinrisk_factor_namess") or 
@@ -709,73 +714,73 @@
 selected(${pregnancy_issues},"foul_smelling")1,0)</t>
   </si>
   <si>
-    <t>refer_pregnancy_issues_note</t>
-  </si>
-  <si>
-    <t>I am referring you to a health facility because I have identified that you have danger sign(s)</t>
-  </si>
-  <si>
-    <t>Nakupa rufaa uende kituo cha afya kwasababu nimekugundua una dalili za hatari.</t>
-  </si>
-  <si>
-    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_issues}=1</t>
-  </si>
-  <si>
-    <t>pregnancy_and_pallor</t>
-  </si>
-  <si>
-    <t>baby_moving</t>
-  </si>
-  <si>
-    <t>Do you feel the baby moving on a daily basis, at least every six hours?</t>
-  </si>
-  <si>
-    <t>Je unahisi mtoto anacheza angalau kila baada ya masaa sita kila siku?</t>
-  </si>
-  <si>
-    <t>${gestation_in_weeks_c} &gt; 24</t>
-  </si>
-  <si>
-    <t>covid19_plam_pallor_note</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Now you are at the stage of comparing your palm with the client’s palm. Before doing this, please keep a 2 meters distance from your client as a precautionary measure to avoid the spread of Corona virus. Please ask your client to show you their palm while still keeping the distance. &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Sasa upo kwenye hatua ya kulinganisha kiganja chako na cha mteja wako. Kabla ya kufanya hivyo, tafadhali hakikisha umekaa umbali wa mita mbili na mteja wako ili kujilinda na uwezekano wa kusambaza maambukizi ya Korona. Tafadhali mwambie mteja akuoneshe kiganja chake. &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>pallor</t>
-  </si>
-  <si>
-    <t>Does the client have pallor? Compare your palm with client's palm. If client's palms are paler than yours, this is pallor.</t>
-  </si>
-  <si>
-    <t>Linganisha kiganja chako na cha mteja. Ikiwa kiganja cha mteja kimepauka sana kuliko chako hili ni tatizo. Iniashiria upungufu wa damu.</t>
-  </si>
-  <si>
-    <t>refer_pregnancy_complications</t>
-  </si>
-  <si>
-    <t>if(selected(${baby_moving},"no") or selected(${pallor},"yes"),1,0)</t>
-  </si>
-  <si>
-    <t>has_pregnancy_complication_note</t>
-  </si>
-  <si>
-    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=1</t>
-  </si>
-  <si>
-    <t>no_pregnancy_complication_note</t>
-  </si>
-  <si>
-    <t>Based on our conversation, I did not identify any health issues, but if you develop any of the signs we discussed today, you should go to a health facility immediately</t>
-  </si>
-  <si>
-    <t>Huna dalili yoyote ya hatari lakini ikitokea ukapatwa na moja ya dalili tulizozijadili unapaswa kwenda kituo cha afya.</t>
-  </si>
-  <si>
-    <t>${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=0 and ${refer_pregnancy_issues}=0 and
+    <t xml:space="preserve">refer_pregnancy_issues_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am referring you to a health facility because I have identified that you have danger sign(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakupa rufaa uende kituo cha afya kwasababu nimekugundua una dalili za hatari.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_issues}=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pregnancy_and_pallor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_moving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you feel the baby moving on a daily basis, at least every six hours?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unahisi mtoto anacheza angalau kila baada ya masaa sita kila siku?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${gestation_in_weeks_c} &gt; 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">covid19_plam_pallor_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Now you are at the stage of comparing your palm with the client’s palm. Before doing this, please keep a 2 meters distance from your client as a precautionary measure to avoid the spread of Corona virus. Please ask your client to show you their palm while still keeping the distance. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Sasa upo kwenye hatua ya kulinganisha kiganja chako na cha mteja wako. Kabla ya kufanya hivyo, tafadhali hakikisha umekaa umbali wa mita mbili na mteja wako ili kujilinda na uwezekano wa kusambaza maambukizi ya Korona. Tafadhali mwambie mteja akuoneshe kiganja chake. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pallor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the client have pallor? Compare your palm with client's palm. If client's palms are paler than yours, this is pallor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linganisha kiganja chako na cha mteja. Ikiwa kiganja cha mteja kimepauka sana kuliko chako hili ni tatizo. Iniashiria upungufu wa damu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(selected(${baby_moving},"no") or selected(${pallor},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_pregnancy_complication_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on our conversation, I did not identify any health issues, but if you develop any of the signs we discussed today, you should go to a health facility immediately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huna dalili yoyote ya hatari lakini ikitokea ukapatwa na moja ya dalili tulizozijadili unapaswa kwenda kituo cha afya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${emergency_danger_sign_referral} = 0 and ${refer_pregnancy_complications}=0 and ${refer_pregnancy_issues}=0 and
 selected(${baby_moving},"yes") and selected(${pallor},"no")</t>
   </si>
   <si>
@@ -785,13 +790,13 @@
     <t xml:space="preserve">fiel-list </t>
   </si>
   <si>
-    <t>select_multiple risk_factors</t>
-  </si>
-  <si>
-    <t>risk_factors</t>
-  </si>
-  <si>
-    <t>Which pregnancy risk factors do you remember?</t>
+    <t xml:space="preserve">select_multiple risk_factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk_factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which pregnancy risk factors do you remember?</t>
   </si>
   <si>
     <t xml:space="preserve">Je unakumbuka sababu zipi za hatari za ujauzito? </t>
@@ -803,13 +808,13 @@
     <t xml:space="preserve">Cannot select "None" with other options </t>
   </si>
   <si>
-    <t>contains(${risk_factor_names}, name) or name = 'none'</t>
-  </si>
-  <si>
-    <t>short_explanation</t>
-  </si>
-  <si>
-    <t>${high_risk_manual}  = "true"  and ${emergency_danger_sign_referral} = 0</t>
+    <t xml:space="preserve">contains(${risk_factor_names}, name) or name = 'none'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short_explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${high_risk_manual}  = "true"  and ${emergency_danger_sign_referral} = 0</t>
   </si>
   <si>
     <t xml:space="preserve">field-list </t>
@@ -818,301 +823,310 @@
     <t xml:space="preserve">previous_pregnancies </t>
   </si>
   <si>
-    <t>More than 5 previous pregnancies</t>
-  </si>
-  <si>
-    <t>Kupata mimba zaidi ya mara 5</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'previous_pregnancies')) and contains(${risk_factor_names}, 'previous_pregnancies')</t>
-  </si>
-  <si>
-    <t>previous_delivery_by_c_section</t>
-  </si>
-  <si>
-    <t>Caesarean section</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa kupasuliwa</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'previous_delivery_by_c_section')) and contains(${risk_factor_names}, 'previous_delivery_by_c_section')</t>
-  </si>
-  <si>
-    <t>previous_delivery_by_vacuum</t>
-  </si>
-  <si>
-    <t>Delivery by vacuum</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa kusaidiwa kuvutwa na mashine</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'previous_delivery_by_vacuum')) and contains(${risk_factor_names}, 'previous_delivery_by_vacuum')</t>
-  </si>
-  <si>
-    <t>previous_stillbirth</t>
-  </si>
-  <si>
-    <t>Stillbirth</t>
+    <t xml:space="preserve">More than 5 previous pregnancies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupata mimba zaidi ya mara 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'previous_pregnancies')) and contains(${risk_factor_names}, 'previous_pregnancies')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_delivery_by_c_section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarean section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kujifungua kwa kupasuliwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'previous_delivery_by_c_section')) and contains(${risk_factor_names}, 'previous_delivery_by_c_section')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_delivery_by_vacuum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery by vacuum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kujifungua kwa kusaidiwa kuvutwa na mashine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'previous_delivery_by_vacuum')) and contains(${risk_factor_names}, 'previous_delivery_by_vacuum')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_stillbirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stillbirth</t>
   </si>
   <si>
     <t xml:space="preserve">Kupoteza mtoto wakati wa kujifungua </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'previous_stillbirth')) and contains(${risk_factor_names}, 'previous_stillbirth')</t>
-  </si>
-  <si>
-    <t>prolonged_labor</t>
-  </si>
-  <si>
-    <t>Prolonged labor (12 hours or more)</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'previous_stillbirth')) and contains(${risk_factor_names}, 'previous_stillbirth')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prolonged_labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prolonged labor (12 hours or more)</t>
   </si>
   <si>
     <t xml:space="preserve"> Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'prolonged_labor')) and contains(${risk_factor_names}, 'prolonged_labor')</t>
-  </si>
-  <si>
-    <t>large_perineal_tear</t>
-  </si>
-  <si>
-    <t>Large perineal tear (close to anus)</t>
-  </si>
-  <si>
-    <t>Kuchanika njia ya uzazi(karibia ya njia ya choo kikubwa)</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'large_perineal_tear')) and contains(${risk_factor_names}, 'large_perineal_tear')</t>
-  </si>
-  <si>
-    <t>retained_placenta</t>
-  </si>
-  <si>
-    <t>Retained placenta</t>
-  </si>
-  <si>
-    <t>Kondo la nyuma kukataa kutoka</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'retained_placenta')) and contains(${risk_factor_names}, 'retained_placenta')</t>
-  </si>
-  <si>
-    <t>aph</t>
-  </si>
-  <si>
-    <t>APH</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'prolonged_labor')) and contains(${risk_factor_names}, 'prolonged_labor')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">large_perineal_tear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large perineal tear (close to anus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuchanika njia ya uzazi(karibia ya njia ya choo kikubwa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'large_perineal_tear')) and contains(${risk_factor_names}, 'large_perineal_tear')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retained_placenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retained placenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kondo la nyuma kukataa kutoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'retained_placenta')) and contains(${risk_factor_names}, 'retained_placenta')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APH</t>
   </si>
   <si>
     <t xml:space="preserve">Kutokwa na damu nyingi kabla ya kujifungua </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'aph')) and contains(${risk_factor_names}, 'aph')</t>
-  </si>
-  <si>
-    <t>postpartum_hemorrage</t>
-  </si>
-  <si>
-    <t>Postpartum hemorrhage</t>
-  </si>
-  <si>
-    <t>Kutokwa damu nyingi baada ya kujifungua</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'postpartum_hemorrage')) and contains(${risk_factor_names}, 'postpartum_hemorrage')</t>
-  </si>
-  <si>
-    <t>enclampsia</t>
-  </si>
-  <si>
-    <t>Eclampsia</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'enclampsia')) and contains(${risk_factor_names}, 'enclampsia')</t>
-  </si>
-  <si>
-    <t>big_baby</t>
-  </si>
-  <si>
-    <t>Big baby in previous or current (more than 4 kg)</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'aph')) and contains(${risk_factor_names}, 'aph')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postpartum_hemorrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postpartum hemorrhage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutokwa damu nyingi baada ya kujifungua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'postpartum_hemorrage')) and contains(${risk_factor_names}, 'postpartum_hemorrage')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enclampsia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eclampsia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kifafa cha mimba
+Mama akipata tatizo hili hukutika mfano wa homa ya mdudu na kupoteza faham, kifafa cha mimba hutokea kabla au baada ya mama kujifungua. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'enclampsia')) and contains(${risk_factor_names}, 'enclampsia')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">big_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big baby in previous or current (more than 4 kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Kujifungua mtoto mkubwa ( zaidi ya kilo 4) (mimba hii au kabla) </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'big_baby')) and contains(${risk_factor_names}, 'big_baby')</t>
-  </si>
-  <si>
-    <t>previous_miscarriages</t>
-  </si>
-  <si>
-    <t>Miscarriage/abortion</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'big_baby')) and contains(${risk_factor_names}, 'big_baby')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_miscarriages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscarriage/abortion</t>
   </si>
   <si>
     <t xml:space="preserve">Mimba kuharibika </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'previous_miscarriages')) and contains(${risk_factor_names}, 'previous_miscarriages')</t>
-  </si>
-  <si>
-    <t>multiple_pregnancy</t>
-  </si>
-  <si>
-    <t>Multiple pregnancy</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'previous_miscarriages')) and contains(${risk_factor_names}, 'previous_miscarriages')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiple_pregnancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple pregnancy</t>
   </si>
   <si>
     <t xml:space="preserve">Kutarajia kuwa na mapacha </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'multiple_pregnancy')) and contains(${risk_factor_names}, 'multiple_pregnancy')</t>
-  </si>
-  <si>
-    <t>malpresentation</t>
-  </si>
-  <si>
-    <t>Malpresentation</t>
-  </si>
-  <si>
-    <t>Milalo mibaya</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'malpresentation')) and contains(${risk_factor_names}, 'malpresentation')</t>
-  </si>
-  <si>
-    <t>breech_position</t>
-  </si>
-  <si>
-    <t>Breech position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mtoto kutanguliza makalio </t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'breech_position')) and contains(${risk_factor_names}, 'breech_position')</t>
-  </si>
-  <si>
-    <t>high_blood_pressure</t>
-  </si>
-  <si>
-    <t>High blood pressure</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'multiple_pregnancy')) and contains(${risk_factor_names}, 'multiple_pregnancy')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malpresentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malpresentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milalo mibaya
+Kutokea akiwa na mlalo usio wa kawaida wakati wa mtoto kuzaliwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'malpresentation')) and contains(${risk_factor_names}, 'malpresentation')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breech_position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breech position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtoto kutanguliza makalio 
+Mtoto kutokeza makalio wakati wa kuzaliwa kawaida atokee kichwa ili azae salama.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'breech_position')) and contains(${risk_factor_names}, 'breech_position')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high_blood_pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High blood pressure</t>
   </si>
   <si>
     <t xml:space="preserve">Shinikizo la damu </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'high_blood_pressure')) and contains(${risk_factor_names}, 'high_blood_pressure')</t>
-  </si>
-  <si>
-    <t>diabetes</t>
-  </si>
-  <si>
-    <t>Diabetes</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'high_blood_pressure')) and contains(${risk_factor_names}, 'high_blood_pressure')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Kisukari </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'diabetes')) and contains(${risk_factor_names}, 'diabetes')</t>
-  </si>
-  <si>
-    <t>sicke_cell</t>
-  </si>
-  <si>
-    <t>Sickle cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seli mundu </t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'sicke_cell')) and contains(${risk_factor_names}, 'sicke_cell')</t>
-  </si>
-  <si>
-    <t>cardiac_disease</t>
-  </si>
-  <si>
-    <t>Cardiac disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maradhi ya moyo </t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'cardiac_disease')) and contains(${risk_factor_names}, 'cardiac_disease')</t>
-  </si>
-  <si>
-    <t>anemia</t>
-  </si>
-  <si>
-    <t>Anemia [received tablets, or didn’t receive because out of stock/too expensive/don’t know]</t>
-  </si>
-  <si>
-    <t>Upungufu wa damu mwilini</t>
-  </si>
-  <si>
-    <t>not(selected(${risk_factors},'anemia')) and contains(${risk_factor_names}, 'anemia')</t>
-  </si>
-  <si>
-    <t>higher_level_facility</t>
-  </si>
-  <si>
-    <t>Advise to deliver at higher-level facility</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'diabetes')) and contains(${risk_factor_names}, 'diabetes')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sicke_cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sickle cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seli mundu 
+Maradhi ya homa ya mifupa/seli nundu, mwenye maradhi haya chembe chembe nyekundu za damu huwa kidogo na hazikukamilika, hupekelea kuwa na ukosefu wa damu mara kwa mara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'sicke_cell')) and contains(${risk_factor_names}, 'sicke_cell')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cardiac_disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiac disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maradhi ya moyo 
+Haya ni maradhi sugu ambapo moyo hushindwa kufanya kazi vizuri na tujuwe kwamba moyo ni kiungo kinacho sambaza damu safi kwenda sehemu zote za mwili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'cardiac_disease')) and contains(${risk_factor_names}, 'cardiac_disease')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anemia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anemia [received tablets, or didn’t receive because out of stock/too expensive/don’t know]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upungufu wa damu mwilini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${risk_factors},'anemia')) and contains(${risk_factor_names}, 'anemia')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">higher_level_facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advise to deliver at higher-level facility</t>
   </si>
   <si>
     <t xml:space="preserve">Kushauriwa kujifungua katika kituo cha afya kikubwa </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'higher_level_facility')) and contains(${risk_factor_names}, 'higher_level_facility')</t>
-  </si>
-  <si>
-    <t>allow_partner_to_deliver_facility</t>
-  </si>
-  <si>
-    <t>Partner permission not given</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'higher_level_facility')) and contains(${risk_factor_names}, 'higher_level_facility')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allow_partner_to_deliver_facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner permission not given</t>
   </si>
   <si>
     <t xml:space="preserve">Mwenwa hajatoa ruhusa ya kujifungua kituo cha afya </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'allow_partner_to_deliver_facility')) and contains(${risk_factor_names}, 'allow_partner_to_deliver_facility')</t>
-  </si>
-  <si>
-    <t>ten_or_more_years</t>
-  </si>
-  <si>
-    <t>Last pregnancy 10 or more years ago</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'allow_partner_to_deliver_facility')) and contains(${risk_factor_names}, 'allow_partner_to_deliver_facility')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ten_or_more_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last pregnancy 10 or more years ago</t>
   </si>
   <si>
     <t xml:space="preserve">Mimba iliyopita ilikuwa miaka kumi ilopita au zaidi </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'ten_or_more_years')) and contains(${risk_factor_names}, 'ten_or_more_years')</t>
-  </si>
-  <si>
-    <t>local_herbs</t>
-  </si>
-  <si>
-    <t>Use of local herbs</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'ten_or_more_years')) and contains(${risk_factor_names}, 'ten_or_more_years')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">local_herbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of local herbs</t>
   </si>
   <si>
     <t xml:space="preserve">Kutumia dawa za mitishamba </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'local_herbs')) and contains(${risk_factor_names}, 'local_herbs')</t>
-  </si>
-  <si>
-    <t>nutrition</t>
-  </si>
-  <si>
-    <t>Follows nutrition restrictions</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'local_herbs')) and contains(${risk_factor_names}, 'local_herbs')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Follows nutrition restrictions</t>
   </si>
   <si>
     <t xml:space="preserve">Kuepuka kula baadhi ya vyakula </t>
   </si>
   <si>
-    <t>not(selected(${risk_factors},'nutrition')) and contains(${risk_factor_names}, 'nutrition')</t>
-  </si>
-  <si>
-    <t>mitigation_strategy</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'nutrition_restrictions')) and contains(${risk_factor_names}, 'nutrition')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_strategy</t>
   </si>
   <si>
     <t xml:space="preserve">Mitigation Strategy </t>
@@ -1121,36 +1135,36 @@
     <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito </t>
   </si>
   <si>
-    <t>risk_factor_list</t>
-  </si>
-  <si>
-    <t>&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
+    <t xml:space="preserve">risk_factor_list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;strong&gt;Considering these risk factors:&lt;/strong&gt;
 [${risk_factor_labels}]</t>
   </si>
   <si>
-    <t>&lt;strong&gt;Ukizingatia sababu zifuatazo za hatari za ujauzito:&lt;/strong&gt;
+    <t xml:space="preserve">&lt;strong&gt;Ukizingatia sababu zifuatazo za hatari za ujauzito:&lt;/strong&gt;
 [${risk_factor_labels_swahili}]</t>
   </si>
   <si>
-    <t>select_multiple mitigation_strategies</t>
+    <t xml:space="preserve">select_multiple mitigation_strategies</t>
   </si>
   <si>
     <t xml:space="preserve">mitigation_strategies </t>
   </si>
   <si>
-    <t>What can you do to continue in good health and have a safe pregnancy all the way through delivery?</t>
+    <t xml:space="preserve">What can you do to continue in good health and have a safe pregnancy all the way through delivery?</t>
   </si>
   <si>
     <t xml:space="preserve">Unaweza kufanya mambo gani ili uweze kuendelea na mimba yako vizuri hadi utakapojifungua? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list}, name) or name = 'none'</t>
-  </si>
-  <si>
-    <t>mitigation_strategy_note</t>
-  </si>
-  <si>
-    <t>I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery</t>
+    <t xml:space="preserve">contains(${mitigation_list}, name) or name = 'none'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_strategy_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Sasa, nitakufahamisha mambo ambayo yatakuwezesha kuendelea na mimba yako vizuri hadi utakapojifungua. </t>
@@ -1159,22 +1173,25 @@
     <t xml:space="preserve">mitigation_strategy </t>
   </si>
   <si>
-    <t>mitigation_strategy_ml</t>
-  </si>
-  <si>
-    <t>${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true" and ${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t>I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery.</t>
-  </si>
-  <si>
-    <t>mitigation_qn</t>
-  </si>
-  <si>
-    <t>(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
-  </si>
-  <si>
-    <t>mitigation_note_1</t>
+    <t xml:space="preserve">mitigation_strategy_ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${high_risk_manual}  = "false"  and ${is_high_risk_pregnancy_ML} = "true" and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I would now like to go through the things you can do to continue in good health and have a safe pregnancy all the way through delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_qn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mkakati wa kuepuka sababu za hatari za ujauzito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(${high_risk_manual}  = "true"  or  ${is_high_risk_pregnancy_ML} = "true") and ${emergency_danger_sign_referral} = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_1</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Facility Delivery ? </t>
@@ -1183,10 +1200,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kujifungulia kituo cha afya ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”facility_delivery“)</t>
-  </si>
-  <si>
-    <t>mitigation_note_2</t>
+    <t xml:space="preserve">contains(${mitigation_list},”facility_delivery“)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_2</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of ANC Visits ? </t>
@@ -1195,10 +1212,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kuhudhuria kliniki wakati wa ujauzito  ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”anc_visits“)</t>
-  </si>
-  <si>
-    <t>mitigation_note_3</t>
+    <t xml:space="preserve">contains(${mitigation_list},”anc_visits“)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_3</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Rest ? </t>
@@ -1207,10 +1224,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kupumzika ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”rest“)</t>
-  </si>
-  <si>
-    <t>mitigation_note_4</t>
+    <t xml:space="preserve">contains(${mitigation_list},”rest“)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_4</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Balanced Diet/Good Nutrition Practices  ? </t>
@@ -1219,10 +1236,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kula vyakula vyenye virutubisho  ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”balanced_diet“)</t>
-  </si>
-  <si>
-    <t>mitigation_note_5</t>
+    <t xml:space="preserve">contains(${mitigation_list},”balanced_diet“)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_5</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of No heavy work  ? </t>
@@ -1231,10 +1248,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kutokufanya kazi ngumu ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”no_heavy_work “)</t>
-  </si>
-  <si>
-    <t>mitigation_note_6</t>
+    <t xml:space="preserve">contains(${mitigation_list},”no_heavy_work “)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_6</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Family Planning  ? </t>
@@ -1243,10 +1260,10 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Kutumia uzazi wa mpango ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”family_planning“)</t>
-  </si>
-  <si>
-    <t>mitigation_note_7</t>
+    <t xml:space="preserve">contains(${mitigation_list},”family_planning“)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_note_7</t>
   </si>
   <si>
     <t xml:space="preserve">Do you understand the importance of Risks of using herbs ? </t>
@@ -1255,7 +1272,7 @@
     <t xml:space="preserve">Je unaelewa umuhimu wa Hatari za kutumia dawa za mitishamba ? </t>
   </si>
   <si>
-    <t>contains(${mitigation_list},”local_herbs_risks“)</t>
+    <t xml:space="preserve">contains(${mitigation_list},”local_herbs_risks“)</t>
   </si>
   <si>
     <t xml:space="preserve">visit_summary </t>
@@ -1267,47 +1284,47 @@
     <t xml:space="preserve">Muhtasari wa tembeleo </t>
   </si>
   <si>
-    <t>needs_referral_note</t>
-  </si>
-  <si>
-    <t>You need to go to the health facility for the following reasons:</t>
-  </si>
-  <si>
-    <t>Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
-  </si>
-  <si>
-    <t>${has_referral}=1</t>
-  </si>
-  <si>
-    <t>needs_referral_danger_signs</t>
-  </si>
-  <si>
-    <t>To address emergency pregnancy danger signs</t>
-  </si>
-  <si>
-    <t>Ili kushughulikia dalili za hatari za dharura za mama mjamzito.</t>
-  </si>
-  <si>
-    <t>${emergency_danger_sign_referral}=1</t>
-  </si>
-  <si>
-    <t>li</t>
-  </si>
-  <si>
-    <t>needs_referral_neonatal_note</t>
-  </si>
-  <si>
-    <t>To address other pregnancy danger signs</t>
-  </si>
-  <si>
-    <t>Ili kushughulikia dalili nyengine za hatari.</t>
-  </si>
-  <si>
-    <t>${refer_pregnancy_issues}=1 or 
+    <t xml:space="preserve">needs_referral_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You need to go to the health facility for the following reasons:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${has_referral}=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs_referral_danger_signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To address emergency pregnancy danger signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ili kushughulikia dalili za hatari za dharura za mama mjamzito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${emergency_danger_sign_referral}=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">li</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needs_referral_neonatal_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To address other pregnancy danger signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ili kushughulikia dalili nyengine za hatari.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${refer_pregnancy_issues}=1 or 
 ${refer_pregnancy_complications}=1</t>
   </si>
   <si>
-    <t>next_visit</t>
+    <t xml:space="preserve">next_visit</t>
   </si>
   <si>
     <t xml:space="preserve">I will visit you again in two weeks. </t>
@@ -1316,70 +1333,82 @@
     <t xml:space="preserve">Nitakutembelea tena baada ya wiki mbili. </t>
   </si>
   <si>
-    <t>has_referral</t>
-  </si>
-  <si>
-    <t>if(${emergency_danger_sign_referral}=1 or
+    <t xml:space="preserve">has_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${emergency_danger_sign_referral}=1 or
 ${refer_pregnancy_issues}=1 or
 ${refer_pregnancy_complications}=1
 1, 0)</t>
   </si>
   <si>
-    <t>refer_flag_emergency_danger_sign</t>
-  </si>
-  <si>
-    <t>../danger_signs/emergency_danger_sign_referral</t>
-  </si>
-  <si>
-    <t>refer_flag_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>../pregnancy_issues_group/subgroup_pregnancy_issues/refer_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>refer_flag_pregnancy_complications</t>
-  </si>
-  <si>
-    <t>../pregnancy_issues_group/pregnancy_and_pallor/refer_pregnancy_complications</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>previous_pregnancies</t>
-  </si>
-  <si>
-    <t>Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
-  </si>
-  <si>
-    <t>higher_facility_delivery</t>
-  </si>
-  <si>
-    <t>nutrition_restrictions</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Hakuna mojawapo</t>
-  </si>
-  <si>
-    <t>mitigation_strategies</t>
-  </si>
-  <si>
-    <t>facility_delivery</t>
+    <t xml:space="preserve">refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../danger_signs/emergency_danger_sign_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../pregnancy_issues_group/subgroup_pregnancy_issues/refer_pregnancy_issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../pregnancy_issues_group/pregnancy_and_pallor/refer_pregnancy_complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_pregnancies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uchungu wa muda mrefu( Zaidi ya masaa 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milalo mibaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mtoto kutanguliza makalio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seli mundu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maradhi ya moyo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">higher_facility_delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nutrition_restrictions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hakuna mojawapo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitigation_strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facility_delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Facility Delivery </t>
   </si>
   <si>
-    <t>Kujifungulia kituo cha afya</t>
-  </si>
-  <si>
-    <t>anc_visits</t>
+    <t xml:space="preserve">Kujifungulia kituo cha afya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anc_visits</t>
   </si>
   <si>
     <t xml:space="preserve">ANC Visits </t>
@@ -1388,16 +1417,16 @@
     <t xml:space="preserve">Kuhudhuria kliniki wakati wa ujauzito </t>
   </si>
   <si>
-    <t>rest</t>
-  </si>
-  <si>
-    <t>Rest</t>
-  </si>
-  <si>
-    <t>Kupumzika</t>
-  </si>
-  <si>
-    <t>balanced_diet</t>
+    <t xml:space="preserve">rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupumzika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balanced_diet</t>
   </si>
   <si>
     <t xml:space="preserve">Balanced Diet/Good Nutrition Practices </t>
@@ -1412,10 +1441,10 @@
     <t xml:space="preserve">No heavy work </t>
   </si>
   <si>
-    <t>Kutokufanya kazi ngumu</t>
-  </si>
-  <si>
-    <t>family_planning</t>
+    <t xml:space="preserve">Kutokufanya kazi ngumu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">family_planning</t>
   </si>
   <si>
     <t xml:space="preserve">Family Planning </t>
@@ -1424,262 +1453,255 @@
     <t xml:space="preserve">Kutumia uzazi wa mpango </t>
   </si>
   <si>
-    <t>local_herb_risks</t>
-  </si>
-  <si>
-    <t>Risks of using herbs</t>
-  </si>
-  <si>
-    <t>Hatari za kutumia dawa za mitishamba</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndio</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>difficulty_breathing</t>
-  </si>
-  <si>
-    <t>Difficulty Breathing</t>
-  </si>
-  <si>
-    <t>Anapumua kwa shida</t>
-  </si>
-  <si>
-    <t>fatigue</t>
-  </si>
-  <si>
-    <t>Fatigue, lethergy</t>
-  </si>
-  <si>
-    <t>Uchovu</t>
-  </si>
-  <si>
-    <t>fever</t>
-  </si>
-  <si>
-    <t>Fever</t>
-  </si>
-  <si>
-    <t>Homa</t>
-  </si>
-  <si>
-    <t>tinnitus</t>
-  </si>
-  <si>
-    <t>Tinnitus</t>
-  </si>
-  <si>
-    <t>Maskio kulia nyenje/kuvuma</t>
-  </si>
-  <si>
-    <t>dizziness</t>
-  </si>
-  <si>
-    <t>Dizziness</t>
-  </si>
-  <si>
-    <t>Kizunguzungu</t>
-  </si>
-  <si>
-    <t>frontal_headache</t>
-  </si>
-  <si>
-    <t>Severe Frontal Headache</t>
-  </si>
-  <si>
-    <t>Kichwa kuuma sana sehemu ya mbele</t>
-  </si>
-  <si>
-    <t>blurred_vision</t>
-  </si>
-  <si>
-    <t>Blurred vision</t>
-  </si>
-  <si>
-    <t>Kutokuona vizuri</t>
-  </si>
-  <si>
-    <t>gastric_pain</t>
-  </si>
-  <si>
-    <t>Severe gastric pain</t>
-  </si>
-  <si>
-    <t>Maumivu makali ya tumbo</t>
-  </si>
-  <si>
-    <t>swelling</t>
-  </si>
-  <si>
-    <t>Swelling of face, arms, fingers, or legs</t>
-  </si>
-  <si>
-    <t>Kuvimba uso,mikono, vidole au miguu</t>
-  </si>
-  <si>
-    <t>early_labor</t>
-  </si>
-  <si>
-    <t>Early labor pain before 9 months gestation</t>
-  </si>
-  <si>
-    <t>Uchungu wa mapema kabla ya miezi tisa</t>
-  </si>
-  <si>
-    <t>liquid_leaking</t>
-  </si>
-  <si>
-    <t>Liquid leaking from vagina</t>
-  </si>
-  <si>
-    <t>Kutoka maji sehemu za siri</t>
-  </si>
-  <si>
-    <t>malaria_signs</t>
-  </si>
-  <si>
-    <t>Signs of malaria (feeling cold, fever, vomiting)</t>
-  </si>
-  <si>
-    <t>Dalili za malaria(kuhisi baridi,homa na kutapika)</t>
-  </si>
-  <si>
-    <t>foul_smelling</t>
-  </si>
-  <si>
-    <t>Foul smelling vaginal discharge</t>
-  </si>
-  <si>
-    <t>kutoa uchafu wenye harufu mbaya sehemu za siri</t>
-  </si>
-  <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>21/12/2020</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>data</t>
+    <t xml:space="preserve">local_herb_risks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risks of using herbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hatari za kutumia dawa za mitishamba</t>
   </si>
   <si>
     <t xml:space="preserve">Hamna mojawapo </t>
   </si>
   <si>
-    <t>Pregnancy Counselling</t>
-  </si>
-  <si>
-    <t>pregnancy_counselling</t>
-  </si>
-  <si>
-    <t>gestation_in_weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO_LABEL </t>
-  </si>
-  <si>
-    <t>../inputs/gestation_in_weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kifafa cha mimba
-Mama akipata tatizo hili hukutika mfano wa homa ya mdudu na kupoteza faham, kifafa cha mimba hutokea kabla au baada ya mama kujifungua. 
-</t>
-  </si>
-  <si>
-    <t>Milalo mibaya
-Kutokea akiwa na mlalo usio wa kawaida wakati wa mtoto kuzaliwa</t>
-  </si>
-  <si>
-    <t>Mtoto kutanguliza makalio 
-Mtoto kutokeza makalio wakati wa kuzaliwa kawaida atokee kichwa ili azae salama.</t>
-  </si>
-  <si>
-    <t>Seli mundu 
-Maradhi ya homa ya mifupa/seli nundu, mwenye maradhi haya chembe chembe nyekundu za damu huwa kidogo na hazikukamilika, hupekelea kuwa na ukosefu wa damu mara kwa mara</t>
-  </si>
-  <si>
-    <t>Maradhi ya moyo 
-Haya ni maradhi sugu ambapo moyo hushindwa kufanya kazi vizuri na tujuwe kwamba moyo ni kiungo kinacho sambaza damu safi kwenda sehemu zote za mwili</t>
-  </si>
-  <si>
-    <t>Mkakati wa kuepuka sababu za hatari za ujauzito</t>
+    <t xml:space="preserve">yes_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hapana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">difficulty_breathing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficulty Breathing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anapumua kwa shida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatigue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatigue, lethergy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uchovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tinnitus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tinnitus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maskio kulia nyenje/kuvuma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dizziness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dizziness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kizunguzungu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frontal_headache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe Frontal Headache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kichwa kuuma sana sehemu ya mbele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blurred_vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blurred vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutokuona vizuri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gastric_pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe gastric pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maumivu makali ya tumbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swelling of face, arms, fingers, or legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuvimba uso,mikono, vidole au miguu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early_labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early labor pain before 9 months gestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uchungu wa mapema kabla ya miezi tisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquid_leaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid leaking from vagina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutoka maji sehemu za siri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malaria_signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signs of malaria (feeling cold, fever, vomiting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalili za malaria(kuhisi baridi,homa na kutapika)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foul_smelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foul smelling vaginal discharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kutoa uchafu wenye harufu mbaya sehemu za siri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregnancy Counselling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pregnancy_counselling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/12/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1693,6 +1715,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1703,25 +1726,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1731,17 +1736,7 @@
       <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1765,7 +1760,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1773,83 +1768,173 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="33">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1908,304 +1993,30 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1D1C1D"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMJ165"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Z165"/>
+  <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.86328125" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
-    <col min="3" max="3" width="62.76953125" customWidth="1"/>
-    <col min="4" max="4" width="50.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14.40625" customWidth="1"/>
-    <col min="6" max="6" width="31.76953125" customWidth="1"/>
-    <col min="7" max="1022" width="14.40625" customWidth="1"/>
-    <col min="1023" max="1025" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="7" style="0" width="14.41"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1023" style="0" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2264,7 +2075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="14.25">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -2276,8 +2087,8 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="3" t="b">
-        <f>FALSE()</f>
+      <c r="F2" s="3" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="G2" s="1"/>
@@ -2292,7 +2103,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2326,15 +2137,15 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="14.25">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>508</v>
+      <c r="C4" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2360,12 +2171,12 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="14.25">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>21</v>
@@ -2394,12 +2205,12 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>21</v>
@@ -2419,12 +2230,12 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="14.25">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>21</v>
@@ -2444,23 +2255,23 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
+      <c r="B8" s="0" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>21</v>
@@ -2480,12 +2291,12 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="14.25">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>21</v>
@@ -2505,15 +2316,15 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="14.25">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2530,15 +2341,15 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -2555,7 +2366,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -2563,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -2580,12 +2391,12 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="14.25">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2603,12 +2414,12 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="14.25">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>21</v>
@@ -2637,12 +2448,12 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:26" ht="14.25">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>21</v>
@@ -2651,7 +2462,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -2673,7 +2484,7 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" spans="1:26" ht="14.25">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -2707,12 +2518,12 @@
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" spans="1:26" ht="14.25">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>21</v>
@@ -2741,12 +2552,12 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2773,9 +2584,9 @@
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" spans="1:26" ht="14.25">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
@@ -2796,12 +2607,12 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="14.25">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -2813,7 +2624,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
@@ -2830,12 +2641,12 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" spans="1:26" ht="14.25">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -2847,7 +2658,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
@@ -2864,12 +2675,12 @@
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
-    <row r="23" spans="1:26" ht="14.25">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2881,7 +2692,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -2898,12 +2709,12 @@
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -2915,7 +2726,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -2932,12 +2743,12 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -2949,7 +2760,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -2966,12 +2777,12 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -2983,7 +2794,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
@@ -3000,12 +2811,12 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -3017,7 +2828,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -3034,12 +2845,12 @@
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -3051,7 +2862,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
@@ -3068,26 +2879,26 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -3095,26 +2906,26 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3122,26 +2933,26 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -3149,12 +2960,12 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4"/>
@@ -3166,7 +2977,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
@@ -3183,12 +2994,12 @@
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3200,7 +3011,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
@@ -3217,12 +3028,12 @@
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="1:26" ht="14.25">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3234,7 +3045,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="4"/>
@@ -3251,12 +3062,12 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="1:26" ht="14.25">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3268,7 +3079,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
@@ -3285,12 +3096,12 @@
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
-    <row r="36" spans="1:26" ht="14.25">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3301,14 +3112,14 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
+      <c r="L36" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
@@ -3319,12 +3130,12 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="14.25">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3336,7 +3147,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M37" s="6"/>
       <c r="N37" s="4"/>
@@ -3353,12 +3164,12 @@
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3369,7 +3180,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="9">
+      <c r="L38" s="9" t="n">
         <v>7</v>
       </c>
       <c r="M38" s="4"/>
@@ -3387,12 +3198,12 @@
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
-    <row r="39" spans="1:26" ht="14.25">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3403,7 +3214,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="9">
+      <c r="L39" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M39" s="4"/>
@@ -3421,12 +3232,12 @@
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
     </row>
-    <row r="40" spans="1:26" ht="14.25">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3438,7 +3249,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M40" s="6"/>
       <c r="N40" s="4"/>
@@ -3455,12 +3266,12 @@
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3472,7 +3283,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M41" s="6"/>
       <c r="N41" s="4"/>
@@ -3489,12 +3300,12 @@
       <c r="Y41" s="4"/>
       <c r="Z41" s="4"/>
     </row>
-    <row r="42" spans="1:26" ht="14.25">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3506,7 +3317,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M42" s="6"/>
       <c r="N42" s="4"/>
@@ -3523,12 +3334,12 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" spans="1:26" ht="14.25">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3540,7 +3351,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="4"/>
@@ -3557,9 +3368,9 @@
       <c r="Y43" s="4"/>
       <c r="Z43" s="4"/>
     </row>
-    <row r="44" spans="1:26" ht="14.25">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>23</v>
@@ -3574,7 +3385,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
@@ -3591,12 +3402,12 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="1:26" ht="14.25">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3608,7 +3419,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M45" s="6"/>
       <c r="N45" s="4"/>
@@ -3625,12 +3436,12 @@
       <c r="Y45" s="4"/>
       <c r="Z45" s="4"/>
     </row>
-    <row r="46" spans="1:26" ht="14.25">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3642,7 +3453,7 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -3659,12 +3470,12 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" spans="1:26" ht="14.25">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -3676,7 +3487,7 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -3693,12 +3504,12 @@
       <c r="Y47" s="4"/>
       <c r="Z47" s="4"/>
     </row>
-    <row r="48" spans="1:26" ht="14.25">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -3710,7 +3521,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -3727,12 +3538,12 @@
       <c r="Y48" s="4"/>
       <c r="Z48" s="4"/>
     </row>
-    <row r="49" spans="1:26" ht="14.25">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -3744,7 +3555,7 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -3761,12 +3572,12 @@
       <c r="Y49" s="4"/>
       <c r="Z49" s="4"/>
     </row>
-    <row r="50" spans="1:26" ht="14.25">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -3778,7 +3589,7 @@
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -3795,12 +3606,12 @@
       <c r="Y50" s="4"/>
       <c r="Z50" s="4"/>
     </row>
-    <row r="51" spans="1:26" ht="14.25">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -3812,7 +3623,7 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -3829,12 +3640,12 @@
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
     </row>
-    <row r="52" spans="1:26" ht="14.25">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -3846,7 +3657,7 @@
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
@@ -3863,12 +3674,12 @@
       <c r="Y52" s="4"/>
       <c r="Z52" s="4"/>
     </row>
-    <row r="53" spans="1:26" ht="14.25">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -3895,12 +3706,12 @@
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
     </row>
-    <row r="54" spans="1:26" ht="14.25">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -3927,18 +3738,18 @@
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
     </row>
-    <row r="55" spans="1:26" ht="14.25">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -3963,18 +3774,18 @@
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
     </row>
-    <row r="56" spans="1:26" ht="409.5">
+    <row r="56" customFormat="false" ht="409.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -3999,12 +3810,12 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -4031,100 +3842,100 @@
       <c r="Y57" s="4"/>
       <c r="Z57" s="4"/>
     </row>
-    <row r="58" spans="1:26">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" t="s">
-        <v>115</v>
+    <row r="58" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>117</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
-      <c r="A59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>119</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26">
-      <c r="A60" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" t="s">
-        <v>118</v>
-      </c>
-      <c r="L60" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26">
-      <c r="A61" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" t="s">
         <v>120</v>
       </c>
-      <c r="L61" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="0" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" spans="1:26">
-      <c r="A62" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="L60" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="L62" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="0" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:26">
-      <c r="A63" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="L61" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="L63" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="0" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="L62" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="L64" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="0" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="65" spans="1:1024">
+      <c r="L63" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="L64" s="0" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E65" s="15"/>
       <c r="F65" s="16"/>
       <c r="G65" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
@@ -4146,18 +3957,18 @@
       <c r="Y65" s="15"/>
       <c r="Z65" s="15"/>
     </row>
-    <row r="66" spans="1:1024">
+    <row r="66" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="15"/>
@@ -4182,18 +3993,18 @@
       <c r="Y66" s="15"/>
       <c r="Z66" s="15"/>
     </row>
-    <row r="67" spans="1:1024" ht="130">
+    <row r="67" customFormat="false" ht="130" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E67" s="15"/>
       <c r="F67" s="15"/>
@@ -4218,18 +4029,18 @@
       <c r="Y67" s="15"/>
       <c r="Z67" s="15"/>
     </row>
-    <row r="68" spans="1:1024">
+    <row r="68" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
@@ -4254,18 +4065,18 @@
       <c r="Y68" s="15"/>
       <c r="Z68" s="15"/>
     </row>
-    <row r="69" spans="1:1024">
+    <row r="69" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
@@ -4290,12 +4101,12 @@
       <c r="Y69" s="15"/>
       <c r="Z69" s="15"/>
     </row>
-    <row r="70" spans="1:1024">
+    <row r="70" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -4322,53 +4133,53 @@
       <c r="Y70" s="15"/>
       <c r="Z70" s="15"/>
     </row>
-    <row r="71" spans="1:1024">
+    <row r="71" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1024">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1024">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1024" s="15" customFormat="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E74" s="18"/>
       <c r="F74" s="19"/>
       <c r="G74" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H74" s="18"/>
       <c r="I74" s="18"/>
@@ -4389,20 +4200,19 @@
       <c r="X74" s="18"/>
       <c r="Y74" s="18"/>
       <c r="Z74" s="18"/>
-      <c r="AMJ74"/>
-    </row>
-    <row r="75" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="75" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
@@ -4426,14 +4236,13 @@
       <c r="X75" s="18"/>
       <c r="Y75" s="18"/>
       <c r="Z75" s="18"/>
-      <c r="AMJ75"/>
-    </row>
-    <row r="76" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="76" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C76" s="18" t="s">
         <v>21</v>
@@ -4442,7 +4251,7 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="18" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H76" s="18"/>
       <c r="I76" s="18"/>
@@ -4463,23 +4272,22 @@
       <c r="X76" s="18"/>
       <c r="Y76" s="18"/>
       <c r="Z76" s="18"/>
-      <c r="AMJ76"/>
-    </row>
-    <row r="77" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="77" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="18"/>
@@ -4502,23 +4310,22 @@
       <c r="X77" s="18"/>
       <c r="Y77" s="18"/>
       <c r="Z77" s="18"/>
-      <c r="AMJ77"/>
-    </row>
-    <row r="78" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="78" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D78" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E78" s="18" t="s">
         <v>163</v>
-      </c>
-      <c r="E78" s="18" t="s">
-        <v>160</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18"/>
@@ -4541,23 +4348,22 @@
       <c r="X78" s="18"/>
       <c r="Y78" s="18"/>
       <c r="Z78" s="18"/>
-      <c r="AMJ78"/>
-    </row>
-    <row r="79" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="79" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="18"/>
@@ -4580,23 +4386,22 @@
       <c r="X79" s="18"/>
       <c r="Y79" s="18"/>
       <c r="Z79" s="18"/>
-      <c r="AMJ79"/>
-    </row>
-    <row r="80" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="80" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18"/>
@@ -4619,14 +4424,13 @@
       <c r="X80" s="18"/>
       <c r="Y80" s="18"/>
       <c r="Z80" s="18"/>
-      <c r="AMJ80"/>
-    </row>
-    <row r="81" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="81" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C81" s="22"/>
       <c r="D81" s="18"/>
@@ -4652,20 +4456,19 @@
       <c r="X81" s="18"/>
       <c r="Y81" s="18"/>
       <c r="Z81" s="18"/>
-      <c r="AMJ81"/>
-    </row>
-    <row r="82" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="82" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
@@ -4689,20 +4492,19 @@
       <c r="X82" s="18"/>
       <c r="Y82" s="18"/>
       <c r="Z82" s="18"/>
-      <c r="AMJ82"/>
-    </row>
-    <row r="83" spans="1:1024" s="15" customFormat="1" ht="39">
+    </row>
+    <row r="83" s="15" customFormat="true" ht="39" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
@@ -4726,14 +4528,13 @@
       <c r="X83" s="18"/>
       <c r="Y83" s="18"/>
       <c r="Z83" s="18"/>
-      <c r="AMJ83"/>
-    </row>
-    <row r="84" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="84" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C84" s="21" t="s">
         <v>21</v>
@@ -4742,7 +4543,7 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="18" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H84" s="18"/>
       <c r="I84" s="18"/>
@@ -4763,23 +4564,22 @@
       <c r="X84" s="18"/>
       <c r="Y84" s="18"/>
       <c r="Z84" s="18"/>
-      <c r="AMJ84"/>
-    </row>
-    <row r="85" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="85" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="18"/>
@@ -4802,23 +4602,22 @@
       <c r="X85" s="18"/>
       <c r="Y85" s="18"/>
       <c r="Z85" s="18"/>
-      <c r="AMJ85"/>
-    </row>
-    <row r="86" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="86" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F86" s="18"/>
       <c r="G86" s="18"/>
@@ -4841,23 +4640,22 @@
       <c r="X86" s="18"/>
       <c r="Y86" s="18"/>
       <c r="Z86" s="18"/>
-      <c r="AMJ86"/>
-    </row>
-    <row r="87" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="87" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F87" s="18"/>
       <c r="G87" s="18"/>
@@ -4880,14 +4678,13 @@
       <c r="X87" s="18"/>
       <c r="Y87" s="18"/>
       <c r="Z87" s="18"/>
-      <c r="AMJ87"/>
-    </row>
-    <row r="88" spans="1:1024" s="15" customFormat="1" ht="14.75">
+    </row>
+    <row r="88" s="15" customFormat="true" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C88" s="21"/>
       <c r="D88" s="18"/>
@@ -4913,14 +4710,13 @@
       <c r="X88" s="18"/>
       <c r="Y88" s="18"/>
       <c r="Z88" s="18"/>
-      <c r="AMJ88"/>
-    </row>
-    <row r="89" spans="1:1024" s="15" customFormat="1" ht="15.5" customHeight="1">
+    </row>
+    <row r="89" s="15" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C89" s="18"/>
       <c r="D89" s="18"/>
@@ -4932,7 +4728,7 @@
       <c r="J89" s="18"/>
       <c r="K89" s="18"/>
       <c r="L89" s="19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M89" s="18"/>
       <c r="N89" s="18"/>
@@ -4948,26 +4744,25 @@
       <c r="X89" s="18"/>
       <c r="Y89" s="18"/>
       <c r="Z89" s="18"/>
-      <c r="AMJ89"/>
-    </row>
-    <row r="90" spans="1:1024" s="15" customFormat="1" ht="13.75" customHeight="1">
+    </row>
+    <row r="90" s="15" customFormat="true" ht="13.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F90" s="18" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G90" s="18"/>
       <c r="H90" s="18"/>
@@ -4989,24 +4784,23 @@
       <c r="X90" s="18"/>
       <c r="Y90" s="18"/>
       <c r="Z90" s="18"/>
-      <c r="AMJ90"/>
-    </row>
-    <row r="91" spans="1:1024" s="15" customFormat="1" ht="24.5" customHeight="1">
+    </row>
+    <row r="91" s="15" customFormat="true" ht="24.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E91" s="18"/>
       <c r="F91" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G91" s="18"/>
       <c r="H91" s="18"/>
@@ -5028,14 +4822,13 @@
       <c r="X91" s="18"/>
       <c r="Y91" s="18"/>
       <c r="Z91" s="18"/>
-      <c r="AMJ91"/>
-    </row>
-    <row r="92" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="92" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -5061,23 +4854,22 @@
       <c r="X92" s="18"/>
       <c r="Y92" s="18"/>
       <c r="Z92" s="18"/>
-      <c r="AMJ92"/>
-    </row>
-    <row r="93" spans="1:1024" s="15" customFormat="1" ht="52">
+    </row>
+    <row r="93" s="15" customFormat="true" ht="52" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G93" s="18"/>
       <c r="H93" s="18"/>
@@ -5099,14 +4891,13 @@
       <c r="X93" s="18"/>
       <c r="Y93" s="18"/>
       <c r="Z93" s="18"/>
-      <c r="AMJ93"/>
-    </row>
-    <row r="94" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="94" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C94" s="18" t="s">
         <v>21</v>
@@ -5114,7 +4905,7 @@
       <c r="D94" s="18"/>
       <c r="E94" s="22"/>
       <c r="G94" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H94" s="18"/>
       <c r="I94" s="18"/>
@@ -5135,38 +4926,37 @@
       <c r="X94" s="18"/>
       <c r="Y94" s="18"/>
       <c r="Z94" s="18"/>
-      <c r="AMJ94"/>
-    </row>
-    <row r="95" spans="1:1024" s="15" customFormat="1" ht="34.25" customHeight="1">
+    </row>
+    <row r="95" s="15" customFormat="true" ht="34.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="18" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F95" s="22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J95" s="18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K95" s="18" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L95" s="18"/>
       <c r="M95" s="18"/>
@@ -5183,14 +4973,13 @@
       <c r="X95" s="18"/>
       <c r="Y95" s="18"/>
       <c r="Z95" s="18"/>
-      <c r="AMJ95"/>
-    </row>
-    <row r="96" spans="1:1024" s="15" customFormat="1" ht="38" customHeight="1">
+    </row>
+    <row r="96" s="15" customFormat="true" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C96" s="19"/>
       <c r="D96" s="18"/>
@@ -5201,7 +4990,7 @@
       <c r="I96" s="18"/>
       <c r="J96" s="18"/>
       <c r="L96" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
@@ -5217,23 +5006,22 @@
       <c r="X96" s="18"/>
       <c r="Y96" s="18"/>
       <c r="Z96" s="18"/>
-      <c r="AMJ96"/>
-    </row>
-    <row r="97" spans="1:1024" s="15" customFormat="1" ht="36.75" customHeight="1">
+    </row>
+    <row r="97" s="15" customFormat="true" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F97" s="18" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G97" s="18"/>
       <c r="H97" s="18"/>
@@ -5255,14 +5043,13 @@
       <c r="X97" s="18"/>
       <c r="Y97" s="18"/>
       <c r="Z97" s="18"/>
-      <c r="AMJ97"/>
-    </row>
-    <row r="98" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="98" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -5288,24 +5075,23 @@
       <c r="X98" s="18"/>
       <c r="Y98" s="18"/>
       <c r="Z98" s="18"/>
-      <c r="AMJ98"/>
-    </row>
-    <row r="99" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="99" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C99" s="18" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="18"/>
       <c r="F99" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H99" s="18"/>
       <c r="I99" s="18"/>
@@ -5326,26 +5112,25 @@
       <c r="X99" s="18"/>
       <c r="Y99" s="18"/>
       <c r="Z99" s="18"/>
-      <c r="AMJ99"/>
-    </row>
-    <row r="100" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="100" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G100" s="18"/>
       <c r="H100" s="18"/>
@@ -5367,23 +5152,22 @@
       <c r="X100" s="18"/>
       <c r="Y100" s="18"/>
       <c r="Z100" s="18"/>
-      <c r="AMJ100"/>
-    </row>
-    <row r="101" spans="1:1024" s="15" customFormat="1" ht="65">
+    </row>
+    <row r="101" s="15" customFormat="true" ht="65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G101" s="18"/>
       <c r="H101" s="18"/>
@@ -5405,26 +5189,25 @@
       <c r="X101" s="18"/>
       <c r="Y101" s="18"/>
       <c r="Z101" s="18"/>
-      <c r="AMJ101"/>
-    </row>
-    <row r="102" spans="1:1024" s="15" customFormat="1" ht="24.75" customHeight="1">
+    </row>
+    <row r="102" s="15" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G102" s="18"/>
       <c r="H102" s="18"/>
@@ -5446,14 +5229,13 @@
       <c r="X102" s="18"/>
       <c r="Y102" s="18"/>
       <c r="Z102" s="18"/>
-      <c r="AMJ102"/>
-    </row>
-    <row r="103" spans="1:1024" s="15" customFormat="1" ht="23" customHeight="1">
+    </row>
+    <row r="103" s="15" customFormat="true" ht="23" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -5464,7 +5246,7 @@
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
       <c r="L103" s="19" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M103" s="18"/>
       <c r="N103" s="18"/>
@@ -5480,23 +5262,22 @@
       <c r="X103" s="18"/>
       <c r="Y103" s="18"/>
       <c r="Z103" s="18"/>
-      <c r="AMJ103"/>
-    </row>
-    <row r="104" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="104" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G104" s="18"/>
       <c r="H104" s="18"/>
@@ -5518,23 +5299,22 @@
       <c r="X104" s="18"/>
       <c r="Y104" s="18"/>
       <c r="Z104" s="18"/>
-      <c r="AMJ104"/>
-    </row>
-    <row r="105" spans="1:1024" s="15" customFormat="1" ht="78">
+    </row>
+    <row r="105" s="15" customFormat="true" ht="78" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F105" s="24" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G105" s="18"/>
       <c r="H105" s="18"/>
@@ -5556,14 +5336,13 @@
       <c r="X105" s="18"/>
       <c r="Y105" s="18"/>
       <c r="Z105" s="18"/>
-      <c r="AMJ105"/>
-    </row>
-    <row r="106" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="106" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -5589,14 +5368,13 @@
       <c r="X106" s="18"/>
       <c r="Y106" s="18"/>
       <c r="Z106" s="18"/>
-      <c r="AMJ106"/>
-    </row>
-    <row r="107" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="107" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -5622,23 +5400,22 @@
       <c r="X107" s="18"/>
       <c r="Y107" s="18"/>
       <c r="Z107" s="18"/>
-      <c r="AMJ107"/>
-    </row>
-    <row r="108" spans="1:1024">
+    </row>
+    <row r="108" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C108" s="15"/>
       <c r="D108" s="15"/>
       <c r="E108" s="15"/>
       <c r="F108" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H108" s="15"/>
       <c r="I108" s="15"/>
@@ -5660,39 +5437,39 @@
       <c r="Y108" s="15"/>
       <c r="Z108" s="15"/>
     </row>
-    <row r="109" spans="1:1024" ht="14.75">
+    <row r="109" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="15"/>
       <c r="I109" s="26" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J109" s="26" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K109" s="26" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L109" s="15"/>
       <c r="M109" s="14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N109" s="15"/>
       <c r="O109" s="15"/>
@@ -5708,12 +5485,12 @@
       <c r="Y109" s="15"/>
       <c r="Z109" s="15"/>
     </row>
-    <row r="110" spans="1:1024">
+    <row r="110" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C110" s="15"/>
       <c r="D110" s="15"/>
@@ -5740,21 +5517,21 @@
       <c r="Y110" s="15"/>
       <c r="Z110" s="15"/>
     </row>
-    <row r="111" spans="1:1024">
+    <row r="111" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
       <c r="F111" s="14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H111" s="15"/>
       <c r="I111" s="15"/>
@@ -5776,22 +5553,22 @@
       <c r="Y111" s="15"/>
       <c r="Z111" s="15"/>
     </row>
-    <row r="112" spans="1:1024" ht="14.75">
+    <row r="112" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15"/>
@@ -5814,22 +5591,22 @@
       <c r="Y112" s="15"/>
       <c r="Z112" s="15"/>
     </row>
-    <row r="113" spans="1:26">
+    <row r="113" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="27" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="15"/>
@@ -5852,741 +5629,733 @@
       <c r="Y113" s="15"/>
       <c r="Z113" s="15"/>
     </row>
-    <row r="114" spans="1:26">
+    <row r="114" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F114" s="27" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="115" spans="1:26">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="116" spans="1:26">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F116" s="27" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="117" spans="1:26">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F117" s="27" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="118" spans="1:26">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F118" s="27" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="119" spans="1:26">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F119" s="27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="120" spans="1:26">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F120" s="27" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="121" spans="1:26" ht="65">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>510</v>
+        <v>287</v>
       </c>
       <c r="F121" s="27" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="122" spans="1:26">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="123" spans="1:26">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="124" spans="1:26">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="125" spans="1:26" ht="39">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="39" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="D125" s="36" t="s">
-        <v>511</v>
+        <v>302</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>303</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="126" spans="1:26" ht="39">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="39" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>512</v>
+        <v>307</v>
       </c>
       <c r="F126" s="27" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="127" spans="1:26">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F127" s="27" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="128" spans="1:26">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F128" s="27" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1024" ht="65">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D129" s="18" t="s">
-        <v>513</v>
+        <v>319</v>
       </c>
       <c r="F129" s="27" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1024" ht="52">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="52" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>514</v>
+        <v>323</v>
       </c>
       <c r="F130" s="27" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1024">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F131" s="27" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1024">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F132" s="27" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1024">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F133" s="27" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1024">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F134" s="27" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1024">
-      <c r="A135" s="28" t="s">
-        <v>110</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F135" s="27" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1024">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F136" s="27" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1024">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1024">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F138" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="G138" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1024" s="15" customFormat="1" ht="39">
+        <v>208</v>
+      </c>
+      <c r="G138" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="139" s="15" customFormat="true" ht="39" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D139" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="F139" s="27"/>
+    </row>
+    <row r="140" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="E140" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I140" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="J140" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="K140" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="M140" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="141" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B141" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C141" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C143" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="F139" s="27"/>
-      <c r="AMJ139"/>
-    </row>
-    <row r="140" spans="1:1024">
-      <c r="A140" s="15" t="s">
+      <c r="D143" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B140" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E140" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I140" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="J140" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="K140" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="M140" s="14" t="s">
+      <c r="F143" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="G143" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="144" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="15" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="141" spans="1:1024" s="15" customFormat="1">
-      <c r="A141" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B141" s="15" t="s">
+      <c r="B144" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C144" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="D141" s="14" t="s">
+      <c r="D144" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="AMJ141"/>
-    </row>
-    <row r="142" spans="1:1024">
-      <c r="A142" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B142" s="15" t="s">
+      <c r="E144" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I144" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="M144" s="14" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="143" spans="1:1024" s="15" customFormat="1">
-      <c r="A143" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B143" s="14" t="s">
+    <row r="145" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B145" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C143" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D143" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="F143" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="G143" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AMJ143"/>
-    </row>
-    <row r="144" spans="1:1024" s="15" customFormat="1">
-      <c r="A144" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="B144" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="C144" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D144" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E144" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I144" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="M144" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="AMJ144"/>
-    </row>
-    <row r="145" spans="1:1024" s="15" customFormat="1">
-      <c r="A145" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B145" s="15" t="s">
-        <v>356</v>
-      </c>
       <c r="C145" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="D145" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D145" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="AMJ145"/>
-    </row>
-    <row r="146" spans="1:1024" s="15" customFormat="1">
+    </row>
+    <row r="146" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="AMJ146"/>
-    </row>
-    <row r="147" spans="1:1024" s="15" customFormat="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="147" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>515</v>
+        <v>368</v>
       </c>
       <c r="F147" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="AMJ147"/>
-    </row>
-    <row r="148" spans="1:1024">
-      <c r="A148" t="s">
-        <v>110</v>
-      </c>
-      <c r="B148" t="s">
-        <v>365</v>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>370</v>
       </c>
       <c r="C148" s="26" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D148" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="C149" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="D149" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="C150" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="D151" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="F151" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="C152" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="D152" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="F152" s="0" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="C153" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="D153" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="D154" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="155" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="F148" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1024">
-      <c r="A149" t="s">
-        <v>110</v>
-      </c>
-      <c r="B149" t="s">
-        <v>369</v>
-      </c>
-      <c r="C149" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="D149" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="F149" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1024">
-      <c r="A150" t="s">
-        <v>110</v>
-      </c>
-      <c r="B150" t="s">
-        <v>373</v>
-      </c>
-      <c r="C150" s="26" t="s">
-        <v>374</v>
-      </c>
-      <c r="D150" s="26" t="s">
-        <v>375</v>
-      </c>
-      <c r="F150" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1024">
-      <c r="A151" t="s">
-        <v>110</v>
-      </c>
-      <c r="B151" t="s">
-        <v>377</v>
-      </c>
-      <c r="C151" s="26" t="s">
-        <v>378</v>
-      </c>
-      <c r="D151" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="F151" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1024">
-      <c r="A152" t="s">
-        <v>110</v>
-      </c>
-      <c r="B152" t="s">
-        <v>381</v>
-      </c>
-      <c r="C152" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="D152" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="F152" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1024">
-      <c r="A153" t="s">
-        <v>110</v>
-      </c>
-      <c r="B153" t="s">
-        <v>385</v>
-      </c>
-      <c r="C153" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="D153" s="26" t="s">
-        <v>387</v>
-      </c>
-      <c r="F153" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1024">
-      <c r="A154" t="s">
-        <v>110</v>
-      </c>
-      <c r="B154" t="s">
-        <v>389</v>
-      </c>
-      <c r="C154" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="D154" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="F154" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1024" s="15" customFormat="1">
-      <c r="A155" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B155" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="AMJ155"/>
-    </row>
-    <row r="156" spans="1:1024">
+    </row>
+    <row r="156" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="C156" t="s">
-        <v>394</v>
-      </c>
-      <c r="D156" t="s">
-        <v>395</v>
-      </c>
-      <c r="G156" t="s">
-        <v>245</v>
+        <v>398</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="G156" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="J156" s="18"/>
     </row>
-    <row r="157" spans="1:1024" s="15" customFormat="1">
+    <row r="157" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D157" s="20" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F157" s="18" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G157" s="18"/>
       <c r="H157" s="18"/>
@@ -6607,26 +6376,25 @@
       <c r="W157" s="18"/>
       <c r="X157" s="18"/>
       <c r="Y157" s="18"/>
-      <c r="AMJ157"/>
-    </row>
-    <row r="158" spans="1:1024" s="15" customFormat="1" ht="26">
+    </row>
+    <row r="158" s="15" customFormat="true" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="D158" s="29" t="s">
-        <v>402</v>
+        <v>406</v>
+      </c>
+      <c r="D158" s="28" t="s">
+        <v>407</v>
       </c>
       <c r="F158" s="19" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H158" s="18"/>
       <c r="I158" s="18"/>
@@ -6646,26 +6414,25 @@
       <c r="W158" s="18"/>
       <c r="X158" s="18"/>
       <c r="Y158" s="18"/>
-      <c r="AMJ158"/>
-    </row>
-    <row r="159" spans="1:1024" s="15" customFormat="1" ht="42.75">
+    </row>
+    <row r="159" s="15" customFormat="true" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D159" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="F159" s="30" t="s">
-        <v>408</v>
+        <v>412</v>
+      </c>
+      <c r="F159" s="29" t="s">
+        <v>413</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H159" s="18"/>
       <c r="I159" s="18"/>
@@ -6684,37 +6451,36 @@
       <c r="W159" s="18"/>
       <c r="X159" s="18"/>
       <c r="Y159" s="18"/>
-      <c r="AMJ159"/>
-    </row>
-    <row r="160" spans="1:1024">
+    </row>
+    <row r="160" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C160" t="s">
-        <v>410</v>
-      </c>
-      <c r="D160" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1024">
+        <v>414</v>
+      </c>
+      <c r="C160" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="D160" s="0" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J161" s="18"/>
     </row>
-    <row r="162" spans="1:1024" s="15" customFormat="1" ht="31" customHeight="1">
+    <row r="162" s="15" customFormat="true" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C162" s="18"/>
       <c r="D162" s="18"/>
@@ -6724,7 +6490,7 @@
       <c r="H162" s="18"/>
       <c r="I162" s="18"/>
       <c r="L162" s="18" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="M162" s="18"/>
       <c r="N162" s="18"/>
@@ -6740,76 +6506,80 @@
       <c r="X162" s="18"/>
       <c r="Y162" s="18"/>
       <c r="Z162" s="18"/>
-      <c r="AMJ162"/>
-    </row>
-    <row r="163" spans="1:1024" s="15" customFormat="1">
-      <c r="A163" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B163" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="L163" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="AMJ163"/>
-    </row>
-    <row r="164" spans="1:1024" s="15" customFormat="1">
-      <c r="A164" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B164" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="L164" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="AMJ164"/>
-    </row>
-    <row r="165" spans="1:1024" s="15" customFormat="1">
-      <c r="A165" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B165" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="L165" s="28" t="s">
+    </row>
+    <row r="163" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B163" s="27" t="s">
         <v>419</v>
       </c>
-      <c r="AMJ165"/>
+      <c r="L163" s="27" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="164" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B164" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="L164" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="165" s="15" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="L165" s="27" t="s">
+        <v>424</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L36:Q36"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z51"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.04296875" customWidth="1"/>
-    <col min="2" max="2" width="25.90625" customWidth="1"/>
-    <col min="3" max="3" width="72.26953125" customWidth="1"/>
-    <col min="4" max="4" width="53.08984375" customWidth="1"/>
-    <col min="5" max="1025" width="14.40625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="72.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="53.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="14.41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="B1" s="31" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="15" t="s">
@@ -6837,18 +6607,18 @@
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>247</v>
+        <v>426</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>250</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
@@ -6873,18 +6643,18 @@
       <c r="Y2" s="18"/>
       <c r="Z2" s="18"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -6909,18 +6679,18 @@
       <c r="Y3" s="18"/>
       <c r="Z3" s="18"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
@@ -6945,18 +6715,18 @@
       <c r="Y4" s="18"/>
       <c r="Z4" s="18"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
@@ -6981,18 +6751,18 @@
       <c r="Y5" s="18"/>
       <c r="Z5" s="18"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
@@ -7017,18 +6787,18 @@
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
@@ -7053,18 +6823,18 @@
       <c r="Y7" s="18"/>
       <c r="Z7" s="18"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
@@ -7089,18 +6859,18 @@
       <c r="Y8" s="18"/>
       <c r="Z8" s="18"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
@@ -7125,18 +6895,18 @@
       <c r="Y9" s="18"/>
       <c r="Z9" s="18"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
@@ -7161,18 +6931,18 @@
       <c r="Y10" s="18"/>
       <c r="Z10" s="18"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
@@ -7197,18 +6967,18 @@
       <c r="Y11" s="18"/>
       <c r="Z11" s="18"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -7233,18 +7003,18 @@
       <c r="Y12" s="18"/>
       <c r="Z12" s="18"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
@@ -7269,18 +7039,18 @@
       <c r="Y13" s="18"/>
       <c r="Z13" s="18"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
@@ -7305,18 +7075,18 @@
       <c r="Y14" s="18"/>
       <c r="Z14" s="18"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
@@ -7341,18 +7111,18 @@
       <c r="Y15" s="18"/>
       <c r="Z15" s="18"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>303</v>
+        <v>429</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
@@ -7377,18 +7147,18 @@
       <c r="Y16" s="18"/>
       <c r="Z16" s="18"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
@@ -7413,18 +7183,18 @@
       <c r="Y17" s="18"/>
       <c r="Z17" s="18"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -7449,18 +7219,18 @@
       <c r="Y18" s="18"/>
       <c r="Z18" s="18"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>315</v>
+        <v>430</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
@@ -7485,18 +7255,18 @@
       <c r="Y19" s="18"/>
       <c r="Z19" s="18"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>319</v>
+        <v>431</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -7521,18 +7291,18 @@
       <c r="Y20" s="18"/>
       <c r="Z20" s="18"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -7557,18 +7327,18 @@
       <c r="Y21" s="18"/>
       <c r="Z21" s="18"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
@@ -7593,18 +7363,18 @@
       <c r="Y22" s="18"/>
       <c r="Z22" s="18"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -7629,18 +7399,18 @@
       <c r="Y23" s="18"/>
       <c r="Z23" s="18"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
@@ -7665,18 +7435,18 @@
       <c r="Y24" s="18"/>
       <c r="Z24" s="18"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
@@ -7701,18 +7471,18 @@
       <c r="Y25" s="18"/>
       <c r="Z25" s="18"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
@@ -7737,18 +7507,18 @@
       <c r="Y26" s="18"/>
       <c r="Z26" s="18"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
@@ -7773,158 +7543,158 @@
       <c r="Y27" s="18"/>
       <c r="Z27" s="18"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D29" s="14" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B30" s="15" t="s">
+      <c r="C35" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>426</v>
-      </c>
       <c r="D35" s="15" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
@@ -7949,18 +7719,18 @@
       <c r="Y38" s="18"/>
       <c r="Z38" s="18"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
@@ -7985,18 +7755,18 @@
       <c r="Y39" s="18"/>
       <c r="Z39" s="18"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
@@ -8021,18 +7791,18 @@
       <c r="Y40" s="18"/>
       <c r="Z40" s="18"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
@@ -8057,18 +7827,18 @@
       <c r="Y41" s="18"/>
       <c r="Z41" s="18"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -8093,18 +7863,18 @@
       <c r="Y42" s="18"/>
       <c r="Z42" s="18"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
@@ -8129,18 +7899,18 @@
       <c r="Y43" s="18"/>
       <c r="Z43" s="18"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -8165,18 +7935,18 @@
       <c r="Y44" s="18"/>
       <c r="Z44" s="18"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -8201,18 +7971,18 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="18"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
@@ -8237,18 +8007,18 @@
       <c r="Y46" s="18"/>
       <c r="Z46" s="18"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
@@ -8273,18 +8043,18 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="18"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
@@ -8309,18 +8079,18 @@
       <c r="Y48" s="18"/>
       <c r="Z48" s="18"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -8345,18 +8115,18 @@
       <c r="Y49" s="18"/>
       <c r="Z49" s="18"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
@@ -8381,18 +8151,18 @@
       <c r="Y50" s="18"/>
       <c r="Z50" s="18"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
@@ -8418,39 +8188,47 @@
       <c r="Z51" s="18"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" customWidth="1"/>
-    <col min="3" max="1025" width="14.40625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="14.41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>495</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>496</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>497</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>500</v>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>507</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>510</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
@@ -8473,21 +8251,21 @@
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>501</v>
+        <v>512</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>513</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="15"/>
@@ -8512,7 +8290,12 @@
       <c r="Z2" s="15"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/forms/app/pregnancy_counselling.xlsx
+++ b/forms/app/pregnancy_counselling.xlsx
@@ -796,10 +796,10 @@
     <t xml:space="preserve">risk_factors</t>
   </si>
   <si>
-    <t xml:space="preserve">Which pregnancy risk factors do you remember?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unakumbuka sababu zipi za hatari za ujauzito? </t>
+    <t xml:space="preserve">Which pregnancy risk factors among those which we discussed in previous visit do you remember?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unakumbuka  hali hatarishi zipi za ujauzito katika zile tulizojadili katika tembeleo lililopita?</t>
   </si>
   <si>
     <t xml:space="preserve">${high_risk_manual}  = "true" </t>
@@ -1123,7 +1123,7 @@
     <t xml:space="preserve">Kuepuka kula baadhi ya vyakula </t>
   </si>
   <si>
-    <t xml:space="preserve">not(selected(${risk_factors},'nutrition_restrictions')) and contains(${risk_factor_names}, 'nutrition')</t>
+    <t xml:space="preserve">not(selected(${risk_factors},'nutrition_restrictions')) and contains(${risk_factor_names}, 'nutrition_restriction')</t>
   </si>
   <si>
     <t xml:space="preserve">mitigation_strategy</t>
@@ -1894,11 +1894,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5437,14 +5437,14 @@
       <c r="Y108" s="15"/>
       <c r="Z108" s="15"/>
     </row>
-    <row r="109" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="15" t="s">
         <v>239</v>
       </c>
       <c r="B109" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C109" s="25" t="s">
+      <c r="C109" s="17" t="s">
         <v>241</v>
       </c>
       <c r="D109" s="15" t="s">
@@ -5458,13 +5458,13 @@
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="15"/>
-      <c r="I109" s="26" t="s">
+      <c r="I109" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="J109" s="26" t="s">
+      <c r="J109" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="K109" s="26" t="s">
+      <c r="K109" s="25" t="s">
         <v>211</v>
       </c>
       <c r="L109" s="15"/>
@@ -5560,7 +5560,7 @@
       <c r="B112" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C112" s="25" t="s">
+      <c r="C112" s="26" t="s">
         <v>250</v>
       </c>
       <c r="D112" s="14" t="s">
@@ -6079,13 +6079,13 @@
       <c r="E140" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="I140" s="26" t="s">
+      <c r="I140" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="J140" s="26" t="s">
+      <c r="J140" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="K140" s="26" t="s">
+      <c r="K140" s="25" t="s">
         <v>211</v>
       </c>
       <c r="M140" s="14" t="s">
@@ -6150,7 +6150,7 @@
       <c r="E144" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="I144" s="26" t="s">
+      <c r="I144" s="25" t="s">
         <v>209</v>
       </c>
       <c r="M144" s="14" t="s">
@@ -6203,10 +6203,10 @@
       <c r="B148" s="0" t="s">
         <v>370</v>
       </c>
-      <c r="C148" s="26" t="s">
+      <c r="C148" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="D148" s="26" t="s">
+      <c r="D148" s="25" t="s">
         <v>372</v>
       </c>
       <c r="F148" s="0" t="s">
@@ -6220,10 +6220,10 @@
       <c r="B149" s="0" t="s">
         <v>374</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="C149" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="25" t="s">
         <v>376</v>
       </c>
       <c r="F149" s="0" t="s">
@@ -6237,10 +6237,10 @@
       <c r="B150" s="0" t="s">
         <v>378</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="C150" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="D150" s="26" t="s">
+      <c r="D150" s="25" t="s">
         <v>380</v>
       </c>
       <c r="F150" s="0" t="s">
@@ -6254,10 +6254,10 @@
       <c r="B151" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C151" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="D151" s="26" t="s">
+      <c r="D151" s="25" t="s">
         <v>384</v>
       </c>
       <c r="F151" s="0" t="s">
@@ -6271,10 +6271,10 @@
       <c r="B152" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="C152" s="25" t="s">
         <v>387</v>
       </c>
-      <c r="D152" s="26" t="s">
+      <c r="D152" s="25" t="s">
         <v>388</v>
       </c>
       <c r="F152" s="0" t="s">
@@ -6288,10 +6288,10 @@
       <c r="B153" s="0" t="s">
         <v>390</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="C153" s="25" t="s">
         <v>391</v>
       </c>
-      <c r="D153" s="26" t="s">
+      <c r="D153" s="25" t="s">
         <v>392</v>
       </c>
       <c r="F153" s="0" t="s">
@@ -6305,10 +6305,10 @@
       <c r="B154" s="0" t="s">
         <v>394</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="C154" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="D154" s="26" t="s">
+      <c r="D154" s="25" t="s">
         <v>396</v>
       </c>
       <c r="F154" s="0" t="s">
@@ -6562,9 +6562,9 @@
   <dimension ref="A1:Z51"/>
   <sheetFormatPr defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="72.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="72.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="53.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="14.41"/>
   </cols>
@@ -8252,22 +8252,22 @@
       <c r="Z1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>512</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>513</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>515</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="26"/>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
